--- a/research/traditional_assets/database/data/hungary/hungary_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_oil_gas_integrated.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="buse_mol" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,49 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.134</v>
+        <v>0.118</v>
       </c>
       <c r="E2">
-        <v>0.105</v>
-      </c>
-      <c r="F2">
-        <v>-0.218</v>
+        <v>0.109</v>
       </c>
       <c r="G2">
-        <v>0.1804342798816615</v>
+        <v>0.1233269302866684</v>
       </c>
       <c r="H2">
-        <v>0.1803266269546981</v>
+        <v>0.1231935871619559</v>
       </c>
       <c r="I2">
-        <v>0.07434319977330334</v>
+        <v>0.07813791339466132</v>
       </c>
       <c r="J2">
-        <v>0.04165693856922961</v>
+        <v>0.06032127837450187</v>
       </c>
       <c r="K2">
-        <v>1346.7</v>
+        <v>1243.1</v>
       </c>
       <c r="L2">
-        <v>0.05369488768211287</v>
+        <v>0.04804604009569785</v>
       </c>
       <c r="M2">
-        <v>624.6</v>
+        <v>547.3</v>
       </c>
       <c r="N2">
-        <v>0.1207306465642215</v>
+        <v>0.1253263109686283</v>
       </c>
       <c r="O2">
-        <v>0.4638004009801738</v>
+        <v>0.4402702920119057</v>
       </c>
       <c r="P2">
-        <v>624.6</v>
+        <v>547.3</v>
       </c>
       <c r="Q2">
-        <v>0.1207306465642215</v>
+        <v>0.1253263109686283</v>
       </c>
       <c r="R2">
-        <v>0.4638004009801738</v>
+        <v>0.4402702920119057</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,70 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>991.7</v>
+        <v>751.9</v>
       </c>
       <c r="V2">
-        <v>0.1916884121001257</v>
+        <v>0.1721776963590566</v>
       </c>
       <c r="W2">
-        <v>0.1532517780938834</v>
+        <v>0.1199915057095146</v>
       </c>
       <c r="X2">
-        <v>0.1448125244533372</v>
+        <v>0.1501252381674756</v>
       </c>
       <c r="Y2">
-        <v>0.008439253640546179</v>
+        <v>-0.03013373245796098</v>
       </c>
       <c r="Z2">
-        <v>2.42290934220294</v>
+        <v>2.084733033092131</v>
       </c>
       <c r="AA2">
-        <v>0.1009309856269604</v>
+        <v>0.12575376162567</v>
       </c>
       <c r="AB2">
-        <v>0.116656378152646</v>
+        <v>0.1181933524455947</v>
       </c>
       <c r="AC2">
-        <v>-0.01572539252568564</v>
+        <v>0.007560409180075334</v>
       </c>
       <c r="AD2">
-        <v>3035.6</v>
+        <v>2984.5</v>
       </c>
       <c r="AE2">
-        <v>8.83971882844129</v>
+        <v>6.949764742941912</v>
       </c>
       <c r="AF2">
-        <v>3044.439718828441</v>
+        <v>2991.449764742942</v>
       </c>
       <c r="AG2">
-        <v>2052.739718828441</v>
+        <v>2239.549764742942</v>
       </c>
       <c r="AH2">
-        <v>0.3704626491544111</v>
+        <v>0.4065326067830328</v>
       </c>
       <c r="AI2">
-        <v>0.2116363563162356</v>
+        <v>0.1919349283734815</v>
       </c>
       <c r="AJ2">
-        <v>0.2840674816640656</v>
+        <v>0.3389893128020783</v>
       </c>
       <c r="AK2">
-        <v>0.1532634211658573</v>
+        <v>0.150975626709251</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="AM2">
-        <v>-264.6</v>
+        <v>-5.799999999999997</v>
       </c>
       <c r="AN2">
-        <v>0.9417852843722466</v>
+        <v>0.9117264301381413</v>
+      </c>
+      <c r="AO2">
+        <v>38.28462998102466</v>
       </c>
       <c r="AP2">
-        <v>0.6368559954668103</v>
+        <v>0.6841536981490356</v>
       </c>
       <c r="AQ2">
-        <v>-7.030612244897958</v>
+        <v>-347.8620689655174</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.134</v>
+        <v>0.118</v>
       </c>
       <c r="E3">
-        <v>0.105</v>
+        <v>0.109</v>
+      </c>
+      <c r="G3">
+        <v>0.1233269302866684</v>
+      </c>
+      <c r="H3">
+        <v>0.1231935871619559</v>
+      </c>
+      <c r="I3">
+        <v>0.07813791339466132</v>
+      </c>
+      <c r="J3">
+        <v>0.06032127837450187</v>
+      </c>
+      <c r="K3">
+        <v>1243.1</v>
+      </c>
+      <c r="L3">
+        <v>0.04804604009569785</v>
+      </c>
+      <c r="M3">
+        <v>547.3</v>
+      </c>
+      <c r="N3">
+        <v>0.1253263109686283</v>
+      </c>
+      <c r="O3">
+        <v>0.4402702920119057</v>
+      </c>
+      <c r="P3">
+        <v>547.3</v>
+      </c>
+      <c r="Q3">
+        <v>0.1253263109686283</v>
+      </c>
+      <c r="R3">
+        <v>0.4402702920119057</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>751.9</v>
+      </c>
+      <c r="V3">
+        <v>0.1721776963590566</v>
+      </c>
+      <c r="W3">
+        <v>0.1199915057095146</v>
+      </c>
+      <c r="X3">
+        <v>0.1501252381674756</v>
+      </c>
+      <c r="Y3">
+        <v>-0.03013373245796098</v>
+      </c>
+      <c r="Z3">
+        <v>2.084733033092131</v>
+      </c>
+      <c r="AA3">
+        <v>0.12575376162567</v>
+      </c>
+      <c r="AB3">
+        <v>0.1181933524455947</v>
+      </c>
+      <c r="AC3">
+        <v>0.007560409180075334</v>
+      </c>
+      <c r="AD3">
+        <v>2984.5</v>
+      </c>
+      <c r="AE3">
+        <v>6.949764742941912</v>
+      </c>
+      <c r="AF3">
+        <v>2991.449764742942</v>
+      </c>
+      <c r="AG3">
+        <v>2239.549764742942</v>
+      </c>
+      <c r="AH3">
+        <v>0.4065326067830328</v>
+      </c>
+      <c r="AI3">
+        <v>0.1919349283734815</v>
+      </c>
+      <c r="AJ3">
+        <v>0.3389893128020783</v>
+      </c>
+      <c r="AK3">
+        <v>0.150975626709251</v>
+      </c>
+      <c r="AL3">
+        <v>52.7</v>
+      </c>
+      <c r="AM3">
+        <v>-5.799999999999997</v>
+      </c>
+      <c r="AN3">
+        <v>0.9117264301381413</v>
+      </c>
+      <c r="AO3">
+        <v>38.28462998102466</v>
+      </c>
+      <c r="AP3">
+        <v>0.6841536981490356</v>
+      </c>
+      <c r="AQ3">
+        <v>-347.8620689655174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MOL Magyar Olaj- és Gázipari Nyilvánosan Muködo Részvénytársaság (BUSE:MOL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUSE:MOL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas (Integrated)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>38.3787476280835</v>
+      </c>
+      <c r="F2">
+        <v>10000000</v>
+      </c>
+      <c r="G2">
+        <v>0.913849494034734</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0.406532606783033</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>4367</v>
+      </c>
+      <c r="L2">
+        <v>7648.07820329699</v>
+      </c>
+      <c r="M2">
+        <v>6606.54976474294</v>
+      </c>
+      <c r="N2">
+        <v>6896.17820329699</v>
+      </c>
+      <c r="O2">
+        <v>2991.44976474294</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0.118193352445595</v>
+      </c>
+      <c r="R2">
+        <v>0.110064948889713</v>
+      </c>
+      <c r="S2">
+        <v>0.0715783142821721</v>
+      </c>
+      <c r="T2">
+        <v>0.06420731428217211</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.150125238167476</v>
+      </c>
+      <c r="X2">
+        <v>0.110064948889713</v>
+      </c>
+      <c r="Y2">
+        <v>1.51771671855847</v>
+      </c>
+      <c r="Z2">
+        <v>0.934922259086021</v>
+      </c>
+      <c r="AA2">
+        <v>2984.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.07865748822216712</v>
+      </c>
+      <c r="AC2">
+        <v>38.37874762808349</v>
+      </c>
+      <c r="AD2">
+        <v>2991.449764742942</v>
+      </c>
+      <c r="AE2">
+        <v>52.7</v>
+      </c>
+      <c r="AF2">
+        <v>1250.9</v>
+      </c>
+      <c r="AG2">
+        <v>3273.46</v>
+      </c>
+      <c r="AH2">
+        <v>0.01885748822216712</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>4367</v>
+      </c>
+      <c r="AK2">
+        <v>0.06873828092673559</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.09</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1708.6</v>
+      </c>
+      <c r="AR2">
+        <v>52.7</v>
+      </c>
+      <c r="AS2">
+        <v>2984.5</v>
+      </c>
+      <c r="AT2">
+        <v>751.9</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1100649488897132</v>
+      </c>
+      <c r="C2">
+        <v>7648.078203296994</v>
+      </c>
+      <c r="D2">
+        <v>6896.178203296994</v>
+      </c>
+      <c r="E2">
+        <v>-2991.449764742942</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>751.9</v>
+      </c>
+      <c r="H2">
+        <v>4367</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3273.46</v>
+      </c>
+      <c r="K2">
+        <v>1250.9</v>
+      </c>
+      <c r="L2">
+        <v>2022.56</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2022.56</v>
+      </c>
+      <c r="O2">
+        <v>182.0304</v>
+      </c>
+      <c r="P2">
+        <v>1840.5296</v>
+      </c>
+      <c r="Q2">
+        <v>3091.4296</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1100649488897132</v>
+      </c>
+      <c r="T2">
+        <v>0.9349222590860211</v>
+      </c>
+      <c r="U2">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V2">
+        <v>0.09</v>
+      </c>
+      <c r="W2">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1101911835785342</v>
+      </c>
+      <c r="C3">
+        <v>7569.801761397207</v>
+      </c>
+      <c r="D3">
+        <v>6891.486259044636</v>
+      </c>
+      <c r="E3">
+        <v>-2917.865267095513</v>
       </c>
       <c r="F3">
-        <v>-0.218</v>
+        <v>73.58449764742942</v>
       </c>
       <c r="G3">
-        <v>0.1804342798816615</v>
+        <v>751.9</v>
       </c>
       <c r="H3">
-        <v>0.1803266269546981</v>
+        <v>4367</v>
       </c>
       <c r="I3">
-        <v>0.07434319977330334</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.04165693856922961</v>
+        <v>3273.46</v>
       </c>
       <c r="K3">
-        <v>1346.7</v>
+        <v>1250.9</v>
       </c>
       <c r="L3">
-        <v>0.05369488768211287</v>
+        <v>2022.56</v>
       </c>
       <c r="M3">
-        <v>624.6</v>
+        <v>5.191937326092585</v>
       </c>
       <c r="N3">
-        <v>0.1207306465642215</v>
+        <v>2017.368062673907</v>
       </c>
       <c r="O3">
-        <v>0.4638004009801738</v>
+        <v>181.5631256406517</v>
       </c>
       <c r="P3">
-        <v>624.6</v>
+        <v>1835.804937033256</v>
       </c>
       <c r="Q3">
-        <v>0.1207306465642215</v>
+        <v>3086.704937033256</v>
       </c>
       <c r="R3">
-        <v>0.4638004009801738</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1106556671067803</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.9435159889422664</v>
       </c>
       <c r="U3">
-        <v>991.7</v>
+        <v>0.07055748822216712</v>
       </c>
       <c r="V3">
-        <v>0.1916884121001257</v>
+        <v>0.09</v>
       </c>
       <c r="W3">
-        <v>0.1532517780938834</v>
-      </c>
-      <c r="X3">
-        <v>0.1448125244533372</v>
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>0.008439253640546179</v>
+        <v>389.557861154338</v>
       </c>
       <c r="Z3">
-        <v>2.42290934220294</v>
-      </c>
-      <c r="AA3">
-        <v>0.1009309856269604</v>
-      </c>
-      <c r="AB3">
-        <v>0.116656378152646</v>
-      </c>
-      <c r="AC3">
-        <v>-0.01572539252568564</v>
-      </c>
-      <c r="AD3">
-        <v>3035.6</v>
-      </c>
-      <c r="AE3">
-        <v>8.83971882844129</v>
-      </c>
-      <c r="AF3">
-        <v>3044.439718828441</v>
-      </c>
-      <c r="AG3">
-        <v>2052.739718828441</v>
-      </c>
-      <c r="AH3">
-        <v>0.3704626491544111</v>
-      </c>
-      <c r="AI3">
-        <v>0.2116363563162356</v>
-      </c>
-      <c r="AJ3">
-        <v>0.2840674816640656</v>
-      </c>
-      <c r="AK3">
-        <v>0.1532634211658573</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-264.6</v>
-      </c>
-      <c r="AN3">
-        <v>0.9417852843722466</v>
-      </c>
-      <c r="AP3">
-        <v>0.6368559954668103</v>
-      </c>
-      <c r="AQ3">
-        <v>-7.030612244897958</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1103174182673552</v>
+      </c>
+      <c r="C4">
+        <v>7491.531699661193</v>
+      </c>
+      <c r="D4">
+        <v>6886.800694956052</v>
+      </c>
+      <c r="E4">
+        <v>-2844.280769448083</v>
+      </c>
+      <c r="F4">
+        <v>147.1689952948588</v>
+      </c>
+      <c r="G4">
+        <v>751.9</v>
+      </c>
+      <c r="H4">
+        <v>4367</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3273.46</v>
+      </c>
+      <c r="K4">
+        <v>1250.9</v>
+      </c>
+      <c r="L4">
+        <v>2022.56</v>
+      </c>
+      <c r="M4">
+        <v>10.38387465218517</v>
+      </c>
+      <c r="N4">
+        <v>2012.176125347815</v>
+      </c>
+      <c r="O4">
+        <v>181.0958512813033</v>
+      </c>
+      <c r="P4">
+        <v>1831.080274066511</v>
+      </c>
+      <c r="Q4">
+        <v>3081.980274066512</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.111258440797665</v>
+      </c>
+      <c r="T4">
+        <v>0.9522851010404759</v>
+      </c>
+      <c r="U4">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V4">
+        <v>0.09</v>
+      </c>
+      <c r="W4">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>194.778930577169</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1104436529561761</v>
+      </c>
+      <c r="C5">
+        <v>7413.268005084061</v>
+      </c>
+      <c r="D5">
+        <v>6882.121498026349</v>
+      </c>
+      <c r="E5">
+        <v>-2770.696271800654</v>
+      </c>
+      <c r="F5">
+        <v>220.7534929422882</v>
+      </c>
+      <c r="G5">
+        <v>751.9</v>
+      </c>
+      <c r="H5">
+        <v>4367</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3273.46</v>
+      </c>
+      <c r="K5">
+        <v>1250.9</v>
+      </c>
+      <c r="L5">
+        <v>2022.56</v>
+      </c>
+      <c r="M5">
+        <v>15.57581197827775</v>
+      </c>
+      <c r="N5">
+        <v>2006.984188021722</v>
+      </c>
+      <c r="O5">
+        <v>180.628576921955</v>
+      </c>
+      <c r="P5">
+        <v>1826.355611099767</v>
+      </c>
+      <c r="Q5">
+        <v>3077.255611099768</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1118736428120732</v>
+      </c>
+      <c r="T5">
+        <v>0.9612350195736999</v>
+      </c>
+      <c r="U5">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V5">
+        <v>0.09</v>
+      </c>
+      <c r="W5">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>129.8526203847793</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1105698876449971</v>
+      </c>
+      <c r="C6">
+        <v>7335.010664696231</v>
+      </c>
+      <c r="D6">
+        <v>6877.448655285949</v>
+      </c>
+      <c r="E6">
+        <v>-2697.111774153224</v>
+      </c>
+      <c r="F6">
+        <v>294.3379905897177</v>
+      </c>
+      <c r="G6">
+        <v>751.9</v>
+      </c>
+      <c r="H6">
+        <v>4367</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3273.46</v>
+      </c>
+      <c r="K6">
+        <v>1250.9</v>
+      </c>
+      <c r="L6">
+        <v>2022.56</v>
+      </c>
+      <c r="M6">
+        <v>20.76774930437034</v>
+      </c>
+      <c r="N6">
+        <v>2001.79225069563</v>
+      </c>
+      <c r="O6">
+        <v>180.1613025626067</v>
+      </c>
+      <c r="P6">
+        <v>1821.630948133023</v>
+      </c>
+      <c r="Q6">
+        <v>3072.530948133023</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1125016615351148</v>
+      </c>
+      <c r="T6">
+        <v>0.9703713947430327</v>
+      </c>
+      <c r="U6">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V6">
+        <v>0.09</v>
+      </c>
+      <c r="W6">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>97.38946528858449</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1106961223338181</v>
+      </c>
+      <c r="C7">
+        <v>7256.75966556333</v>
+      </c>
+      <c r="D7">
+        <v>6872.782153800477</v>
+      </c>
+      <c r="E7">
+        <v>-2623.527276505795</v>
+      </c>
+      <c r="F7">
+        <v>367.9224882371471</v>
+      </c>
+      <c r="G7">
+        <v>751.9</v>
+      </c>
+      <c r="H7">
+        <v>4367</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3273.46</v>
+      </c>
+      <c r="K7">
+        <v>1250.9</v>
+      </c>
+      <c r="L7">
+        <v>2022.56</v>
+      </c>
+      <c r="M7">
+        <v>25.95968663046293</v>
+      </c>
+      <c r="N7">
+        <v>1996.600313369537</v>
+      </c>
+      <c r="O7">
+        <v>179.6940282032583</v>
+      </c>
+      <c r="P7">
+        <v>1816.906285166279</v>
+      </c>
+      <c r="Q7">
+        <v>3067.806285166279</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1131429017049574</v>
+      </c>
+      <c r="T7">
+        <v>0.9797001146527726</v>
+      </c>
+      <c r="U7">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V7">
+        <v>0.09</v>
+      </c>
+      <c r="W7">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>77.91157223086759</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1108223570226391</v>
+      </c>
+      <c r="C8">
+        <v>7178.514994786063</v>
+      </c>
+      <c r="D8">
+        <v>6868.121980670639</v>
+      </c>
+      <c r="E8">
+        <v>-2549.942778858366</v>
+      </c>
+      <c r="F8">
+        <v>441.5069858845765</v>
+      </c>
+      <c r="G8">
+        <v>751.9</v>
+      </c>
+      <c r="H8">
+        <v>4367</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3273.46</v>
+      </c>
+      <c r="K8">
+        <v>1250.9</v>
+      </c>
+      <c r="L8">
+        <v>2022.56</v>
+      </c>
+      <c r="M8">
+        <v>31.15162395655551</v>
+      </c>
+      <c r="N8">
+        <v>1991.408376043444</v>
+      </c>
+      <c r="O8">
+        <v>179.22675384391</v>
+      </c>
+      <c r="P8">
+        <v>1812.181622199534</v>
+      </c>
+      <c r="Q8">
+        <v>3063.081622199535</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1137977852826689</v>
+      </c>
+      <c r="T8">
+        <v>0.9892273179648475</v>
+      </c>
+      <c r="U8">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V8">
+        <v>0.09</v>
+      </c>
+      <c r="W8">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>64.92631019238966</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1109485917114601</v>
+      </c>
+      <c r="C9">
+        <v>7100.276639500097</v>
+      </c>
+      <c r="D9">
+        <v>6863.468123032104</v>
+      </c>
+      <c r="E9">
+        <v>-2476.358281210936</v>
+      </c>
+      <c r="F9">
+        <v>515.091483532006</v>
+      </c>
+      <c r="G9">
+        <v>751.9</v>
+      </c>
+      <c r="H9">
+        <v>4367</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3273.46</v>
+      </c>
+      <c r="K9">
+        <v>1250.9</v>
+      </c>
+      <c r="L9">
+        <v>2022.56</v>
+      </c>
+      <c r="M9">
+        <v>36.3435612826481</v>
+      </c>
+      <c r="N9">
+        <v>1986.216438717352</v>
+      </c>
+      <c r="O9">
+        <v>178.7594794845617</v>
+      </c>
+      <c r="P9">
+        <v>1807.45695923279</v>
+      </c>
+      <c r="Q9">
+        <v>3058.35695923279</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1144667523781807</v>
+      </c>
+      <c r="T9">
+        <v>0.9989594073696552</v>
+      </c>
+      <c r="U9">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V9">
+        <v>0.09</v>
+      </c>
+      <c r="W9">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>55.65112302204827</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.111074826400281</v>
+      </c>
+      <c r="C10">
+        <v>7022.044586875948</v>
+      </c>
+      <c r="D10">
+        <v>6858.820568055384</v>
+      </c>
+      <c r="E10">
+        <v>-2402.773783563507</v>
+      </c>
+      <c r="F10">
+        <v>588.6759811794353</v>
+      </c>
+      <c r="G10">
+        <v>751.9</v>
+      </c>
+      <c r="H10">
+        <v>4367</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3273.46</v>
+      </c>
+      <c r="K10">
+        <v>1250.9</v>
+      </c>
+      <c r="L10">
+        <v>2022.56</v>
+      </c>
+      <c r="M10">
+        <v>41.53549860874068</v>
+      </c>
+      <c r="N10">
+        <v>1981.024501391259</v>
+      </c>
+      <c r="O10">
+        <v>178.2922051252133</v>
+      </c>
+      <c r="P10">
+        <v>1802.732296266046</v>
+      </c>
+      <c r="Q10">
+        <v>3053.632296266046</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1151502622366383</v>
+      </c>
+      <c r="T10">
+        <v>1.008903063935437</v>
+      </c>
+      <c r="U10">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V10">
+        <v>0.09</v>
+      </c>
+      <c r="W10">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>48.69473264429224</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.111201061089102</v>
+      </c>
+      <c r="C11">
+        <v>6943.818824118853</v>
+      </c>
+      <c r="D11">
+        <v>6854.179302945718</v>
+      </c>
+      <c r="E11">
+        <v>-2329.189285916077</v>
+      </c>
+      <c r="F11">
+        <v>662.2604788268648</v>
+      </c>
+      <c r="G11">
+        <v>751.9</v>
+      </c>
+      <c r="H11">
+        <v>4367</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3273.46</v>
+      </c>
+      <c r="K11">
+        <v>1250.9</v>
+      </c>
+      <c r="L11">
+        <v>2022.56</v>
+      </c>
+      <c r="M11">
+        <v>46.72743593483327</v>
+      </c>
+      <c r="N11">
+        <v>1975.832564065167</v>
+      </c>
+      <c r="O11">
+        <v>177.824930765865</v>
+      </c>
+      <c r="P11">
+        <v>1798.007633299302</v>
+      </c>
+      <c r="Q11">
+        <v>3048.907633299302</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1158487942897874</v>
+      </c>
+      <c r="T11">
+        <v>1.019065262403763</v>
+      </c>
+      <c r="U11">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V11">
+        <v>0.09</v>
+      </c>
+      <c r="W11">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>43.28420679492644</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.111327295777923</v>
+      </c>
+      <c r="C12">
+        <v>6865.599338468656</v>
+      </c>
+      <c r="D12">
+        <v>6849.544314942951</v>
+      </c>
+      <c r="E12">
+        <v>-2255.604788268648</v>
+      </c>
+      <c r="F12">
+        <v>735.8449764742942</v>
+      </c>
+      <c r="G12">
+        <v>751.9</v>
+      </c>
+      <c r="H12">
+        <v>4367</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3273.46</v>
+      </c>
+      <c r="K12">
+        <v>1250.9</v>
+      </c>
+      <c r="L12">
+        <v>2022.56</v>
+      </c>
+      <c r="M12">
+        <v>51.91937326092585</v>
+      </c>
+      <c r="N12">
+        <v>1970.640626739074</v>
+      </c>
+      <c r="O12">
+        <v>177.3576564065167</v>
+      </c>
+      <c r="P12">
+        <v>1793.282970332557</v>
+      </c>
+      <c r="Q12">
+        <v>3044.182970332557</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1165628492774509</v>
+      </c>
+      <c r="T12">
+        <v>1.029453287504719</v>
+      </c>
+      <c r="U12">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V12">
+        <v>0.09</v>
+      </c>
+      <c r="W12">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>38.9557861154338</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.111453530466744</v>
+      </c>
+      <c r="C13">
+        <v>6787.386117199702</v>
+      </c>
+      <c r="D13">
+        <v>6844.915591321426</v>
+      </c>
+      <c r="E13">
+        <v>-2182.020290621218</v>
+      </c>
+      <c r="F13">
+        <v>809.4294741217236</v>
+      </c>
+      <c r="G13">
+        <v>751.9</v>
+      </c>
+      <c r="H13">
+        <v>4367</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3273.46</v>
+      </c>
+      <c r="K13">
+        <v>1250.9</v>
+      </c>
+      <c r="L13">
+        <v>2022.56</v>
+      </c>
+      <c r="M13">
+        <v>57.11131058701844</v>
+      </c>
+      <c r="N13">
+        <v>1965.448689412982</v>
+      </c>
+      <c r="O13">
+        <v>176.8903820471683</v>
+      </c>
+      <c r="P13">
+        <v>1788.558307365813</v>
+      </c>
+      <c r="Q13">
+        <v>3039.458307365813</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1172929504446124</v>
+      </c>
+      <c r="T13">
+        <v>1.040074751371988</v>
+      </c>
+      <c r="U13">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V13">
+        <v>0.09</v>
+      </c>
+      <c r="W13">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>35.41435101403072</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1115797651555649</v>
+      </c>
+      <c r="C14">
+        <v>6709.179147620702</v>
+      </c>
+      <c r="D14">
+        <v>6840.293119389855</v>
+      </c>
+      <c r="E14">
+        <v>-2108.435792973789</v>
+      </c>
+      <c r="F14">
+        <v>883.0139717691529</v>
+      </c>
+      <c r="G14">
+        <v>751.9</v>
+      </c>
+      <c r="H14">
+        <v>4367</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3273.46</v>
+      </c>
+      <c r="K14">
+        <v>1250.9</v>
+      </c>
+      <c r="L14">
+        <v>2022.56</v>
+      </c>
+      <c r="M14">
+        <v>62.30324791311102</v>
+      </c>
+      <c r="N14">
+        <v>1960.256752086889</v>
+      </c>
+      <c r="O14">
+        <v>176.42310768782</v>
+      </c>
+      <c r="P14">
+        <v>1783.833644399069</v>
+      </c>
+      <c r="Q14">
+        <v>3034.733644399069</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1180396448201185</v>
+      </c>
+      <c r="T14">
+        <v>1.050937612145332</v>
+      </c>
+      <c r="U14">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V14">
+        <v>0.09</v>
+      </c>
+      <c r="W14">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>32.46315509619484</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1117059998443859</v>
+      </c>
+      <c r="C15">
+        <v>6630.978417074627</v>
+      </c>
+      <c r="D15">
+        <v>6835.67688649121</v>
+      </c>
+      <c r="E15">
+        <v>-2034.85129532636</v>
+      </c>
+      <c r="F15">
+        <v>956.5984694165825</v>
+      </c>
+      <c r="G15">
+        <v>751.9</v>
+      </c>
+      <c r="H15">
+        <v>4367</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3273.46</v>
+      </c>
+      <c r="K15">
+        <v>1250.9</v>
+      </c>
+      <c r="L15">
+        <v>2022.56</v>
+      </c>
+      <c r="M15">
+        <v>67.49518523920361</v>
+      </c>
+      <c r="N15">
+        <v>1955.064814760796</v>
+      </c>
+      <c r="O15">
+        <v>175.9558333284717</v>
+      </c>
+      <c r="P15">
+        <v>1779.108981432325</v>
+      </c>
+      <c r="Q15">
+        <v>3030.008981432325</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1188035045835673</v>
+      </c>
+      <c r="T15">
+        <v>1.062050193855994</v>
+      </c>
+      <c r="U15">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V15">
+        <v>0.09</v>
+      </c>
+      <c r="W15">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>29.96598931956446</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1118322345332069</v>
+      </c>
+      <c r="C16">
+        <v>6552.7839129386</v>
+      </c>
+      <c r="D16">
+        <v>6831.066880002612</v>
+      </c>
+      <c r="E16">
+        <v>-1961.26679767893</v>
+      </c>
+      <c r="F16">
+        <v>1030.182967064012</v>
+      </c>
+      <c r="G16">
+        <v>751.9</v>
+      </c>
+      <c r="H16">
+        <v>4367</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3273.46</v>
+      </c>
+      <c r="K16">
+        <v>1250.9</v>
+      </c>
+      <c r="L16">
+        <v>2022.56</v>
+      </c>
+      <c r="M16">
+        <v>72.68712256529621</v>
+      </c>
+      <c r="N16">
+        <v>1949.872877434704</v>
+      </c>
+      <c r="O16">
+        <v>175.4885589691233</v>
+      </c>
+      <c r="P16">
+        <v>1774.38431846558</v>
+      </c>
+      <c r="Q16">
+        <v>3025.28431846558</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1195851285275614</v>
+      </c>
+      <c r="T16">
+        <v>1.073421207699462</v>
+      </c>
+      <c r="U16">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V16">
+        <v>0.09</v>
+      </c>
+      <c r="W16">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>27.82556151102413</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1119584692220279</v>
+      </c>
+      <c r="C17">
+        <v>6474.595622623763</v>
+      </c>
+      <c r="D17">
+        <v>6826.463087335204</v>
+      </c>
+      <c r="E17">
+        <v>-1887.682300031501</v>
+      </c>
+      <c r="F17">
+        <v>1103.767464711441</v>
+      </c>
+      <c r="G17">
+        <v>751.9</v>
+      </c>
+      <c r="H17">
+        <v>4367</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3273.46</v>
+      </c>
+      <c r="K17">
+        <v>1250.9</v>
+      </c>
+      <c r="L17">
+        <v>2022.56</v>
+      </c>
+      <c r="M17">
+        <v>77.87905989138876</v>
+      </c>
+      <c r="N17">
+        <v>1944.680940108611</v>
+      </c>
+      <c r="O17">
+        <v>175.021284609775</v>
+      </c>
+      <c r="P17">
+        <v>1769.659655498836</v>
+      </c>
+      <c r="Q17">
+        <v>3020.559655498836</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1203851436231789</v>
+      </c>
+      <c r="T17">
+        <v>1.085059774809835</v>
+      </c>
+      <c r="U17">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V17">
+        <v>0.09</v>
+      </c>
+      <c r="W17">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>25.97052407695587</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1120847039108488</v>
+      </c>
+      <c r="C18">
+        <v>6396.413533575176</v>
+      </c>
+      <c r="D18">
+        <v>6821.865495934047</v>
+      </c>
+      <c r="E18">
+        <v>-1814.097802384071</v>
+      </c>
+      <c r="F18">
+        <v>1177.351962358871</v>
+      </c>
+      <c r="G18">
+        <v>751.9</v>
+      </c>
+      <c r="H18">
+        <v>4367</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3273.46</v>
+      </c>
+      <c r="K18">
+        <v>1250.9</v>
+      </c>
+      <c r="L18">
+        <v>2022.56</v>
+      </c>
+      <c r="M18">
+        <v>83.07099721748136</v>
+      </c>
+      <c r="N18">
+        <v>1939.489002782519</v>
+      </c>
+      <c r="O18">
+        <v>174.5540102504267</v>
+      </c>
+      <c r="P18">
+        <v>1764.934992532092</v>
+      </c>
+      <c r="Q18">
+        <v>3015.834992532092</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1212042066972635</v>
+      </c>
+      <c r="T18">
+        <v>1.096975450660931</v>
+      </c>
+      <c r="U18">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V18">
+        <v>0.09</v>
+      </c>
+      <c r="W18">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>24.34736632214612</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1122109385996698</v>
+      </c>
+      <c r="C19">
+        <v>6318.237633271703</v>
+      </c>
+      <c r="D19">
+        <v>6817.274093278003</v>
+      </c>
+      <c r="E19">
+        <v>-1740.513304736642</v>
+      </c>
+      <c r="F19">
+        <v>1250.9364600063</v>
+      </c>
+      <c r="G19">
+        <v>751.9</v>
+      </c>
+      <c r="H19">
+        <v>4367</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3273.46</v>
+      </c>
+      <c r="K19">
+        <v>1250.9</v>
+      </c>
+      <c r="L19">
+        <v>2022.56</v>
+      </c>
+      <c r="M19">
+        <v>88.26293454357396</v>
+      </c>
+      <c r="N19">
+        <v>1934.297065456426</v>
+      </c>
+      <c r="O19">
+        <v>174.0867358910783</v>
+      </c>
+      <c r="P19">
+        <v>1760.210329565348</v>
+      </c>
+      <c r="Q19">
+        <v>3011.110329565347</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1220430062309646</v>
+      </c>
+      <c r="T19">
+        <v>1.109178251231331</v>
+      </c>
+      <c r="U19">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V19">
+        <v>0.09</v>
+      </c>
+      <c r="W19">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>22.91516830319635</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1123371732884908</v>
+      </c>
+      <c r="C20">
+        <v>6240.067909225889</v>
+      </c>
+      <c r="D20">
+        <v>6812.688866879618</v>
+      </c>
+      <c r="E20">
+        <v>-1666.928807089213</v>
+      </c>
+      <c r="F20">
+        <v>1324.52095765373</v>
+      </c>
+      <c r="G20">
+        <v>751.9</v>
+      </c>
+      <c r="H20">
+        <v>4367</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3273.46</v>
+      </c>
+      <c r="K20">
+        <v>1250.9</v>
+      </c>
+      <c r="L20">
+        <v>2022.56</v>
+      </c>
+      <c r="M20">
+        <v>93.45487186966653</v>
+      </c>
+      <c r="N20">
+        <v>1929.105128130333</v>
+      </c>
+      <c r="O20">
+        <v>173.61946153173</v>
+      </c>
+      <c r="P20">
+        <v>1755.485666598604</v>
+      </c>
+      <c r="Q20">
+        <v>3006.385666598604</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1229022642898779</v>
+      </c>
+      <c r="T20">
+        <v>1.121678681083936</v>
+      </c>
+      <c r="U20">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V20">
+        <v>0.09</v>
+      </c>
+      <c r="W20">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>21.64210339746322</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1124634079773118</v>
+      </c>
+      <c r="C21">
+        <v>6161.90434898385</v>
+      </c>
+      <c r="D21">
+        <v>6808.10980428501</v>
+      </c>
+      <c r="E21">
+        <v>-1593.344309441783</v>
+      </c>
+      <c r="F21">
+        <v>1398.105455301159</v>
+      </c>
+      <c r="G21">
+        <v>751.9</v>
+      </c>
+      <c r="H21">
+        <v>4367</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3273.46</v>
+      </c>
+      <c r="K21">
+        <v>1250.9</v>
+      </c>
+      <c r="L21">
+        <v>2022.56</v>
+      </c>
+      <c r="M21">
+        <v>98.64680919575912</v>
+      </c>
+      <c r="N21">
+        <v>1923.913190804241</v>
+      </c>
+      <c r="O21">
+        <v>173.1521871723817</v>
+      </c>
+      <c r="P21">
+        <v>1750.761003631859</v>
+      </c>
+      <c r="Q21">
+        <v>3001.661003631859</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1237827385971594</v>
+      </c>
+      <c r="T21">
+        <v>1.134487763525494</v>
+      </c>
+      <c r="U21">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V21">
+        <v>0.09</v>
+      </c>
+      <c r="W21">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>20.50304532391252</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1125896426661328</v>
+      </c>
+      <c r="C22">
+        <v>6083.746940125171</v>
+      </c>
+      <c r="D22">
+        <v>6803.53689307376</v>
+      </c>
+      <c r="E22">
+        <v>-1519.759811794354</v>
+      </c>
+      <c r="F22">
+        <v>1471.689952948588</v>
+      </c>
+      <c r="G22">
+        <v>751.9</v>
+      </c>
+      <c r="H22">
+        <v>4367</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3273.46</v>
+      </c>
+      <c r="K22">
+        <v>1250.9</v>
+      </c>
+      <c r="L22">
+        <v>2022.56</v>
+      </c>
+      <c r="M22">
+        <v>103.8387465218517</v>
+      </c>
+      <c r="N22">
+        <v>1918.721253478148</v>
+      </c>
+      <c r="O22">
+        <v>172.6849128130333</v>
+      </c>
+      <c r="P22">
+        <v>1746.036340665115</v>
+      </c>
+      <c r="Q22">
+        <v>2996.936340665115</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.124685224762123</v>
+      </c>
+      <c r="T22">
+        <v>1.147617073028091</v>
+      </c>
+      <c r="U22">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V22">
+        <v>0.09</v>
+      </c>
+      <c r="W22">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>19.4778930577169</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1127158773549538</v>
+      </c>
+      <c r="C23">
+        <v>6005.595670262779</v>
+      </c>
+      <c r="D23">
+        <v>6798.970120858797</v>
+      </c>
+      <c r="E23">
+        <v>-1446.175314146924</v>
+      </c>
+      <c r="F23">
+        <v>1545.274450596018</v>
+      </c>
+      <c r="G23">
+        <v>751.9</v>
+      </c>
+      <c r="H23">
+        <v>4367</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3273.46</v>
+      </c>
+      <c r="K23">
+        <v>1250.9</v>
+      </c>
+      <c r="L23">
+        <v>2022.56</v>
+      </c>
+      <c r="M23">
+        <v>109.0306838479443</v>
+      </c>
+      <c r="N23">
+        <v>1913.529316152056</v>
+      </c>
+      <c r="O23">
+        <v>172.217638453685</v>
+      </c>
+      <c r="P23">
+        <v>1741.311677698371</v>
+      </c>
+      <c r="Q23">
+        <v>2992.211677698371</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1256105586780983</v>
+      </c>
+      <c r="T23">
+        <v>1.161078770113032</v>
+      </c>
+      <c r="U23">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V23">
+        <v>0.09</v>
+      </c>
+      <c r="W23">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>18.55037434068276</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1128421120437747</v>
+      </c>
+      <c r="C24">
+        <v>5927.450527042838</v>
+      </c>
+      <c r="D24">
+        <v>6794.409475286286</v>
+      </c>
+      <c r="E24">
+        <v>-1372.590816499495</v>
+      </c>
+      <c r="F24">
+        <v>1618.858948243447</v>
+      </c>
+      <c r="G24">
+        <v>751.9</v>
+      </c>
+      <c r="H24">
+        <v>4367</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3273.46</v>
+      </c>
+      <c r="K24">
+        <v>1250.9</v>
+      </c>
+      <c r="L24">
+        <v>2022.56</v>
+      </c>
+      <c r="M24">
+        <v>114.2226211740369</v>
+      </c>
+      <c r="N24">
+        <v>1908.337378825963</v>
+      </c>
+      <c r="O24">
+        <v>171.7503640943367</v>
+      </c>
+      <c r="P24">
+        <v>1736.587014731626</v>
+      </c>
+      <c r="Q24">
+        <v>2987.487014731626</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1265596191047396</v>
+      </c>
+      <c r="T24">
+        <v>1.1748856389181</v>
+      </c>
+      <c r="U24">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V24">
+        <v>0.09</v>
+      </c>
+      <c r="W24">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>17.70717550701536</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1129683467325957</v>
+      </c>
+      <c r="C25">
+        <v>5849.311498144638</v>
+      </c>
+      <c r="D25">
+        <v>6789.854944035515</v>
+      </c>
+      <c r="E25">
+        <v>-1299.006318852066</v>
+      </c>
+      <c r="F25">
+        <v>1692.443445890877</v>
+      </c>
+      <c r="G25">
+        <v>751.9</v>
+      </c>
+      <c r="H25">
+        <v>4367</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3273.46</v>
+      </c>
+      <c r="K25">
+        <v>1250.9</v>
+      </c>
+      <c r="L25">
+        <v>2022.56</v>
+      </c>
+      <c r="M25">
+        <v>119.4145585001295</v>
+      </c>
+      <c r="N25">
+        <v>1903.14544149987</v>
+      </c>
+      <c r="O25">
+        <v>171.2830897349883</v>
+      </c>
+      <c r="P25">
+        <v>1731.862351764882</v>
+      </c>
+      <c r="Q25">
+        <v>2982.762351764882</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1275333304515534</v>
+      </c>
+      <c r="T25">
+        <v>1.189051127692131</v>
+      </c>
+      <c r="U25">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V25">
+        <v>0.09</v>
+      </c>
+      <c r="W25">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>16.93729831105817</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1130945814214167</v>
+      </c>
+      <c r="C26">
+        <v>5771.178571280479</v>
+      </c>
+      <c r="D26">
+        <v>6785.306514818786</v>
+      </c>
+      <c r="E26">
+        <v>-1225.421821204636</v>
+      </c>
+      <c r="F26">
+        <v>1766.027943538306</v>
+      </c>
+      <c r="G26">
+        <v>751.9</v>
+      </c>
+      <c r="H26">
+        <v>4367</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3273.46</v>
+      </c>
+      <c r="K26">
+        <v>1250.9</v>
+      </c>
+      <c r="L26">
+        <v>2022.56</v>
+      </c>
+      <c r="M26">
+        <v>124.606495826222</v>
+      </c>
+      <c r="N26">
+        <v>1897.953504173778</v>
+      </c>
+      <c r="O26">
+        <v>170.81581537564</v>
+      </c>
+      <c r="P26">
+        <v>1727.137688798138</v>
+      </c>
+      <c r="Q26">
+        <v>2978.037688798138</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1285326657811781</v>
+      </c>
+      <c r="T26">
+        <v>1.20358939248653</v>
+      </c>
+      <c r="U26">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V26">
+        <v>0.09</v>
+      </c>
+      <c r="W26">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>16.23157754809742</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1132208161102377</v>
+      </c>
+      <c r="C27">
+        <v>5693.051734195573</v>
+      </c>
+      <c r="D27">
+        <v>6780.764175381309</v>
+      </c>
+      <c r="E27">
+        <v>-1151.837323557207</v>
+      </c>
+      <c r="F27">
+        <v>1839.612441185735</v>
+      </c>
+      <c r="G27">
+        <v>751.9</v>
+      </c>
+      <c r="H27">
+        <v>4367</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3273.46</v>
+      </c>
+      <c r="K27">
+        <v>1250.9</v>
+      </c>
+      <c r="L27">
+        <v>2022.56</v>
+      </c>
+      <c r="M27">
+        <v>129.7984331523146</v>
+      </c>
+      <c r="N27">
+        <v>1892.761566847685</v>
+      </c>
+      <c r="O27">
+        <v>170.3485410162917</v>
+      </c>
+      <c r="P27">
+        <v>1722.413025831394</v>
+      </c>
+      <c r="Q27">
+        <v>2973.313025831394</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1295586500529262</v>
+      </c>
+      <c r="T27">
+        <v>1.218515344342114</v>
+      </c>
+      <c r="U27">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V27">
+        <v>0.09</v>
+      </c>
+      <c r="W27">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>15.58231444617352</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1133470507990586</v>
+      </c>
+      <c r="C28">
+        <v>5614.930974667916</v>
+      </c>
+      <c r="D28">
+        <v>6776.22791350108</v>
+      </c>
+      <c r="E28">
+        <v>-1078.252825909777</v>
+      </c>
+      <c r="F28">
+        <v>1913.196938833165</v>
+      </c>
+      <c r="G28">
+        <v>751.9</v>
+      </c>
+      <c r="H28">
+        <v>4367</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3273.46</v>
+      </c>
+      <c r="K28">
+        <v>1250.9</v>
+      </c>
+      <c r="L28">
+        <v>2022.56</v>
+      </c>
+      <c r="M28">
+        <v>134.9903704784072</v>
+      </c>
+      <c r="N28">
+        <v>1887.569629521593</v>
+      </c>
+      <c r="O28">
+        <v>169.8812666569434</v>
+      </c>
+      <c r="P28">
+        <v>1717.688362864649</v>
+      </c>
+      <c r="Q28">
+        <v>2968.58836286465</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1306123636293161</v>
+      </c>
+      <c r="T28">
+        <v>1.233844700301903</v>
+      </c>
+      <c r="U28">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V28">
+        <v>0.09</v>
+      </c>
+      <c r="W28">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>14.98299465978223</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1134732854878796</v>
+      </c>
+      <c r="C29">
+        <v>5536.816280508191</v>
+      </c>
+      <c r="D29">
+        <v>6771.697716988786</v>
+      </c>
+      <c r="E29">
+        <v>-1004.668328262348</v>
+      </c>
+      <c r="F29">
+        <v>1986.781436480594</v>
+      </c>
+      <c r="G29">
+        <v>751.9</v>
+      </c>
+      <c r="H29">
+        <v>4367</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3273.46</v>
+      </c>
+      <c r="K29">
+        <v>1250.9</v>
+      </c>
+      <c r="L29">
+        <v>2022.56</v>
+      </c>
+      <c r="M29">
+        <v>140.1823078044998</v>
+      </c>
+      <c r="N29">
+        <v>1882.3776921955</v>
+      </c>
+      <c r="O29">
+        <v>169.413992297595</v>
+      </c>
+      <c r="P29">
+        <v>1712.963699897905</v>
+      </c>
+      <c r="Q29">
+        <v>2963.863699897905</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1316949460708126</v>
+      </c>
+      <c r="T29">
+        <v>1.249594038616755</v>
+      </c>
+      <c r="U29">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V29">
+        <v>0.09</v>
+      </c>
+      <c r="W29">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>14.42806893164215</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1135995201767006</v>
+      </c>
+      <c r="C30">
+        <v>5458.70763955966</v>
+      </c>
+      <c r="D30">
+        <v>6767.173573687684</v>
+      </c>
+      <c r="E30">
+        <v>-931.083830614918</v>
+      </c>
+      <c r="F30">
+        <v>2060.365934128024</v>
+      </c>
+      <c r="G30">
+        <v>751.9</v>
+      </c>
+      <c r="H30">
+        <v>4367</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3273.46</v>
+      </c>
+      <c r="K30">
+        <v>1250.9</v>
+      </c>
+      <c r="L30">
+        <v>2022.56</v>
+      </c>
+      <c r="M30">
+        <v>145.3742451305924</v>
+      </c>
+      <c r="N30">
+        <v>1877.185754869407</v>
+      </c>
+      <c r="O30">
+        <v>168.9467179382467</v>
+      </c>
+      <c r="P30">
+        <v>1708.239036931161</v>
+      </c>
+      <c r="Q30">
+        <v>2959.139036931161</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.132807600246795</v>
+      </c>
+      <c r="T30">
+        <v>1.265780858551463</v>
+      </c>
+      <c r="U30">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V30">
+        <v>0.09</v>
+      </c>
+      <c r="W30">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>13.91278075551207</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1137257548655216</v>
+      </c>
+      <c r="C31">
+        <v>5380.605039698044</v>
+      </c>
+      <c r="D31">
+        <v>6762.655471473498</v>
+      </c>
+      <c r="E31">
+        <v>-857.499332967489</v>
+      </c>
+      <c r="F31">
+        <v>2133.950431775453</v>
+      </c>
+      <c r="G31">
+        <v>751.9</v>
+      </c>
+      <c r="H31">
+        <v>4367</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3273.46</v>
+      </c>
+      <c r="K31">
+        <v>1250.9</v>
+      </c>
+      <c r="L31">
+        <v>2022.56</v>
+      </c>
+      <c r="M31">
+        <v>150.566182456685</v>
+      </c>
+      <c r="N31">
+        <v>1871.993817543315</v>
+      </c>
+      <c r="O31">
+        <v>168.4794435788983</v>
+      </c>
+      <c r="P31">
+        <v>1703.514373964417</v>
+      </c>
+      <c r="Q31">
+        <v>2954.414373964417</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1339515967939319</v>
+      </c>
+      <c r="T31">
+        <v>1.282423645244896</v>
+      </c>
+      <c r="U31">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V31">
+        <v>0.09</v>
+      </c>
+      <c r="W31">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>13.43302969497717</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1138519895543426</v>
+      </c>
+      <c r="C32">
+        <v>5302.508468831425</v>
+      </c>
+      <c r="D32">
+        <v>6758.143398254308</v>
+      </c>
+      <c r="E32">
+        <v>-783.9148353200599</v>
+      </c>
+      <c r="F32">
+        <v>2207.534929422882</v>
+      </c>
+      <c r="G32">
+        <v>751.9</v>
+      </c>
+      <c r="H32">
+        <v>4367</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3273.46</v>
+      </c>
+      <c r="K32">
+        <v>1250.9</v>
+      </c>
+      <c r="L32">
+        <v>2022.56</v>
+      </c>
+      <c r="M32">
+        <v>155.7581197827775</v>
+      </c>
+      <c r="N32">
+        <v>1866.801880217222</v>
+      </c>
+      <c r="O32">
+        <v>168.01216921955</v>
+      </c>
+      <c r="P32">
+        <v>1698.789710997672</v>
+      </c>
+      <c r="Q32">
+        <v>2949.689710997673</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1351282789567013</v>
+      </c>
+      <c r="T32">
+        <v>1.299541940129569</v>
+      </c>
+      <c r="U32">
+        <v>0.07055748822216712</v>
+      </c>
+      <c r="V32">
+        <v>0.09</v>
+      </c>
+      <c r="W32">
+        <v>0.06420731428217208</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>12.98526203847793</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1142885342431635</v>
+      </c>
+      <c r="C33">
+        <v>5213.366630254385</v>
+      </c>
+      <c r="D33">
+        <v>6742.586057324697</v>
+      </c>
+      <c r="E33">
+        <v>-710.3303376726303</v>
+      </c>
+      <c r="F33">
+        <v>2281.119427070312</v>
+      </c>
+      <c r="G33">
+        <v>751.9</v>
+      </c>
+      <c r="H33">
+        <v>4367</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3273.46</v>
+      </c>
+      <c r="K33">
+        <v>1250.9</v>
+      </c>
+      <c r="L33">
+        <v>2022.56</v>
+      </c>
+      <c r="M33">
+        <v>163.4592884786474</v>
+      </c>
+      <c r="N33">
+        <v>1859.100711521352</v>
+      </c>
+      <c r="O33">
+        <v>167.3190640369217</v>
+      </c>
+      <c r="P33">
+        <v>1691.781647484431</v>
+      </c>
+      <c r="Q33">
+        <v>2942.681647484431</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1363390678488264</v>
+      </c>
+      <c r="T33">
+        <v>1.317156417474668</v>
+      </c>
+      <c r="U33">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V33">
+        <v>0.09</v>
+      </c>
+      <c r="W33">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>12.37347855129203</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1144247789319845</v>
+      </c>
+      <c r="C34">
+        <v>5134.941373973492</v>
+      </c>
+      <c r="D34">
+        <v>6737.745298691233</v>
+      </c>
+      <c r="E34">
+        <v>-636.7458400252008</v>
+      </c>
+      <c r="F34">
+        <v>2354.703924717741</v>
+      </c>
+      <c r="G34">
+        <v>751.9</v>
+      </c>
+      <c r="H34">
+        <v>4367</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3273.46</v>
+      </c>
+      <c r="K34">
+        <v>1250.9</v>
+      </c>
+      <c r="L34">
+        <v>2022.56</v>
+      </c>
+      <c r="M34">
+        <v>168.7321687521522</v>
+      </c>
+      <c r="N34">
+        <v>1853.827831247848</v>
+      </c>
+      <c r="O34">
+        <v>166.8445048123063</v>
+      </c>
+      <c r="P34">
+        <v>1686.983326435542</v>
+      </c>
+      <c r="Q34">
+        <v>2937.883326435542</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1375854681789551</v>
+      </c>
+      <c r="T34">
+        <v>1.335288967682858</v>
+      </c>
+      <c r="U34">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V34">
+        <v>0.09</v>
+      </c>
+      <c r="W34">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>11.98680734656415</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1145610236208055</v>
+      </c>
+      <c r="C35">
+        <v>5056.523063434966</v>
+      </c>
+      <c r="D35">
+        <v>6732.911485800138</v>
+      </c>
+      <c r="E35">
+        <v>-563.1613423777712</v>
+      </c>
+      <c r="F35">
+        <v>2428.288422365171</v>
+      </c>
+      <c r="G35">
+        <v>751.9</v>
+      </c>
+      <c r="H35">
+        <v>4367</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3273.46</v>
+      </c>
+      <c r="K35">
+        <v>1250.9</v>
+      </c>
+      <c r="L35">
+        <v>2022.56</v>
+      </c>
+      <c r="M35">
+        <v>174.005049025657</v>
+      </c>
+      <c r="N35">
+        <v>1848.554950974343</v>
+      </c>
+      <c r="O35">
+        <v>166.3699455876909</v>
+      </c>
+      <c r="P35">
+        <v>1682.185005386652</v>
+      </c>
+      <c r="Q35">
+        <v>2933.085005386652</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1388690744890876</v>
+      </c>
+      <c r="T35">
+        <v>1.353962788046517</v>
+      </c>
+      <c r="U35">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V35">
+        <v>0.09</v>
+      </c>
+      <c r="W35">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>11.62357076030463</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1146972683096265</v>
+      </c>
+      <c r="C36">
+        <v>4978.111683700417</v>
+      </c>
+      <c r="D36">
+        <v>6728.084603713019</v>
+      </c>
+      <c r="E36">
+        <v>-489.5768447303417</v>
+      </c>
+      <c r="F36">
+        <v>2501.8729200126</v>
+      </c>
+      <c r="G36">
+        <v>751.9</v>
+      </c>
+      <c r="H36">
+        <v>4367</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3273.46</v>
+      </c>
+      <c r="K36">
+        <v>1250.9</v>
+      </c>
+      <c r="L36">
+        <v>2022.56</v>
+      </c>
+      <c r="M36">
+        <v>179.2779292991617</v>
+      </c>
+      <c r="N36">
+        <v>1843.282070700838</v>
+      </c>
+      <c r="O36">
+        <v>165.8953863630754</v>
+      </c>
+      <c r="P36">
+        <v>1677.386684337763</v>
+      </c>
+      <c r="Q36">
+        <v>2928.286684337763</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1401915779601333</v>
+      </c>
+      <c r="T36">
+        <v>1.373202481754529</v>
+      </c>
+      <c r="U36">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V36">
+        <v>0.09</v>
+      </c>
+      <c r="W36">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>11.28170103206038</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1148335129984475</v>
+      </c>
+      <c r="C37">
+        <v>4899.707219874268</v>
+      </c>
+      <c r="D37">
+        <v>6723.264637534298</v>
+      </c>
+      <c r="E37">
+        <v>-415.9923470829121</v>
+      </c>
+      <c r="F37">
+        <v>2575.45741766003</v>
+      </c>
+      <c r="G37">
+        <v>751.9</v>
+      </c>
+      <c r="H37">
+        <v>4367</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3273.46</v>
+      </c>
+      <c r="K37">
+        <v>1250.9</v>
+      </c>
+      <c r="L37">
+        <v>2022.56</v>
+      </c>
+      <c r="M37">
+        <v>184.5508095726665</v>
+      </c>
+      <c r="N37">
+        <v>1838.009190427333</v>
+      </c>
+      <c r="O37">
+        <v>165.42082713846</v>
+      </c>
+      <c r="P37">
+        <v>1672.588363288873</v>
+      </c>
+      <c r="Q37">
+        <v>2923.488363288873</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1415547738456727</v>
+      </c>
+      <c r="T37">
+        <v>1.393034166038172</v>
+      </c>
+      <c r="U37">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V37">
+        <v>0.09</v>
+      </c>
+      <c r="W37">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>10.95936671685865</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1149697576872684</v>
+      </c>
+      <c r="C38">
+        <v>4821.309657103592</v>
+      </c>
+      <c r="D38">
+        <v>6718.451572411052</v>
+      </c>
+      <c r="E38">
+        <v>-342.4078494354831</v>
+      </c>
+      <c r="F38">
+        <v>2649.041915307459</v>
+      </c>
+      <c r="G38">
+        <v>751.9</v>
+      </c>
+      <c r="H38">
+        <v>4367</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3273.46</v>
+      </c>
+      <c r="K38">
+        <v>1250.9</v>
+      </c>
+      <c r="L38">
+        <v>2022.56</v>
+      </c>
+      <c r="M38">
+        <v>189.8236898461712</v>
+      </c>
+      <c r="N38">
+        <v>1832.736310153829</v>
+      </c>
+      <c r="O38">
+        <v>164.9462679138446</v>
+      </c>
+      <c r="P38">
+        <v>1667.790042239984</v>
+      </c>
+      <c r="Q38">
+        <v>2918.690042239984</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1429605696026351</v>
+      </c>
+      <c r="T38">
+        <v>1.413485590455678</v>
+      </c>
+      <c r="U38">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V38">
+        <v>0.09</v>
+      </c>
+      <c r="W38">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>10.65493986361258</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1151060023760894</v>
+      </c>
+      <c r="C39">
+        <v>4742.918980577962</v>
+      </c>
+      <c r="D39">
+        <v>6713.645393532852</v>
+      </c>
+      <c r="E39">
+        <v>-268.8233517880535</v>
+      </c>
+      <c r="F39">
+        <v>2722.626412954889</v>
+      </c>
+      <c r="G39">
+        <v>751.9</v>
+      </c>
+      <c r="H39">
+        <v>4367</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3273.46</v>
+      </c>
+      <c r="K39">
+        <v>1250.9</v>
+      </c>
+      <c r="L39">
+        <v>2022.56</v>
+      </c>
+      <c r="M39">
+        <v>195.096570119676</v>
+      </c>
+      <c r="N39">
+        <v>1827.463429880324</v>
+      </c>
+      <c r="O39">
+        <v>164.4717086892292</v>
+      </c>
+      <c r="P39">
+        <v>1662.991721191095</v>
+      </c>
+      <c r="Q39">
+        <v>2913.891721191095</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1444109937963266</v>
+      </c>
+      <c r="T39">
+        <v>1.434586266441995</v>
+      </c>
+      <c r="U39">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V39">
+        <v>0.09</v>
+      </c>
+      <c r="W39">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>10.36696851594737</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1152422470649104</v>
+      </c>
+      <c r="C40">
+        <v>4664.535175529307</v>
+      </c>
+      <c r="D40">
+        <v>6708.846086131624</v>
+      </c>
+      <c r="E40">
+        <v>-195.2388541406244</v>
+      </c>
+      <c r="F40">
+        <v>2796.210910602318</v>
+      </c>
+      <c r="G40">
+        <v>751.9</v>
+      </c>
+      <c r="H40">
+        <v>4367</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3273.46</v>
+      </c>
+      <c r="K40">
+        <v>1250.9</v>
+      </c>
+      <c r="L40">
+        <v>2022.56</v>
+      </c>
+      <c r="M40">
+        <v>200.3694503931808</v>
+      </c>
+      <c r="N40">
+        <v>1822.190549606819</v>
+      </c>
+      <c r="O40">
+        <v>163.9971494646137</v>
+      </c>
+      <c r="P40">
+        <v>1658.193400142205</v>
+      </c>
+      <c r="Q40">
+        <v>2909.093400142206</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1459082058672339</v>
+      </c>
+      <c r="T40">
+        <v>1.456367609395611</v>
+      </c>
+      <c r="U40">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V40">
+        <v>0.09</v>
+      </c>
+      <c r="W40">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>10.09415355500139</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1153784917537314</v>
+      </c>
+      <c r="C41">
+        <v>4586.158227231745</v>
+      </c>
+      <c r="D41">
+        <v>6704.053635481492</v>
+      </c>
+      <c r="E41">
+        <v>-121.6543564931949</v>
+      </c>
+      <c r="F41">
+        <v>2869.795408249747</v>
+      </c>
+      <c r="G41">
+        <v>751.9</v>
+      </c>
+      <c r="H41">
+        <v>4367</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3273.46</v>
+      </c>
+      <c r="K41">
+        <v>1250.9</v>
+      </c>
+      <c r="L41">
+        <v>2022.56</v>
+      </c>
+      <c r="M41">
+        <v>205.6423306666855</v>
+      </c>
+      <c r="N41">
+        <v>1816.917669333315</v>
+      </c>
+      <c r="O41">
+        <v>163.5225902399983</v>
+      </c>
+      <c r="P41">
+        <v>1653.395079093316</v>
+      </c>
+      <c r="Q41">
+        <v>2904.295079093316</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1474545068584988</v>
+      </c>
+      <c r="T41">
+        <v>1.47886309474115</v>
+      </c>
+      <c r="U41">
+        <v>0.07165748822216711</v>
+      </c>
+      <c r="V41">
+        <v>0.09</v>
+      </c>
+      <c r="W41">
+        <v>0.06520831428217207</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>9.835329104873148</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1163155364425524</v>
+      </c>
+      <c r="C42">
+        <v>4479.797458692865</v>
+      </c>
+      <c r="D42">
+        <v>6671.277364590042</v>
+      </c>
+      <c r="E42">
+        <v>-48.06985884576534</v>
+      </c>
+      <c r="F42">
+        <v>2943.379905897177</v>
+      </c>
+      <c r="G42">
+        <v>751.9</v>
+      </c>
+      <c r="H42">
+        <v>4367</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3273.46</v>
+      </c>
+      <c r="K42">
+        <v>1250.9</v>
+      </c>
+      <c r="L42">
+        <v>2022.56</v>
+      </c>
+      <c r="M42">
+        <v>217.3906467331641</v>
+      </c>
+      <c r="N42">
+        <v>1805.169353266836</v>
+      </c>
+      <c r="O42">
+        <v>162.4652417940152</v>
+      </c>
+      <c r="P42">
+        <v>1642.704111472821</v>
+      </c>
+      <c r="Q42">
+        <v>2893.604111472821</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1490523512161392</v>
+      </c>
+      <c r="T42">
+        <v>1.502108429598207</v>
+      </c>
+      <c r="U42">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V42">
+        <v>0.09</v>
+      </c>
+      <c r="W42">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>9.303804144262882</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1164718011313733</v>
+      </c>
+      <c r="C43">
+        <v>4400.778234897562</v>
+      </c>
+      <c r="D43">
+        <v>6665.842638442169</v>
+      </c>
+      <c r="E43">
+        <v>25.5146388016642</v>
+      </c>
+      <c r="F43">
+        <v>3016.964403544606</v>
+      </c>
+      <c r="G43">
+        <v>751.9</v>
+      </c>
+      <c r="H43">
+        <v>4367</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3273.46</v>
+      </c>
+      <c r="K43">
+        <v>1250.9</v>
+      </c>
+      <c r="L43">
+        <v>2022.56</v>
+      </c>
+      <c r="M43">
+        <v>222.8254129014932</v>
+      </c>
+      <c r="N43">
+        <v>1799.734587098507</v>
+      </c>
+      <c r="O43">
+        <v>161.9761128388656</v>
+      </c>
+      <c r="P43">
+        <v>1637.758474259641</v>
+      </c>
+      <c r="Q43">
+        <v>2888.658474259641</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1507043597892929</v>
+      </c>
+      <c r="T43">
+        <v>1.526141741908046</v>
+      </c>
+      <c r="U43">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V43">
+        <v>0.09</v>
+      </c>
+      <c r="W43">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>9.076882091963787</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1166280658201943</v>
+      </c>
+      <c r="C44">
+        <v>4321.76785864515</v>
+      </c>
+      <c r="D44">
+        <v>6660.416759837186</v>
+      </c>
+      <c r="E44">
+        <v>99.09913644909329</v>
+      </c>
+      <c r="F44">
+        <v>3090.548901192035</v>
+      </c>
+      <c r="G44">
+        <v>751.9</v>
+      </c>
+      <c r="H44">
+        <v>4367</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3273.46</v>
+      </c>
+      <c r="K44">
+        <v>1250.9</v>
+      </c>
+      <c r="L44">
+        <v>2022.56</v>
+      </c>
+      <c r="M44">
+        <v>228.2601790698223</v>
+      </c>
+      <c r="N44">
+        <v>1794.299820930178</v>
+      </c>
+      <c r="O44">
+        <v>161.486983883716</v>
+      </c>
+      <c r="P44">
+        <v>1632.812837046462</v>
+      </c>
+      <c r="Q44">
+        <v>2883.712837046462</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1524133341753139</v>
+      </c>
+      <c r="T44">
+        <v>1.55100378912512</v>
+      </c>
+      <c r="U44">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V44">
+        <v>0.09</v>
+      </c>
+      <c r="W44">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>8.860765851678934</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1167843305090153</v>
+      </c>
+      <c r="C45">
+        <v>4242.766308347973</v>
+      </c>
+      <c r="D45">
+        <v>6654.999707187439</v>
+      </c>
+      <c r="E45">
+        <v>172.6836340965228</v>
+      </c>
+      <c r="F45">
+        <v>3164.133398839465</v>
+      </c>
+      <c r="G45">
+        <v>751.9</v>
+      </c>
+      <c r="H45">
+        <v>4367</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3273.46</v>
+      </c>
+      <c r="K45">
+        <v>1250.9</v>
+      </c>
+      <c r="L45">
+        <v>2022.56</v>
+      </c>
+      <c r="M45">
+        <v>233.6949452381514</v>
+      </c>
+      <c r="N45">
+        <v>1788.865054761849</v>
+      </c>
+      <c r="O45">
+        <v>160.9978549285664</v>
+      </c>
+      <c r="P45">
+        <v>1627.867199833282</v>
+      </c>
+      <c r="Q45">
+        <v>2878.767199833283</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1541822725748795</v>
+      </c>
+      <c r="T45">
+        <v>1.576738188876126</v>
+      </c>
+      <c r="U45">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V45">
+        <v>0.09</v>
+      </c>
+      <c r="W45">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.654701529546866</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1169405951978363</v>
+      </c>
+      <c r="C46">
+        <v>4163.773562488539</v>
+      </c>
+      <c r="D46">
+        <v>6649.591458975434</v>
+      </c>
+      <c r="E46">
+        <v>246.2681317439524</v>
+      </c>
+      <c r="F46">
+        <v>3237.717896486894</v>
+      </c>
+      <c r="G46">
+        <v>751.9</v>
+      </c>
+      <c r="H46">
+        <v>4367</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3273.46</v>
+      </c>
+      <c r="K46">
+        <v>1250.9</v>
+      </c>
+      <c r="L46">
+        <v>2022.56</v>
+      </c>
+      <c r="M46">
+        <v>239.1297114064805</v>
+      </c>
+      <c r="N46">
+        <v>1783.430288593519</v>
+      </c>
+      <c r="O46">
+        <v>160.5087259734167</v>
+      </c>
+      <c r="P46">
+        <v>1622.921562620103</v>
+      </c>
+      <c r="Q46">
+        <v>2873.821562620103</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1560143873458581</v>
+      </c>
+      <c r="T46">
+        <v>1.603391674332526</v>
+      </c>
+      <c r="U46">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V46">
+        <v>0.09</v>
+      </c>
+      <c r="W46">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.458003767511709</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1170968598866573</v>
+      </c>
+      <c r="C47">
+        <v>4084.789599619252</v>
+      </c>
+      <c r="D47">
+        <v>6644.191993753577</v>
+      </c>
+      <c r="E47">
+        <v>319.8526293913819</v>
+      </c>
+      <c r="F47">
+        <v>3311.302394134324</v>
+      </c>
+      <c r="G47">
+        <v>751.9</v>
+      </c>
+      <c r="H47">
+        <v>4367</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3273.46</v>
+      </c>
+      <c r="K47">
+        <v>1250.9</v>
+      </c>
+      <c r="L47">
+        <v>2022.56</v>
+      </c>
+      <c r="M47">
+        <v>244.5644775748096</v>
+      </c>
+      <c r="N47">
+        <v>1777.99552242519</v>
+      </c>
+      <c r="O47">
+        <v>160.0195970182671</v>
+      </c>
+      <c r="P47">
+        <v>1617.975925406923</v>
+      </c>
+      <c r="Q47">
+        <v>2868.875925406923</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1579131244721451</v>
+      </c>
+      <c r="T47">
+        <v>1.631014377441886</v>
+      </c>
+      <c r="U47">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V47">
+        <v>0.09</v>
+      </c>
+      <c r="W47">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.270048128233672</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1172531245754782</v>
+      </c>
+      <c r="C48">
+        <v>4005.814398362119</v>
+      </c>
+      <c r="D48">
+        <v>6638.801290143872</v>
+      </c>
+      <c r="E48">
+        <v>393.437127038811</v>
+      </c>
+      <c r="F48">
+        <v>3384.886891781753</v>
+      </c>
+      <c r="G48">
+        <v>751.9</v>
+      </c>
+      <c r="H48">
+        <v>4367</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3273.46</v>
+      </c>
+      <c r="K48">
+        <v>1250.9</v>
+      </c>
+      <c r="L48">
+        <v>2022.56</v>
+      </c>
+      <c r="M48">
+        <v>249.9992437431387</v>
+      </c>
+      <c r="N48">
+        <v>1772.560756256861</v>
+      </c>
+      <c r="O48">
+        <v>159.5304680631175</v>
+      </c>
+      <c r="P48">
+        <v>1613.030288193744</v>
+      </c>
+      <c r="Q48">
+        <v>2863.930288193744</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.159882185195702</v>
+      </c>
+      <c r="T48">
+        <v>1.65966014362937</v>
+      </c>
+      <c r="U48">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V48">
+        <v>0.09</v>
+      </c>
+      <c r="W48">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>8.09026447327207</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1174093892642992</v>
+      </c>
+      <c r="C49">
+        <v>3926.84793740847</v>
+      </c>
+      <c r="D49">
+        <v>6633.419326837653</v>
+      </c>
+      <c r="E49">
+        <v>467.0216246862406</v>
+      </c>
+      <c r="F49">
+        <v>3458.471389429183</v>
+      </c>
+      <c r="G49">
+        <v>751.9</v>
+      </c>
+      <c r="H49">
+        <v>4367</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3273.46</v>
+      </c>
+      <c r="K49">
+        <v>1250.9</v>
+      </c>
+      <c r="L49">
+        <v>2022.56</v>
+      </c>
+      <c r="M49">
+        <v>255.4340099114678</v>
+      </c>
+      <c r="N49">
+        <v>1767.125990088532</v>
+      </c>
+      <c r="O49">
+        <v>159.0413391079679</v>
+      </c>
+      <c r="P49">
+        <v>1608.084650980564</v>
+      </c>
+      <c r="Q49">
+        <v>2858.984650980564</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1619255500975063</v>
+      </c>
+      <c r="T49">
+        <v>1.689386882125816</v>
+      </c>
+      <c r="U49">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V49">
+        <v>0.09</v>
+      </c>
+      <c r="W49">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>7.918131186606707</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1175656539531202</v>
+      </c>
+      <c r="C50">
+        <v>3847.890195518678</v>
+      </c>
+      <c r="D50">
+        <v>6628.04608259529</v>
+      </c>
+      <c r="E50">
+        <v>540.6061223336696</v>
+      </c>
+      <c r="F50">
+        <v>3532.055887076612</v>
+      </c>
+      <c r="G50">
+        <v>751.9</v>
+      </c>
+      <c r="H50">
+        <v>4367</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3273.46</v>
+      </c>
+      <c r="K50">
+        <v>1250.9</v>
+      </c>
+      <c r="L50">
+        <v>2022.56</v>
+      </c>
+      <c r="M50">
+        <v>260.8687760797969</v>
+      </c>
+      <c r="N50">
+        <v>1761.691223920203</v>
+      </c>
+      <c r="O50">
+        <v>158.5522101528183</v>
+      </c>
+      <c r="P50">
+        <v>1603.139013767385</v>
+      </c>
+      <c r="Q50">
+        <v>2854.039013767385</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1640475059570723</v>
+      </c>
+      <c r="T50">
+        <v>1.720256956718279</v>
+      </c>
+      <c r="U50">
+        <v>0.07385748822216712</v>
+      </c>
+      <c r="V50">
+        <v>0.09</v>
+      </c>
+      <c r="W50">
+        <v>0.06721031428217208</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.753170120219068</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1183907686419411</v>
+      </c>
+      <c r="C51">
+        <v>3746.077409644493</v>
+      </c>
+      <c r="D51">
+        <v>6599.817794368535</v>
+      </c>
+      <c r="E51">
+        <v>614.1906199810992</v>
+      </c>
+      <c r="F51">
+        <v>3605.640384724041</v>
+      </c>
+      <c r="G51">
+        <v>751.9</v>
+      </c>
+      <c r="H51">
+        <v>4367</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3273.46</v>
+      </c>
+      <c r="K51">
+        <v>1250.9</v>
+      </c>
+      <c r="L51">
+        <v>2022.56</v>
+      </c>
+      <c r="M51">
+        <v>271.712002825212</v>
+      </c>
+      <c r="N51">
+        <v>1750.847997174788</v>
+      </c>
+      <c r="O51">
+        <v>157.5763197457309</v>
+      </c>
+      <c r="P51">
+        <v>1593.271677429057</v>
+      </c>
+      <c r="Q51">
+        <v>2844.171677429057</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1662526757719154</v>
+      </c>
+      <c r="T51">
+        <v>1.752337622471231</v>
+      </c>
+      <c r="U51">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V51">
+        <v>0.09</v>
+      </c>
+      <c r="W51">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.443763907997396</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1185606833307621</v>
+      </c>
+      <c r="C52">
+        <v>3666.709730100079</v>
+      </c>
+      <c r="D52">
+        <v>6594.034612471551</v>
+      </c>
+      <c r="E52">
+        <v>687.7751176285287</v>
+      </c>
+      <c r="F52">
+        <v>3679.224882371471</v>
+      </c>
+      <c r="G52">
+        <v>751.9</v>
+      </c>
+      <c r="H52">
+        <v>4367</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3273.46</v>
+      </c>
+      <c r="K52">
+        <v>1250.9</v>
+      </c>
+      <c r="L52">
+        <v>2022.56</v>
+      </c>
+      <c r="M52">
+        <v>277.2571457400123</v>
+      </c>
+      <c r="N52">
+        <v>1745.302854259988</v>
+      </c>
+      <c r="O52">
+        <v>157.0772568833989</v>
+      </c>
+      <c r="P52">
+        <v>1588.225597376589</v>
+      </c>
+      <c r="Q52">
+        <v>2839.125597376589</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1685460523793522</v>
+      </c>
+      <c r="T52">
+        <v>1.785701514854301</v>
+      </c>
+      <c r="U52">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V52">
+        <v>0.09</v>
+      </c>
+      <c r="W52">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>7.294888629837447</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1187305980195831</v>
+      </c>
+      <c r="C53">
+        <v>3587.352176869069</v>
+      </c>
+      <c r="D53">
+        <v>6588.26155688797</v>
+      </c>
+      <c r="E53">
+        <v>761.3596152759583</v>
+      </c>
+      <c r="F53">
+        <v>3752.8093800189</v>
+      </c>
+      <c r="G53">
+        <v>751.9</v>
+      </c>
+      <c r="H53">
+        <v>4367</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3273.46</v>
+      </c>
+      <c r="K53">
+        <v>1250.9</v>
+      </c>
+      <c r="L53">
+        <v>2022.56</v>
+      </c>
+      <c r="M53">
+        <v>282.8022886548126</v>
+      </c>
+      <c r="N53">
+        <v>1739.757711345187</v>
+      </c>
+      <c r="O53">
+        <v>156.5781940210668</v>
+      </c>
+      <c r="P53">
+        <v>1583.179517324121</v>
+      </c>
+      <c r="Q53">
+        <v>2834.07951732412</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1709330361952558</v>
+      </c>
+      <c r="T53">
+        <v>1.82042719876321</v>
+      </c>
+      <c r="U53">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V53">
+        <v>0.09</v>
+      </c>
+      <c r="W53">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>7.15185159787985</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1189005127084041</v>
+      </c>
+      <c r="C54">
+        <v>3508.004723378067</v>
+      </c>
+      <c r="D54">
+        <v>6582.498601044397</v>
+      </c>
+      <c r="E54">
+        <v>834.9441129233878</v>
+      </c>
+      <c r="F54">
+        <v>3826.39387766633</v>
+      </c>
+      <c r="G54">
+        <v>751.9</v>
+      </c>
+      <c r="H54">
+        <v>4367</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3273.46</v>
+      </c>
+      <c r="K54">
+        <v>1250.9</v>
+      </c>
+      <c r="L54">
+        <v>2022.56</v>
+      </c>
+      <c r="M54">
+        <v>288.3474315696128</v>
+      </c>
+      <c r="N54">
+        <v>1734.212568430387</v>
+      </c>
+      <c r="O54">
+        <v>156.0791311587348</v>
+      </c>
+      <c r="P54">
+        <v>1578.133437271652</v>
+      </c>
+      <c r="Q54">
+        <v>2829.033437271652</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1734194776701555</v>
+      </c>
+      <c r="T54">
+        <v>1.856599786168324</v>
+      </c>
+      <c r="U54">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V54">
+        <v>0.09</v>
+      </c>
+      <c r="W54">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>7.014315990228315</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1190704273972251</v>
+      </c>
+      <c r="C55">
+        <v>3428.66734314657</v>
+      </c>
+      <c r="D55">
+        <v>6576.74571846033</v>
+      </c>
+      <c r="E55">
+        <v>908.5286105708174</v>
+      </c>
+      <c r="F55">
+        <v>3899.978375313759</v>
+      </c>
+      <c r="G55">
+        <v>751.9</v>
+      </c>
+      <c r="H55">
+        <v>4367</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3273.46</v>
+      </c>
+      <c r="K55">
+        <v>1250.9</v>
+      </c>
+      <c r="L55">
+        <v>2022.56</v>
+      </c>
+      <c r="M55">
+        <v>293.8925744844131</v>
+      </c>
+      <c r="N55">
+        <v>1728.667425515587</v>
+      </c>
+      <c r="O55">
+        <v>155.5800682964028</v>
+      </c>
+      <c r="P55">
+        <v>1573.087357219184</v>
+      </c>
+      <c r="Q55">
+        <v>2823.987357219184</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1760117251652636</v>
+      </c>
+      <c r="T55">
+        <v>1.894311632611953</v>
+      </c>
+      <c r="U55">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V55">
+        <v>0.09</v>
+      </c>
+      <c r="W55">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>6.881970405507024</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1192403420860461</v>
+      </c>
+      <c r="C56">
+        <v>3349.340009786572</v>
+      </c>
+      <c r="D56">
+        <v>6571.002882747761</v>
+      </c>
+      <c r="E56">
+        <v>982.1131082182465</v>
+      </c>
+      <c r="F56">
+        <v>3973.562872961189</v>
+      </c>
+      <c r="G56">
+        <v>751.9</v>
+      </c>
+      <c r="H56">
+        <v>4367</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3273.46</v>
+      </c>
+      <c r="K56">
+        <v>1250.9</v>
+      </c>
+      <c r="L56">
+        <v>2022.56</v>
+      </c>
+      <c r="M56">
+        <v>299.4377173992133</v>
+      </c>
+      <c r="N56">
+        <v>1723.122282600787</v>
+      </c>
+      <c r="O56">
+        <v>155.0810054340708</v>
+      </c>
+      <c r="P56">
+        <v>1568.041277166716</v>
+      </c>
+      <c r="Q56">
+        <v>2818.941277166716</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1787166790732025</v>
+      </c>
+      <c r="T56">
+        <v>1.933663124553132</v>
+      </c>
+      <c r="U56">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V56">
+        <v>0.09</v>
+      </c>
+      <c r="W56">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.754526509108747</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.119410256774867</v>
+      </c>
+      <c r="C57">
+        <v>3270.022697002151</v>
+      </c>
+      <c r="D57">
+        <v>6565.27006761077</v>
+      </c>
+      <c r="E57">
+        <v>1055.697605865676</v>
+      </c>
+      <c r="F57">
+        <v>4047.147370608618</v>
+      </c>
+      <c r="G57">
+        <v>751.9</v>
+      </c>
+      <c r="H57">
+        <v>4367</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3273.46</v>
+      </c>
+      <c r="K57">
+        <v>1250.9</v>
+      </c>
+      <c r="L57">
+        <v>2022.56</v>
+      </c>
+      <c r="M57">
+        <v>304.9828603140136</v>
+      </c>
+      <c r="N57">
+        <v>1717.577139685986</v>
+      </c>
+      <c r="O57">
+        <v>154.5819425717388</v>
+      </c>
+      <c r="P57">
+        <v>1562.995197114248</v>
+      </c>
+      <c r="Q57">
+        <v>2813.895197114248</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1815418531548275</v>
+      </c>
+      <c r="T57">
+        <v>1.974763571691696</v>
+      </c>
+      <c r="U57">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V57">
+        <v>0.09</v>
+      </c>
+      <c r="W57">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.63171693621586</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.119580171463688</v>
+      </c>
+      <c r="C58">
+        <v>3190.715378589073</v>
+      </c>
+      <c r="D58">
+        <v>6559.547246845122</v>
+      </c>
+      <c r="E58">
+        <v>1129.282103513106</v>
+      </c>
+      <c r="F58">
+        <v>4120.731868256048</v>
+      </c>
+      <c r="G58">
+        <v>751.9</v>
+      </c>
+      <c r="H58">
+        <v>4367</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3273.46</v>
+      </c>
+      <c r="K58">
+        <v>1250.9</v>
+      </c>
+      <c r="L58">
+        <v>2022.56</v>
+      </c>
+      <c r="M58">
+        <v>310.5280032288139</v>
+      </c>
+      <c r="N58">
+        <v>1712.031996771186</v>
+      </c>
+      <c r="O58">
+        <v>154.0828797094067</v>
+      </c>
+      <c r="P58">
+        <v>1557.949117061779</v>
+      </c>
+      <c r="Q58">
+        <v>2808.849117061779</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1844954442401628</v>
+      </c>
+      <c r="T58">
+        <v>2.017732220972922</v>
+      </c>
+      <c r="U58">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V58">
+        <v>0.09</v>
+      </c>
+      <c r="W58">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.51329341949772</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.119750086152509</v>
+      </c>
+      <c r="C59">
+        <v>3111.418028434392</v>
+      </c>
+      <c r="D59">
+        <v>6553.83439433787</v>
+      </c>
+      <c r="E59">
+        <v>1202.866601160535</v>
+      </c>
+      <c r="F59">
+        <v>4194.316365903477</v>
+      </c>
+      <c r="G59">
+        <v>751.9</v>
+      </c>
+      <c r="H59">
+        <v>4367</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3273.46</v>
+      </c>
+      <c r="K59">
+        <v>1250.9</v>
+      </c>
+      <c r="L59">
+        <v>2022.56</v>
+      </c>
+      <c r="M59">
+        <v>316.0731461436141</v>
+      </c>
+      <c r="N59">
+        <v>1706.486853856386</v>
+      </c>
+      <c r="O59">
+        <v>153.5838168470747</v>
+      </c>
+      <c r="P59">
+        <v>1552.903037009311</v>
+      </c>
+      <c r="Q59">
+        <v>2803.803037009311</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1875864116550486</v>
+      </c>
+      <c r="T59">
+        <v>2.062699412081182</v>
+      </c>
+      <c r="U59">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V59">
+        <v>0.09</v>
+      </c>
+      <c r="W59">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>6.399025113892498</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.11992000084133</v>
+      </c>
+      <c r="C60">
+        <v>3032.13062051605</v>
+      </c>
+      <c r="D60">
+        <v>6548.131484066957</v>
+      </c>
+      <c r="E60">
+        <v>1276.451098807964</v>
+      </c>
+      <c r="F60">
+        <v>4267.900863550906</v>
+      </c>
+      <c r="G60">
+        <v>751.9</v>
+      </c>
+      <c r="H60">
+        <v>4367</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3273.46</v>
+      </c>
+      <c r="K60">
+        <v>1250.9</v>
+      </c>
+      <c r="L60">
+        <v>2022.56</v>
+      </c>
+      <c r="M60">
+        <v>321.6182890584143</v>
+      </c>
+      <c r="N60">
+        <v>1700.941710941586</v>
+      </c>
+      <c r="O60">
+        <v>153.0847539847427</v>
+      </c>
+      <c r="P60">
+        <v>1547.856956956843</v>
+      </c>
+      <c r="Q60">
+        <v>2798.756956956843</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1908245679944528</v>
+      </c>
+      <c r="T60">
+        <v>2.109807898004121</v>
+      </c>
+      <c r="U60">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V60">
+        <v>0.09</v>
+      </c>
+      <c r="W60">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>6.288697094687454</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.120089915530151</v>
+      </c>
+      <c r="C61">
+        <v>2952.853128902486</v>
+      </c>
+      <c r="D61">
+        <v>6542.438490100822</v>
+      </c>
+      <c r="E61">
+        <v>1350.035596455393</v>
+      </c>
+      <c r="F61">
+        <v>4341.485361198335</v>
+      </c>
+      <c r="G61">
+        <v>751.9</v>
+      </c>
+      <c r="H61">
+        <v>4367</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3273.46</v>
+      </c>
+      <c r="K61">
+        <v>1250.9</v>
+      </c>
+      <c r="L61">
+        <v>2022.56</v>
+      </c>
+      <c r="M61">
+        <v>327.1634319732145</v>
+      </c>
+      <c r="N61">
+        <v>1695.396568026785</v>
+      </c>
+      <c r="O61">
+        <v>152.5856911224107</v>
+      </c>
+      <c r="P61">
+        <v>1542.810876904375</v>
+      </c>
+      <c r="Q61">
+        <v>2793.710876904375</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1942206831796816</v>
+      </c>
+      <c r="T61">
+        <v>2.15921435885013</v>
+      </c>
+      <c r="U61">
+        <v>0.07535748822216712</v>
+      </c>
+      <c r="V61">
+        <v>0.09</v>
+      </c>
+      <c r="W61">
+        <v>0.06857531428217208</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>6.18210900833682</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1210242302189719</v>
+      </c>
+      <c r="C62">
+        <v>2848.140433541275</v>
+      </c>
+      <c r="D62">
+        <v>6511.31029238704</v>
+      </c>
+      <c r="E62">
+        <v>1423.620094102822</v>
+      </c>
+      <c r="F62">
+        <v>4415.069858845764</v>
+      </c>
+      <c r="G62">
+        <v>751.9</v>
+      </c>
+      <c r="H62">
+        <v>4367</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3273.46</v>
+      </c>
+      <c r="K62">
+        <v>1250.9</v>
+      </c>
+      <c r="L62">
+        <v>2022.56</v>
+      </c>
+      <c r="M62">
+        <v>338.8896726903988</v>
+      </c>
+      <c r="N62">
+        <v>1683.670327309601</v>
+      </c>
+      <c r="O62">
+        <v>151.5303294578641</v>
+      </c>
+      <c r="P62">
+        <v>1532.139997851737</v>
+      </c>
+      <c r="Q62">
+        <v>2783.039997851737</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1977866041241717</v>
+      </c>
+      <c r="T62">
+        <v>2.21109114273844</v>
+      </c>
+      <c r="U62">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V62">
+        <v>0.09</v>
+      </c>
+      <c r="W62">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.968196032482113</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1212068849077929</v>
+      </c>
+      <c r="C63">
+        <v>2768.505082951392</v>
+      </c>
+      <c r="D63">
+        <v>6505.259439444587</v>
+      </c>
+      <c r="E63">
+        <v>1497.204591750252</v>
+      </c>
+      <c r="F63">
+        <v>4488.654356493194</v>
+      </c>
+      <c r="G63">
+        <v>751.9</v>
+      </c>
+      <c r="H63">
+        <v>4367</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3273.46</v>
+      </c>
+      <c r="K63">
+        <v>1250.9</v>
+      </c>
+      <c r="L63">
+        <v>2022.56</v>
+      </c>
+      <c r="M63">
+        <v>344.5378339019055</v>
+      </c>
+      <c r="N63">
+        <v>1678.022166098094</v>
+      </c>
+      <c r="O63">
+        <v>151.0219949488285</v>
+      </c>
+      <c r="P63">
+        <v>1527.000171149266</v>
+      </c>
+      <c r="Q63">
+        <v>2777.900171149266</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.201535392809405</v>
+      </c>
+      <c r="T63">
+        <v>2.265628274518458</v>
+      </c>
+      <c r="U63">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V63">
+        <v>0.09</v>
+      </c>
+      <c r="W63">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.870356753261094</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1213895395966139</v>
+      </c>
+      <c r="C64">
+        <v>2688.880967835657</v>
+      </c>
+      <c r="D64">
+        <v>6499.219821976281</v>
+      </c>
+      <c r="E64">
+        <v>1570.789089397681</v>
+      </c>
+      <c r="F64">
+        <v>4562.238854140624</v>
+      </c>
+      <c r="G64">
+        <v>751.9</v>
+      </c>
+      <c r="H64">
+        <v>4367</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3273.46</v>
+      </c>
+      <c r="K64">
+        <v>1250.9</v>
+      </c>
+      <c r="L64">
+        <v>2022.56</v>
+      </c>
+      <c r="M64">
+        <v>350.1859951134121</v>
+      </c>
+      <c r="N64">
+        <v>1672.374004886588</v>
+      </c>
+      <c r="O64">
+        <v>150.5136604397929</v>
+      </c>
+      <c r="P64">
+        <v>1521.860344446795</v>
+      </c>
+      <c r="Q64">
+        <v>2772.760344446795</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2054814861622821</v>
+      </c>
+      <c r="T64">
+        <v>2.323035781655319</v>
+      </c>
+      <c r="U64">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V64">
+        <v>0.09</v>
+      </c>
+      <c r="W64">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.7756735798214</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1215721942854349</v>
+      </c>
+      <c r="C65">
+        <v>2609.268056929356</v>
+      </c>
+      <c r="D65">
+        <v>6493.19140871741</v>
+      </c>
+      <c r="E65">
+        <v>1644.373587045111</v>
+      </c>
+      <c r="F65">
+        <v>4635.823351788054</v>
+      </c>
+      <c r="G65">
+        <v>751.9</v>
+      </c>
+      <c r="H65">
+        <v>4367</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3273.46</v>
+      </c>
+      <c r="K65">
+        <v>1250.9</v>
+      </c>
+      <c r="L65">
+        <v>2022.56</v>
+      </c>
+      <c r="M65">
+        <v>355.8341563249188</v>
+      </c>
+      <c r="N65">
+        <v>1666.725843675081</v>
+      </c>
+      <c r="O65">
+        <v>150.0053259307573</v>
+      </c>
+      <c r="P65">
+        <v>1516.720517744324</v>
+      </c>
+      <c r="Q65">
+        <v>2767.620517744324</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.209640881858558</v>
+      </c>
+      <c r="T65">
+        <v>2.383546397286064</v>
+      </c>
+      <c r="U65">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V65">
+        <v>0.09</v>
+      </c>
+      <c r="W65">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.683996221411535</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1217548489742558</v>
+      </c>
+      <c r="C66">
+        <v>2529.666319083671</v>
+      </c>
+      <c r="D66">
+        <v>6487.174168519154</v>
+      </c>
+      <c r="E66">
+        <v>1717.958084692541</v>
+      </c>
+      <c r="F66">
+        <v>4709.407849435483</v>
+      </c>
+      <c r="G66">
+        <v>751.9</v>
+      </c>
+      <c r="H66">
+        <v>4367</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3273.46</v>
+      </c>
+      <c r="K66">
+        <v>1250.9</v>
+      </c>
+      <c r="L66">
+        <v>2022.56</v>
+      </c>
+      <c r="M66">
+        <v>361.4823175364254</v>
+      </c>
+      <c r="N66">
+        <v>1661.077682463575</v>
+      </c>
+      <c r="O66">
+        <v>149.4969914217217</v>
+      </c>
+      <c r="P66">
+        <v>1511.580691041853</v>
+      </c>
+      <c r="Q66">
+        <v>2762.480691041853</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2140313550935159</v>
+      </c>
+      <c r="T66">
+        <v>2.447418713785184</v>
+      </c>
+      <c r="U66">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V66">
+        <v>0.09</v>
+      </c>
+      <c r="W66">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.595183780451981</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1219375036630768</v>
+      </c>
+      <c r="C67">
+        <v>2450.075723265131</v>
+      </c>
+      <c r="D67">
+        <v>6481.168070348044</v>
+      </c>
+      <c r="E67">
+        <v>1791.542582339971</v>
+      </c>
+      <c r="F67">
+        <v>4782.992347082913</v>
+      </c>
+      <c r="G67">
+        <v>751.9</v>
+      </c>
+      <c r="H67">
+        <v>4367</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3273.46</v>
+      </c>
+      <c r="K67">
+        <v>1250.9</v>
+      </c>
+      <c r="L67">
+        <v>2022.56</v>
+      </c>
+      <c r="M67">
+        <v>367.1304787479321</v>
+      </c>
+      <c r="N67">
+        <v>1655.429521252068</v>
+      </c>
+      <c r="O67">
+        <v>148.9886569126861</v>
+      </c>
+      <c r="P67">
+        <v>1506.440864339382</v>
+      </c>
+      <c r="Q67">
+        <v>2757.340864339382</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2186727125133285</v>
+      </c>
+      <c r="T67">
+        <v>2.514940876941397</v>
+      </c>
+      <c r="U67">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V67">
+        <v>0.09</v>
+      </c>
+      <c r="W67">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.509104029983487</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1221201583518978</v>
+      </c>
+      <c r="C68">
+        <v>2370.496238555098</v>
+      </c>
+      <c r="D68">
+        <v>6475.17308328544</v>
+      </c>
+      <c r="E68">
+        <v>1865.1270799874</v>
+      </c>
+      <c r="F68">
+        <v>4856.576844730342</v>
+      </c>
+      <c r="G68">
+        <v>751.9</v>
+      </c>
+      <c r="H68">
+        <v>4367</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3273.46</v>
+      </c>
+      <c r="K68">
+        <v>1250.9</v>
+      </c>
+      <c r="L68">
+        <v>2022.56</v>
+      </c>
+      <c r="M68">
+        <v>372.7786399594387</v>
+      </c>
+      <c r="N68">
+        <v>1649.781360040561</v>
+      </c>
+      <c r="O68">
+        <v>148.4803224036505</v>
+      </c>
+      <c r="P68">
+        <v>1501.301037636911</v>
+      </c>
+      <c r="Q68">
+        <v>2752.201037636911</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.223587090957836</v>
+      </c>
+      <c r="T68">
+        <v>2.586434932047975</v>
+      </c>
+      <c r="U68">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V68">
+        <v>0.09</v>
+      </c>
+      <c r="W68">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.42563275680192</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1223028130407188</v>
+      </c>
+      <c r="C69">
+        <v>2290.927834149216</v>
+      </c>
+      <c r="D69">
+        <v>6469.189176526987</v>
+      </c>
+      <c r="E69">
+        <v>1938.711577634829</v>
+      </c>
+      <c r="F69">
+        <v>4930.161342377771</v>
+      </c>
+      <c r="G69">
+        <v>751.9</v>
+      </c>
+      <c r="H69">
+        <v>4367</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3273.46</v>
+      </c>
+      <c r="K69">
+        <v>1250.9</v>
+      </c>
+      <c r="L69">
+        <v>2022.56</v>
+      </c>
+      <c r="M69">
+        <v>378.4268011709453</v>
+      </c>
+      <c r="N69">
+        <v>1644.133198829055</v>
+      </c>
+      <c r="O69">
+        <v>147.9719878946149</v>
+      </c>
+      <c r="P69">
+        <v>1496.16121093444</v>
+      </c>
+      <c r="Q69">
+        <v>2747.06121093444</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2287993105201924</v>
+      </c>
+      <c r="T69">
+        <v>2.662261960191316</v>
+      </c>
+      <c r="U69">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V69">
+        <v>0.09</v>
+      </c>
+      <c r="W69">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.344653163416817</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1224854677295398</v>
+      </c>
+      <c r="C70">
+        <v>2211.370479356899</v>
+      </c>
+      <c r="D70">
+        <v>6463.2163193821</v>
+      </c>
+      <c r="E70">
+        <v>2012.296075282259</v>
+      </c>
+      <c r="F70">
+        <v>5003.745840025201</v>
+      </c>
+      <c r="G70">
+        <v>751.9</v>
+      </c>
+      <c r="H70">
+        <v>4367</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3273.46</v>
+      </c>
+      <c r="K70">
+        <v>1250.9</v>
+      </c>
+      <c r="L70">
+        <v>2022.56</v>
+      </c>
+      <c r="M70">
+        <v>384.074962382452</v>
+      </c>
+      <c r="N70">
+        <v>1638.485037617548</v>
+      </c>
+      <c r="O70">
+        <v>147.4636533855793</v>
+      </c>
+      <c r="P70">
+        <v>1491.021384231969</v>
+      </c>
+      <c r="Q70">
+        <v>2741.921384231969</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2343372938051961</v>
+      </c>
+      <c r="T70">
+        <v>2.742828177593615</v>
+      </c>
+      <c r="U70">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V70">
+        <v>0.09</v>
+      </c>
+      <c r="W70">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.266055322778334</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1226681224183607</v>
+      </c>
+      <c r="C71">
+        <v>2131.824143600796</v>
+      </c>
+      <c r="D71">
+        <v>6457.254481273426</v>
+      </c>
+      <c r="E71">
+        <v>2085.880572929688</v>
+      </c>
+      <c r="F71">
+        <v>5077.33033767263</v>
+      </c>
+      <c r="G71">
+        <v>751.9</v>
+      </c>
+      <c r="H71">
+        <v>4367</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3273.46</v>
+      </c>
+      <c r="K71">
+        <v>1250.9</v>
+      </c>
+      <c r="L71">
+        <v>2022.56</v>
+      </c>
+      <c r="M71">
+        <v>389.7231235939587</v>
+      </c>
+      <c r="N71">
+        <v>1632.836876406041</v>
+      </c>
+      <c r="O71">
+        <v>146.9553188765437</v>
+      </c>
+      <c r="P71">
+        <v>1485.881557529498</v>
+      </c>
+      <c r="Q71">
+        <v>2736.781557529498</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2402325663343936</v>
+      </c>
+      <c r="T71">
+        <v>2.828592215473482</v>
+      </c>
+      <c r="U71">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V71">
+        <v>0.09</v>
+      </c>
+      <c r="W71">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.189735680419227</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1228507771071817</v>
+      </c>
+      <c r="C72">
+        <v>2052.288796416276</v>
+      </c>
+      <c r="D72">
+        <v>6451.303631736336</v>
+      </c>
+      <c r="E72">
+        <v>2159.465070577118</v>
+      </c>
+      <c r="F72">
+        <v>5150.91483532006</v>
+      </c>
+      <c r="G72">
+        <v>751.9</v>
+      </c>
+      <c r="H72">
+        <v>4367</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3273.46</v>
+      </c>
+      <c r="K72">
+        <v>1250.9</v>
+      </c>
+      <c r="L72">
+        <v>2022.56</v>
+      </c>
+      <c r="M72">
+        <v>395.3712848054654</v>
+      </c>
+      <c r="N72">
+        <v>1627.188715194535</v>
+      </c>
+      <c r="O72">
+        <v>146.4469843675081</v>
+      </c>
+      <c r="P72">
+        <v>1480.741730827026</v>
+      </c>
+      <c r="Q72">
+        <v>2731.641730827027</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2465208570322042</v>
+      </c>
+      <c r="T72">
+        <v>2.920073855878673</v>
+      </c>
+      <c r="U72">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V72">
+        <v>0.09</v>
+      </c>
+      <c r="W72">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.115596599270381</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1230334317960027</v>
+      </c>
+      <c r="C73">
+        <v>1972.764407450908</v>
+      </c>
+      <c r="D73">
+        <v>6445.363740418396</v>
+      </c>
+      <c r="E73">
+        <v>2233.049568224546</v>
+      </c>
+      <c r="F73">
+        <v>5224.499332967488</v>
+      </c>
+      <c r="G73">
+        <v>751.9</v>
+      </c>
+      <c r="H73">
+        <v>4367</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3273.46</v>
+      </c>
+      <c r="K73">
+        <v>1250.9</v>
+      </c>
+      <c r="L73">
+        <v>2022.56</v>
+      </c>
+      <c r="M73">
+        <v>401.0194460169719</v>
+      </c>
+      <c r="N73">
+        <v>1621.540553983028</v>
+      </c>
+      <c r="O73">
+        <v>145.9386498584725</v>
+      </c>
+      <c r="P73">
+        <v>1475.601904124556</v>
+      </c>
+      <c r="Q73">
+        <v>2726.501904124556</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2532428229505535</v>
+      </c>
+      <c r="T73">
+        <v>3.017864574932497</v>
+      </c>
+      <c r="U73">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V73">
+        <v>0.09</v>
+      </c>
+      <c r="W73">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.043545942942631</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1232160864848237</v>
+      </c>
+      <c r="C74">
+        <v>1893.250946463937</v>
+      </c>
+      <c r="D74">
+        <v>6439.434777078855</v>
+      </c>
+      <c r="E74">
+        <v>2306.634065871976</v>
+      </c>
+      <c r="F74">
+        <v>5298.083830614918</v>
+      </c>
+      <c r="G74">
+        <v>751.9</v>
+      </c>
+      <c r="H74">
+        <v>4367</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3273.46</v>
+      </c>
+      <c r="K74">
+        <v>1250.9</v>
+      </c>
+      <c r="L74">
+        <v>2022.56</v>
+      </c>
+      <c r="M74">
+        <v>406.6676072284786</v>
+      </c>
+      <c r="N74">
+        <v>1615.892392771521</v>
+      </c>
+      <c r="O74">
+        <v>145.4303153494369</v>
+      </c>
+      <c r="P74">
+        <v>1470.462077422084</v>
+      </c>
+      <c r="Q74">
+        <v>2721.362077422084</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.260444929291642</v>
+      </c>
+      <c r="T74">
+        <v>3.12264034534731</v>
+      </c>
+      <c r="U74">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V74">
+        <v>0.09</v>
+      </c>
+      <c r="W74">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.973496693735093</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1233987411736447</v>
+      </c>
+      <c r="C75">
+        <v>1813.748383325784</v>
+      </c>
+      <c r="D75">
+        <v>6433.516711588131</v>
+      </c>
+      <c r="E75">
+        <v>2380.218563519405</v>
+      </c>
+      <c r="F75">
+        <v>5371.668328262347</v>
+      </c>
+      <c r="G75">
+        <v>751.9</v>
+      </c>
+      <c r="H75">
+        <v>4367</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3273.46</v>
+      </c>
+      <c r="K75">
+        <v>1250.9</v>
+      </c>
+      <c r="L75">
+        <v>2022.56</v>
+      </c>
+      <c r="M75">
+        <v>412.3157684399852</v>
+      </c>
+      <c r="N75">
+        <v>1610.244231560015</v>
+      </c>
+      <c r="O75">
+        <v>144.9219808404013</v>
+      </c>
+      <c r="P75">
+        <v>1465.322250719613</v>
+      </c>
+      <c r="Q75">
+        <v>2716.222250719613</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2681805249913298</v>
+      </c>
+      <c r="T75">
+        <v>3.235177283940998</v>
+      </c>
+      <c r="U75">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V75">
+        <v>0.09</v>
+      </c>
+      <c r="W75">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.905366602040092</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1235813958624656</v>
+      </c>
+      <c r="C76">
+        <v>1734.256688017525</v>
+      </c>
+      <c r="D76">
+        <v>6427.609513927303</v>
+      </c>
+      <c r="E76">
+        <v>2453.803061166835</v>
+      </c>
+      <c r="F76">
+        <v>5445.252825909777</v>
+      </c>
+      <c r="G76">
+        <v>751.9</v>
+      </c>
+      <c r="H76">
+        <v>4367</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3273.46</v>
+      </c>
+      <c r="K76">
+        <v>1250.9</v>
+      </c>
+      <c r="L76">
+        <v>2022.56</v>
+      </c>
+      <c r="M76">
+        <v>417.9639296514919</v>
+      </c>
+      <c r="N76">
+        <v>1604.596070348508</v>
+      </c>
+      <c r="O76">
+        <v>144.4136463313657</v>
+      </c>
+      <c r="P76">
+        <v>1460.182424017142</v>
+      </c>
+      <c r="Q76">
+        <v>2711.082424017142</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2765111665140703</v>
+      </c>
+      <c r="T76">
+        <v>3.356370910118815</v>
+      </c>
+      <c r="U76">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V76">
+        <v>0.09</v>
+      </c>
+      <c r="W76">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.839077864174685</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1237640505512866</v>
+      </c>
+      <c r="C77">
+        <v>1654.77583063039</v>
+      </c>
+      <c r="D77">
+        <v>6421.713154187597</v>
+      </c>
+      <c r="E77">
+        <v>2527.387558814264</v>
+      </c>
+      <c r="F77">
+        <v>5518.837323557206</v>
+      </c>
+      <c r="G77">
+        <v>751.9</v>
+      </c>
+      <c r="H77">
+        <v>4367</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3273.46</v>
+      </c>
+      <c r="K77">
+        <v>1250.9</v>
+      </c>
+      <c r="L77">
+        <v>2022.56</v>
+      </c>
+      <c r="M77">
+        <v>423.6120908629986</v>
+      </c>
+      <c r="N77">
+        <v>1598.947909137001</v>
+      </c>
+      <c r="O77">
+        <v>143.9053118223301</v>
+      </c>
+      <c r="P77">
+        <v>1455.042597314671</v>
+      </c>
+      <c r="Q77">
+        <v>2705.942597314671</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2855082593586302</v>
+      </c>
+      <c r="T77">
+        <v>3.487260026390859</v>
+      </c>
+      <c r="U77">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V77">
+        <v>0.09</v>
+      </c>
+      <c r="W77">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.774556825985689</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1239467052401076</v>
+      </c>
+      <c r="C78">
+        <v>1575.305781365255</v>
+      </c>
+      <c r="D78">
+        <v>6415.827602569891</v>
+      </c>
+      <c r="E78">
+        <v>2600.972056461693</v>
+      </c>
+      <c r="F78">
+        <v>5592.421821204635</v>
+      </c>
+      <c r="G78">
+        <v>751.9</v>
+      </c>
+      <c r="H78">
+        <v>4367</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3273.46</v>
+      </c>
+      <c r="K78">
+        <v>1250.9</v>
+      </c>
+      <c r="L78">
+        <v>2022.56</v>
+      </c>
+      <c r="M78">
+        <v>429.2602520745052</v>
+      </c>
+      <c r="N78">
+        <v>1593.299747925495</v>
+      </c>
+      <c r="O78">
+        <v>143.3969773132945</v>
+      </c>
+      <c r="P78">
+        <v>1449.9027706122</v>
+      </c>
+      <c r="Q78">
+        <v>2700.8027706122</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2952551099402367</v>
+      </c>
+      <c r="T78">
+        <v>3.629056569018906</v>
+      </c>
+      <c r="U78">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V78">
+        <v>0.09</v>
+      </c>
+      <c r="W78">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.7117337098543</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1241293599289286</v>
+      </c>
+      <c r="C79">
+        <v>1495.846510532136</v>
+      </c>
+      <c r="D79">
+        <v>6409.952829384201</v>
+      </c>
+      <c r="E79">
+        <v>2674.556554109123</v>
+      </c>
+      <c r="F79">
+        <v>5666.006318852065</v>
+      </c>
+      <c r="G79">
+        <v>751.9</v>
+      </c>
+      <c r="H79">
+        <v>4367</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3273.46</v>
+      </c>
+      <c r="K79">
+        <v>1250.9</v>
+      </c>
+      <c r="L79">
+        <v>2022.56</v>
+      </c>
+      <c r="M79">
+        <v>434.9084132860119</v>
+      </c>
+      <c r="N79">
+        <v>1587.651586713988</v>
+      </c>
+      <c r="O79">
+        <v>142.8886428042589</v>
+      </c>
+      <c r="P79">
+        <v>1444.762943909729</v>
+      </c>
+      <c r="Q79">
+        <v>2695.662943909729</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3058495127463308</v>
+      </c>
+      <c r="T79">
+        <v>3.783183245788522</v>
+      </c>
+      <c r="U79">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V79">
+        <v>0.09</v>
+      </c>
+      <c r="W79">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.650542362973074</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1243120146177495</v>
+      </c>
+      <c r="C80">
+        <v>1416.397988549701</v>
+      </c>
+      <c r="D80">
+        <v>6404.088805049196</v>
+      </c>
+      <c r="E80">
+        <v>2748.141051756552</v>
+      </c>
+      <c r="F80">
+        <v>5739.590816499494</v>
+      </c>
+      <c r="G80">
+        <v>751.9</v>
+      </c>
+      <c r="H80">
+        <v>4367</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3273.46</v>
+      </c>
+      <c r="K80">
+        <v>1250.9</v>
+      </c>
+      <c r="L80">
+        <v>2022.56</v>
+      </c>
+      <c r="M80">
+        <v>440.5565744975185</v>
+      </c>
+      <c r="N80">
+        <v>1582.003425502481</v>
+      </c>
+      <c r="O80">
+        <v>142.3803082952233</v>
+      </c>
+      <c r="P80">
+        <v>1439.623117207258</v>
+      </c>
+      <c r="Q80">
+        <v>2690.523117207258</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3174070430802515</v>
+      </c>
+      <c r="T80">
+        <v>3.951321438628102</v>
+      </c>
+      <c r="U80">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V80">
+        <v>0.09</v>
+      </c>
+      <c r="W80">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.590920024986239</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1244946693065705</v>
+      </c>
+      <c r="C81">
+        <v>1336.96018594476</v>
+      </c>
+      <c r="D81">
+        <v>6398.235500091685</v>
+      </c>
+      <c r="E81">
+        <v>2821.725549403982</v>
+      </c>
+      <c r="F81">
+        <v>5813.175314146924</v>
+      </c>
+      <c r="G81">
+        <v>751.9</v>
+      </c>
+      <c r="H81">
+        <v>4367</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3273.46</v>
+      </c>
+      <c r="K81">
+        <v>1250.9</v>
+      </c>
+      <c r="L81">
+        <v>2022.56</v>
+      </c>
+      <c r="M81">
+        <v>446.2047357090252</v>
+      </c>
+      <c r="N81">
+        <v>1576.355264290975</v>
+      </c>
+      <c r="O81">
+        <v>141.8719737861877</v>
+      </c>
+      <c r="P81">
+        <v>1434.483290504787</v>
+      </c>
+      <c r="Q81">
+        <v>2685.383290504788</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3300652905888314</v>
+      </c>
+      <c r="T81">
+        <v>4.135472792690501</v>
+      </c>
+      <c r="U81">
+        <v>0.07675748822216712</v>
+      </c>
+      <c r="V81">
+        <v>0.09</v>
+      </c>
+      <c r="W81">
+        <v>0.06984931428217207</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.532807113277554</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1265701239953915</v>
+      </c>
+      <c r="C82">
+        <v>1197.610000703033</v>
+      </c>
+      <c r="D82">
+        <v>6332.469812497387</v>
+      </c>
+      <c r="E82">
+        <v>2895.310047051411</v>
+      </c>
+      <c r="F82">
+        <v>5886.759811794353</v>
+      </c>
+      <c r="G82">
+        <v>751.9</v>
+      </c>
+      <c r="H82">
+        <v>4367</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3273.46</v>
+      </c>
+      <c r="K82">
+        <v>1250.9</v>
+      </c>
+      <c r="L82">
+        <v>2022.56</v>
+      </c>
+      <c r="M82">
+        <v>467.1584724311971</v>
+      </c>
+      <c r="N82">
+        <v>1555.401527568803</v>
+      </c>
+      <c r="O82">
+        <v>139.9861374811922</v>
+      </c>
+      <c r="P82">
+        <v>1415.415390087611</v>
+      </c>
+      <c r="Q82">
+        <v>2666.31539008761</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3439893628482693</v>
+      </c>
+      <c r="T82">
+        <v>4.338039282159139</v>
+      </c>
+      <c r="U82">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V82">
+        <v>0.09</v>
+      </c>
+      <c r="W82">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.329494420756506</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1267764386842125</v>
+      </c>
+      <c r="C83">
+        <v>1117.561736851664</v>
+      </c>
+      <c r="D83">
+        <v>6326.006046293448</v>
+      </c>
+      <c r="E83">
+        <v>2968.894544698841</v>
+      </c>
+      <c r="F83">
+        <v>5960.344309441783</v>
+      </c>
+      <c r="G83">
+        <v>751.9</v>
+      </c>
+      <c r="H83">
+        <v>4367</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3273.46</v>
+      </c>
+      <c r="K83">
+        <v>1250.9</v>
+      </c>
+      <c r="L83">
+        <v>2022.56</v>
+      </c>
+      <c r="M83">
+        <v>472.9979533365872</v>
+      </c>
+      <c r="N83">
+        <v>1549.562046663413</v>
+      </c>
+      <c r="O83">
+        <v>139.4605841997071</v>
+      </c>
+      <c r="P83">
+        <v>1410.101462463706</v>
+      </c>
+      <c r="Q83">
+        <v>2661.001462463706</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3593791269244901</v>
+      </c>
+      <c r="T83">
+        <v>4.561928559992896</v>
+      </c>
+      <c r="U83">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V83">
+        <v>0.09</v>
+      </c>
+      <c r="W83">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.276043872352104</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1269827533730334</v>
+      </c>
+      <c r="C84">
+        <v>1037.526655114614</v>
+      </c>
+      <c r="D84">
+        <v>6319.555462203827</v>
+      </c>
+      <c r="E84">
+        <v>3042.47904234627</v>
+      </c>
+      <c r="F84">
+        <v>6033.928807089213</v>
+      </c>
+      <c r="G84">
+        <v>751.9</v>
+      </c>
+      <c r="H84">
+        <v>4367</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3273.46</v>
+      </c>
+      <c r="K84">
+        <v>1250.9</v>
+      </c>
+      <c r="L84">
+        <v>2022.56</v>
+      </c>
+      <c r="M84">
+        <v>478.8374342419771</v>
+      </c>
+      <c r="N84">
+        <v>1543.722565758023</v>
+      </c>
+      <c r="O84">
+        <v>138.9350309182221</v>
+      </c>
+      <c r="P84">
+        <v>1404.787534839801</v>
+      </c>
+      <c r="Q84">
+        <v>2655.687534839801</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3764788647869576</v>
+      </c>
+      <c r="T84">
+        <v>4.810694424252627</v>
+      </c>
+      <c r="U84">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V84">
+        <v>0.09</v>
+      </c>
+      <c r="W84">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.223896995860006</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1271890680618545</v>
+      </c>
+      <c r="C85">
+        <v>957.5047152078268</v>
+      </c>
+      <c r="D85">
+        <v>6313.118019944469</v>
+      </c>
+      <c r="E85">
+        <v>3116.0635399937</v>
+      </c>
+      <c r="F85">
+        <v>6107.513304736642</v>
+      </c>
+      <c r="G85">
+        <v>751.9</v>
+      </c>
+      <c r="H85">
+        <v>4367</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3273.46</v>
+      </c>
+      <c r="K85">
+        <v>1250.9</v>
+      </c>
+      <c r="L85">
+        <v>2022.56</v>
+      </c>
+      <c r="M85">
+        <v>484.676915147367</v>
+      </c>
+      <c r="N85">
+        <v>1537.883084852633</v>
+      </c>
+      <c r="O85">
+        <v>138.409477636737</v>
+      </c>
+      <c r="P85">
+        <v>1399.473607215896</v>
+      </c>
+      <c r="Q85">
+        <v>2650.373607215896</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3955903365155979</v>
+      </c>
+      <c r="T85">
+        <v>5.08872686077821</v>
+      </c>
+      <c r="U85">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V85">
+        <v>0.09</v>
+      </c>
+      <c r="W85">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.173006670608681</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1273953827506754</v>
+      </c>
+      <c r="C86">
+        <v>877.495877011228</v>
+      </c>
+      <c r="D86">
+        <v>6306.693679395299</v>
+      </c>
+      <c r="E86">
+        <v>3189.648037641129</v>
+      </c>
+      <c r="F86">
+        <v>6181.097802384071</v>
+      </c>
+      <c r="G86">
+        <v>751.9</v>
+      </c>
+      <c r="H86">
+        <v>4367</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3273.46</v>
+      </c>
+      <c r="K86">
+        <v>1250.9</v>
+      </c>
+      <c r="L86">
+        <v>2022.56</v>
+      </c>
+      <c r="M86">
+        <v>490.516396052757</v>
+      </c>
+      <c r="N86">
+        <v>1532.043603947243</v>
+      </c>
+      <c r="O86">
+        <v>137.8839243552518</v>
+      </c>
+      <c r="P86">
+        <v>1394.159679591991</v>
+      </c>
+      <c r="Q86">
+        <v>2645.059679591991</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4170907422103179</v>
+      </c>
+      <c r="T86">
+        <v>5.401513351869486</v>
+      </c>
+      <c r="U86">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V86">
+        <v>0.09</v>
+      </c>
+      <c r="W86">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.123328019768101</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1276016974394964</v>
+      </c>
+      <c r="C87">
+        <v>797.5001005678823</v>
+      </c>
+      <c r="D87">
+        <v>6300.282400599383</v>
+      </c>
+      <c r="E87">
+        <v>3263.232535288558</v>
+      </c>
+      <c r="F87">
+        <v>6254.6823000315</v>
+      </c>
+      <c r="G87">
+        <v>751.9</v>
+      </c>
+      <c r="H87">
+        <v>4367</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3273.46</v>
+      </c>
+      <c r="K87">
+        <v>1250.9</v>
+      </c>
+      <c r="L87">
+        <v>2022.56</v>
+      </c>
+      <c r="M87">
+        <v>496.3558769581469</v>
+      </c>
+      <c r="N87">
+        <v>1526.204123041853</v>
+      </c>
+      <c r="O87">
+        <v>137.3583710737668</v>
+      </c>
+      <c r="P87">
+        <v>1388.845751968086</v>
+      </c>
+      <c r="Q87">
+        <v>2639.745751968087</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4414578686643342</v>
+      </c>
+      <c r="T87">
+        <v>5.756004708439603</v>
+      </c>
+      <c r="U87">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V87">
+        <v>0.09</v>
+      </c>
+      <c r="W87">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.074818278359064</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1278080121283174</v>
+      </c>
+      <c r="C88">
+        <v>717.5173460831666</v>
+      </c>
+      <c r="D88">
+        <v>6293.884143762097</v>
+      </c>
+      <c r="E88">
+        <v>3336.817032935988</v>
+      </c>
+      <c r="F88">
+        <v>6328.26679767893</v>
+      </c>
+      <c r="G88">
+        <v>751.9</v>
+      </c>
+      <c r="H88">
+        <v>4367</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3273.46</v>
+      </c>
+      <c r="K88">
+        <v>1250.9</v>
+      </c>
+      <c r="L88">
+        <v>2022.56</v>
+      </c>
+      <c r="M88">
+        <v>502.1953578635369</v>
+      </c>
+      <c r="N88">
+        <v>1520.364642136463</v>
+      </c>
+      <c r="O88">
+        <v>136.8328177922817</v>
+      </c>
+      <c r="P88">
+        <v>1383.531824344181</v>
+      </c>
+      <c r="Q88">
+        <v>2634.431824344181</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.46930601318321</v>
+      </c>
+      <c r="T88">
+        <v>6.161137687376879</v>
+      </c>
+      <c r="U88">
+        <v>0.07935748822216712</v>
+      </c>
+      <c r="V88">
+        <v>0.09</v>
+      </c>
+      <c r="W88">
+        <v>0.07221531428217208</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>4.027436670471168</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1301519168171384</v>
+      </c>
+      <c r="C89">
+        <v>572.1454506123746</v>
+      </c>
+      <c r="D89">
+        <v>6222.096745938734</v>
+      </c>
+      <c r="E89">
+        <v>3410.401530583417</v>
+      </c>
+      <c r="F89">
+        <v>6401.851295326359</v>
+      </c>
+      <c r="G89">
+        <v>751.9</v>
+      </c>
+      <c r="H89">
+        <v>4367</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3273.46</v>
+      </c>
+      <c r="K89">
+        <v>1250.9</v>
+      </c>
+      <c r="L89">
+        <v>2022.56</v>
+      </c>
+      <c r="M89">
+        <v>525.319837266308</v>
+      </c>
+      <c r="N89">
+        <v>1497.240162733692</v>
+      </c>
+      <c r="O89">
+        <v>134.7516146460323</v>
+      </c>
+      <c r="P89">
+        <v>1362.48854808766</v>
+      </c>
+      <c r="Q89">
+        <v>2613.38854808766</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5014384876280665</v>
+      </c>
+      <c r="T89">
+        <v>6.628598816919889</v>
+      </c>
+      <c r="U89">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V89">
+        <v>0.09</v>
+      </c>
+      <c r="W89">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.850149673625735</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1303828015059593</v>
+      </c>
+      <c r="C90">
+        <v>491.5780864001545</v>
+      </c>
+      <c r="D90">
+        <v>6215.113879373944</v>
+      </c>
+      <c r="E90">
+        <v>3483.986028230847</v>
+      </c>
+      <c r="F90">
+        <v>6475.435792973789</v>
+      </c>
+      <c r="G90">
+        <v>751.9</v>
+      </c>
+      <c r="H90">
+        <v>4367</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3273.46</v>
+      </c>
+      <c r="K90">
+        <v>1250.9</v>
+      </c>
+      <c r="L90">
+        <v>2022.56</v>
+      </c>
+      <c r="M90">
+        <v>531.3579963153461</v>
+      </c>
+      <c r="N90">
+        <v>1491.202003684654</v>
+      </c>
+      <c r="O90">
+        <v>134.2081803316188</v>
+      </c>
+      <c r="P90">
+        <v>1356.993823353035</v>
+      </c>
+      <c r="Q90">
+        <v>2607.893823353035</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5389263744803993</v>
+      </c>
+      <c r="T90">
+        <v>7.17397013472007</v>
+      </c>
+      <c r="U90">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V90">
+        <v>0.09</v>
+      </c>
+      <c r="W90">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.806397972789078</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1306136861947803</v>
+      </c>
+      <c r="C91">
+        <v>411.0263779279448</v>
+      </c>
+      <c r="D91">
+        <v>6208.146668549163</v>
+      </c>
+      <c r="E91">
+        <v>3557.570525878276</v>
+      </c>
+      <c r="F91">
+        <v>6549.020290621218</v>
+      </c>
+      <c r="G91">
+        <v>751.9</v>
+      </c>
+      <c r="H91">
+        <v>4367</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3273.46</v>
+      </c>
+      <c r="K91">
+        <v>1250.9</v>
+      </c>
+      <c r="L91">
+        <v>2022.56</v>
+      </c>
+      <c r="M91">
+        <v>537.3961553643841</v>
+      </c>
+      <c r="N91">
+        <v>1485.163844635616</v>
+      </c>
+      <c r="O91">
+        <v>133.6647460172054</v>
+      </c>
+      <c r="P91">
+        <v>1351.49909861841</v>
+      </c>
+      <c r="Q91">
+        <v>2602.399098618411</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5832302407604287</v>
+      </c>
+      <c r="T91">
+        <v>7.818499873938462</v>
+      </c>
+      <c r="U91">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V91">
+        <v>0.09</v>
+      </c>
+      <c r="W91">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.763629456240887</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1308445708836013</v>
+      </c>
+      <c r="C92">
+        <v>330.4902726039345</v>
+      </c>
+      <c r="D92">
+        <v>6201.195060872583</v>
+      </c>
+      <c r="E92">
+        <v>3631.155023525706</v>
+      </c>
+      <c r="F92">
+        <v>6622.604788268648</v>
+      </c>
+      <c r="G92">
+        <v>751.9</v>
+      </c>
+      <c r="H92">
+        <v>4367</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3273.46</v>
+      </c>
+      <c r="K92">
+        <v>1250.9</v>
+      </c>
+      <c r="L92">
+        <v>2022.56</v>
+      </c>
+      <c r="M92">
+        <v>543.4343144134222</v>
+      </c>
+      <c r="N92">
+        <v>1479.125685586578</v>
+      </c>
+      <c r="O92">
+        <v>133.121311702792</v>
+      </c>
+      <c r="P92">
+        <v>1346.004373883786</v>
+      </c>
+      <c r="Q92">
+        <v>2596.904373883786</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6363948802964642</v>
+      </c>
+      <c r="T92">
+        <v>8.591935561000534</v>
+      </c>
+      <c r="U92">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V92">
+        <v>0.09</v>
+      </c>
+      <c r="W92">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>3.721811351171543</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1310754555724223</v>
+      </c>
+      <c r="C93">
+        <v>249.9697180716057</v>
+      </c>
+      <c r="D93">
+        <v>6194.259003987683</v>
+      </c>
+      <c r="E93">
+        <v>3704.739521173135</v>
+      </c>
+      <c r="F93">
+        <v>6696.189285916077</v>
+      </c>
+      <c r="G93">
+        <v>751.9</v>
+      </c>
+      <c r="H93">
+        <v>4367</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3273.46</v>
+      </c>
+      <c r="K93">
+        <v>1250.9</v>
+      </c>
+      <c r="L93">
+        <v>2022.56</v>
+      </c>
+      <c r="M93">
+        <v>549.4724734624601</v>
+      </c>
+      <c r="N93">
+        <v>1473.08752653754</v>
+      </c>
+      <c r="O93">
+        <v>132.5778773883786</v>
+      </c>
+      <c r="P93">
+        <v>1340.509649149161</v>
+      </c>
+      <c r="Q93">
+        <v>2591.409649149161</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7013738841738411</v>
+      </c>
+      <c r="T93">
+        <v>9.537245845187513</v>
+      </c>
+      <c r="U93">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V93">
+        <v>0.09</v>
+      </c>
+      <c r="W93">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>3.680912325334494</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1313063402612433</v>
+      </c>
+      <c r="C94">
+        <v>169.4646622084247</v>
+      </c>
+      <c r="D94">
+        <v>6187.338445771931</v>
+      </c>
+      <c r="E94">
+        <v>3778.324018820564</v>
+      </c>
+      <c r="F94">
+        <v>6769.773783563506</v>
+      </c>
+      <c r="G94">
+        <v>751.9</v>
+      </c>
+      <c r="H94">
+        <v>4367</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3273.46</v>
+      </c>
+      <c r="K94">
+        <v>1250.9</v>
+      </c>
+      <c r="L94">
+        <v>2022.56</v>
+      </c>
+      <c r="M94">
+        <v>555.5106325114981</v>
+      </c>
+      <c r="N94">
+        <v>1467.049367488502</v>
+      </c>
+      <c r="O94">
+        <v>132.0344430739652</v>
+      </c>
+      <c r="P94">
+        <v>1335.014924414537</v>
+      </c>
+      <c r="Q94">
+        <v>2585.914924414537</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7825976390205622</v>
+      </c>
+      <c r="T94">
+        <v>10.71888370042124</v>
+      </c>
+      <c r="U94">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V94">
+        <v>0.09</v>
+      </c>
+      <c r="W94">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>3.640902408754771</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1315372249500643</v>
+      </c>
+      <c r="C95">
+        <v>88.9750531245345</v>
+      </c>
+      <c r="D95">
+        <v>6180.433334335471</v>
+      </c>
+      <c r="E95">
+        <v>3851.908516467994</v>
+      </c>
+      <c r="F95">
+        <v>6843.358281210936</v>
+      </c>
+      <c r="G95">
+        <v>751.9</v>
+      </c>
+      <c r="H95">
+        <v>4367</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3273.46</v>
+      </c>
+      <c r="K95">
+        <v>1250.9</v>
+      </c>
+      <c r="L95">
+        <v>2022.56</v>
+      </c>
+      <c r="M95">
+        <v>561.5487915605362</v>
+      </c>
+      <c r="N95">
+        <v>1461.011208439464</v>
+      </c>
+      <c r="O95">
+        <v>131.4910087595517</v>
+      </c>
+      <c r="P95">
+        <v>1329.520199679912</v>
+      </c>
+      <c r="Q95">
+        <v>2580.420199679912</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8870281809663463</v>
+      </c>
+      <c r="T95">
+        <v>12.23813237143603</v>
+      </c>
+      <c r="U95">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V95">
+        <v>0.09</v>
+      </c>
+      <c r="W95">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>3.60175292048859</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1317681096388852</v>
+      </c>
+      <c r="C96">
+        <v>8.500839161456497</v>
+      </c>
+      <c r="D96">
+        <v>6173.543618019822</v>
+      </c>
+      <c r="E96">
+        <v>3925.493014115423</v>
+      </c>
+      <c r="F96">
+        <v>6916.942778858365</v>
+      </c>
+      <c r="G96">
+        <v>751.9</v>
+      </c>
+      <c r="H96">
+        <v>4367</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3273.46</v>
+      </c>
+      <c r="K96">
+        <v>1250.9</v>
+      </c>
+      <c r="L96">
+        <v>2022.56</v>
+      </c>
+      <c r="M96">
+        <v>567.5869506095742</v>
+      </c>
+      <c r="N96">
+        <v>1454.973049390426</v>
+      </c>
+      <c r="O96">
+        <v>130.9475744451383</v>
+      </c>
+      <c r="P96">
+        <v>1324.025474945287</v>
+      </c>
+      <c r="Q96">
+        <v>2574.925474945288</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.026268903560725</v>
+      </c>
+      <c r="T96">
+        <v>14.26379726612241</v>
+      </c>
+      <c r="U96">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V96">
+        <v>0.09</v>
+      </c>
+      <c r="W96">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>3.563436400057861</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1319989943277062</v>
+      </c>
+      <c r="C97">
+        <v>-71.9580311091986</v>
+      </c>
+      <c r="D97">
+        <v>6166.669245396597</v>
+      </c>
+      <c r="E97">
+        <v>3999.077511762853</v>
+      </c>
+      <c r="F97">
+        <v>6990.527276505795</v>
+      </c>
+      <c r="G97">
+        <v>751.9</v>
+      </c>
+      <c r="H97">
+        <v>4367</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3273.46</v>
+      </c>
+      <c r="K97">
+        <v>1250.9</v>
+      </c>
+      <c r="L97">
+        <v>2022.56</v>
+      </c>
+      <c r="M97">
+        <v>573.6251096586122</v>
+      </c>
+      <c r="N97">
+        <v>1448.934890341388</v>
+      </c>
+      <c r="O97">
+        <v>130.4041401307249</v>
+      </c>
+      <c r="P97">
+        <v>1318.530750210663</v>
+      </c>
+      <c r="Q97">
+        <v>2569.430750210663</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.221205915192856</v>
+      </c>
+      <c r="T97">
+        <v>17.09972811868335</v>
+      </c>
+      <c r="U97">
+        <v>0.08205748822216712</v>
+      </c>
+      <c r="V97">
+        <v>0.09</v>
+      </c>
+      <c r="W97">
+        <v>0.07467231428217208</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>3.525926543215146</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1363357990165271</v>
+      </c>
+      <c r="C98">
+        <v>-271.8805392000777</v>
+      </c>
+      <c r="D98">
+        <v>6040.331234953146</v>
+      </c>
+      <c r="E98">
+        <v>4072.662009410281</v>
+      </c>
+      <c r="F98">
+        <v>7064.111774153223</v>
+      </c>
+      <c r="G98">
+        <v>751.9</v>
+      </c>
+      <c r="H98">
+        <v>4367</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3273.46</v>
+      </c>
+      <c r="K98">
+        <v>1250.9</v>
+      </c>
+      <c r="L98">
+        <v>2022.56</v>
+      </c>
+      <c r="M98">
+        <v>612.8645940461703</v>
+      </c>
+      <c r="N98">
+        <v>1409.69540595383</v>
+      </c>
+      <c r="O98">
+        <v>126.8725865358447</v>
+      </c>
+      <c r="P98">
+        <v>1282.822819417985</v>
+      </c>
+      <c r="Q98">
+        <v>2533.722819417985</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.513611432641048</v>
+      </c>
+      <c r="T98">
+        <v>21.3536243975247</v>
+      </c>
+      <c r="U98">
+        <v>0.08675748822216711</v>
+      </c>
+      <c r="V98">
+        <v>0.09</v>
+      </c>
+      <c r="W98">
+        <v>0.07894931428217207</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>3.300174328307877</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1366094537053482</v>
+      </c>
+      <c r="C99">
+        <v>-353.2636268530468</v>
+      </c>
+      <c r="D99">
+        <v>6032.532644947607</v>
+      </c>
+      <c r="E99">
+        <v>4146.246507057711</v>
+      </c>
+      <c r="F99">
+        <v>7137.696271800653</v>
+      </c>
+      <c r="G99">
+        <v>751.9</v>
+      </c>
+      <c r="H99">
+        <v>4367</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3273.46</v>
+      </c>
+      <c r="K99">
+        <v>1250.9</v>
+      </c>
+      <c r="L99">
+        <v>2022.56</v>
+      </c>
+      <c r="M99">
+        <v>619.2486002341512</v>
+      </c>
+      <c r="N99">
+        <v>1403.311399765849</v>
+      </c>
+      <c r="O99">
+        <v>126.2980259789264</v>
+      </c>
+      <c r="P99">
+        <v>1277.013373786922</v>
+      </c>
+      <c r="Q99">
+        <v>2527.913373786922</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.000953961721373</v>
+      </c>
+      <c r="T99">
+        <v>28.44345152892703</v>
+      </c>
+      <c r="U99">
+        <v>0.08675748822216711</v>
+      </c>
+      <c r="V99">
+        <v>0.09</v>
+      </c>
+      <c r="W99">
+        <v>0.07894931428217207</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>3.266151912552126</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1368831083941691</v>
+      </c>
+      <c r="C100">
+        <v>-434.6266031632231</v>
+      </c>
+      <c r="D100">
+        <v>6024.75416628486</v>
+      </c>
+      <c r="E100">
+        <v>4219.83100470514</v>
+      </c>
+      <c r="F100">
+        <v>7211.280769448083</v>
+      </c>
+      <c r="G100">
+        <v>751.9</v>
+      </c>
+      <c r="H100">
+        <v>4367</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3273.46</v>
+      </c>
+      <c r="K100">
+        <v>1250.9</v>
+      </c>
+      <c r="L100">
+        <v>2022.56</v>
+      </c>
+      <c r="M100">
+        <v>625.6326064221322</v>
+      </c>
+      <c r="N100">
+        <v>1396.927393577868</v>
+      </c>
+      <c r="O100">
+        <v>125.7234654220081</v>
+      </c>
+      <c r="P100">
+        <v>1271.20392815586</v>
+      </c>
+      <c r="Q100">
+        <v>2522.10392815586</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.975639019882022</v>
+      </c>
+      <c r="T100">
+        <v>42.62310579173167</v>
+      </c>
+      <c r="U100">
+        <v>0.08675748822216711</v>
+      </c>
+      <c r="V100">
+        <v>0.09</v>
+      </c>
+      <c r="W100">
+        <v>0.07894931428217207</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.232823831811798</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1371567630829901</v>
+      </c>
+      <c r="C101">
+        <v>-515.9695458264359</v>
+      </c>
+      <c r="D101">
+        <v>6016.995721269077</v>
+      </c>
+      <c r="E101">
+        <v>4293.415502352571</v>
+      </c>
+      <c r="F101">
+        <v>7284.865267095513</v>
+      </c>
+      <c r="G101">
+        <v>751.9</v>
+      </c>
+      <c r="H101">
+        <v>4367</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3273.46</v>
+      </c>
+      <c r="K101">
+        <v>1250.9</v>
+      </c>
+      <c r="L101">
+        <v>2022.56</v>
+      </c>
+      <c r="M101">
+        <v>632.0166126101132</v>
+      </c>
+      <c r="N101">
+        <v>1390.543387389887</v>
+      </c>
+      <c r="O101">
+        <v>125.1489048650898</v>
+      </c>
+      <c r="P101">
+        <v>1265.394482524797</v>
+      </c>
+      <c r="Q101">
+        <v>2516.294482524797</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.89969419436397</v>
+      </c>
+      <c r="T101">
+        <v>85.1620685801456</v>
+      </c>
+      <c r="U101">
+        <v>0.08675748822216711</v>
+      </c>
+      <c r="V101">
+        <v>0.09</v>
+      </c>
+      <c r="W101">
+        <v>0.07894931428217207</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.200169045631881</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hungary/hungary_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_oil_gas_integrated.xlsx
@@ -647,10 +647,10 @@
         <v>0.1199915057095146</v>
       </c>
       <c r="X2">
-        <v>0.1501252381674756</v>
+        <v>0.150101692839244</v>
       </c>
       <c r="Y2">
-        <v>-0.03013373245796098</v>
+        <v>-0.03011018712972939</v>
       </c>
       <c r="Z2">
         <v>2.084733033092131</v>
@@ -659,10 +659,10 @@
         <v>0.12575376162567</v>
       </c>
       <c r="AB2">
-        <v>0.1181933524455947</v>
+        <v>0.1181793790610266</v>
       </c>
       <c r="AC2">
-        <v>0.007560409180075334</v>
+        <v>0.007574382564643378</v>
       </c>
       <c r="AD2">
         <v>2984.5</v>
@@ -781,10 +781,10 @@
         <v>0.1199915057095146</v>
       </c>
       <c r="X3">
-        <v>0.1501252381674756</v>
+        <v>0.150101692839244</v>
       </c>
       <c r="Y3">
-        <v>-0.03013373245796098</v>
+        <v>-0.03011018712972939</v>
       </c>
       <c r="Z3">
         <v>2.084733033092131</v>
@@ -793,10 +793,10 @@
         <v>0.12575376162567</v>
       </c>
       <c r="AB3">
-        <v>0.1181933524455947</v>
+        <v>0.1181793790610266</v>
       </c>
       <c r="AC3">
-        <v>0.007560409180075334</v>
+        <v>0.007574382564643378</v>
       </c>
       <c r="AD3">
         <v>2984.5</v>
@@ -1151,13 +1151,13 @@
         <v>4367</v>
       </c>
       <c r="L2">
-        <v>7648.07820329699</v>
+        <v>7648.10171937811</v>
       </c>
       <c r="M2">
         <v>6606.54976474294</v>
       </c>
       <c r="N2">
-        <v>6896.17820329699</v>
+        <v>6896.20171937811</v>
       </c>
       <c r="O2">
         <v>2991.44976474294</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.118193352445595</v>
+        <v>0.118179379061027</v>
       </c>
       <c r="R2">
-        <v>0.110064948889713</v>
+        <v>0.110050444831616</v>
       </c>
       <c r="S2">
         <v>0.0715783142821721</v>
       </c>
       <c r="T2">
-        <v>0.06420731428217211</v>
+        <v>0.0629333142821721</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.150125238167476</v>
+        <v>0.150101692839244</v>
       </c>
       <c r="X2">
-        <v>0.110064948889713</v>
+        <v>0.110050444831616</v>
       </c>
       <c r="Y2">
         <v>1.51771671855847</v>
@@ -1230,7 +1230,7 @@
         <v>4367</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524602</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1100649488897132</v>
+        <v>0.1100504448316159</v>
       </c>
       <c r="C2">
-        <v>7648.078203296994</v>
+        <v>7648.101719378108</v>
       </c>
       <c r="D2">
-        <v>6896.178203296994</v>
+        <v>6896.201719378108</v>
       </c>
       <c r="E2">
         <v>-2991.449764742942</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1100649488897132</v>
+        <v>0.1100504448316159</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.09</v>
       </c>
       <c r="W2">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1101911835785342</v>
+        <v>0.1101639525740892</v>
       </c>
       <c r="C3">
-        <v>7569.801761397207</v>
+        <v>7570.297947124152</v>
       </c>
       <c r="D3">
-        <v>6891.486259044636</v>
+        <v>6891.982444771582</v>
       </c>
       <c r="E3">
         <v>-2917.865267095513</v>
@@ -1533,37 +1533,37 @@
         <v>2022.56</v>
       </c>
       <c r="M3">
-        <v>5.191937326092585</v>
+        <v>5.088919029386184</v>
       </c>
       <c r="N3">
-        <v>2017.368062673907</v>
+        <v>2017.471080970614</v>
       </c>
       <c r="O3">
-        <v>181.5631256406517</v>
+        <v>181.5723972873552</v>
       </c>
       <c r="P3">
-        <v>1835.804937033256</v>
+        <v>1835.898683683258</v>
       </c>
       <c r="Q3">
-        <v>3086.704937033256</v>
+        <v>3086.798683683259</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1106556671067803</v>
+        <v>0.110641029728553</v>
       </c>
       <c r="T3">
         <v>0.9435159889422664</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.09</v>
       </c>
       <c r="W3">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>389.557861154338</v>
+        <v>397.4439342266284</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1103174182673552</v>
+        <v>0.1102774603165625</v>
       </c>
       <c r="C4">
-        <v>7491.531699661193</v>
+        <v>7492.49933463602</v>
       </c>
       <c r="D4">
-        <v>6886.800694956052</v>
+        <v>6887.768329930879</v>
       </c>
       <c r="E4">
         <v>-2844.280769448083</v>
@@ -1615,37 +1615,37 @@
         <v>2022.56</v>
       </c>
       <c r="M4">
-        <v>10.38387465218517</v>
+        <v>10.17783805877237</v>
       </c>
       <c r="N4">
-        <v>2012.176125347815</v>
+        <v>2012.382161941228</v>
       </c>
       <c r="O4">
-        <v>181.0958512813033</v>
+        <v>181.1143945747105</v>
       </c>
       <c r="P4">
-        <v>1831.080274066511</v>
+        <v>1831.267767366517</v>
       </c>
       <c r="Q4">
-        <v>3081.980274066512</v>
+        <v>3082.167767366517</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.111258440797665</v>
+        <v>0.1112436673784888</v>
       </c>
       <c r="T4">
         <v>0.9522851010404759</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.09</v>
       </c>
       <c r="W4">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>194.778930577169</v>
+        <v>198.7219671133142</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1104436529561761</v>
+        <v>0.1103909680590357</v>
       </c>
       <c r="C5">
-        <v>7413.268005084061</v>
+        <v>7414.705872454653</v>
       </c>
       <c r="D5">
-        <v>6882.121498026349</v>
+        <v>6883.559365396942</v>
       </c>
       <c r="E5">
         <v>-2770.696271800654</v>
@@ -1697,37 +1697,37 @@
         <v>2022.56</v>
       </c>
       <c r="M5">
-        <v>15.57581197827775</v>
+        <v>15.26675708815855</v>
       </c>
       <c r="N5">
-        <v>2006.984188021722</v>
+        <v>2007.293242911841</v>
       </c>
       <c r="O5">
-        <v>180.628576921955</v>
+        <v>180.6563918620657</v>
       </c>
       <c r="P5">
-        <v>1826.355611099767</v>
+        <v>1826.636851049776</v>
       </c>
       <c r="Q5">
-        <v>3077.255611099768</v>
+        <v>3077.536851049776</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1118736428120732</v>
+        <v>0.11185873054698</v>
       </c>
       <c r="T5">
         <v>0.9612350195736999</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.09</v>
       </c>
       <c r="W5">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>129.8526203847793</v>
+        <v>132.4813114088761</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1105698876449971</v>
+        <v>0.1105044758015089</v>
       </c>
       <c r="C6">
-        <v>7335.010664696231</v>
+        <v>7336.917551144095</v>
       </c>
       <c r="D6">
-        <v>6877.448655285949</v>
+        <v>6879.355541733813</v>
       </c>
       <c r="E6">
         <v>-2697.111774153224</v>
@@ -1779,37 +1779,37 @@
         <v>2022.56</v>
       </c>
       <c r="M6">
-        <v>20.76774930437034</v>
+        <v>20.35567611754474</v>
       </c>
       <c r="N6">
-        <v>2001.79225069563</v>
+        <v>2002.204323882455</v>
       </c>
       <c r="O6">
-        <v>180.1613025626067</v>
+        <v>180.198389149421</v>
       </c>
       <c r="P6">
-        <v>1821.630948133023</v>
+        <v>1822.005934733034</v>
       </c>
       <c r="Q6">
-        <v>3072.530948133023</v>
+        <v>3072.905934733034</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1125016615351148</v>
+        <v>0.1124866075314813</v>
       </c>
       <c r="T6">
         <v>0.9703713947430327</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.09</v>
       </c>
       <c r="W6">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>97.38946528858449</v>
+        <v>99.36098355665709</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1106961223338181</v>
+        <v>0.1106179835439822</v>
       </c>
       <c r="C7">
-        <v>7256.75966556333</v>
+        <v>7259.134361291429</v>
       </c>
       <c r="D7">
-        <v>6872.782153800477</v>
+        <v>6875.156849528576</v>
       </c>
       <c r="E7">
         <v>-2623.527276505795</v>
@@ -1861,37 +1861,37 @@
         <v>2022.56</v>
       </c>
       <c r="M7">
-        <v>25.95968663046293</v>
+        <v>25.44459514693092</v>
       </c>
       <c r="N7">
-        <v>1996.600313369537</v>
+        <v>1997.115404853069</v>
       </c>
       <c r="O7">
-        <v>179.6940282032583</v>
+        <v>179.7403864367762</v>
       </c>
       <c r="P7">
-        <v>1816.906285166279</v>
+        <v>1817.375018416293</v>
       </c>
       <c r="Q7">
-        <v>3067.806285166279</v>
+        <v>3068.275018416293</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1131429017049574</v>
+        <v>0.1131277029788143</v>
       </c>
       <c r="T7">
         <v>0.9797001146527726</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.09</v>
       </c>
       <c r="W7">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>77.91157223086759</v>
+        <v>79.48878684532566</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1108223570226391</v>
+        <v>0.1107314912864555</v>
       </c>
       <c r="C8">
-        <v>7178.514994786063</v>
+        <v>7181.356293506706</v>
       </c>
       <c r="D8">
-        <v>6868.121980670639</v>
+        <v>6870.963279391282</v>
       </c>
       <c r="E8">
         <v>-2549.942778858366</v>
@@ -1943,37 +1943,37 @@
         <v>2022.56</v>
       </c>
       <c r="M8">
-        <v>31.15162395655551</v>
+        <v>30.5335141763171</v>
       </c>
       <c r="N8">
-        <v>1991.408376043444</v>
+        <v>1992.026485823683</v>
       </c>
       <c r="O8">
-        <v>179.22675384391</v>
+        <v>179.2823837241314</v>
       </c>
       <c r="P8">
-        <v>1812.181622199534</v>
+        <v>1812.744102099551</v>
       </c>
       <c r="Q8">
-        <v>3063.081622199535</v>
+        <v>3063.644102099552</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1137977852826689</v>
+        <v>0.113782438754814</v>
       </c>
       <c r="T8">
         <v>0.9892273179648475</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.09</v>
       </c>
       <c r="W8">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>64.92631019238966</v>
+        <v>66.24065570443807</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1109485917114601</v>
+        <v>0.1108449990289288</v>
       </c>
       <c r="C9">
-        <v>7100.276639500097</v>
+        <v>7103.583338422868</v>
       </c>
       <c r="D9">
-        <v>6863.468123032104</v>
+        <v>6866.774821954875</v>
       </c>
       <c r="E9">
         <v>-2476.358281210936</v>
@@ -2025,37 +2025,37 @@
         <v>2022.56</v>
       </c>
       <c r="M9">
-        <v>36.3435612826481</v>
+        <v>35.6224332057033</v>
       </c>
       <c r="N9">
-        <v>1986.216438717352</v>
+        <v>1986.937566794297</v>
       </c>
       <c r="O9">
-        <v>178.7594794845617</v>
+        <v>178.8243810114867</v>
       </c>
       <c r="P9">
-        <v>1807.45695923279</v>
+        <v>1808.11318578281</v>
       </c>
       <c r="Q9">
-        <v>3058.35695923279</v>
+        <v>3059.01318578281</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1144667523781807</v>
+        <v>0.1144512548700825</v>
       </c>
       <c r="T9">
         <v>0.9989594073696552</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.09</v>
       </c>
       <c r="W9">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>55.65112302204827</v>
+        <v>56.77770488951833</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.111074826400281</v>
+        <v>0.1109585067714021</v>
       </c>
       <c r="C10">
-        <v>7022.044586875948</v>
+        <v>7025.815486695691</v>
       </c>
       <c r="D10">
-        <v>6858.820568055384</v>
+        <v>6862.591467875127</v>
       </c>
       <c r="E10">
         <v>-2402.773783563507</v>
@@ -2107,37 +2107,37 @@
         <v>2022.56</v>
       </c>
       <c r="M10">
-        <v>41.53549860874068</v>
+        <v>40.71135223508947</v>
       </c>
       <c r="N10">
-        <v>1981.024501391259</v>
+        <v>1981.848647764911</v>
       </c>
       <c r="O10">
-        <v>178.2922051252133</v>
+        <v>178.3663782988419</v>
       </c>
       <c r="P10">
-        <v>1802.732296266046</v>
+        <v>1803.482269466069</v>
       </c>
       <c r="Q10">
-        <v>3053.632296266046</v>
+        <v>3054.382269466068</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1151502622366383</v>
+        <v>0.1151346104661177</v>
       </c>
       <c r="T10">
         <v>1.008903063935437</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.09</v>
       </c>
       <c r="W10">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>48.69473264429224</v>
+        <v>49.68049177832854</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.111201061089102</v>
+        <v>0.1110720145138753</v>
       </c>
       <c r="C11">
-        <v>6943.818824118853</v>
+        <v>6948.052729003701</v>
       </c>
       <c r="D11">
-        <v>6854.179302945718</v>
+        <v>6858.413207830566</v>
       </c>
       <c r="E11">
         <v>-2329.189285916077</v>
@@ -2189,37 +2189,37 @@
         <v>2022.56</v>
       </c>
       <c r="M11">
-        <v>46.72743593483327</v>
+        <v>45.80027126447565</v>
       </c>
       <c r="N11">
-        <v>1975.832564065167</v>
+        <v>1976.759728735524</v>
       </c>
       <c r="O11">
-        <v>177.824930765865</v>
+        <v>177.9083755861972</v>
       </c>
       <c r="P11">
-        <v>1798.007633299302</v>
+        <v>1798.851353149327</v>
       </c>
       <c r="Q11">
-        <v>3048.907633299302</v>
+        <v>3049.751353149327</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1158487942897874</v>
+        <v>0.1158329848664613</v>
       </c>
       <c r="T11">
         <v>1.019065262403763</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V11">
         <v>0.09</v>
       </c>
       <c r="W11">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.28420679492644</v>
+        <v>44.16043713629204</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.111327295777923</v>
+        <v>0.1111855222563486</v>
       </c>
       <c r="C12">
-        <v>6865.599338468656</v>
+        <v>6870.29505604811</v>
       </c>
       <c r="D12">
-        <v>6849.544314942951</v>
+        <v>6854.240032522405</v>
       </c>
       <c r="E12">
         <v>-2255.604788268648</v>
@@ -2271,37 +2271,37 @@
         <v>2022.56</v>
       </c>
       <c r="M12">
-        <v>51.91937326092585</v>
+        <v>50.88919029386184</v>
       </c>
       <c r="N12">
-        <v>1970.640626739074</v>
+        <v>1971.670809706138</v>
       </c>
       <c r="O12">
-        <v>177.3576564065167</v>
+        <v>177.4503728735524</v>
       </c>
       <c r="P12">
-        <v>1793.282970332557</v>
+        <v>1794.220436832586</v>
       </c>
       <c r="Q12">
-        <v>3044.182970332557</v>
+        <v>3045.120436832586</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1165628492774509</v>
+        <v>0.1165468786979237</v>
       </c>
       <c r="T12">
         <v>1.029453287504719</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V12">
         <v>0.09</v>
       </c>
       <c r="W12">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>38.9557861154338</v>
+        <v>39.74439342266283</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.111453530466744</v>
+        <v>0.1112990299988218</v>
       </c>
       <c r="C13">
-        <v>6787.386117199702</v>
+        <v>6792.542458552757</v>
       </c>
       <c r="D13">
-        <v>6844.915591321426</v>
+        <v>6850.071932674481</v>
       </c>
       <c r="E13">
         <v>-2182.020290621218</v>
@@ -2353,37 +2353,37 @@
         <v>2022.56</v>
       </c>
       <c r="M13">
-        <v>57.11131058701844</v>
+        <v>55.97810932324803</v>
       </c>
       <c r="N13">
-        <v>1965.448689412982</v>
+        <v>1966.581890676752</v>
       </c>
       <c r="O13">
-        <v>176.8903820471683</v>
+        <v>176.9923701609077</v>
       </c>
       <c r="P13">
-        <v>1788.558307365813</v>
+        <v>1789.589520515844</v>
       </c>
       <c r="Q13">
-        <v>3039.458307365813</v>
+        <v>3040.489520515845</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1172929504446124</v>
+        <v>0.1172768150873965</v>
       </c>
       <c r="T13">
         <v>1.040074751371988</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V13">
         <v>0.09</v>
       </c>
       <c r="W13">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.41435101403072</v>
+        <v>36.1312667478753</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1115797651555649</v>
+        <v>0.1114125377412951</v>
       </c>
       <c r="C14">
-        <v>6709.179147620702</v>
+        <v>6714.794927264025</v>
       </c>
       <c r="D14">
-        <v>6840.293119389855</v>
+        <v>6845.908899033178</v>
       </c>
       <c r="E14">
         <v>-2108.435792973789</v>
@@ -2435,37 +2435,37 @@
         <v>2022.56</v>
       </c>
       <c r="M14">
-        <v>62.30324791311102</v>
+        <v>61.0670283526342</v>
       </c>
       <c r="N14">
-        <v>1960.256752086889</v>
+        <v>1961.492971647366</v>
       </c>
       <c r="O14">
-        <v>176.42310768782</v>
+        <v>176.5343674482629</v>
       </c>
       <c r="P14">
-        <v>1783.833644399069</v>
+        <v>1784.958604199103</v>
       </c>
       <c r="Q14">
-        <v>3034.733644399069</v>
+        <v>3035.858604199103</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1180396448201185</v>
+        <v>0.1180233409402664</v>
       </c>
       <c r="T14">
         <v>1.050937612145332</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V14">
         <v>0.09</v>
       </c>
       <c r="W14">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.46315509619484</v>
+        <v>33.12032785221903</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1117059998443859</v>
+        <v>0.1115260454837683</v>
       </c>
       <c r="C15">
-        <v>6630.978417074627</v>
+        <v>6637.052452950777</v>
       </c>
       <c r="D15">
-        <v>6835.67688649121</v>
+        <v>6841.75092236736</v>
       </c>
       <c r="E15">
         <v>-2034.85129532636</v>
@@ -2517,37 +2517,37 @@
         <v>2022.56</v>
       </c>
       <c r="M15">
-        <v>67.49518523920361</v>
+        <v>66.1559473820204</v>
       </c>
       <c r="N15">
-        <v>1955.064814760796</v>
+        <v>1956.404052617979</v>
       </c>
       <c r="O15">
-        <v>175.9558333284717</v>
+        <v>176.0763647356181</v>
       </c>
       <c r="P15">
-        <v>1779.108981432325</v>
+        <v>1780.327687882361</v>
       </c>
       <c r="Q15">
-        <v>3030.008981432325</v>
+        <v>3031.227687882361</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1188035045835673</v>
+        <v>0.1187870283069954</v>
       </c>
       <c r="T15">
         <v>1.062050193855994</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V15">
         <v>0.09</v>
       </c>
       <c r="W15">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.96598931956446</v>
+        <v>30.57261032512525</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1118322345332069</v>
+        <v>0.1116395532262416</v>
       </c>
       <c r="C16">
-        <v>6552.7839129386</v>
+        <v>6559.315026404293</v>
       </c>
       <c r="D16">
-        <v>6831.066880002612</v>
+        <v>6837.597993468306</v>
       </c>
       <c r="E16">
         <v>-1961.26679767893</v>
@@ -2599,37 +2599,37 @@
         <v>2022.56</v>
       </c>
       <c r="M16">
-        <v>72.68712256529621</v>
+        <v>71.24486641140659</v>
       </c>
       <c r="N16">
-        <v>1949.872877434704</v>
+        <v>1951.315133588593</v>
       </c>
       <c r="O16">
-        <v>175.4885589691233</v>
+        <v>175.6183620229734</v>
       </c>
       <c r="P16">
-        <v>1774.38431846558</v>
+        <v>1775.69677156562</v>
       </c>
       <c r="Q16">
-        <v>3025.28431846558</v>
+        <v>3026.59677156562</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1195851285275614</v>
+        <v>0.1195684758450437</v>
       </c>
       <c r="T16">
         <v>1.073421207699462</v>
       </c>
       <c r="U16">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V16">
         <v>0.09</v>
       </c>
       <c r="W16">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.82556151102413</v>
+        <v>28.38885244475916</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1119584692220279</v>
+        <v>0.1117530609687149</v>
       </c>
       <c r="C17">
-        <v>6474.595622623763</v>
+        <v>6481.582638438199</v>
       </c>
       <c r="D17">
-        <v>6826.463087335204</v>
+        <v>6833.45010314964</v>
       </c>
       <c r="E17">
         <v>-1887.682300031501</v>
@@ -2681,37 +2681,37 @@
         <v>2022.56</v>
       </c>
       <c r="M17">
-        <v>77.87905989138876</v>
+        <v>76.33378544079275</v>
       </c>
       <c r="N17">
-        <v>1944.680940108611</v>
+        <v>1946.226214559207</v>
       </c>
       <c r="O17">
-        <v>175.021284609775</v>
+        <v>175.1603593103286</v>
       </c>
       <c r="P17">
-        <v>1769.659655498836</v>
+        <v>1771.065855248879</v>
       </c>
       <c r="Q17">
-        <v>3020.559655498836</v>
+        <v>3021.965855248879</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1203851436231789</v>
+        <v>0.1203683103839872</v>
       </c>
       <c r="T17">
         <v>1.085059774809835</v>
       </c>
       <c r="U17">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V17">
         <v>0.09</v>
       </c>
       <c r="W17">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.97052407695587</v>
+        <v>26.49626228177523</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1120847039108488</v>
+        <v>0.1118665687111882</v>
       </c>
       <c r="C18">
-        <v>6396.413533575176</v>
+        <v>6403.85527988839</v>
       </c>
       <c r="D18">
-        <v>6821.865495934047</v>
+        <v>6829.307242247261</v>
       </c>
       <c r="E18">
         <v>-1814.097802384071</v>
@@ -2763,37 +2763,37 @@
         <v>2022.56</v>
       </c>
       <c r="M18">
-        <v>83.07099721748136</v>
+        <v>81.42270447017894</v>
       </c>
       <c r="N18">
-        <v>1939.489002782519</v>
+        <v>1941.137295529821</v>
       </c>
       <c r="O18">
-        <v>174.5540102504267</v>
+        <v>174.7023565976839</v>
       </c>
       <c r="P18">
-        <v>1764.934992532092</v>
+        <v>1766.434938932137</v>
       </c>
       <c r="Q18">
-        <v>3015.834992532092</v>
+        <v>3017.334938932137</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1212042066972635</v>
+        <v>0.1211871886024293</v>
       </c>
       <c r="T18">
         <v>1.096975450660931</v>
       </c>
       <c r="U18">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V18">
         <v>0.09</v>
       </c>
       <c r="W18">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.34736632214612</v>
+        <v>24.84024588916427</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1122109385996698</v>
+        <v>0.1119800764536614</v>
       </c>
       <c r="C19">
-        <v>6318.237633271703</v>
+        <v>6326.132941612984</v>
       </c>
       <c r="D19">
-        <v>6817.274093278003</v>
+        <v>6825.169401619284</v>
       </c>
       <c r="E19">
         <v>-1740.513304736642</v>
@@ -2845,37 +2845,37 @@
         <v>2022.56</v>
       </c>
       <c r="M19">
-        <v>88.26293454357396</v>
+        <v>86.51162349956513</v>
       </c>
       <c r="N19">
-        <v>1934.297065456426</v>
+        <v>1936.048376500435</v>
       </c>
       <c r="O19">
-        <v>174.0867358910783</v>
+        <v>174.2443538850391</v>
       </c>
       <c r="P19">
-        <v>1760.210329565348</v>
+        <v>1761.804022615396</v>
       </c>
       <c r="Q19">
-        <v>3011.110329565347</v>
+        <v>3012.704022615396</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1220430062309646</v>
+        <v>0.1220257988261352</v>
       </c>
       <c r="T19">
         <v>1.109178251231331</v>
       </c>
       <c r="U19">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V19">
         <v>0.09</v>
       </c>
       <c r="W19">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.91516830319635</v>
+        <v>23.37905495450755</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1123371732884908</v>
+        <v>0.1120935841961347</v>
       </c>
       <c r="C20">
-        <v>6240.067909225889</v>
+        <v>6248.415614492229</v>
       </c>
       <c r="D20">
-        <v>6812.688866879618</v>
+        <v>6821.036572145959</v>
       </c>
       <c r="E20">
         <v>-1666.928807089213</v>
@@ -2927,37 +2927,37 @@
         <v>2022.56</v>
       </c>
       <c r="M20">
-        <v>93.45487186966653</v>
+        <v>91.60054252895131</v>
       </c>
       <c r="N20">
-        <v>1929.105128130333</v>
+        <v>1930.959457471049</v>
       </c>
       <c r="O20">
-        <v>173.61946153173</v>
+        <v>173.7863511723944</v>
       </c>
       <c r="P20">
-        <v>1755.485666598604</v>
+        <v>1757.173106298654</v>
       </c>
       <c r="Q20">
-        <v>3006.385666598604</v>
+        <v>3008.073106298654</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1229022642898779</v>
+        <v>0.1228848629577362</v>
       </c>
       <c r="T20">
         <v>1.121678681083936</v>
       </c>
       <c r="U20">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V20">
         <v>0.09</v>
       </c>
       <c r="W20">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.64210339746322</v>
+        <v>22.08021856814602</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1124634079773118</v>
+        <v>0.112207091938608</v>
       </c>
       <c r="C21">
-        <v>6161.90434898385</v>
+        <v>6170.703289428458</v>
       </c>
       <c r="D21">
-        <v>6808.10980428501</v>
+        <v>6816.908744729617</v>
       </c>
       <c r="E21">
         <v>-1593.344309441783</v>
@@ -3009,37 +3009,37 @@
         <v>2022.56</v>
       </c>
       <c r="M21">
-        <v>98.64680919575912</v>
+        <v>96.6894615583375</v>
       </c>
       <c r="N21">
-        <v>1923.913190804241</v>
+        <v>1925.870538441662</v>
       </c>
       <c r="O21">
-        <v>173.1521871723817</v>
+        <v>173.3283484597496</v>
       </c>
       <c r="P21">
-        <v>1750.761003631859</v>
+        <v>1752.542189981913</v>
       </c>
       <c r="Q21">
-        <v>3001.661003631859</v>
+        <v>3003.442189981913</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1237827385971594</v>
+        <v>0.1237651385493769</v>
       </c>
       <c r="T21">
         <v>1.134487763525494</v>
       </c>
       <c r="U21">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V21">
         <v>0.09</v>
       </c>
       <c r="W21">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.50304532391252</v>
+        <v>20.91810180140149</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1125896426661328</v>
+        <v>0.1123205996810812</v>
       </c>
       <c r="C22">
-        <v>6083.746940125171</v>
+        <v>6092.995957346007</v>
       </c>
       <c r="D22">
-        <v>6803.53689307376</v>
+        <v>6812.785910294596</v>
       </c>
       <c r="E22">
         <v>-1519.759811794354</v>
@@ -3091,37 +3091,37 @@
         <v>2022.56</v>
       </c>
       <c r="M22">
-        <v>103.8387465218517</v>
+        <v>101.7783805877237</v>
       </c>
       <c r="N22">
-        <v>1918.721253478148</v>
+        <v>1920.781619412276</v>
       </c>
       <c r="O22">
-        <v>172.6849128130333</v>
+        <v>172.8703457471049</v>
       </c>
       <c r="P22">
-        <v>1746.036340665115</v>
+        <v>1747.911273665171</v>
       </c>
       <c r="Q22">
-        <v>2996.936340665115</v>
+        <v>2998.811273665171</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.124685224762123</v>
+        <v>0.1246674210308085</v>
       </c>
       <c r="T22">
         <v>1.147617073028091</v>
       </c>
       <c r="U22">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V22">
         <v>0.09</v>
       </c>
       <c r="W22">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.4778930577169</v>
+        <v>19.87219671133142</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1127158773549538</v>
+        <v>0.1124341074235545</v>
       </c>
       <c r="C23">
-        <v>6005.595670262779</v>
+        <v>6015.29360919116</v>
       </c>
       <c r="D23">
-        <v>6798.970120858797</v>
+        <v>6808.668059787177</v>
       </c>
       <c r="E23">
         <v>-1446.175314146924</v>
@@ -3173,37 +3173,37 @@
         <v>2022.56</v>
       </c>
       <c r="M23">
-        <v>109.0306838479443</v>
+        <v>106.8672996171099</v>
       </c>
       <c r="N23">
-        <v>1913.529316152056</v>
+        <v>1915.69270038289</v>
       </c>
       <c r="O23">
-        <v>172.217638453685</v>
+        <v>172.4123430344601</v>
       </c>
       <c r="P23">
-        <v>1741.311677698371</v>
+        <v>1743.28035734843</v>
       </c>
       <c r="Q23">
-        <v>2992.211677698371</v>
+        <v>2994.18035734843</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1256105586780983</v>
+        <v>0.1255925461067068</v>
       </c>
       <c r="T23">
         <v>1.161078770113032</v>
       </c>
       <c r="U23">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V23">
         <v>0.09</v>
       </c>
       <c r="W23">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.55037434068276</v>
+        <v>18.92590162983944</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1128421120437747</v>
+        <v>0.1125476151660278</v>
       </c>
       <c r="C24">
-        <v>5927.450527042838</v>
+        <v>5937.596235932067</v>
       </c>
       <c r="D24">
-        <v>6794.409475286286</v>
+        <v>6804.555184175515</v>
       </c>
       <c r="E24">
         <v>-1372.590816499495</v>
@@ -3255,37 +3255,37 @@
         <v>2022.56</v>
       </c>
       <c r="M24">
-        <v>114.2226211740369</v>
+        <v>111.9562186464961</v>
       </c>
       <c r="N24">
-        <v>1908.337378825963</v>
+        <v>1910.603781353504</v>
       </c>
       <c r="O24">
-        <v>171.7503640943367</v>
+        <v>171.9543403218153</v>
       </c>
       <c r="P24">
-        <v>1736.587014731626</v>
+        <v>1738.649441031688</v>
       </c>
       <c r="Q24">
-        <v>2987.487014731626</v>
+        <v>2989.549441031689</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1265596191047396</v>
+        <v>0.1265413923383973</v>
       </c>
       <c r="T24">
         <v>1.1748856389181</v>
       </c>
       <c r="U24">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V24">
         <v>0.09</v>
       </c>
       <c r="W24">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.70717550701536</v>
+        <v>18.06563337393765</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1129683467325957</v>
+        <v>0.112661122908501</v>
       </c>
       <c r="C25">
-        <v>5849.311498144638</v>
+        <v>5859.903828558701</v>
       </c>
       <c r="D25">
-        <v>6789.854944035515</v>
+        <v>6800.447274449578</v>
       </c>
       <c r="E25">
         <v>-1299.006318852066</v>
@@ -3337,37 +3337,37 @@
         <v>2022.56</v>
       </c>
       <c r="M25">
-        <v>119.4145585001295</v>
+        <v>117.0451376758822</v>
       </c>
       <c r="N25">
-        <v>1903.14544149987</v>
+        <v>1905.514862324118</v>
       </c>
       <c r="O25">
-        <v>171.2830897349883</v>
+        <v>171.4963376091706</v>
       </c>
       <c r="P25">
-        <v>1731.862351764882</v>
+        <v>1734.018524714947</v>
       </c>
       <c r="Q25">
-        <v>2982.762351764882</v>
+        <v>2984.918524714947</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1275333304515534</v>
+        <v>0.1275148839267551</v>
       </c>
       <c r="T25">
         <v>1.189051127692131</v>
       </c>
       <c r="U25">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V25">
         <v>0.09</v>
       </c>
       <c r="W25">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.93729831105817</v>
+        <v>17.28017105333167</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1130945814214167</v>
+        <v>0.1127746306509743</v>
       </c>
       <c r="C26">
-        <v>5771.178571280479</v>
+        <v>5782.216378082772</v>
       </c>
       <c r="D26">
-        <v>6785.306514818786</v>
+        <v>6796.344321621078</v>
       </c>
       <c r="E26">
         <v>-1225.421821204636</v>
@@ -3419,37 +3419,37 @@
         <v>2022.56</v>
       </c>
       <c r="M26">
-        <v>124.606495826222</v>
+        <v>122.1340567052684</v>
       </c>
       <c r="N26">
-        <v>1897.953504173778</v>
+        <v>1900.425943294731</v>
       </c>
       <c r="O26">
-        <v>170.81581537564</v>
+        <v>171.0383348965258</v>
       </c>
       <c r="P26">
-        <v>1727.137688798138</v>
+        <v>1729.387608398206</v>
       </c>
       <c r="Q26">
-        <v>2978.037688798138</v>
+        <v>2980.287608398206</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1285326657811781</v>
+        <v>0.1285139937148066</v>
       </c>
       <c r="T26">
         <v>1.20358939248653</v>
       </c>
       <c r="U26">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V26">
         <v>0.09</v>
       </c>
       <c r="W26">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.23157754809742</v>
+        <v>16.56016392610952</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1132208161102377</v>
+        <v>0.1128881383934476</v>
       </c>
       <c r="C27">
-        <v>5693.051734195573</v>
+        <v>5704.533875537667</v>
       </c>
       <c r="D27">
-        <v>6780.764175381309</v>
+        <v>6792.246316723403</v>
       </c>
       <c r="E27">
         <v>-1151.837323557207</v>
@@ -3501,37 +3501,37 @@
         <v>2022.56</v>
       </c>
       <c r="M27">
-        <v>129.7984331523146</v>
+        <v>127.2229757346546</v>
       </c>
       <c r="N27">
-        <v>1892.761566847685</v>
+        <v>1895.337024265345</v>
       </c>
       <c r="O27">
-        <v>170.3485410162917</v>
+        <v>170.5803321838811</v>
       </c>
       <c r="P27">
-        <v>1722.413025831394</v>
+        <v>1724.756692081464</v>
       </c>
       <c r="Q27">
-        <v>2973.313025831394</v>
+        <v>2975.656692081464</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1295586500529262</v>
+        <v>0.1295397464305394</v>
       </c>
       <c r="T27">
         <v>1.218515344342114</v>
       </c>
       <c r="U27">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V27">
         <v>0.09</v>
       </c>
       <c r="W27">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.58231444617352</v>
+        <v>15.89775736906514</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1133470507990586</v>
+        <v>0.1130016461359208</v>
       </c>
       <c r="C28">
-        <v>5614.930974667916</v>
+        <v>5626.856311978392</v>
       </c>
       <c r="D28">
-        <v>6776.22791350108</v>
+        <v>6788.153250811558</v>
       </c>
       <c r="E28">
         <v>-1078.252825909777</v>
@@ -3583,37 +3583,37 @@
         <v>2022.56</v>
       </c>
       <c r="M28">
-        <v>134.9903704784072</v>
+        <v>132.3118947640408</v>
       </c>
       <c r="N28">
-        <v>1887.569629521593</v>
+        <v>1890.248105235959</v>
       </c>
       <c r="O28">
-        <v>169.8812666569434</v>
+        <v>170.1223294712363</v>
       </c>
       <c r="P28">
-        <v>1717.688362864649</v>
+        <v>1720.125775764723</v>
       </c>
       <c r="Q28">
-        <v>2968.58836286465</v>
+        <v>2971.025775764723</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1306123636293161</v>
+        <v>0.1305932221926434</v>
       </c>
       <c r="T28">
         <v>1.233844700301903</v>
       </c>
       <c r="U28">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V28">
         <v>0.09</v>
       </c>
       <c r="W28">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.98299465978223</v>
+        <v>15.28630516256263</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1134732854878796</v>
+        <v>0.1131151538783941</v>
       </c>
       <c r="C29">
-        <v>5536.816280508191</v>
+        <v>5549.183678481498</v>
       </c>
       <c r="D29">
-        <v>6771.697716988786</v>
+        <v>6784.065114962093</v>
       </c>
       <c r="E29">
         <v>-1004.668328262348</v>
@@ -3665,37 +3665,37 @@
         <v>2022.56</v>
       </c>
       <c r="M29">
-        <v>140.1823078044998</v>
+        <v>137.400813793427</v>
       </c>
       <c r="N29">
-        <v>1882.3776921955</v>
+        <v>1885.159186206573</v>
       </c>
       <c r="O29">
-        <v>169.413992297595</v>
+        <v>169.6643267585916</v>
       </c>
       <c r="P29">
-        <v>1712.963699897905</v>
+        <v>1715.494859447981</v>
       </c>
       <c r="Q29">
-        <v>2963.863699897905</v>
+        <v>2966.394859447982</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1316949460708126</v>
+        <v>0.131675560304394</v>
       </c>
       <c r="T29">
         <v>1.249594038616755</v>
       </c>
       <c r="U29">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V29">
         <v>0.09</v>
       </c>
       <c r="W29">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.42806893164215</v>
+        <v>14.72014571209735</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1135995201767006</v>
+        <v>0.1132286616208674</v>
       </c>
       <c r="C30">
-        <v>5458.70763955966</v>
+        <v>5471.515966145018</v>
       </c>
       <c r="D30">
-        <v>6767.173573687684</v>
+        <v>6779.981900273043</v>
       </c>
       <c r="E30">
         <v>-931.083830614918</v>
@@ -3747,37 +3747,37 @@
         <v>2022.56</v>
       </c>
       <c r="M30">
-        <v>145.3742451305924</v>
+        <v>142.4897328228132</v>
       </c>
       <c r="N30">
-        <v>1877.185754869407</v>
+        <v>1880.070267177187</v>
       </c>
       <c r="O30">
-        <v>168.9467179382467</v>
+        <v>169.2063240459468</v>
       </c>
       <c r="P30">
-        <v>1708.239036931161</v>
+        <v>1710.86394313124</v>
       </c>
       <c r="Q30">
-        <v>2959.139036931161</v>
+        <v>2961.76394313124</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.132807600246795</v>
+        <v>0.1327879633636933</v>
       </c>
       <c r="T30">
         <v>1.265780858551463</v>
       </c>
       <c r="U30">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V30">
         <v>0.09</v>
       </c>
       <c r="W30">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.91278075551207</v>
+        <v>14.19442622237958</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1137257548655216</v>
+        <v>0.1133421693633406</v>
       </c>
       <c r="C31">
-        <v>5380.605039698044</v>
+        <v>5393.853166088411</v>
       </c>
       <c r="D31">
-        <v>6762.655471473498</v>
+        <v>6775.903597863864</v>
       </c>
       <c r="E31">
         <v>-857.499332967489</v>
@@ -3829,37 +3829,37 @@
         <v>2022.56</v>
       </c>
       <c r="M31">
-        <v>150.566182456685</v>
+        <v>147.5786518521993</v>
       </c>
       <c r="N31">
-        <v>1871.993817543315</v>
+        <v>1874.981348147801</v>
       </c>
       <c r="O31">
-        <v>168.4794435788983</v>
+        <v>168.748321333302</v>
       </c>
       <c r="P31">
-        <v>1703.514373964417</v>
+        <v>1706.233026814499</v>
       </c>
       <c r="Q31">
-        <v>2954.414373964417</v>
+        <v>2957.133026814498</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1339515967939319</v>
+        <v>0.1339317017204376</v>
       </c>
       <c r="T31">
         <v>1.282423645244896</v>
       </c>
       <c r="U31">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V31">
         <v>0.09</v>
       </c>
       <c r="W31">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.43302969497717</v>
+        <v>13.70496324919408</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1138519895543426</v>
+        <v>0.1134556771058139</v>
       </c>
       <c r="C32">
-        <v>5302.508468831425</v>
+        <v>5316.195269452481</v>
       </c>
       <c r="D32">
-        <v>6758.143398254308</v>
+        <v>6771.830198875364</v>
       </c>
       <c r="E32">
         <v>-783.9148353200599</v>
@@ -3911,37 +3911,37 @@
         <v>2022.56</v>
       </c>
       <c r="M32">
-        <v>155.7581197827775</v>
+        <v>152.6675708815855</v>
       </c>
       <c r="N32">
-        <v>1866.801880217222</v>
+        <v>1869.892429118414</v>
       </c>
       <c r="O32">
-        <v>168.01216921955</v>
+        <v>168.2903186206573</v>
       </c>
       <c r="P32">
-        <v>1698.789710997672</v>
+        <v>1701.602110497757</v>
       </c>
       <c r="Q32">
-        <v>2949.689710997673</v>
+        <v>2952.502110497757</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1351282789567013</v>
+        <v>0.1351081183159461</v>
       </c>
       <c r="T32">
         <v>1.299541940129569</v>
       </c>
       <c r="U32">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V32">
         <v>0.09</v>
       </c>
       <c r="W32">
-        <v>0.06420731428217208</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.98526203847793</v>
+        <v>13.24813114088761</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1142885342431635</v>
+        <v>0.1135691848482872</v>
       </c>
       <c r="C33">
-        <v>5213.366630254385</v>
+        <v>5238.542267399328</v>
       </c>
       <c r="D33">
-        <v>6742.586057324697</v>
+        <v>6767.76169446964</v>
       </c>
       <c r="E33">
         <v>-710.3303376726303</v>
@@ -3993,45 +3993,45 @@
         <v>2022.56</v>
       </c>
       <c r="M33">
-        <v>163.4592884786474</v>
+        <v>157.7564899109717</v>
       </c>
       <c r="N33">
-        <v>1859.100711521352</v>
+        <v>1864.803510089028</v>
       </c>
       <c r="O33">
-        <v>167.3190640369217</v>
+        <v>167.8323159080125</v>
       </c>
       <c r="P33">
-        <v>1691.781647484431</v>
+        <v>1696.971194181016</v>
       </c>
       <c r="Q33">
-        <v>2942.681647484431</v>
+        <v>2947.871194181016</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1363390678488264</v>
+        <v>0.1363186339432084</v>
       </c>
       <c r="T33">
         <v>1.317156417474668</v>
       </c>
       <c r="U33">
-        <v>0.07165748822216711</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V33">
         <v>0.09</v>
       </c>
       <c r="W33">
-        <v>0.06520831428217207</v>
+        <v>0.06293331428217208</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>12.37347855129203</v>
+        <v>12.82077207182672</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1144247789319845</v>
+        <v>0.1141194925907604</v>
       </c>
       <c r="C34">
-        <v>5134.941373973492</v>
+        <v>5145.301968291707</v>
       </c>
       <c r="D34">
-        <v>6737.745298691233</v>
+        <v>6748.105893009449</v>
       </c>
       <c r="E34">
         <v>-636.7458400252008</v>
@@ -4075,37 +4075,37 @@
         <v>2022.56</v>
       </c>
       <c r="M34">
-        <v>168.7321687521522</v>
+        <v>166.3774648274345</v>
       </c>
       <c r="N34">
-        <v>1853.827831247848</v>
+        <v>1856.182535172565</v>
       </c>
       <c r="O34">
-        <v>166.8445048123063</v>
+        <v>167.0564281655309</v>
       </c>
       <c r="P34">
-        <v>1686.983326435542</v>
+        <v>1689.126107007035</v>
       </c>
       <c r="Q34">
-        <v>2937.883326435542</v>
+        <v>2940.026107007035</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1375854681789551</v>
+        <v>0.1375647529712726</v>
       </c>
       <c r="T34">
         <v>1.335288967682858</v>
       </c>
       <c r="U34">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V34">
         <v>0.09</v>
       </c>
       <c r="W34">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.98680734656415</v>
+        <v>12.15645401315488</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1145610236208055</v>
+        <v>0.1142466503332337</v>
       </c>
       <c r="C35">
-        <v>5056.523063434966</v>
+        <v>5067.1918992634</v>
       </c>
       <c r="D35">
-        <v>6732.911485800138</v>
+        <v>6743.580321628571</v>
       </c>
       <c r="E35">
         <v>-563.1613423777712</v>
@@ -4157,37 +4157,37 @@
         <v>2022.56</v>
       </c>
       <c r="M35">
-        <v>174.005049025657</v>
+        <v>171.5767606032918</v>
       </c>
       <c r="N35">
-        <v>1848.554950974343</v>
+        <v>1850.983239396708</v>
       </c>
       <c r="O35">
-        <v>166.3699455876909</v>
+        <v>166.5884915457037</v>
       </c>
       <c r="P35">
-        <v>1682.185005386652</v>
+        <v>1684.394747851004</v>
       </c>
       <c r="Q35">
-        <v>2933.085005386652</v>
+        <v>2935.294747851005</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1388690744890876</v>
+        <v>0.138848069582264</v>
       </c>
       <c r="T35">
         <v>1.353962788046517</v>
       </c>
       <c r="U35">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V35">
         <v>0.09</v>
       </c>
       <c r="W35">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.62357076030463</v>
+        <v>11.78807661881685</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1146972683096265</v>
+        <v>0.114373808075707</v>
       </c>
       <c r="C36">
-        <v>4978.111683700417</v>
+        <v>4989.087896254372</v>
       </c>
       <c r="D36">
-        <v>6728.084603713019</v>
+        <v>6739.060816266973</v>
       </c>
       <c r="E36">
         <v>-489.5768447303417</v>
@@ -4239,37 +4239,37 @@
         <v>2022.56</v>
       </c>
       <c r="M36">
-        <v>179.2779292991617</v>
+        <v>176.7760563791491</v>
       </c>
       <c r="N36">
-        <v>1843.282070700838</v>
+        <v>1845.783943620851</v>
       </c>
       <c r="O36">
-        <v>165.8953863630754</v>
+        <v>166.1205549258766</v>
       </c>
       <c r="P36">
-        <v>1677.386684337763</v>
+        <v>1679.663388694974</v>
       </c>
       <c r="Q36">
-        <v>2928.286684337763</v>
+        <v>2930.563388694974</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1401915779601333</v>
+        <v>0.1401702745754068</v>
       </c>
       <c r="T36">
         <v>1.373202481754529</v>
       </c>
       <c r="U36">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V36">
         <v>0.09</v>
       </c>
       <c r="W36">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.28170103206038</v>
+        <v>11.44136848296929</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1148335129984475</v>
+        <v>0.1145009658181802</v>
       </c>
       <c r="C37">
-        <v>4899.707219874268</v>
+        <v>4910.989947076568</v>
       </c>
       <c r="D37">
-        <v>6723.264637534298</v>
+        <v>6734.547364736598</v>
       </c>
       <c r="E37">
         <v>-415.9923470829121</v>
@@ -4321,37 +4321,37 @@
         <v>2022.56</v>
       </c>
       <c r="M37">
-        <v>184.5508095726665</v>
+        <v>181.9753521550065</v>
       </c>
       <c r="N37">
-        <v>1838.009190427333</v>
+        <v>1840.584647844993</v>
       </c>
       <c r="O37">
-        <v>165.42082713846</v>
+        <v>165.6526183060494</v>
       </c>
       <c r="P37">
-        <v>1672.588363288873</v>
+        <v>1674.932029538944</v>
       </c>
       <c r="Q37">
-        <v>2923.488363288873</v>
+        <v>2925.832029538944</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1415547738456727</v>
+        <v>0.1415331627991077</v>
       </c>
       <c r="T37">
         <v>1.393034166038172</v>
       </c>
       <c r="U37">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V37">
         <v>0.09</v>
       </c>
       <c r="W37">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.95936671685865</v>
+        <v>11.11447224059874</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1149697576872684</v>
+        <v>0.1146281235606535</v>
       </c>
       <c r="C38">
-        <v>4821.309657103592</v>
+        <v>4832.898039574561</v>
       </c>
       <c r="D38">
-        <v>6718.451572411052</v>
+        <v>6730.039954882021</v>
       </c>
       <c r="E38">
         <v>-342.4078494354831</v>
@@ -4403,37 +4403,37 @@
         <v>2022.56</v>
       </c>
       <c r="M38">
-        <v>189.8236898461712</v>
+        <v>187.1746479308638</v>
       </c>
       <c r="N38">
-        <v>1832.736310153829</v>
+        <v>1835.385352069136</v>
       </c>
       <c r="O38">
-        <v>164.9462679138446</v>
+        <v>165.1846816862223</v>
       </c>
       <c r="P38">
-        <v>1667.790042239984</v>
+        <v>1670.200670382914</v>
       </c>
       <c r="Q38">
-        <v>2918.690042239984</v>
+        <v>2921.100670382914</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1429605696026351</v>
+        <v>0.1429386412797993</v>
       </c>
       <c r="T38">
         <v>1.413485590455678</v>
       </c>
       <c r="U38">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V38">
         <v>0.09</v>
       </c>
       <c r="W38">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.65493986361258</v>
+        <v>10.80573690058211</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1151060023760894</v>
+        <v>0.1147552813031268</v>
       </c>
       <c r="C39">
-        <v>4742.918980577962</v>
+        <v>4754.812161625443</v>
       </c>
       <c r="D39">
-        <v>6713.645393532852</v>
+        <v>6725.538574580332</v>
       </c>
       <c r="E39">
         <v>-268.8233517880535</v>
@@ -4485,37 +4485,37 @@
         <v>2022.56</v>
       </c>
       <c r="M39">
-        <v>195.096570119676</v>
+        <v>192.3739437067211</v>
       </c>
       <c r="N39">
-        <v>1827.463429880324</v>
+        <v>1830.186056293279</v>
       </c>
       <c r="O39">
-        <v>164.4717086892292</v>
+        <v>164.7167450663951</v>
       </c>
       <c r="P39">
-        <v>1662.991721191095</v>
+        <v>1665.469311226884</v>
       </c>
       <c r="Q39">
-        <v>2913.891721191095</v>
+        <v>2916.369311226884</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1444109937963266</v>
+        <v>0.1443887381249573</v>
       </c>
       <c r="T39">
         <v>1.434586266441995</v>
       </c>
       <c r="U39">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V39">
         <v>0.09</v>
       </c>
       <c r="W39">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.36696851594737</v>
+        <v>10.51368995732314</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1152422470649104</v>
+        <v>0.1148824390456</v>
       </c>
       <c r="C40">
-        <v>4664.535175529307</v>
+        <v>4676.732301138722</v>
       </c>
       <c r="D40">
-        <v>6708.846086131624</v>
+        <v>6721.04321174104</v>
       </c>
       <c r="E40">
         <v>-195.2388541406244</v>
@@ -4567,37 +4567,37 @@
         <v>2022.56</v>
       </c>
       <c r="M40">
-        <v>200.3694503931808</v>
+        <v>197.5732394825784</v>
       </c>
       <c r="N40">
-        <v>1822.190549606819</v>
+        <v>1824.986760517422</v>
       </c>
       <c r="O40">
-        <v>163.9971494646137</v>
+        <v>164.2488084465679</v>
       </c>
       <c r="P40">
-        <v>1658.193400142205</v>
+        <v>1660.737952070854</v>
       </c>
       <c r="Q40">
-        <v>2909.093400142206</v>
+        <v>2911.637952070854</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1459082058672339</v>
+        <v>0.145885612287701</v>
       </c>
       <c r="T40">
         <v>1.456367609395611</v>
       </c>
       <c r="U40">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V40">
         <v>0.09</v>
       </c>
       <c r="W40">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.09415355500139</v>
+        <v>10.23701390581463</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1153784917537314</v>
+        <v>0.1150095967880733</v>
       </c>
       <c r="C41">
-        <v>4586.158227231745</v>
+        <v>4598.658446056207</v>
       </c>
       <c r="D41">
-        <v>6704.053635481492</v>
+        <v>6716.553854305955</v>
       </c>
       <c r="E41">
         <v>-121.6543564931949</v>
@@ -4649,37 +4649,37 @@
         <v>2022.56</v>
       </c>
       <c r="M41">
-        <v>205.6423306666855</v>
+        <v>202.7725352584358</v>
       </c>
       <c r="N41">
-        <v>1816.917669333315</v>
+        <v>1819.787464741564</v>
       </c>
       <c r="O41">
-        <v>163.5225902399983</v>
+        <v>163.7808718267408</v>
       </c>
       <c r="P41">
-        <v>1653.395079093316</v>
+        <v>1656.006592914823</v>
       </c>
       <c r="Q41">
-        <v>2904.295079093316</v>
+        <v>2906.906592914824</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1474545068584988</v>
+        <v>0.1474315642918462</v>
       </c>
       <c r="T41">
         <v>1.47886309474115</v>
       </c>
       <c r="U41">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V41">
         <v>0.09</v>
       </c>
       <c r="W41">
-        <v>0.06520831428217207</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.835329104873148</v>
+        <v>9.974526369768103</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1163155364425524</v>
+        <v>0.1157555545305466</v>
       </c>
       <c r="C42">
-        <v>4479.797458692865</v>
+        <v>4498.857916223962</v>
       </c>
       <c r="D42">
-        <v>6671.277364590042</v>
+        <v>6690.337822121139</v>
       </c>
       <c r="E42">
         <v>-48.06985884576534</v>
@@ -4731,37 +4731,37 @@
         <v>2022.56</v>
       </c>
       <c r="M42">
-        <v>217.3906467331641</v>
+        <v>212.9755768743183</v>
       </c>
       <c r="N42">
-        <v>1805.169353266836</v>
+        <v>1809.584423125682</v>
       </c>
       <c r="O42">
-        <v>162.4652417940152</v>
+        <v>162.8625980813113</v>
       </c>
       <c r="P42">
-        <v>1642.704111472821</v>
+        <v>1646.72182504437</v>
       </c>
       <c r="Q42">
-        <v>2893.604111472821</v>
+        <v>2897.621825044371</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1490523512161392</v>
+        <v>0.1490290480294629</v>
       </c>
       <c r="T42">
         <v>1.502108429598207</v>
       </c>
       <c r="U42">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V42">
         <v>0.09</v>
       </c>
       <c r="W42">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.303804144262882</v>
+        <v>9.496675767633011</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1164718011313733</v>
+        <v>0.1158981822730198</v>
       </c>
       <c r="C43">
-        <v>4400.778234897562</v>
+        <v>4420.284179681456</v>
       </c>
       <c r="D43">
-        <v>6665.842638442169</v>
+        <v>6685.348583226063</v>
       </c>
       <c r="E43">
         <v>25.5146388016642</v>
@@ -4813,37 +4813,37 @@
         <v>2022.56</v>
       </c>
       <c r="M43">
-        <v>222.8254129014932</v>
+        <v>218.2999662961763</v>
       </c>
       <c r="N43">
-        <v>1799.734587098507</v>
+        <v>1804.260033703824</v>
       </c>
       <c r="O43">
-        <v>161.9761128388656</v>
+        <v>162.3834030333441</v>
       </c>
       <c r="P43">
-        <v>1637.758474259641</v>
+        <v>1641.876630670479</v>
       </c>
       <c r="Q43">
-        <v>2888.658474259641</v>
+        <v>2892.77663067048</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1507043597892929</v>
+        <v>0.1506806837581852</v>
       </c>
       <c r="T43">
         <v>1.526141741908046</v>
       </c>
       <c r="U43">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V43">
         <v>0.09</v>
       </c>
       <c r="W43">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.076882091963787</v>
+        <v>9.265049529398057</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1166280658201943</v>
+        <v>0.1160408100154931</v>
       </c>
       <c r="C44">
-        <v>4321.76785864515</v>
+        <v>4341.717878923499</v>
       </c>
       <c r="D44">
-        <v>6660.416759837186</v>
+        <v>6680.366780115535</v>
       </c>
       <c r="E44">
         <v>99.09913644909329</v>
@@ -4895,37 +4895,37 @@
         <v>2022.56</v>
       </c>
       <c r="M44">
-        <v>228.2601790698223</v>
+        <v>223.6243557180342</v>
       </c>
       <c r="N44">
-        <v>1794.299820930178</v>
+        <v>1798.935644281966</v>
       </c>
       <c r="O44">
-        <v>161.486983883716</v>
+        <v>161.9042079853769</v>
       </c>
       <c r="P44">
-        <v>1632.812837046462</v>
+        <v>1637.031436296589</v>
       </c>
       <c r="Q44">
-        <v>2883.712837046462</v>
+        <v>2887.931436296589</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1524133341753139</v>
+        <v>0.1523892724430704</v>
       </c>
       <c r="T44">
         <v>1.55100378912512</v>
       </c>
       <c r="U44">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V44">
         <v>0.09</v>
       </c>
       <c r="W44">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.860765851678934</v>
+        <v>9.044453112031439</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1167843305090153</v>
+        <v>0.1161834377579664</v>
       </c>
       <c r="C45">
-        <v>4242.766308347973</v>
+        <v>4263.158997339426</v>
       </c>
       <c r="D45">
-        <v>6654.999707187439</v>
+        <v>6675.392396178891</v>
       </c>
       <c r="E45">
         <v>172.6836340965228</v>
@@ -4977,37 +4977,37 @@
         <v>2022.56</v>
       </c>
       <c r="M45">
-        <v>233.6949452381514</v>
+        <v>228.9487451398922</v>
       </c>
       <c r="N45">
-        <v>1788.865054761849</v>
+        <v>1793.611254860108</v>
       </c>
       <c r="O45">
-        <v>160.9978549285664</v>
+        <v>161.4250129374097</v>
       </c>
       <c r="P45">
-        <v>1627.867199833282</v>
+        <v>1632.186241922698</v>
       </c>
       <c r="Q45">
-        <v>2878.767199833283</v>
+        <v>2883.086241922698</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1541822725748795</v>
+        <v>0.1541578116081269</v>
       </c>
       <c r="T45">
         <v>1.576738188876126</v>
       </c>
       <c r="U45">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V45">
         <v>0.09</v>
       </c>
       <c r="W45">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.654701529546866</v>
+        <v>8.834116993146985</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1169405951978363</v>
+        <v>0.1163260655004396</v>
       </c>
       <c r="C46">
-        <v>4163.773562488539</v>
+        <v>4184.607518368005</v>
       </c>
       <c r="D46">
-        <v>6649.591458975434</v>
+        <v>6670.4254148549</v>
       </c>
       <c r="E46">
         <v>246.2681317439524</v>
@@ -5059,37 +5059,37 @@
         <v>2022.56</v>
       </c>
       <c r="M46">
-        <v>239.1297114064805</v>
+        <v>234.2731345617501</v>
       </c>
       <c r="N46">
-        <v>1783.430288593519</v>
+        <v>1788.28686543825</v>
       </c>
       <c r="O46">
-        <v>160.5087259734167</v>
+        <v>160.9458178894425</v>
       </c>
       <c r="P46">
-        <v>1622.921562620103</v>
+        <v>1627.341047548807</v>
       </c>
       <c r="Q46">
-        <v>2873.821562620103</v>
+        <v>2878.241047548808</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1560143873458581</v>
+        <v>0.1559895128862213</v>
       </c>
       <c r="T46">
         <v>1.603391674332526</v>
       </c>
       <c r="U46">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V46">
         <v>0.09</v>
       </c>
       <c r="W46">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.458003767511709</v>
+        <v>8.633341606939101</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1170968598866573</v>
+        <v>0.1164686932429129</v>
       </c>
       <c r="C47">
-        <v>4084.789599619252</v>
+        <v>4106.063425497265</v>
       </c>
       <c r="D47">
-        <v>6644.191993753577</v>
+        <v>6665.46581963159</v>
       </c>
       <c r="E47">
         <v>319.8526293913819</v>
@@ -5141,37 +5141,37 @@
         <v>2022.56</v>
       </c>
       <c r="M47">
-        <v>244.5644775748096</v>
+        <v>239.5975239836081</v>
       </c>
       <c r="N47">
-        <v>1777.99552242519</v>
+        <v>1782.962476016392</v>
       </c>
       <c r="O47">
-        <v>160.0195970182671</v>
+        <v>160.4666228414752</v>
       </c>
       <c r="P47">
-        <v>1617.975925406923</v>
+        <v>1622.495853174916</v>
       </c>
       <c r="Q47">
-        <v>2868.875925406923</v>
+        <v>2873.395853174917</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1579131244721451</v>
+        <v>0.157887821483519</v>
       </c>
       <c r="T47">
         <v>1.631014377441886</v>
       </c>
       <c r="U47">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V47">
         <v>0.09</v>
       </c>
       <c r="W47">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.270048128233672</v>
+        <v>8.44148957122934</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1172531245754782</v>
+        <v>0.1166113209853862</v>
       </c>
       <c r="C48">
-        <v>4005.814398362119</v>
+        <v>4027.526702264302</v>
       </c>
       <c r="D48">
-        <v>6638.801290143872</v>
+        <v>6660.513594046056</v>
       </c>
       <c r="E48">
         <v>393.437127038811</v>
@@ -5223,37 +5223,37 @@
         <v>2022.56</v>
       </c>
       <c r="M48">
-        <v>249.9992437431387</v>
+        <v>244.9219134054661</v>
       </c>
       <c r="N48">
-        <v>1772.560756256861</v>
+        <v>1777.638086594534</v>
       </c>
       <c r="O48">
-        <v>159.5304680631175</v>
+        <v>159.987427793508</v>
       </c>
       <c r="P48">
-        <v>1613.030288193744</v>
+        <v>1617.650658801026</v>
       </c>
       <c r="Q48">
-        <v>2863.930288193744</v>
+        <v>2868.550658801026</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.159882185195702</v>
+        <v>0.1598564378066426</v>
       </c>
       <c r="T48">
         <v>1.65966014362937</v>
       </c>
       <c r="U48">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V48">
         <v>0.09</v>
       </c>
       <c r="W48">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.09026447327207</v>
+        <v>8.257978928376531</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1174093892642992</v>
+        <v>0.1167539487278594</v>
       </c>
       <c r="C49">
-        <v>3926.84793740847</v>
+        <v>3948.997332255109</v>
       </c>
       <c r="D49">
-        <v>6633.419326837653</v>
+        <v>6655.568721684292</v>
       </c>
       <c r="E49">
         <v>467.0216246862406</v>
@@ -5305,37 +5305,37 @@
         <v>2022.56</v>
       </c>
       <c r="M49">
-        <v>255.4340099114678</v>
+        <v>250.246302827324</v>
       </c>
       <c r="N49">
-        <v>1767.125990088532</v>
+        <v>1772.313697172676</v>
       </c>
       <c r="O49">
-        <v>159.0413391079679</v>
+        <v>159.5082327455408</v>
       </c>
       <c r="P49">
-        <v>1608.084650980564</v>
+        <v>1612.805464427135</v>
       </c>
       <c r="Q49">
-        <v>2858.984650980564</v>
+        <v>2863.705464427135</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1619255500975063</v>
+        <v>0.1618993415381859</v>
       </c>
       <c r="T49">
         <v>1.689386882125816</v>
       </c>
       <c r="U49">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V49">
         <v>0.09</v>
       </c>
       <c r="W49">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.918131186606707</v>
+        <v>8.082277249049369</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1175656539531202</v>
+        <v>0.1168965764703327</v>
       </c>
       <c r="C50">
-        <v>3847.890195518678</v>
+        <v>3870.475299104376</v>
       </c>
       <c r="D50">
-        <v>6628.04608259529</v>
+        <v>6650.631186180988</v>
       </c>
       <c r="E50">
         <v>540.6061223336696</v>
@@ -5387,37 +5387,37 @@
         <v>2022.56</v>
       </c>
       <c r="M50">
-        <v>260.8687760797969</v>
+        <v>255.5706922491819</v>
       </c>
       <c r="N50">
-        <v>1761.691223920203</v>
+        <v>1766.989307750818</v>
       </c>
       <c r="O50">
-        <v>158.5522101528183</v>
+        <v>159.0290376975736</v>
       </c>
       <c r="P50">
-        <v>1603.139013767385</v>
+        <v>1607.960270053244</v>
       </c>
       <c r="Q50">
-        <v>2854.039013767385</v>
+        <v>2858.860270053245</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1640475059570723</v>
+        <v>0.1640208184901732</v>
       </c>
       <c r="T50">
         <v>1.720256956718279</v>
       </c>
       <c r="U50">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V50">
         <v>0.09</v>
       </c>
       <c r="W50">
-        <v>0.06721031428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.753170120219068</v>
+        <v>7.913896473027509</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1183907686419411</v>
+        <v>0.117039204212806</v>
       </c>
       <c r="C51">
-        <v>3746.077409644493</v>
+        <v>3791.960586495325</v>
       </c>
       <c r="D51">
-        <v>6599.817794368535</v>
+        <v>6645.700971219367</v>
       </c>
       <c r="E51">
         <v>614.1906199810992</v>
@@ -5469,45 +5469,45 @@
         <v>2022.56</v>
       </c>
       <c r="M51">
-        <v>271.712002825212</v>
+        <v>260.8950816710399</v>
       </c>
       <c r="N51">
-        <v>1750.847997174788</v>
+        <v>1761.66491832896</v>
       </c>
       <c r="O51">
-        <v>157.5763197457309</v>
+        <v>158.5498426496064</v>
       </c>
       <c r="P51">
-        <v>1593.271677429057</v>
+        <v>1603.115075679354</v>
       </c>
       <c r="Q51">
-        <v>2844.171677429057</v>
+        <v>2854.015075679354</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1662526757719154</v>
+        <v>0.1662254906167483</v>
       </c>
       <c r="T51">
         <v>1.752337622471231</v>
       </c>
       <c r="U51">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V51">
         <v>0.09</v>
       </c>
       <c r="W51">
-        <v>0.06857531428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.443763907997396</v>
+        <v>7.752388381741233</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1185606833307621</v>
+        <v>0.1171818319552792</v>
       </c>
       <c r="C52">
-        <v>3666.709730100079</v>
+        <v>3713.453178159531</v>
       </c>
       <c r="D52">
-        <v>6594.034612471551</v>
+        <v>6640.778060531002</v>
       </c>
       <c r="E52">
         <v>687.7751176285287</v>
@@ -5551,45 +5551,45 @@
         <v>2022.56</v>
       </c>
       <c r="M52">
-        <v>277.2571457400123</v>
+        <v>266.2194710928979</v>
       </c>
       <c r="N52">
-        <v>1745.302854259988</v>
+        <v>1756.340528907102</v>
       </c>
       <c r="O52">
-        <v>157.0772568833989</v>
+        <v>158.0706476016392</v>
       </c>
       <c r="P52">
-        <v>1588.225597376589</v>
+        <v>1598.269881305463</v>
       </c>
       <c r="Q52">
-        <v>2839.125597376589</v>
+        <v>2849.169881305463</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1685460523793522</v>
+        <v>0.1685183496283864</v>
       </c>
       <c r="T52">
         <v>1.785701514854301</v>
       </c>
       <c r="U52">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V52">
         <v>0.09</v>
       </c>
       <c r="W52">
-        <v>0.06857531428217208</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>7.294888629837447</v>
+        <v>7.597340614106407</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1187305980195831</v>
+        <v>0.1176957396977525</v>
       </c>
       <c r="C53">
-        <v>3587.352176869069</v>
+        <v>3622.191066167028</v>
       </c>
       <c r="D53">
-        <v>6588.26155688797</v>
+        <v>6623.100446185928</v>
       </c>
       <c r="E53">
         <v>761.3596152759583</v>
@@ -5633,37 +5633,37 @@
         <v>2022.56</v>
       </c>
       <c r="M53">
-        <v>282.8022886548126</v>
+        <v>274.546108018771</v>
       </c>
       <c r="N53">
-        <v>1739.757711345187</v>
+        <v>1748.013891981229</v>
       </c>
       <c r="O53">
-        <v>156.5781940210668</v>
+        <v>157.3212502783106</v>
       </c>
       <c r="P53">
-        <v>1583.179517324121</v>
+        <v>1590.692641702918</v>
       </c>
       <c r="Q53">
-        <v>2834.07951732412</v>
+        <v>2841.592641702919</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1709330361952558</v>
+        <v>0.1709047947221321</v>
       </c>
       <c r="T53">
         <v>1.82042719876321</v>
       </c>
       <c r="U53">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V53">
         <v>0.09</v>
       </c>
       <c r="W53">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.15185159787985</v>
+        <v>7.366922862595144</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1189005127084041</v>
+        <v>0.1178456474402258</v>
       </c>
       <c r="C54">
-        <v>3508.004723378067</v>
+        <v>3543.467696128035</v>
       </c>
       <c r="D54">
-        <v>6582.498601044397</v>
+        <v>6617.961573794365</v>
       </c>
       <c r="E54">
         <v>834.9441129233878</v>
@@ -5715,37 +5715,37 @@
         <v>2022.56</v>
       </c>
       <c r="M54">
-        <v>288.3474315696128</v>
+        <v>279.9293650387469</v>
       </c>
       <c r="N54">
-        <v>1734.212568430387</v>
+        <v>1742.630634961253</v>
       </c>
       <c r="O54">
-        <v>156.0791311587348</v>
+        <v>156.8367571465128</v>
       </c>
       <c r="P54">
-        <v>1578.133437271652</v>
+        <v>1585.79387781474</v>
       </c>
       <c r="Q54">
-        <v>2829.033437271652</v>
+        <v>2836.693877814741</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1734194776701555</v>
+        <v>0.1733906750281173</v>
       </c>
       <c r="T54">
         <v>1.856599786168324</v>
       </c>
       <c r="U54">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V54">
         <v>0.09</v>
       </c>
       <c r="W54">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.014315990228315</v>
+        <v>7.225251269083699</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1190704273972251</v>
+        <v>0.117995555182699</v>
       </c>
       <c r="C55">
-        <v>3428.66734314657</v>
+        <v>3464.752294422168</v>
       </c>
       <c r="D55">
-        <v>6576.74571846033</v>
+        <v>6612.830669735928</v>
       </c>
       <c r="E55">
         <v>908.5286105708174</v>
@@ -5797,37 +5797,37 @@
         <v>2022.56</v>
       </c>
       <c r="M55">
-        <v>293.8925744844131</v>
+        <v>285.3126220587228</v>
       </c>
       <c r="N55">
-        <v>1728.667425515587</v>
+        <v>1737.247377941277</v>
       </c>
       <c r="O55">
-        <v>155.5800682964028</v>
+        <v>156.3522640147149</v>
       </c>
       <c r="P55">
-        <v>1573.087357219184</v>
+        <v>1580.895113926562</v>
       </c>
       <c r="Q55">
-        <v>2823.987357219184</v>
+        <v>2831.795113926562</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1760117251652636</v>
+        <v>0.1759823374747826</v>
       </c>
       <c r="T55">
         <v>1.894311632611953</v>
       </c>
       <c r="U55">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V55">
         <v>0.09</v>
       </c>
       <c r="W55">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.881970405507024</v>
+        <v>7.088925773440611</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1192403420860461</v>
+        <v>0.1181454629251723</v>
       </c>
       <c r="C56">
-        <v>3349.340009786572</v>
+        <v>3386.044842530241</v>
       </c>
       <c r="D56">
-        <v>6571.002882747761</v>
+        <v>6607.70771549143</v>
       </c>
       <c r="E56">
         <v>982.1131082182465</v>
@@ -5879,37 +5879,37 @@
         <v>2022.56</v>
       </c>
       <c r="M56">
-        <v>299.4377173992133</v>
+        <v>290.6958790786987</v>
       </c>
       <c r="N56">
-        <v>1723.122282600787</v>
+        <v>1731.864120921301</v>
       </c>
       <c r="O56">
-        <v>155.0810054340708</v>
+        <v>155.8677708829171</v>
       </c>
       <c r="P56">
-        <v>1568.041277166716</v>
+        <v>1575.996350038384</v>
       </c>
       <c r="Q56">
-        <v>2818.941277166716</v>
+        <v>2826.896350038384</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1787166790732025</v>
+        <v>0.17868668089739</v>
       </c>
       <c r="T56">
         <v>1.933663124553132</v>
       </c>
       <c r="U56">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V56">
         <v>0.09</v>
       </c>
       <c r="W56">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.754526509108747</v>
+        <v>6.957649370228747</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.119410256774867</v>
+        <v>0.1182953706676455</v>
       </c>
       <c r="C57">
-        <v>3270.022697002151</v>
+        <v>3307.345321990416</v>
       </c>
       <c r="D57">
-        <v>6565.27006761077</v>
+        <v>6602.592692599034</v>
       </c>
       <c r="E57">
         <v>1055.697605865676</v>
@@ -5961,37 +5961,37 @@
         <v>2022.56</v>
       </c>
       <c r="M57">
-        <v>304.9828603140136</v>
+        <v>296.0791360986746</v>
       </c>
       <c r="N57">
-        <v>1717.577139685986</v>
+        <v>1726.480863901325</v>
       </c>
       <c r="O57">
-        <v>154.5819425717388</v>
+        <v>155.3832777511193</v>
       </c>
       <c r="P57">
-        <v>1562.995197114248</v>
+        <v>1571.097586150206</v>
       </c>
       <c r="Q57">
-        <v>2813.895197114248</v>
+        <v>2821.997586150206</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1815418531548275</v>
+        <v>0.181511217361002</v>
       </c>
       <c r="T57">
         <v>1.974763571691696</v>
       </c>
       <c r="U57">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V57">
         <v>0.09</v>
       </c>
       <c r="W57">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.63171693621586</v>
+        <v>6.831146654406407</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.119580171463688</v>
+        <v>0.1184452784101188</v>
       </c>
       <c r="C58">
-        <v>3190.715378589073</v>
+        <v>3228.653714397972</v>
       </c>
       <c r="D58">
-        <v>6559.547246845122</v>
+        <v>6597.485582654021</v>
       </c>
       <c r="E58">
         <v>1129.282103513106</v>
@@ -6043,37 +6043,37 @@
         <v>2022.56</v>
       </c>
       <c r="M58">
-        <v>310.5280032288139</v>
+        <v>301.4623931186505</v>
       </c>
       <c r="N58">
-        <v>1712.031996771186</v>
+        <v>1721.097606881349</v>
       </c>
       <c r="O58">
-        <v>154.0828797094067</v>
+        <v>154.8987846193214</v>
       </c>
       <c r="P58">
-        <v>1557.949117061779</v>
+        <v>1566.198822262028</v>
       </c>
       <c r="Q58">
-        <v>2808.849117061779</v>
+        <v>2817.098822262028</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1844954442401628</v>
+        <v>0.1844641418456874</v>
       </c>
       <c r="T58">
         <v>2.017732220972922</v>
       </c>
       <c r="U58">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V58">
         <v>0.09</v>
       </c>
       <c r="W58">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.51329341949772</v>
+        <v>6.709161892720577</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.119750086152509</v>
+        <v>0.1185951861525921</v>
       </c>
       <c r="C59">
-        <v>3111.418028434392</v>
+        <v>3149.970001405094</v>
       </c>
       <c r="D59">
-        <v>6553.83439433787</v>
+        <v>6592.386367308572</v>
       </c>
       <c r="E59">
         <v>1202.866601160535</v>
@@ -6125,37 +6125,37 @@
         <v>2022.56</v>
       </c>
       <c r="M59">
-        <v>316.0731461436141</v>
+        <v>306.8456501386264</v>
       </c>
       <c r="N59">
-        <v>1706.486853856386</v>
+        <v>1715.714349861374</v>
       </c>
       <c r="O59">
-        <v>153.5838168470747</v>
+        <v>154.4142914875236</v>
       </c>
       <c r="P59">
-        <v>1552.903037009311</v>
+        <v>1561.30005837385</v>
       </c>
       <c r="Q59">
-        <v>2803.803037009311</v>
+        <v>2812.20005837385</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1875864116550486</v>
+        <v>0.1875544116552419</v>
       </c>
       <c r="T59">
         <v>2.062699412081182</v>
       </c>
       <c r="U59">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V59">
         <v>0.09</v>
       </c>
       <c r="W59">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.399025113892498</v>
+        <v>6.591457298111445</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.11992000084133</v>
+        <v>0.1187450938950654</v>
       </c>
       <c r="C60">
-        <v>3032.13062051605</v>
+        <v>3071.294164720641</v>
       </c>
       <c r="D60">
-        <v>6548.131484066957</v>
+        <v>6587.295028271547</v>
       </c>
       <c r="E60">
         <v>1276.451098807964</v>
@@ -6207,37 +6207,37 @@
         <v>2022.56</v>
       </c>
       <c r="M60">
-        <v>321.6182890584143</v>
+        <v>312.2289071586023</v>
       </c>
       <c r="N60">
-        <v>1700.941710941586</v>
+        <v>1710.331092841398</v>
       </c>
       <c r="O60">
-        <v>153.0847539847427</v>
+        <v>153.9297983557258</v>
       </c>
       <c r="P60">
-        <v>1547.856956956843</v>
+        <v>1556.401294485672</v>
       </c>
       <c r="Q60">
-        <v>2798.756956956843</v>
+        <v>2807.301294485672</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1908245679944528</v>
+        <v>0.1907918371700132</v>
       </c>
       <c r="T60">
         <v>2.109807898004121</v>
       </c>
       <c r="U60">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V60">
         <v>0.09</v>
       </c>
       <c r="W60">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.288697094687454</v>
+        <v>6.477811482626764</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.120089915530151</v>
+        <v>0.1188950016375386</v>
       </c>
       <c r="C61">
-        <v>2952.853128902486</v>
+        <v>2992.626186109938</v>
       </c>
       <c r="D61">
-        <v>6542.438490100822</v>
+        <v>6582.211547308274</v>
       </c>
       <c r="E61">
         <v>1350.035596455393</v>
@@ -6289,37 +6289,37 @@
         <v>2022.56</v>
       </c>
       <c r="M61">
-        <v>327.1634319732145</v>
+        <v>317.6121641785782</v>
       </c>
       <c r="N61">
-        <v>1695.396568026785</v>
+        <v>1704.947835821422</v>
       </c>
       <c r="O61">
-        <v>152.5856911224107</v>
+        <v>153.445305223928</v>
       </c>
       <c r="P61">
-        <v>1542.810876904375</v>
+        <v>1551.502530597494</v>
       </c>
       <c r="Q61">
-        <v>2793.710876904375</v>
+        <v>2802.402530597494</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1942206831796816</v>
+        <v>0.1941871858806271</v>
       </c>
       <c r="T61">
         <v>2.15921435885013</v>
       </c>
       <c r="U61">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V61">
         <v>0.09</v>
       </c>
       <c r="W61">
-        <v>0.06857531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.18210900833682</v>
+        <v>6.36801806766699</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1210242302189719</v>
+        <v>0.1190449093800119</v>
       </c>
       <c r="C62">
-        <v>2848.140433541275</v>
+        <v>2913.966047394554</v>
       </c>
       <c r="D62">
-        <v>6511.31029238704</v>
+        <v>6577.135906240319</v>
       </c>
       <c r="E62">
         <v>1423.620094102822</v>
@@ -6371,45 +6371,45 @@
         <v>2022.56</v>
       </c>
       <c r="M62">
-        <v>338.8896726903988</v>
+        <v>322.995421198554</v>
       </c>
       <c r="N62">
-        <v>1683.670327309601</v>
+        <v>1699.564578801446</v>
       </c>
       <c r="O62">
-        <v>151.5303294578641</v>
+        <v>152.9608120921301</v>
       </c>
       <c r="P62">
-        <v>1532.139997851737</v>
+        <v>1546.603766709316</v>
       </c>
       <c r="Q62">
-        <v>2783.039997851737</v>
+        <v>2797.503766709316</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1977866041241717</v>
+        <v>0.1977523020267716</v>
       </c>
       <c r="T62">
         <v>2.21109114273844</v>
       </c>
       <c r="U62">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V62">
         <v>0.09</v>
       </c>
       <c r="W62">
-        <v>0.06984931428217207</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y62">
-        <v>5.968196032482113</v>
+        <v>6.261884433205873</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1212068849077929</v>
+        <v>0.1191948171224851</v>
       </c>
       <c r="C63">
-        <v>2768.505082951392</v>
+        <v>2835.313730452081</v>
       </c>
       <c r="D63">
-        <v>6505.259439444587</v>
+        <v>6572.068086945276</v>
       </c>
       <c r="E63">
         <v>1497.204591750252</v>
@@ -6453,45 +6453,45 @@
         <v>2022.56</v>
       </c>
       <c r="M63">
-        <v>344.5378339019055</v>
+        <v>328.37867821853</v>
       </c>
       <c r="N63">
-        <v>1678.022166098094</v>
+        <v>1694.18132178147</v>
       </c>
       <c r="O63">
-        <v>151.0219949488285</v>
+        <v>152.4763189603323</v>
       </c>
       <c r="P63">
-        <v>1527.000171149266</v>
+        <v>1541.705002821138</v>
       </c>
       <c r="Q63">
-        <v>2777.900171149266</v>
+        <v>2792.605002821138</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.201535392809405</v>
+        <v>0.2015002446419492</v>
       </c>
       <c r="T63">
         <v>2.265628274518458</v>
       </c>
       <c r="U63">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V63">
         <v>0.09</v>
       </c>
       <c r="W63">
-        <v>0.06984931428217207</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y63">
-        <v>5.870356753261094</v>
+        <v>6.159230590038564</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1213895395966139</v>
+        <v>0.1199089248649584</v>
       </c>
       <c r="C64">
-        <v>2688.880967835657</v>
+        <v>2737.694744429046</v>
       </c>
       <c r="D64">
-        <v>6499.219821976281</v>
+        <v>6548.03359856967</v>
       </c>
       <c r="E64">
         <v>1570.789089397681</v>
@@ -6535,37 +6535,37 @@
         <v>2022.56</v>
       </c>
       <c r="M64">
-        <v>350.1859951134121</v>
+        <v>338.3241740926464</v>
       </c>
       <c r="N64">
-        <v>1672.374004886588</v>
+        <v>1684.235825907354</v>
       </c>
       <c r="O64">
-        <v>150.5136604397929</v>
+        <v>151.5812243316618</v>
       </c>
       <c r="P64">
-        <v>1521.860344446795</v>
+        <v>1532.654601575692</v>
       </c>
       <c r="Q64">
-        <v>2772.760344446795</v>
+        <v>2783.554601575692</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2054814861622821</v>
+        <v>0.2054454473947677</v>
       </c>
       <c r="T64">
         <v>2.323035781655319</v>
       </c>
       <c r="U64">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V64">
         <v>0.09</v>
       </c>
       <c r="W64">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.7756735798214</v>
+        <v>5.978171691172572</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1215721942854349</v>
+        <v>0.1200679326074317</v>
       </c>
       <c r="C65">
-        <v>2609.268056929356</v>
+        <v>2658.782485563783</v>
       </c>
       <c r="D65">
-        <v>6493.19140871741</v>
+        <v>6542.705837351837</v>
       </c>
       <c r="E65">
         <v>1644.373587045111</v>
@@ -6617,37 +6617,37 @@
         <v>2022.56</v>
       </c>
       <c r="M65">
-        <v>355.8341563249188</v>
+        <v>343.7810156102698</v>
       </c>
       <c r="N65">
-        <v>1666.725843675081</v>
+        <v>1678.77898438973</v>
       </c>
       <c r="O65">
-        <v>150.0053259307573</v>
+        <v>151.0901085950757</v>
       </c>
       <c r="P65">
-        <v>1516.720517744324</v>
+        <v>1527.688875794654</v>
       </c>
       <c r="Q65">
-        <v>2767.620517744324</v>
+        <v>2778.588875794655</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.209640881858558</v>
+        <v>0.2096039043504413</v>
       </c>
       <c r="T65">
         <v>2.383546397286064</v>
       </c>
       <c r="U65">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V65">
         <v>0.09</v>
       </c>
       <c r="W65">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.683996221411535</v>
+        <v>5.883280077026975</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1217548489742558</v>
+        <v>0.1202269403499049</v>
       </c>
       <c r="C66">
-        <v>2529.666319083671</v>
+        <v>2579.878889440596</v>
       </c>
       <c r="D66">
-        <v>6487.174168519154</v>
+        <v>6537.386738876079</v>
       </c>
       <c r="E66">
         <v>1717.958084692541</v>
@@ -6699,37 +6699,37 @@
         <v>2022.56</v>
       </c>
       <c r="M66">
-        <v>361.4823175364254</v>
+        <v>349.2378571278932</v>
       </c>
       <c r="N66">
-        <v>1661.077682463575</v>
+        <v>1673.322142872107</v>
       </c>
       <c r="O66">
-        <v>149.4969914217217</v>
+        <v>150.5989928584896</v>
       </c>
       <c r="P66">
-        <v>1511.580691041853</v>
+        <v>1522.723150013617</v>
       </c>
       <c r="Q66">
-        <v>2762.480691041853</v>
+        <v>2773.623150013617</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2140313550935159</v>
+        <v>0.2139933866925412</v>
       </c>
       <c r="T66">
         <v>2.447418713785184</v>
       </c>
       <c r="U66">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V66">
         <v>0.09</v>
       </c>
       <c r="W66">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.595183780451981</v>
+        <v>5.791353825823428</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1219375036630768</v>
+        <v>0.1203859480923782</v>
       </c>
       <c r="C67">
-        <v>2450.075723265131</v>
+        <v>2500.983934948701</v>
       </c>
       <c r="D67">
-        <v>6481.168070348044</v>
+        <v>6532.076282031614</v>
       </c>
       <c r="E67">
         <v>1791.542582339971</v>
@@ -6781,37 +6781,37 @@
         <v>2022.56</v>
       </c>
       <c r="M67">
-        <v>367.1304787479321</v>
+        <v>354.6946986455165</v>
       </c>
       <c r="N67">
-        <v>1655.429521252068</v>
+        <v>1667.865301354484</v>
       </c>
       <c r="O67">
-        <v>148.9886569126861</v>
+        <v>150.1078771219035</v>
       </c>
       <c r="P67">
-        <v>1506.440864339382</v>
+        <v>1517.75742423258</v>
       </c>
       <c r="Q67">
-        <v>2757.340864339382</v>
+        <v>2768.65742423258</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2186727125133285</v>
+        <v>0.2186336965970468</v>
       </c>
       <c r="T67">
         <v>2.514940876941397</v>
       </c>
       <c r="U67">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V67">
         <v>0.09</v>
       </c>
       <c r="W67">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.509104029983487</v>
+        <v>5.702256074656915</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1221201583518978</v>
+        <v>0.1205449558348515</v>
       </c>
       <c r="C68">
-        <v>2370.496238555098</v>
+        <v>2422.097601045855</v>
       </c>
       <c r="D68">
-        <v>6475.17308328544</v>
+        <v>6526.774445776197</v>
       </c>
       <c r="E68">
         <v>1865.1270799874</v>
@@ -6863,37 +6863,37 @@
         <v>2022.56</v>
       </c>
       <c r="M68">
-        <v>372.7786399594387</v>
+        <v>360.1515401631398</v>
       </c>
       <c r="N68">
-        <v>1649.781360040561</v>
+        <v>1662.40845983686</v>
       </c>
       <c r="O68">
-        <v>148.4803224036505</v>
+        <v>149.6167613853174</v>
       </c>
       <c r="P68">
-        <v>1501.301037636911</v>
+        <v>1512.791698451543</v>
       </c>
       <c r="Q68">
-        <v>2752.201037636911</v>
+        <v>2763.691698451543</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.223587090957836</v>
+        <v>0.2235469659076998</v>
       </c>
       <c r="T68">
         <v>2.586434932047975</v>
       </c>
       <c r="U68">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V68">
         <v>0.09</v>
       </c>
       <c r="W68">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.42563275680192</v>
+        <v>5.61585825534393</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1223028130407188</v>
+        <v>0.1207039635773248</v>
       </c>
       <c r="C69">
-        <v>2290.927834149216</v>
+        <v>2343.219866758075</v>
       </c>
       <c r="D69">
-        <v>6469.189176526987</v>
+        <v>6521.481209135846</v>
       </c>
       <c r="E69">
         <v>1938.711577634829</v>
@@ -6945,37 +6945,37 @@
         <v>2022.56</v>
       </c>
       <c r="M69">
-        <v>378.4268011709453</v>
+        <v>365.6083816807632</v>
       </c>
       <c r="N69">
-        <v>1644.133198829055</v>
+        <v>1656.951618319237</v>
       </c>
       <c r="O69">
-        <v>147.9719878946149</v>
+        <v>149.1256456487313</v>
       </c>
       <c r="P69">
-        <v>1496.16121093444</v>
+        <v>1507.825972670506</v>
       </c>
       <c r="Q69">
-        <v>2747.06121093444</v>
+        <v>2758.725972670506</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2287993105201924</v>
+        <v>0.2287580091159681</v>
       </c>
       <c r="T69">
         <v>2.662261960191316</v>
       </c>
       <c r="U69">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V69">
         <v>0.09</v>
       </c>
       <c r="W69">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.344653163416817</v>
+        <v>5.532039475413424</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1224854677295398</v>
+        <v>0.120862971319798</v>
       </c>
       <c r="C70">
-        <v>2211.370479356899</v>
+        <v>2264.350711179364</v>
       </c>
       <c r="D70">
-        <v>6463.2163193821</v>
+        <v>6516.196551204565</v>
       </c>
       <c r="E70">
         <v>2012.296075282259</v>
@@ -7027,37 +7027,37 @@
         <v>2022.56</v>
       </c>
       <c r="M70">
-        <v>384.074962382452</v>
+        <v>371.0652231983865</v>
       </c>
       <c r="N70">
-        <v>1638.485037617548</v>
+        <v>1651.494776801613</v>
       </c>
       <c r="O70">
-        <v>147.4636533855793</v>
+        <v>148.6345299121452</v>
       </c>
       <c r="P70">
-        <v>1491.021384231969</v>
+        <v>1502.860246889468</v>
       </c>
       <c r="Q70">
-        <v>2741.921384231969</v>
+        <v>2753.760246889468</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2343372938051961</v>
+        <v>0.2342947425247532</v>
       </c>
       <c r="T70">
         <v>2.742828177593615</v>
       </c>
       <c r="U70">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V70">
         <v>0.09</v>
       </c>
       <c r="W70">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.266055322778334</v>
+        <v>5.450685953716167</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1226681224183607</v>
+        <v>0.1210219790622713</v>
       </c>
       <c r="C71">
-        <v>2131.824143600796</v>
+        <v>2185.490113471432</v>
       </c>
       <c r="D71">
-        <v>6457.254481273426</v>
+        <v>6510.920451144062</v>
       </c>
       <c r="E71">
         <v>2085.880572929688</v>
@@ -7109,37 +7109,37 @@
         <v>2022.56</v>
       </c>
       <c r="M71">
-        <v>389.7231235939587</v>
+        <v>376.5220647160098</v>
       </c>
       <c r="N71">
-        <v>1632.836876406041</v>
+        <v>1646.03793528399</v>
       </c>
       <c r="O71">
-        <v>146.9553188765437</v>
+        <v>148.1434141755591</v>
       </c>
       <c r="P71">
-        <v>1485.881557529498</v>
+        <v>1497.894521108431</v>
       </c>
       <c r="Q71">
-        <v>2736.781557529498</v>
+        <v>2748.794521108431</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2402325663343936</v>
+        <v>0.2401886845405567</v>
       </c>
       <c r="T71">
         <v>2.828592215473482</v>
       </c>
       <c r="U71">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V71">
         <v>0.09</v>
       </c>
       <c r="W71">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.189735680419227</v>
+        <v>5.371690505111586</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1228507771071817</v>
+        <v>0.1211809868047446</v>
       </c>
       <c r="C72">
-        <v>2052.288796416276</v>
+        <v>2106.638052863427</v>
       </c>
       <c r="D72">
-        <v>6451.303631736336</v>
+        <v>6505.652888183487</v>
       </c>
       <c r="E72">
         <v>2159.465070577118</v>
@@ -7191,37 +7191,37 @@
         <v>2022.56</v>
       </c>
       <c r="M72">
-        <v>395.3712848054654</v>
+        <v>381.9789062336332</v>
       </c>
       <c r="N72">
-        <v>1627.188715194535</v>
+        <v>1640.581093766367</v>
       </c>
       <c r="O72">
-        <v>146.4469843675081</v>
+        <v>147.652298438973</v>
       </c>
       <c r="P72">
-        <v>1480.741730827026</v>
+        <v>1492.928795327394</v>
       </c>
       <c r="Q72">
-        <v>2731.641730827027</v>
+        <v>2743.828795327394</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2465208570322042</v>
+        <v>0.2464755560240804</v>
       </c>
       <c r="T72">
         <v>2.920073855878673</v>
       </c>
       <c r="U72">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V72">
         <v>0.09</v>
       </c>
       <c r="W72">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.115596599270381</v>
+        <v>5.294952069324276</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1230334317960027</v>
+        <v>0.1213399945472178</v>
       </c>
       <c r="C73">
-        <v>1972.764407450908</v>
+        <v>2027.794508651662</v>
       </c>
       <c r="D73">
-        <v>6445.363740418396</v>
+        <v>6500.39384161915</v>
       </c>
       <c r="E73">
         <v>2233.049568224546</v>
@@ -7273,37 +7273,37 @@
         <v>2022.56</v>
       </c>
       <c r="M73">
-        <v>401.0194460169719</v>
+        <v>387.4357477512564</v>
       </c>
       <c r="N73">
-        <v>1621.540553983028</v>
+        <v>1635.124252248743</v>
       </c>
       <c r="O73">
-        <v>145.9386498584725</v>
+        <v>147.1611827023869</v>
       </c>
       <c r="P73">
-        <v>1475.601904124556</v>
+        <v>1487.963069546357</v>
       </c>
       <c r="Q73">
-        <v>2726.501904124556</v>
+        <v>2738.863069546357</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2532428229505535</v>
+        <v>0.2531960048512953</v>
       </c>
       <c r="T73">
         <v>3.017864574932497</v>
       </c>
       <c r="U73">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V73">
         <v>0.09</v>
       </c>
       <c r="W73">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.043545942942631</v>
+        <v>5.220375279615485</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1232160864848237</v>
+        <v>0.1214990022896911</v>
       </c>
       <c r="C74">
-        <v>1893.250946463937</v>
+        <v>1948.959460199334</v>
       </c>
       <c r="D74">
-        <v>6439.434777078855</v>
+        <v>6495.143290814252</v>
       </c>
       <c r="E74">
         <v>2306.634065871976</v>
@@ -7355,37 +7355,37 @@
         <v>2022.56</v>
       </c>
       <c r="M74">
-        <v>406.6676072284786</v>
+        <v>392.8925892688798</v>
       </c>
       <c r="N74">
-        <v>1615.892392771521</v>
+        <v>1629.66741073112</v>
       </c>
       <c r="O74">
-        <v>145.4303153494369</v>
+        <v>146.6700669658008</v>
       </c>
       <c r="P74">
-        <v>1470.462077422084</v>
+        <v>1482.997343765319</v>
       </c>
       <c r="Q74">
-        <v>2721.362077422084</v>
+        <v>2733.897343765319</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.260444929291642</v>
+        <v>0.2603964857375971</v>
       </c>
       <c r="T74">
         <v>3.12264034534731</v>
       </c>
       <c r="U74">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V74">
         <v>0.09</v>
       </c>
       <c r="W74">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.973496693735093</v>
+        <v>5.147870067398602</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1233987411736447</v>
+        <v>0.1216580100321643</v>
       </c>
       <c r="C75">
-        <v>1813.748383325784</v>
+        <v>1870.132886936272</v>
       </c>
       <c r="D75">
-        <v>6433.516711588131</v>
+        <v>6489.90121519862</v>
       </c>
       <c r="E75">
         <v>2380.218563519405</v>
@@ -7437,37 +7437,37 @@
         <v>2022.56</v>
       </c>
       <c r="M75">
-        <v>412.3157684399852</v>
+        <v>398.3494307865031</v>
       </c>
       <c r="N75">
-        <v>1610.244231560015</v>
+        <v>1624.210569213497</v>
       </c>
       <c r="O75">
-        <v>144.9219808404013</v>
+        <v>146.1789512292147</v>
       </c>
       <c r="P75">
-        <v>1465.322250719613</v>
+        <v>1478.031617984282</v>
       </c>
       <c r="Q75">
-        <v>2716.222250719613</v>
+        <v>2728.931617984282</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2681805249913298</v>
+        <v>0.2681303355784397</v>
       </c>
       <c r="T75">
         <v>3.235177283940998</v>
       </c>
       <c r="U75">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V75">
         <v>0.09</v>
       </c>
       <c r="W75">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.905366602040092</v>
+        <v>5.077351299352047</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1235813958624656</v>
+        <v>0.1218170177746376</v>
       </c>
       <c r="C76">
-        <v>1734.256688017525</v>
+        <v>1791.314768358649</v>
       </c>
       <c r="D76">
-        <v>6427.609513927303</v>
+        <v>6484.667594268427</v>
       </c>
       <c r="E76">
         <v>2453.803061166835</v>
@@ -7519,37 +7519,37 @@
         <v>2022.56</v>
       </c>
       <c r="M76">
-        <v>417.9639296514919</v>
+        <v>403.8062723041265</v>
       </c>
       <c r="N76">
-        <v>1604.596070348508</v>
+        <v>1618.753727695874</v>
       </c>
       <c r="O76">
-        <v>144.4136463313657</v>
+        <v>145.6878354926286</v>
       </c>
       <c r="P76">
-        <v>1460.182424017142</v>
+        <v>1473.065892203245</v>
       </c>
       <c r="Q76">
-        <v>2711.082424017142</v>
+        <v>2723.965892203245</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2765111665140703</v>
+        <v>0.276459096945501</v>
       </c>
       <c r="T76">
         <v>3.356370910118815</v>
       </c>
       <c r="U76">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V76">
         <v>0.09</v>
       </c>
       <c r="W76">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.839077864174685</v>
+        <v>5.008738443955398</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1237640505512866</v>
+        <v>0.1219760255171109</v>
       </c>
       <c r="C77">
-        <v>1654.77583063039</v>
+        <v>1712.505084028733</v>
       </c>
       <c r="D77">
-        <v>6421.713154187597</v>
+        <v>6479.44240758594</v>
       </c>
       <c r="E77">
         <v>2527.387558814264</v>
@@ -7601,37 +7601,37 @@
         <v>2022.56</v>
       </c>
       <c r="M77">
-        <v>423.6120908629986</v>
+        <v>409.2631138217498</v>
       </c>
       <c r="N77">
-        <v>1598.947909137001</v>
+        <v>1613.29688617825</v>
       </c>
       <c r="O77">
-        <v>143.9053118223301</v>
+        <v>145.1967197560425</v>
       </c>
       <c r="P77">
-        <v>1455.042597314671</v>
+        <v>1468.100166422208</v>
       </c>
       <c r="Q77">
-        <v>2705.942597314671</v>
+        <v>2719.000166422208</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2855082593586302</v>
+        <v>0.2854541592219273</v>
       </c>
       <c r="T77">
         <v>3.487260026390859</v>
       </c>
       <c r="U77">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V77">
         <v>0.09</v>
       </c>
       <c r="W77">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.774556825985689</v>
+        <v>4.941955264702658</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1239467052401076</v>
+        <v>0.1221350332595841</v>
       </c>
       <c r="C78">
-        <v>1575.305781365255</v>
+        <v>1633.703813574604</v>
       </c>
       <c r="D78">
-        <v>6415.827602569891</v>
+        <v>6474.22563477924</v>
       </c>
       <c r="E78">
         <v>2600.972056461693</v>
@@ -7683,37 +7683,37 @@
         <v>2022.56</v>
       </c>
       <c r="M78">
-        <v>429.2602520745052</v>
+        <v>414.7199553393731</v>
       </c>
       <c r="N78">
-        <v>1593.299747925495</v>
+        <v>1607.840044660627</v>
       </c>
       <c r="O78">
-        <v>143.3969773132945</v>
+        <v>144.7056040194564</v>
       </c>
       <c r="P78">
-        <v>1449.9027706122</v>
+        <v>1463.134440641171</v>
       </c>
       <c r="Q78">
-        <v>2700.8027706122</v>
+        <v>2714.03444064117</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2952551099402367</v>
+        <v>0.295198810021389</v>
       </c>
       <c r="T78">
         <v>3.629056569018906</v>
       </c>
       <c r="U78">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V78">
         <v>0.09</v>
       </c>
       <c r="W78">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.7117337098543</v>
+        <v>4.876929537535519</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1241293599289286</v>
+        <v>0.1222940410020574</v>
       </c>
       <c r="C79">
-        <v>1495.846510532136</v>
+        <v>1554.910936689898</v>
       </c>
       <c r="D79">
-        <v>6409.952829384201</v>
+        <v>6469.017255541964</v>
       </c>
       <c r="E79">
         <v>2674.556554109123</v>
@@ -7765,37 +7765,37 @@
         <v>2022.56</v>
       </c>
       <c r="M79">
-        <v>434.9084132860119</v>
+        <v>420.1767968569965</v>
       </c>
       <c r="N79">
-        <v>1587.651586713988</v>
+        <v>1602.383203143003</v>
       </c>
       <c r="O79">
-        <v>142.8886428042589</v>
+        <v>144.2144882828703</v>
       </c>
       <c r="P79">
-        <v>1444.762943909729</v>
+        <v>1458.168714860133</v>
       </c>
       <c r="Q79">
-        <v>2695.662943909729</v>
+        <v>2709.068714860133</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3058495127463308</v>
+        <v>0.3057908217599344</v>
       </c>
       <c r="T79">
         <v>3.783183245788522</v>
       </c>
       <c r="U79">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V79">
         <v>0.09</v>
       </c>
       <c r="W79">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.650542362973074</v>
+        <v>4.813592790294797</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1243120146177495</v>
+        <v>0.1224530487445307</v>
       </c>
       <c r="C80">
-        <v>1416.397988549701</v>
+        <v>1476.126433133551</v>
       </c>
       <c r="D80">
-        <v>6404.088805049196</v>
+        <v>6463.817249633046</v>
       </c>
       <c r="E80">
         <v>2748.141051756552</v>
@@ -7847,37 +7847,37 @@
         <v>2022.56</v>
       </c>
       <c r="M80">
-        <v>440.5565744975185</v>
+        <v>425.6336383746197</v>
       </c>
       <c r="N80">
-        <v>1582.003425502481</v>
+        <v>1596.92636162538</v>
       </c>
       <c r="O80">
-        <v>142.3803082952233</v>
+        <v>143.7233725462842</v>
       </c>
       <c r="P80">
-        <v>1439.623117207258</v>
+        <v>1453.202989079096</v>
       </c>
       <c r="Q80">
-        <v>2690.523117207258</v>
+        <v>2704.102989079096</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3174070430802515</v>
+        <v>0.3173457436565294</v>
       </c>
       <c r="T80">
         <v>3.951321438628102</v>
       </c>
       <c r="U80">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V80">
         <v>0.09</v>
       </c>
       <c r="W80">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.590920024986239</v>
+        <v>4.751880062214095</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1244946693065705</v>
+        <v>0.1226120564870039</v>
       </c>
       <c r="C81">
-        <v>1336.96018594476</v>
+        <v>1397.350282729518</v>
       </c>
       <c r="D81">
-        <v>6398.235500091685</v>
+        <v>6458.625596876443</v>
       </c>
       <c r="E81">
         <v>2821.725549403982</v>
@@ -7929,37 +7929,37 @@
         <v>2022.56</v>
       </c>
       <c r="M81">
-        <v>446.2047357090252</v>
+        <v>431.0904798922431</v>
       </c>
       <c r="N81">
-        <v>1576.355264290975</v>
+        <v>1591.469520107757</v>
       </c>
       <c r="O81">
-        <v>141.8719737861877</v>
+        <v>143.2322568096981</v>
       </c>
       <c r="P81">
-        <v>1434.483290504787</v>
+        <v>1448.237263298059</v>
       </c>
       <c r="Q81">
-        <v>2685.383290504788</v>
+        <v>2699.137263298059</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3300652905888314</v>
+        <v>0.330001134305181</v>
       </c>
       <c r="T81">
         <v>4.135472792690501</v>
       </c>
       <c r="U81">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V81">
         <v>0.09</v>
       </c>
       <c r="W81">
-        <v>0.06984931428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.532807113277554</v>
+        <v>4.691729681679739</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1265701239953915</v>
+        <v>0.1227710642294772</v>
       </c>
       <c r="C82">
-        <v>1197.610000703033</v>
+        <v>1318.582465366528</v>
       </c>
       <c r="D82">
-        <v>6332.469812497387</v>
+        <v>6453.442277160882</v>
       </c>
       <c r="E82">
         <v>2895.310047051411</v>
@@ -8011,45 +8011,45 @@
         <v>2022.56</v>
       </c>
       <c r="M82">
-        <v>467.1584724311971</v>
+        <v>436.5473214098665</v>
       </c>
       <c r="N82">
-        <v>1555.401527568803</v>
+        <v>1586.012678590133</v>
       </c>
       <c r="O82">
-        <v>139.9861374811922</v>
+        <v>142.741141073112</v>
       </c>
       <c r="P82">
-        <v>1415.415390087611</v>
+        <v>1443.271537517021</v>
       </c>
       <c r="Q82">
-        <v>2666.31539008761</v>
+        <v>2694.171537517022</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3439893628482693</v>
+        <v>0.3439220640186978</v>
       </c>
       <c r="T82">
         <v>4.338039282159139</v>
       </c>
       <c r="U82">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V82">
         <v>0.09</v>
       </c>
       <c r="W82">
-        <v>0.07221531428217208</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.329494420756506</v>
+        <v>4.633083060658743</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1267764386842125</v>
+        <v>0.1229300719719505</v>
       </c>
       <c r="C83">
-        <v>1117.561736851664</v>
+        <v>1239.822960997817</v>
       </c>
       <c r="D83">
-        <v>6326.006046293448</v>
+        <v>6448.267270439601</v>
       </c>
       <c r="E83">
         <v>2968.894544698841</v>
@@ -8093,45 +8093,45 @@
         <v>2022.56</v>
       </c>
       <c r="M83">
-        <v>472.9979533365872</v>
+        <v>442.0041629274898</v>
       </c>
       <c r="N83">
-        <v>1549.562046663413</v>
+        <v>1580.55583707251</v>
       </c>
       <c r="O83">
-        <v>139.4605841997071</v>
+        <v>142.2500253365259</v>
       </c>
       <c r="P83">
-        <v>1410.101462463706</v>
+        <v>1438.305811735984</v>
       </c>
       <c r="Q83">
-        <v>2661.001462463706</v>
+        <v>2689.205811735985</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3593791269244901</v>
+        <v>0.35930835475469</v>
       </c>
       <c r="T83">
         <v>4.561928559992896</v>
       </c>
       <c r="U83">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V83">
         <v>0.09</v>
       </c>
       <c r="W83">
-        <v>0.07221531428217208</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>4.276043872352104</v>
+        <v>4.575884504354313</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1269827533730334</v>
+        <v>0.1230890797144237</v>
       </c>
       <c r="C84">
-        <v>1037.526655114614</v>
+        <v>1161.071749640873</v>
       </c>
       <c r="D84">
-        <v>6319.555462203827</v>
+        <v>6443.100556730086</v>
       </c>
       <c r="E84">
         <v>3042.47904234627</v>
@@ -8175,45 +8175,45 @@
         <v>2022.56</v>
       </c>
       <c r="M84">
-        <v>478.8374342419771</v>
+        <v>447.4610044451131</v>
       </c>
       <c r="N84">
-        <v>1543.722565758023</v>
+        <v>1575.098995554887</v>
       </c>
       <c r="O84">
-        <v>138.9350309182221</v>
+        <v>141.7589095999398</v>
       </c>
       <c r="P84">
-        <v>1404.787534839801</v>
+        <v>1433.340085954947</v>
       </c>
       <c r="Q84">
-        <v>2655.687534839801</v>
+        <v>2684.240085954947</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3764788647869576</v>
+        <v>0.376404233350237</v>
       </c>
       <c r="T84">
         <v>4.810694424252627</v>
       </c>
       <c r="U84">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V84">
         <v>0.09</v>
       </c>
       <c r="W84">
-        <v>0.07221531428217208</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.223896995860006</v>
+        <v>4.520081034789017</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1271890680618545</v>
+        <v>0.125136337456897</v>
       </c>
       <c r="C85">
-        <v>957.5047152078268</v>
+        <v>1021.696757447519</v>
       </c>
       <c r="D85">
-        <v>6313.118019944469</v>
+        <v>6377.310062184161</v>
       </c>
       <c r="E85">
         <v>3116.0635399937</v>
@@ -8257,37 +8257,37 @@
         <v>2022.56</v>
       </c>
       <c r="M85">
-        <v>484.676915147367</v>
+        <v>468.186629224578</v>
       </c>
       <c r="N85">
-        <v>1537.883084852633</v>
+        <v>1554.373370775422</v>
       </c>
       <c r="O85">
-        <v>138.409477636737</v>
+        <v>139.893603369788</v>
       </c>
       <c r="P85">
-        <v>1399.473607215896</v>
+        <v>1414.479767405634</v>
       </c>
       <c r="Q85">
-        <v>2650.373607215896</v>
+        <v>2665.379767405634</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3955903365155979</v>
+        <v>0.3955113917805542</v>
       </c>
       <c r="T85">
         <v>5.08872686077821</v>
       </c>
       <c r="U85">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V85">
         <v>0.09</v>
       </c>
       <c r="W85">
-        <v>0.07221531428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.173006670608681</v>
+        <v>4.319986675719067</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1273953827506754</v>
+        <v>0.1253180951993703</v>
       </c>
       <c r="C86">
-        <v>877.495877011228</v>
+        <v>942.3361871971101</v>
       </c>
       <c r="D86">
-        <v>6306.693679395299</v>
+        <v>6371.533989581181</v>
       </c>
       <c r="E86">
         <v>3189.648037641129</v>
@@ -8339,37 +8339,37 @@
         <v>2022.56</v>
       </c>
       <c r="M86">
-        <v>490.516396052757</v>
+        <v>473.8274319863199</v>
       </c>
       <c r="N86">
-        <v>1532.043603947243</v>
+        <v>1548.73256801368</v>
       </c>
       <c r="O86">
-        <v>137.8839243552518</v>
+        <v>139.3859311212312</v>
       </c>
       <c r="P86">
-        <v>1394.159679591991</v>
+        <v>1409.346636892449</v>
       </c>
       <c r="Q86">
-        <v>2645.059679591991</v>
+        <v>2660.246636892449</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4170907422103179</v>
+        <v>0.4170069450146608</v>
       </c>
       <c r="T86">
         <v>5.401513351869486</v>
       </c>
       <c r="U86">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V86">
         <v>0.09</v>
       </c>
       <c r="W86">
-        <v>0.07221531428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.123328019768101</v>
+        <v>4.268558262912887</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1276016974394964</v>
+        <v>0.1254998529418436</v>
       </c>
       <c r="C87">
-        <v>797.5001005678823</v>
+        <v>862.9860705154006</v>
       </c>
       <c r="D87">
-        <v>6300.282400599383</v>
+        <v>6365.768370546901</v>
       </c>
       <c r="E87">
         <v>3263.232535288558</v>
@@ -8421,37 +8421,37 @@
         <v>2022.56</v>
       </c>
       <c r="M87">
-        <v>496.3558769581469</v>
+        <v>479.4682347480618</v>
       </c>
       <c r="N87">
-        <v>1526.204123041853</v>
+        <v>1543.091765251938</v>
       </c>
       <c r="O87">
-        <v>137.3583710737668</v>
+        <v>138.8782588726744</v>
       </c>
       <c r="P87">
-        <v>1388.845751968086</v>
+        <v>1404.213506379264</v>
       </c>
       <c r="Q87">
-        <v>2639.745751968087</v>
+        <v>2655.113506379264</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4414578686643342</v>
+        <v>0.4413685720133152</v>
       </c>
       <c r="T87">
         <v>5.756004708439603</v>
       </c>
       <c r="U87">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V87">
         <v>0.09</v>
       </c>
       <c r="W87">
-        <v>0.07221531428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.074818278359064</v>
+        <v>4.21833993040803</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1278080121283174</v>
+        <v>0.1256816106843168</v>
       </c>
       <c r="C88">
-        <v>717.5173460831666</v>
+        <v>783.6463790496573</v>
       </c>
       <c r="D88">
-        <v>6293.884143762097</v>
+        <v>6360.013176728587</v>
       </c>
       <c r="E88">
         <v>3336.817032935988</v>
@@ -8503,37 +8503,37 @@
         <v>2022.56</v>
       </c>
       <c r="M88">
-        <v>502.1953578635369</v>
+        <v>485.1090375098038</v>
       </c>
       <c r="N88">
-        <v>1520.364642136463</v>
+        <v>1537.450962490196</v>
       </c>
       <c r="O88">
-        <v>136.8328177922817</v>
+        <v>138.3705866241176</v>
       </c>
       <c r="P88">
-        <v>1383.531824344181</v>
+        <v>1399.080375866079</v>
       </c>
       <c r="Q88">
-        <v>2634.431824344181</v>
+        <v>2649.980375866079</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.46930601318321</v>
+        <v>0.4692104314403487</v>
       </c>
       <c r="T88">
         <v>6.161137687376879</v>
       </c>
       <c r="U88">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V88">
         <v>0.09</v>
       </c>
       <c r="W88">
-        <v>0.07221531428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.027436670471168</v>
+        <v>4.16928946610096</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1301519168171384</v>
+        <v>0.1258633684267901</v>
       </c>
       <c r="C89">
-        <v>572.1454506123746</v>
+        <v>704.3170845495861</v>
       </c>
       <c r="D89">
-        <v>6222.096745938734</v>
+        <v>6354.268379875945</v>
       </c>
       <c r="E89">
         <v>3410.401530583417</v>
@@ -8585,45 +8585,45 @@
         <v>2022.56</v>
       </c>
       <c r="M89">
-        <v>525.319837266308</v>
+        <v>490.7498402715456</v>
       </c>
       <c r="N89">
-        <v>1497.240162733692</v>
+        <v>1531.810159728454</v>
       </c>
       <c r="O89">
-        <v>134.7516146460323</v>
+        <v>137.8629143755609</v>
       </c>
       <c r="P89">
-        <v>1362.48854808766</v>
+        <v>1393.947245352894</v>
       </c>
       <c r="Q89">
-        <v>2613.38854808766</v>
+        <v>2644.847245352894</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5014384876280665</v>
+        <v>0.5013356538561566</v>
       </c>
       <c r="T89">
         <v>6.628598816919889</v>
       </c>
       <c r="U89">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V89">
         <v>0.09</v>
       </c>
       <c r="W89">
-        <v>0.07467231428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y89">
-        <v>3.850149673625735</v>
+        <v>4.121366598674513</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1303828015059593</v>
+        <v>0.1260451261692633</v>
       </c>
       <c r="C90">
-        <v>491.5780864001545</v>
+        <v>624.9981588668697</v>
       </c>
       <c r="D90">
-        <v>6215.113879373944</v>
+        <v>6348.533951840659</v>
       </c>
       <c r="E90">
         <v>3483.986028230847</v>
@@ -8667,45 +8667,45 @@
         <v>2022.56</v>
       </c>
       <c r="M90">
-        <v>531.3579963153461</v>
+        <v>496.3906430332876</v>
       </c>
       <c r="N90">
-        <v>1491.202003684654</v>
+        <v>1526.169356966712</v>
       </c>
       <c r="O90">
-        <v>134.2081803316188</v>
+        <v>137.3552421270041</v>
       </c>
       <c r="P90">
-        <v>1356.993823353035</v>
+        <v>1388.814114839708</v>
       </c>
       <c r="Q90">
-        <v>2607.893823353035</v>
+        <v>2639.714114839708</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5389263744803993</v>
+        <v>0.5388150800079327</v>
       </c>
       <c r="T90">
         <v>7.17397013472007</v>
       </c>
       <c r="U90">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V90">
         <v>0.09</v>
       </c>
       <c r="W90">
-        <v>0.07467231428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.806397972789078</v>
+        <v>4.074532887325937</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1306136861947803</v>
+        <v>0.1262268839117366</v>
       </c>
       <c r="C91">
-        <v>411.0263779279448</v>
+        <v>545.6895739547117</v>
       </c>
       <c r="D91">
-        <v>6208.146668549163</v>
+        <v>6342.80986457593</v>
       </c>
       <c r="E91">
         <v>3557.570525878276</v>
@@ -8749,45 +8749,45 @@
         <v>2022.56</v>
       </c>
       <c r="M91">
-        <v>537.3961553643841</v>
+        <v>502.0314457950295</v>
       </c>
       <c r="N91">
-        <v>1485.163844635616</v>
+        <v>1520.528554204971</v>
       </c>
       <c r="O91">
-        <v>133.6647460172054</v>
+        <v>136.8475698784473</v>
       </c>
       <c r="P91">
-        <v>1351.49909861841</v>
+        <v>1383.680984326523</v>
       </c>
       <c r="Q91">
-        <v>2602.399098618411</v>
+        <v>2634.580984326523</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5832302407604287</v>
+        <v>0.5831089472782133</v>
       </c>
       <c r="T91">
         <v>7.818499873938462</v>
       </c>
       <c r="U91">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V91">
         <v>0.09</v>
       </c>
       <c r="W91">
-        <v>0.07467231428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.763629456240887</v>
+        <v>4.028751618929017</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1308445708836013</v>
+        <v>0.1292751416542099</v>
       </c>
       <c r="C92">
-        <v>330.4902726039345</v>
+        <v>377.621726724431</v>
       </c>
       <c r="D92">
-        <v>6201.195060872583</v>
+        <v>6248.326514993079</v>
       </c>
       <c r="E92">
         <v>3631.155023525706</v>
@@ -8831,37 +8831,37 @@
         <v>2022.56</v>
       </c>
       <c r="M92">
-        <v>543.4343144134222</v>
+        <v>530.8513653157117</v>
       </c>
       <c r="N92">
-        <v>1479.125685586578</v>
+        <v>1491.708634684288</v>
       </c>
       <c r="O92">
-        <v>133.121311702792</v>
+        <v>134.2537771215859</v>
       </c>
       <c r="P92">
-        <v>1346.004373883786</v>
+        <v>1357.454857562702</v>
       </c>
       <c r="Q92">
-        <v>2596.904373883786</v>
+        <v>2608.354857562702</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6363948802964642</v>
+        <v>0.6362615880025501</v>
       </c>
       <c r="T92">
         <v>8.591935561000534</v>
       </c>
       <c r="U92">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V92">
         <v>0.09</v>
       </c>
       <c r="W92">
-        <v>0.07467231428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.721811351171543</v>
+        <v>3.810030701903024</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1310754555724223</v>
+        <v>0.1294887493966831</v>
       </c>
       <c r="C93">
-        <v>249.9697180716057</v>
+        <v>297.521702713444</v>
       </c>
       <c r="D93">
-        <v>6194.259003987683</v>
+        <v>6241.810988629521</v>
       </c>
       <c r="E93">
         <v>3704.739521173135</v>
@@ -8913,37 +8913,37 @@
         <v>2022.56</v>
       </c>
       <c r="M93">
-        <v>549.4724734624601</v>
+        <v>536.7497138192196</v>
       </c>
       <c r="N93">
-        <v>1473.08752653754</v>
+        <v>1485.81028618078</v>
       </c>
       <c r="O93">
-        <v>132.5778773883786</v>
+        <v>133.7229257562702</v>
       </c>
       <c r="P93">
-        <v>1340.509649149161</v>
+        <v>1352.08736042451</v>
       </c>
       <c r="Q93">
-        <v>2591.409649149161</v>
+        <v>2602.98736042451</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7013738841738411</v>
+        <v>0.7012259266656286</v>
       </c>
       <c r="T93">
         <v>9.537245845187513</v>
       </c>
       <c r="U93">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V93">
         <v>0.09</v>
       </c>
       <c r="W93">
-        <v>0.07467231428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.680912325334494</v>
+        <v>3.768162232651343</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1313063402612433</v>
+        <v>0.1297023571391564</v>
       </c>
       <c r="C94">
-        <v>169.4646622084247</v>
+        <v>217.4352528530162</v>
       </c>
       <c r="D94">
-        <v>6187.338445771931</v>
+        <v>6235.309036416523</v>
       </c>
       <c r="E94">
         <v>3778.324018820564</v>
@@ -8995,37 +8995,37 @@
         <v>2022.56</v>
       </c>
       <c r="M94">
-        <v>555.5106325114981</v>
+        <v>542.6480623227275</v>
       </c>
       <c r="N94">
-        <v>1467.049367488502</v>
+        <v>1479.911937677272</v>
       </c>
       <c r="O94">
-        <v>132.0344430739652</v>
+        <v>133.1920743909545</v>
       </c>
       <c r="P94">
-        <v>1335.014924414537</v>
+        <v>1346.719863286318</v>
       </c>
       <c r="Q94">
-        <v>2585.914924414537</v>
+        <v>2597.619863286318</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7825976390205622</v>
+        <v>0.7824313499944767</v>
       </c>
       <c r="T94">
         <v>10.71888370042124</v>
       </c>
       <c r="U94">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V94">
         <v>0.09</v>
       </c>
       <c r="W94">
-        <v>0.07467231428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.640902408754771</v>
+        <v>3.727203947513829</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1315372249500643</v>
+        <v>0.1299159648816297</v>
       </c>
       <c r="C95">
-        <v>88.9750531245345</v>
+        <v>137.3623347676394</v>
       </c>
       <c r="D95">
-        <v>6180.433334335471</v>
+        <v>6228.820615978576</v>
       </c>
       <c r="E95">
         <v>3851.908516467994</v>
@@ -9077,37 +9077,37 @@
         <v>2022.56</v>
       </c>
       <c r="M95">
-        <v>561.5487915605362</v>
+        <v>548.5464108262354</v>
       </c>
       <c r="N95">
-        <v>1461.011208439464</v>
+        <v>1474.013589173765</v>
       </c>
       <c r="O95">
-        <v>131.4910087595517</v>
+        <v>132.6612230256388</v>
       </c>
       <c r="P95">
-        <v>1329.520199679912</v>
+        <v>1341.352366148126</v>
       </c>
       <c r="Q95">
-        <v>2580.420199679912</v>
+        <v>2592.252366148126</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8870281809663463</v>
+        <v>0.8868383228458526</v>
       </c>
       <c r="T95">
         <v>12.23813237143603</v>
       </c>
       <c r="U95">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V95">
         <v>0.09</v>
       </c>
       <c r="W95">
-        <v>0.07467231428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.60175292048859</v>
+        <v>3.687126485712604</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1317681096388852</v>
+        <v>0.130129572624103</v>
       </c>
       <c r="C96">
-        <v>8.500839161456497</v>
+        <v>57.30290625800444</v>
       </c>
       <c r="D96">
-        <v>6173.543618019822</v>
+        <v>6222.34568511637</v>
       </c>
       <c r="E96">
         <v>3925.493014115423</v>
@@ -9159,37 +9159,37 @@
         <v>2022.56</v>
       </c>
       <c r="M96">
-        <v>567.5869506095742</v>
+        <v>554.4447593297433</v>
       </c>
       <c r="N96">
-        <v>1454.973049390426</v>
+        <v>1468.115240670257</v>
       </c>
       <c r="O96">
-        <v>130.9475744451383</v>
+        <v>132.1303716603231</v>
       </c>
       <c r="P96">
-        <v>1324.025474945287</v>
+        <v>1335.984869009934</v>
       </c>
       <c r="Q96">
-        <v>2574.925474945288</v>
+        <v>2586.884869009934</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.026268903560725</v>
+        <v>1.026047619981021</v>
       </c>
       <c r="T96">
         <v>14.26379726612241</v>
       </c>
       <c r="U96">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V96">
         <v>0.09</v>
       </c>
       <c r="W96">
-        <v>0.07467231428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.563436400057861</v>
+        <v>3.647901735864598</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1319989943277062</v>
+        <v>0.1303431803665762</v>
       </c>
       <c r="C97">
-        <v>-71.9580311091986</v>
+        <v>-22.74307469991436</v>
       </c>
       <c r="D97">
-        <v>6166.669245396597</v>
+        <v>6215.884201805881</v>
       </c>
       <c r="E97">
         <v>3999.077511762853</v>
@@ -9241,37 +9241,37 @@
         <v>2022.56</v>
       </c>
       <c r="M97">
-        <v>573.6251096586122</v>
+        <v>560.3431078332512</v>
       </c>
       <c r="N97">
-        <v>1448.934890341388</v>
+        <v>1462.216892166749</v>
       </c>
       <c r="O97">
-        <v>130.4041401307249</v>
+        <v>131.5995202950074</v>
       </c>
       <c r="P97">
-        <v>1318.530750210663</v>
+        <v>1330.617371871741</v>
       </c>
       <c r="Q97">
-        <v>2569.430750210663</v>
+        <v>2581.517371871741</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.221205915192856</v>
+        <v>1.220940635970257</v>
       </c>
       <c r="T97">
         <v>17.09972811868335</v>
       </c>
       <c r="U97">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V97">
         <v>0.09</v>
       </c>
       <c r="W97">
-        <v>0.07467231428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.525926543215146</v>
+        <v>3.609502770223918</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1363357990165271</v>
+        <v>0.1305567881090495</v>
       </c>
       <c r="C98">
-        <v>-271.8805392000777</v>
+        <v>-102.7756499557618</v>
       </c>
       <c r="D98">
-        <v>6040.331234953146</v>
+        <v>6209.436124197462</v>
       </c>
       <c r="E98">
         <v>4072.662009410281</v>
@@ -9323,45 +9323,45 @@
         <v>2022.56</v>
       </c>
       <c r="M98">
-        <v>612.8645940461703</v>
+        <v>566.241456336759</v>
       </c>
       <c r="N98">
-        <v>1409.69540595383</v>
+        <v>1456.318543663241</v>
       </c>
       <c r="O98">
-        <v>126.8725865358447</v>
+        <v>131.0686689296917</v>
       </c>
       <c r="P98">
-        <v>1282.822819417985</v>
+        <v>1325.249874733549</v>
       </c>
       <c r="Q98">
-        <v>2533.722819417985</v>
+        <v>2576.149874733549</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.513611432641048</v>
+        <v>1.513280159954106</v>
       </c>
       <c r="T98">
         <v>21.3536243975247</v>
       </c>
       <c r="U98">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V98">
         <v>0.09</v>
       </c>
       <c r="W98">
-        <v>0.07894931428217207</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>3.300174328307877</v>
+        <v>3.571903783034086</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1366094537053482</v>
+        <v>0.1307703958515227</v>
       </c>
       <c r="C99">
-        <v>-353.2636268530468</v>
+        <v>-182.7948611857191</v>
       </c>
       <c r="D99">
-        <v>6032.532644947607</v>
+        <v>6203.001410614935</v>
       </c>
       <c r="E99">
         <v>4146.246507057711</v>
@@ -9405,45 +9405,45 @@
         <v>2022.56</v>
       </c>
       <c r="M99">
-        <v>619.2486002341512</v>
+        <v>572.1398048402671</v>
       </c>
       <c r="N99">
-        <v>1403.311399765849</v>
+        <v>1450.420195159733</v>
       </c>
       <c r="O99">
-        <v>126.2980259789264</v>
+        <v>130.537817564376</v>
       </c>
       <c r="P99">
-        <v>1277.013373786922</v>
+        <v>1319.882377595357</v>
       </c>
       <c r="Q99">
-        <v>2527.913373786922</v>
+        <v>2570.782377595357</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.000953961721373</v>
+        <v>2.000512699927193</v>
       </c>
       <c r="T99">
         <v>28.44345152892703</v>
       </c>
       <c r="U99">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V99">
         <v>0.09</v>
       </c>
       <c r="W99">
-        <v>0.07894931428217207</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y99">
-        <v>3.266151912552126</v>
+        <v>3.535080032693528</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1368831083941691</v>
+        <v>0.133481043593996</v>
       </c>
       <c r="C100">
-        <v>-434.6266031632231</v>
+        <v>-336.8914644849083</v>
       </c>
       <c r="D100">
-        <v>6024.75416628486</v>
+        <v>6122.489304963175</v>
       </c>
       <c r="E100">
         <v>4219.83100470514</v>
@@ -9487,37 +9487,37 @@
         <v>2022.56</v>
       </c>
       <c r="M100">
-        <v>625.6326064221322</v>
+        <v>598.2297394982295</v>
       </c>
       <c r="N100">
-        <v>1396.927393577868</v>
+        <v>1424.33026050177</v>
       </c>
       <c r="O100">
-        <v>125.7234654220081</v>
+        <v>128.1897234451593</v>
       </c>
       <c r="P100">
-        <v>1271.20392815586</v>
+        <v>1296.140537056611</v>
       </c>
       <c r="Q100">
-        <v>2522.10392815586</v>
+        <v>2547.040537056611</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.975639019882022</v>
+        <v>2.974977779873366</v>
       </c>
       <c r="T100">
         <v>42.62310579173167</v>
       </c>
       <c r="U100">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V100">
         <v>0.09</v>
       </c>
       <c r="W100">
-        <v>0.07894931428217207</v>
+        <v>0.07549131428217208</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.232823831811798</v>
+        <v>3.380908481240736</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1371567630829901</v>
+        <v>0.1337201313364693</v>
       </c>
       <c r="C101">
-        <v>-515.9695458264359</v>
+        <v>-417.4771971517739</v>
       </c>
       <c r="D101">
-        <v>6016.995721269077</v>
+        <v>6115.488069943739</v>
       </c>
       <c r="E101">
         <v>4293.415502352571</v>
@@ -9569,37 +9569,37 @@
         <v>2022.56</v>
       </c>
       <c r="M101">
-        <v>632.0166126101132</v>
+        <v>604.3341245951502</v>
       </c>
       <c r="N101">
-        <v>1390.543387389887</v>
+        <v>1418.22587540485</v>
       </c>
       <c r="O101">
-        <v>125.1489048650898</v>
+        <v>127.6403287864365</v>
       </c>
       <c r="P101">
-        <v>1265.394482524797</v>
+        <v>1290.585546618413</v>
       </c>
       <c r="Q101">
-        <v>2516.294482524797</v>
+        <v>2541.485546618414</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.89969419436397</v>
+        <v>5.898373019711888</v>
       </c>
       <c r="T101">
         <v>85.1620685801456</v>
       </c>
       <c r="U101">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V101">
         <v>0.09</v>
       </c>
       <c r="W101">
-        <v>0.07894931428217207</v>
+        <v>0.07549131428217208</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>3.200169045631881</v>
+        <v>3.346757890521132</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/hungary/hungary_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_oil_gas_integrated.xlsx
@@ -1133,43 +1133,43 @@
         <v>38.3787476280835</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>397.443934226628</v>
       </c>
       <c r="G2">
         <v>0.913849494034734</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0224791192339083</v>
       </c>
       <c r="I2">
         <v>0.406532606783033</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>4367</v>
       </c>
       <c r="L2">
-        <v>7648.10171937811</v>
+        <v>7570.29794712415</v>
       </c>
       <c r="M2">
         <v>6606.54976474294</v>
       </c>
       <c r="N2">
-        <v>6896.20171937811</v>
+        <v>6891.98244477158</v>
       </c>
       <c r="O2">
         <v>2991.44976474294</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>73.5844976474294</v>
       </c>
       <c r="Q2">
         <v>0.118179379061027</v>
       </c>
       <c r="R2">
-        <v>0.110050444831616</v>
+        <v>0.110163952574089</v>
       </c>
       <c r="S2">
         <v>0.0715783142821721</v>
@@ -1191,13 +1191,13 @@
         <v>0.150101692839244</v>
       </c>
       <c r="X2">
-        <v>0.110050444831616</v>
+        <v>0.110641029728553</v>
       </c>
       <c r="Y2">
         <v>1.51771671855847</v>
       </c>
       <c r="Z2">
-        <v>0.934922259086021</v>
+        <v>0.943515988942266</v>
       </c>
       <c r="AA2">
         <v>2984.5</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1100504448316159</v>
+        <v>0.1101639525740892</v>
       </c>
       <c r="C2">
-        <v>7648.101719378108</v>
+        <v>7570.297947124152</v>
       </c>
       <c r="D2">
-        <v>6896.201719378108</v>
+        <v>6891.982444771582</v>
       </c>
       <c r="E2">
-        <v>-2991.449764742942</v>
+        <v>-2917.865267095513</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>73.58449764742942</v>
       </c>
       <c r="G2">
         <v>751.9</v>
@@ -1451,28 +1451,28 @@
         <v>2022.56</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.088919029386184</v>
       </c>
       <c r="N2">
-        <v>2022.56</v>
+        <v>2017.471080970614</v>
       </c>
       <c r="O2">
-        <v>182.0304</v>
+        <v>181.5723972873552</v>
       </c>
       <c r="P2">
-        <v>1840.5296</v>
+        <v>1835.898683683258</v>
       </c>
       <c r="Q2">
-        <v>3091.4296</v>
+        <v>3086.798683683259</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1100504448316159</v>
+        <v>0.110641029728553</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9435159889422664</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>397.4439342266284</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1101639525740892</v>
+        <v>0.1102774603165625</v>
       </c>
       <c r="C3">
-        <v>7570.297947124152</v>
+        <v>7492.49933463602</v>
       </c>
       <c r="D3">
-        <v>6891.982444771582</v>
+        <v>6887.768329930879</v>
       </c>
       <c r="E3">
-        <v>-2917.865267095513</v>
+        <v>-2844.280769448083</v>
       </c>
       <c r="F3">
-        <v>73.58449764742942</v>
+        <v>147.1689952948588</v>
       </c>
       <c r="G3">
         <v>751.9</v>
@@ -1533,28 +1533,28 @@
         <v>2022.56</v>
       </c>
       <c r="M3">
-        <v>5.088919029386184</v>
+        <v>10.17783805877237</v>
       </c>
       <c r="N3">
-        <v>2017.471080970614</v>
+        <v>2012.382161941228</v>
       </c>
       <c r="O3">
-        <v>181.5723972873552</v>
+        <v>181.1143945747105</v>
       </c>
       <c r="P3">
-        <v>1835.898683683258</v>
+        <v>1831.267767366517</v>
       </c>
       <c r="Q3">
-        <v>3086.798683683259</v>
+        <v>3082.167767366517</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.110641029728553</v>
+        <v>0.1112436673784888</v>
       </c>
       <c r="T3">
-        <v>0.9435159889422664</v>
+        <v>0.9522851010404759</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>397.4439342266284</v>
+        <v>198.7219671133142</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1102774603165625</v>
+        <v>0.1103909680590357</v>
       </c>
       <c r="C4">
-        <v>7492.49933463602</v>
+        <v>7414.705872454653</v>
       </c>
       <c r="D4">
-        <v>6887.768329930879</v>
+        <v>6883.559365396942</v>
       </c>
       <c r="E4">
-        <v>-2844.280769448083</v>
+        <v>-2770.696271800654</v>
       </c>
       <c r="F4">
-        <v>147.1689952948588</v>
+        <v>220.7534929422882</v>
       </c>
       <c r="G4">
         <v>751.9</v>
@@ -1615,28 +1615,28 @@
         <v>2022.56</v>
       </c>
       <c r="M4">
-        <v>10.17783805877237</v>
+        <v>15.26675708815855</v>
       </c>
       <c r="N4">
-        <v>2012.382161941228</v>
+        <v>2007.293242911841</v>
       </c>
       <c r="O4">
-        <v>181.1143945747105</v>
+        <v>180.6563918620657</v>
       </c>
       <c r="P4">
-        <v>1831.267767366517</v>
+        <v>1826.636851049776</v>
       </c>
       <c r="Q4">
-        <v>3082.167767366517</v>
+        <v>3077.536851049776</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1112436673784888</v>
+        <v>0.11185873054698</v>
       </c>
       <c r="T4">
-        <v>0.9522851010404759</v>
+        <v>0.9612350195736999</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>198.7219671133142</v>
+        <v>132.4813114088761</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1103909680590357</v>
+        <v>0.1105044758015089</v>
       </c>
       <c r="C5">
-        <v>7414.705872454653</v>
+        <v>7336.917551144095</v>
       </c>
       <c r="D5">
-        <v>6883.559365396942</v>
+        <v>6879.355541733813</v>
       </c>
       <c r="E5">
-        <v>-2770.696271800654</v>
+        <v>-2697.111774153224</v>
       </c>
       <c r="F5">
-        <v>220.7534929422882</v>
+        <v>294.3379905897177</v>
       </c>
       <c r="G5">
         <v>751.9</v>
@@ -1697,28 +1697,28 @@
         <v>2022.56</v>
       </c>
       <c r="M5">
-        <v>15.26675708815855</v>
+        <v>20.35567611754474</v>
       </c>
       <c r="N5">
-        <v>2007.293242911841</v>
+        <v>2002.204323882455</v>
       </c>
       <c r="O5">
-        <v>180.6563918620657</v>
+        <v>180.198389149421</v>
       </c>
       <c r="P5">
-        <v>1826.636851049776</v>
+        <v>1822.005934733034</v>
       </c>
       <c r="Q5">
-        <v>3077.536851049776</v>
+        <v>3072.905934733034</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.11185873054698</v>
+        <v>0.1124866075314813</v>
       </c>
       <c r="T5">
-        <v>0.9612350195736999</v>
+        <v>0.9703713947430327</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>132.4813114088761</v>
+        <v>99.36098355665709</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1105044758015089</v>
+        <v>0.1106179835439822</v>
       </c>
       <c r="C6">
-        <v>7336.917551144095</v>
+        <v>7259.134361291429</v>
       </c>
       <c r="D6">
-        <v>6879.355541733813</v>
+        <v>6875.156849528576</v>
       </c>
       <c r="E6">
-        <v>-2697.111774153224</v>
+        <v>-2623.527276505795</v>
       </c>
       <c r="F6">
-        <v>294.3379905897177</v>
+        <v>367.9224882371471</v>
       </c>
       <c r="G6">
         <v>751.9</v>
@@ -1779,28 +1779,28 @@
         <v>2022.56</v>
       </c>
       <c r="M6">
-        <v>20.35567611754474</v>
+        <v>25.44459514693092</v>
       </c>
       <c r="N6">
-        <v>2002.204323882455</v>
+        <v>1997.115404853069</v>
       </c>
       <c r="O6">
-        <v>180.198389149421</v>
+        <v>179.7403864367762</v>
       </c>
       <c r="P6">
-        <v>1822.005934733034</v>
+        <v>1817.375018416293</v>
       </c>
       <c r="Q6">
-        <v>3072.905934733034</v>
+        <v>3068.275018416293</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1124866075314813</v>
+        <v>0.1131277029788143</v>
       </c>
       <c r="T6">
-        <v>0.9703713947430327</v>
+        <v>0.9797001146527726</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>99.36098355665709</v>
+        <v>79.48878684532566</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1106179835439822</v>
+        <v>0.1107314912864555</v>
       </c>
       <c r="C7">
-        <v>7259.134361291429</v>
+        <v>7181.356293506706</v>
       </c>
       <c r="D7">
-        <v>6875.156849528576</v>
+        <v>6870.963279391282</v>
       </c>
       <c r="E7">
-        <v>-2623.527276505795</v>
+        <v>-2549.942778858366</v>
       </c>
       <c r="F7">
-        <v>367.9224882371471</v>
+        <v>441.5069858845765</v>
       </c>
       <c r="G7">
         <v>751.9</v>
@@ -1861,28 +1861,28 @@
         <v>2022.56</v>
       </c>
       <c r="M7">
-        <v>25.44459514693092</v>
+        <v>30.53351417631711</v>
       </c>
       <c r="N7">
-        <v>1997.115404853069</v>
+        <v>1992.026485823683</v>
       </c>
       <c r="O7">
-        <v>179.7403864367762</v>
+        <v>179.2823837241314</v>
       </c>
       <c r="P7">
-        <v>1817.375018416293</v>
+        <v>1812.744102099551</v>
       </c>
       <c r="Q7">
-        <v>3068.275018416293</v>
+        <v>3063.644102099552</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1131277029788143</v>
+        <v>0.113782438754814</v>
       </c>
       <c r="T7">
-        <v>0.9797001146527726</v>
+        <v>0.9892273179648475</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>79.48878684532566</v>
+        <v>66.24065570443805</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1107314912864555</v>
+        <v>0.1108449990289288</v>
       </c>
       <c r="C8">
-        <v>7181.356293506706</v>
+        <v>7103.583338422868</v>
       </c>
       <c r="D8">
-        <v>6870.963279391282</v>
+        <v>6866.774821954875</v>
       </c>
       <c r="E8">
-        <v>-2549.942778858366</v>
+        <v>-2476.358281210936</v>
       </c>
       <c r="F8">
-        <v>441.5069858845765</v>
+        <v>515.0914835320059</v>
       </c>
       <c r="G8">
         <v>751.9</v>
@@ -1943,28 +1943,28 @@
         <v>2022.56</v>
       </c>
       <c r="M8">
-        <v>30.5335141763171</v>
+        <v>35.62243320570329</v>
       </c>
       <c r="N8">
-        <v>1992.026485823683</v>
+        <v>1986.937566794297</v>
       </c>
       <c r="O8">
-        <v>179.2823837241314</v>
+        <v>178.8243810114867</v>
       </c>
       <c r="P8">
-        <v>1812.744102099551</v>
+        <v>1808.11318578281</v>
       </c>
       <c r="Q8">
-        <v>3063.644102099552</v>
+        <v>3059.01318578281</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.113782438754814</v>
+        <v>0.1144512548700825</v>
       </c>
       <c r="T8">
-        <v>0.9892273179648475</v>
+        <v>0.9989594073696549</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.24065570443807</v>
+        <v>56.77770488951833</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1108449990289288</v>
+        <v>0.1109585067714021</v>
       </c>
       <c r="C9">
-        <v>7103.583338422868</v>
+        <v>7025.815486695691</v>
       </c>
       <c r="D9">
-        <v>6866.774821954875</v>
+        <v>6862.591467875127</v>
       </c>
       <c r="E9">
-        <v>-2476.358281210936</v>
+        <v>-2402.773783563507</v>
       </c>
       <c r="F9">
-        <v>515.091483532006</v>
+        <v>588.6759811794353</v>
       </c>
       <c r="G9">
         <v>751.9</v>
@@ -2025,28 +2025,28 @@
         <v>2022.56</v>
       </c>
       <c r="M9">
-        <v>35.6224332057033</v>
+        <v>40.71135223508947</v>
       </c>
       <c r="N9">
-        <v>1986.937566794297</v>
+        <v>1981.848647764911</v>
       </c>
       <c r="O9">
-        <v>178.8243810114867</v>
+        <v>178.3663782988419</v>
       </c>
       <c r="P9">
-        <v>1808.11318578281</v>
+        <v>1803.482269466069</v>
       </c>
       <c r="Q9">
-        <v>3059.01318578281</v>
+        <v>3054.382269466068</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1144512548700825</v>
+        <v>0.1151346104661177</v>
       </c>
       <c r="T9">
-        <v>0.9989594073696552</v>
+        <v>1.008903063935437</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.77770488951833</v>
+        <v>49.68049177832854</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1109585067714021</v>
+        <v>0.1110720145138753</v>
       </c>
       <c r="C10">
-        <v>7025.815486695691</v>
+        <v>6948.052729003701</v>
       </c>
       <c r="D10">
-        <v>6862.591467875127</v>
+        <v>6858.413207830566</v>
       </c>
       <c r="E10">
-        <v>-2402.773783563507</v>
+        <v>-2329.189285916077</v>
       </c>
       <c r="F10">
-        <v>588.6759811794353</v>
+        <v>662.2604788268648</v>
       </c>
       <c r="G10">
         <v>751.9</v>
@@ -2107,28 +2107,28 @@
         <v>2022.56</v>
       </c>
       <c r="M10">
-        <v>40.71135223508947</v>
+        <v>45.80027126447565</v>
       </c>
       <c r="N10">
-        <v>1981.848647764911</v>
+        <v>1976.759728735524</v>
       </c>
       <c r="O10">
-        <v>178.3663782988419</v>
+        <v>177.9083755861972</v>
       </c>
       <c r="P10">
-        <v>1803.482269466069</v>
+        <v>1798.851353149327</v>
       </c>
       <c r="Q10">
-        <v>3054.382269466068</v>
+        <v>3049.751353149327</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1151346104661177</v>
+        <v>0.1158329848664613</v>
       </c>
       <c r="T10">
-        <v>1.008903063935437</v>
+        <v>1.019065262403763</v>
       </c>
       <c r="U10">
         <v>0.06915748822216712</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.68049177832854</v>
+        <v>44.16043713629204</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1110720145138753</v>
+        <v>0.1111855222563486</v>
       </c>
       <c r="C11">
-        <v>6948.052729003701</v>
+        <v>6870.295056048111</v>
       </c>
       <c r="D11">
-        <v>6858.413207830566</v>
+        <v>6854.240032522405</v>
       </c>
       <c r="E11">
-        <v>-2329.189285916077</v>
+        <v>-2255.604788268648</v>
       </c>
       <c r="F11">
-        <v>662.2604788268648</v>
+        <v>735.8449764742941</v>
       </c>
       <c r="G11">
         <v>751.9</v>
@@ -2189,28 +2189,28 @@
         <v>2022.56</v>
       </c>
       <c r="M11">
-        <v>45.80027126447565</v>
+        <v>50.88919029386184</v>
       </c>
       <c r="N11">
-        <v>1976.759728735524</v>
+        <v>1971.670809706138</v>
       </c>
       <c r="O11">
-        <v>177.9083755861972</v>
+        <v>177.4503728735524</v>
       </c>
       <c r="P11">
-        <v>1798.851353149327</v>
+        <v>1794.220436832586</v>
       </c>
       <c r="Q11">
-        <v>3049.751353149327</v>
+        <v>3045.120436832586</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1158329848664613</v>
+        <v>0.1165468786979237</v>
       </c>
       <c r="T11">
-        <v>1.019065262403763</v>
+        <v>1.029453287504719</v>
       </c>
       <c r="U11">
         <v>0.06915748822216712</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.16043713629204</v>
+        <v>39.74439342266284</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1111855222563486</v>
+        <v>0.1112990299988218</v>
       </c>
       <c r="C12">
-        <v>6870.29505604811</v>
+        <v>6792.542458552757</v>
       </c>
       <c r="D12">
-        <v>6854.240032522405</v>
+        <v>6850.071932674481</v>
       </c>
       <c r="E12">
-        <v>-2255.604788268648</v>
+        <v>-2182.020290621218</v>
       </c>
       <c r="F12">
-        <v>735.8449764742942</v>
+        <v>809.4294741217236</v>
       </c>
       <c r="G12">
         <v>751.9</v>
@@ -2271,28 +2271,28 @@
         <v>2022.56</v>
       </c>
       <c r="M12">
-        <v>50.88919029386184</v>
+        <v>55.97810932324803</v>
       </c>
       <c r="N12">
-        <v>1971.670809706138</v>
+        <v>1966.581890676752</v>
       </c>
       <c r="O12">
-        <v>177.4503728735524</v>
+        <v>176.9923701609077</v>
       </c>
       <c r="P12">
-        <v>1794.220436832586</v>
+        <v>1789.589520515844</v>
       </c>
       <c r="Q12">
-        <v>3045.120436832586</v>
+        <v>3040.489520515845</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1165468786979237</v>
+        <v>0.1172768150873965</v>
       </c>
       <c r="T12">
-        <v>1.029453287504719</v>
+        <v>1.040074751371988</v>
       </c>
       <c r="U12">
         <v>0.06915748822216712</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.74439342266283</v>
+        <v>36.1312667478753</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1112990299988218</v>
+        <v>0.1114125377412951</v>
       </c>
       <c r="C13">
-        <v>6792.542458552757</v>
+        <v>6714.794927264025</v>
       </c>
       <c r="D13">
-        <v>6850.071932674481</v>
+        <v>6845.908899033178</v>
       </c>
       <c r="E13">
-        <v>-2182.020290621218</v>
+        <v>-2108.435792973789</v>
       </c>
       <c r="F13">
-        <v>809.4294741217236</v>
+        <v>883.0139717691529</v>
       </c>
       <c r="G13">
         <v>751.9</v>
@@ -2353,28 +2353,28 @@
         <v>2022.56</v>
       </c>
       <c r="M13">
-        <v>55.97810932324803</v>
+        <v>61.0670283526342</v>
       </c>
       <c r="N13">
-        <v>1966.581890676752</v>
+        <v>1961.492971647366</v>
       </c>
       <c r="O13">
-        <v>176.9923701609077</v>
+        <v>176.5343674482629</v>
       </c>
       <c r="P13">
-        <v>1789.589520515844</v>
+        <v>1784.958604199103</v>
       </c>
       <c r="Q13">
-        <v>3040.489520515845</v>
+        <v>3035.858604199103</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1172768150873965</v>
+        <v>0.1180233409402664</v>
       </c>
       <c r="T13">
-        <v>1.040074751371988</v>
+        <v>1.050937612145332</v>
       </c>
       <c r="U13">
         <v>0.06915748822216712</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.1312667478753</v>
+        <v>33.12032785221903</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1114125377412951</v>
+        <v>0.1115260454837683</v>
       </c>
       <c r="C14">
-        <v>6714.794927264025</v>
+        <v>6637.052452950777</v>
       </c>
       <c r="D14">
-        <v>6845.908899033178</v>
+        <v>6841.75092236736</v>
       </c>
       <c r="E14">
-        <v>-2108.435792973789</v>
+        <v>-2034.85129532636</v>
       </c>
       <c r="F14">
-        <v>883.0139717691529</v>
+        <v>956.5984694165825</v>
       </c>
       <c r="G14">
         <v>751.9</v>
@@ -2435,28 +2435,28 @@
         <v>2022.56</v>
       </c>
       <c r="M14">
-        <v>61.0670283526342</v>
+        <v>66.1559473820204</v>
       </c>
       <c r="N14">
-        <v>1961.492971647366</v>
+        <v>1956.404052617979</v>
       </c>
       <c r="O14">
-        <v>176.5343674482629</v>
+        <v>176.0763647356181</v>
       </c>
       <c r="P14">
-        <v>1784.958604199103</v>
+        <v>1780.327687882361</v>
       </c>
       <c r="Q14">
-        <v>3035.858604199103</v>
+        <v>3031.227687882361</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1180233409402664</v>
+        <v>0.1187870283069954</v>
       </c>
       <c r="T14">
-        <v>1.050937612145332</v>
+        <v>1.062050193855994</v>
       </c>
       <c r="U14">
         <v>0.06915748822216712</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.12032785221903</v>
+        <v>30.57261032512525</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1115260454837683</v>
+        <v>0.1116395532262416</v>
       </c>
       <c r="C15">
-        <v>6637.052452950777</v>
+        <v>6559.315026404293</v>
       </c>
       <c r="D15">
-        <v>6841.75092236736</v>
+        <v>6837.597993468306</v>
       </c>
       <c r="E15">
-        <v>-2034.85129532636</v>
+        <v>-1961.26679767893</v>
       </c>
       <c r="F15">
-        <v>956.5984694165825</v>
+        <v>1030.182967064012</v>
       </c>
       <c r="G15">
         <v>751.9</v>
@@ -2517,28 +2517,28 @@
         <v>2022.56</v>
       </c>
       <c r="M15">
-        <v>66.1559473820204</v>
+        <v>71.24486641140659</v>
       </c>
       <c r="N15">
-        <v>1956.404052617979</v>
+        <v>1951.315133588593</v>
       </c>
       <c r="O15">
-        <v>176.0763647356181</v>
+        <v>175.6183620229734</v>
       </c>
       <c r="P15">
-        <v>1780.327687882361</v>
+        <v>1775.69677156562</v>
       </c>
       <c r="Q15">
-        <v>3031.227687882361</v>
+        <v>3026.59677156562</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1187870283069954</v>
+        <v>0.1195684758450437</v>
       </c>
       <c r="T15">
-        <v>1.062050193855994</v>
+        <v>1.073421207699462</v>
       </c>
       <c r="U15">
         <v>0.06915748822216712</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.57261032512525</v>
+        <v>28.38885244475916</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1116395532262416</v>
+        <v>0.1117530609687149</v>
       </c>
       <c r="C16">
-        <v>6559.315026404293</v>
+        <v>6481.582638438198</v>
       </c>
       <c r="D16">
-        <v>6837.597993468306</v>
+        <v>6833.45010314964</v>
       </c>
       <c r="E16">
-        <v>-1961.26679767893</v>
+        <v>-1887.682300031501</v>
       </c>
       <c r="F16">
-        <v>1030.182967064012</v>
+        <v>1103.767464711441</v>
       </c>
       <c r="G16">
         <v>751.9</v>
@@ -2599,28 +2599,28 @@
         <v>2022.56</v>
       </c>
       <c r="M16">
-        <v>71.24486641140659</v>
+        <v>76.33378544079277</v>
       </c>
       <c r="N16">
-        <v>1951.315133588593</v>
+        <v>1946.226214559207</v>
       </c>
       <c r="O16">
-        <v>175.6183620229734</v>
+        <v>175.1603593103286</v>
       </c>
       <c r="P16">
-        <v>1775.69677156562</v>
+        <v>1771.065855248879</v>
       </c>
       <c r="Q16">
-        <v>3026.59677156562</v>
+        <v>3021.965855248879</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1195684758450437</v>
+        <v>0.1203683103839872</v>
       </c>
       <c r="T16">
-        <v>1.073421207699462</v>
+        <v>1.085059774809835</v>
       </c>
       <c r="U16">
         <v>0.06915748822216712</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.38885244475916</v>
+        <v>26.49626228177522</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1117530609687149</v>
+        <v>0.1118665687111882</v>
       </c>
       <c r="C17">
-        <v>6481.582638438199</v>
+        <v>6403.85527988839</v>
       </c>
       <c r="D17">
-        <v>6833.45010314964</v>
+        <v>6829.307242247261</v>
       </c>
       <c r="E17">
-        <v>-1887.682300031501</v>
+        <v>-1814.097802384071</v>
       </c>
       <c r="F17">
-        <v>1103.767464711441</v>
+        <v>1177.351962358871</v>
       </c>
       <c r="G17">
         <v>751.9</v>
@@ -2681,28 +2681,28 @@
         <v>2022.56</v>
       </c>
       <c r="M17">
-        <v>76.33378544079275</v>
+        <v>81.42270447017894</v>
       </c>
       <c r="N17">
-        <v>1946.226214559207</v>
+        <v>1941.137295529821</v>
       </c>
       <c r="O17">
-        <v>175.1603593103286</v>
+        <v>174.7023565976839</v>
       </c>
       <c r="P17">
-        <v>1771.065855248879</v>
+        <v>1766.434938932137</v>
       </c>
       <c r="Q17">
-        <v>3021.965855248879</v>
+        <v>3017.334938932137</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1203683103839872</v>
+        <v>0.1211871886024293</v>
       </c>
       <c r="T17">
-        <v>1.085059774809835</v>
+        <v>1.096975450660931</v>
       </c>
       <c r="U17">
         <v>0.06915748822216712</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.49626228177523</v>
+        <v>24.84024588916427</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1118665687111882</v>
+        <v>0.1119800764536614</v>
       </c>
       <c r="C18">
-        <v>6403.85527988839</v>
+        <v>6326.132941612984</v>
       </c>
       <c r="D18">
-        <v>6829.307242247261</v>
+        <v>6825.169401619284</v>
       </c>
       <c r="E18">
-        <v>-1814.097802384071</v>
+        <v>-1740.513304736642</v>
       </c>
       <c r="F18">
-        <v>1177.351962358871</v>
+        <v>1250.9364600063</v>
       </c>
       <c r="G18">
         <v>751.9</v>
@@ -2763,28 +2763,28 @@
         <v>2022.56</v>
       </c>
       <c r="M18">
-        <v>81.42270447017894</v>
+        <v>86.51162349956513</v>
       </c>
       <c r="N18">
-        <v>1941.137295529821</v>
+        <v>1936.048376500435</v>
       </c>
       <c r="O18">
-        <v>174.7023565976839</v>
+        <v>174.2443538850391</v>
       </c>
       <c r="P18">
-        <v>1766.434938932137</v>
+        <v>1761.804022615396</v>
       </c>
       <c r="Q18">
-        <v>3017.334938932137</v>
+        <v>3012.704022615396</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1211871886024293</v>
+        <v>0.1220257988261352</v>
       </c>
       <c r="T18">
-        <v>1.096975450660931</v>
+        <v>1.109178251231331</v>
       </c>
       <c r="U18">
         <v>0.06915748822216712</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.84024588916427</v>
+        <v>23.37905495450755</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1119800764536614</v>
+        <v>0.1120935841961347</v>
       </c>
       <c r="C19">
-        <v>6326.132941612984</v>
+        <v>6248.415614492229</v>
       </c>
       <c r="D19">
-        <v>6825.169401619284</v>
+        <v>6821.036572145959</v>
       </c>
       <c r="E19">
-        <v>-1740.513304736642</v>
+        <v>-1666.928807089212</v>
       </c>
       <c r="F19">
-        <v>1250.9364600063</v>
+        <v>1324.52095765373</v>
       </c>
       <c r="G19">
         <v>751.9</v>
@@ -2845,28 +2845,28 @@
         <v>2022.56</v>
       </c>
       <c r="M19">
-        <v>86.51162349956513</v>
+        <v>91.60054252895134</v>
       </c>
       <c r="N19">
-        <v>1936.048376500435</v>
+        <v>1930.959457471049</v>
       </c>
       <c r="O19">
-        <v>174.2443538850391</v>
+        <v>173.7863511723944</v>
       </c>
       <c r="P19">
-        <v>1761.804022615396</v>
+        <v>1757.173106298654</v>
       </c>
       <c r="Q19">
-        <v>3012.704022615396</v>
+        <v>3008.073106298654</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1220257988261352</v>
+        <v>0.1228848629577362</v>
       </c>
       <c r="T19">
-        <v>1.109178251231331</v>
+        <v>1.121678681083936</v>
       </c>
       <c r="U19">
         <v>0.06915748822216712</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.37905495450755</v>
+        <v>22.08021856814601</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1120935841961347</v>
+        <v>0.112207091938608</v>
       </c>
       <c r="C20">
-        <v>6248.415614492229</v>
+        <v>6170.703289428458</v>
       </c>
       <c r="D20">
-        <v>6821.036572145959</v>
+        <v>6816.908744729617</v>
       </c>
       <c r="E20">
-        <v>-1666.928807089213</v>
+        <v>-1593.344309441783</v>
       </c>
       <c r="F20">
-        <v>1324.52095765373</v>
+        <v>1398.105455301159</v>
       </c>
       <c r="G20">
         <v>751.9</v>
@@ -2927,28 +2927,28 @@
         <v>2022.56</v>
       </c>
       <c r="M20">
-        <v>91.60054252895131</v>
+        <v>96.6894615583375</v>
       </c>
       <c r="N20">
-        <v>1930.959457471049</v>
+        <v>1925.870538441662</v>
       </c>
       <c r="O20">
-        <v>173.7863511723944</v>
+        <v>173.3283484597496</v>
       </c>
       <c r="P20">
-        <v>1757.173106298654</v>
+        <v>1752.542189981913</v>
       </c>
       <c r="Q20">
-        <v>3008.073106298654</v>
+        <v>3003.442189981913</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1228848629577362</v>
+        <v>0.1237651385493769</v>
       </c>
       <c r="T20">
-        <v>1.121678681083936</v>
+        <v>1.134487763525494</v>
       </c>
       <c r="U20">
         <v>0.06915748822216712</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.08021856814602</v>
+        <v>20.91810180140149</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.112207091938608</v>
+        <v>0.1123205996810812</v>
       </c>
       <c r="C21">
-        <v>6170.703289428458</v>
+        <v>6092.995957346007</v>
       </c>
       <c r="D21">
-        <v>6816.908744729617</v>
+        <v>6812.785910294596</v>
       </c>
       <c r="E21">
-        <v>-1593.344309441783</v>
+        <v>-1519.759811794354</v>
       </c>
       <c r="F21">
-        <v>1398.105455301159</v>
+        <v>1471.689952948588</v>
       </c>
       <c r="G21">
         <v>751.9</v>
@@ -3009,28 +3009,28 @@
         <v>2022.56</v>
       </c>
       <c r="M21">
-        <v>96.6894615583375</v>
+        <v>101.7783805877237</v>
       </c>
       <c r="N21">
-        <v>1925.870538441662</v>
+        <v>1920.781619412276</v>
       </c>
       <c r="O21">
-        <v>173.3283484597496</v>
+        <v>172.8703457471049</v>
       </c>
       <c r="P21">
-        <v>1752.542189981913</v>
+        <v>1747.911273665171</v>
       </c>
       <c r="Q21">
-        <v>3003.442189981913</v>
+        <v>2998.811273665171</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1237651385493769</v>
+        <v>0.1246674210308085</v>
       </c>
       <c r="T21">
-        <v>1.134487763525494</v>
+        <v>1.147617073028091</v>
       </c>
       <c r="U21">
         <v>0.06915748822216712</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.91810180140149</v>
+        <v>19.87219671133142</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1123205996810812</v>
+        <v>0.1124341074235545</v>
       </c>
       <c r="C22">
-        <v>6092.995957346007</v>
+        <v>6015.293609191159</v>
       </c>
       <c r="D22">
-        <v>6812.785910294596</v>
+        <v>6808.668059787177</v>
       </c>
       <c r="E22">
-        <v>-1519.759811794354</v>
+        <v>-1446.175314146924</v>
       </c>
       <c r="F22">
-        <v>1471.689952948588</v>
+        <v>1545.274450596018</v>
       </c>
       <c r="G22">
         <v>751.9</v>
@@ -3091,28 +3091,28 @@
         <v>2022.56</v>
       </c>
       <c r="M22">
-        <v>101.7783805877237</v>
+        <v>106.8672996171099</v>
       </c>
       <c r="N22">
-        <v>1920.781619412276</v>
+        <v>1915.69270038289</v>
       </c>
       <c r="O22">
-        <v>172.8703457471049</v>
+        <v>172.4123430344601</v>
       </c>
       <c r="P22">
-        <v>1747.911273665171</v>
+        <v>1743.28035734843</v>
       </c>
       <c r="Q22">
-        <v>2998.811273665171</v>
+        <v>2994.18035734843</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1246674210308085</v>
+        <v>0.1255925461067068</v>
       </c>
       <c r="T22">
-        <v>1.147617073028091</v>
+        <v>1.161078770113032</v>
       </c>
       <c r="U22">
         <v>0.06915748822216712</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.87219671133142</v>
+        <v>18.92590162983944</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1124341074235545</v>
+        <v>0.1125476151660278</v>
       </c>
       <c r="C23">
-        <v>6015.29360919116</v>
+        <v>5937.596235932067</v>
       </c>
       <c r="D23">
-        <v>6808.668059787177</v>
+        <v>6804.555184175515</v>
       </c>
       <c r="E23">
-        <v>-1446.175314146924</v>
+        <v>-1372.590816499495</v>
       </c>
       <c r="F23">
-        <v>1545.274450596018</v>
+        <v>1618.858948243447</v>
       </c>
       <c r="G23">
         <v>751.9</v>
@@ -3173,28 +3173,28 @@
         <v>2022.56</v>
       </c>
       <c r="M23">
-        <v>106.8672996171099</v>
+        <v>111.9562186464961</v>
       </c>
       <c r="N23">
-        <v>1915.69270038289</v>
+        <v>1910.603781353504</v>
       </c>
       <c r="O23">
-        <v>172.4123430344601</v>
+        <v>171.9543403218153</v>
       </c>
       <c r="P23">
-        <v>1743.28035734843</v>
+        <v>1738.649441031688</v>
       </c>
       <c r="Q23">
-        <v>2994.18035734843</v>
+        <v>2989.549441031689</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1255925461067068</v>
+        <v>0.1265413923383973</v>
       </c>
       <c r="T23">
-        <v>1.161078770113032</v>
+        <v>1.1748856389181</v>
       </c>
       <c r="U23">
         <v>0.06915748822216712</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.92590162983944</v>
+        <v>18.06563337393765</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1125476151660278</v>
+        <v>0.112661122908501</v>
       </c>
       <c r="C24">
-        <v>5937.596235932067</v>
+        <v>5859.903828558701</v>
       </c>
       <c r="D24">
-        <v>6804.555184175515</v>
+        <v>6800.447274449578</v>
       </c>
       <c r="E24">
-        <v>-1372.590816499495</v>
+        <v>-1299.006318852066</v>
       </c>
       <c r="F24">
-        <v>1618.858948243447</v>
+        <v>1692.443445890877</v>
       </c>
       <c r="G24">
         <v>751.9</v>
@@ -3255,28 +3255,28 @@
         <v>2022.56</v>
       </c>
       <c r="M24">
-        <v>111.9562186464961</v>
+        <v>117.0451376758822</v>
       </c>
       <c r="N24">
-        <v>1910.603781353504</v>
+        <v>1905.514862324118</v>
       </c>
       <c r="O24">
-        <v>171.9543403218153</v>
+        <v>171.4963376091706</v>
       </c>
       <c r="P24">
-        <v>1738.649441031688</v>
+        <v>1734.018524714947</v>
       </c>
       <c r="Q24">
-        <v>2989.549441031689</v>
+        <v>2984.918524714947</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1265413923383973</v>
+        <v>0.1275148839267551</v>
       </c>
       <c r="T24">
-        <v>1.1748856389181</v>
+        <v>1.189051127692131</v>
       </c>
       <c r="U24">
         <v>0.06915748822216712</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.06563337393765</v>
+        <v>17.28017105333167</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.112661122908501</v>
+        <v>0.1127746306509743</v>
       </c>
       <c r="C25">
-        <v>5859.903828558701</v>
+        <v>5782.216378082771</v>
       </c>
       <c r="D25">
-        <v>6800.447274449578</v>
+        <v>6796.344321621078</v>
       </c>
       <c r="E25">
-        <v>-1299.006318852066</v>
+        <v>-1225.421821204636</v>
       </c>
       <c r="F25">
-        <v>1692.443445890877</v>
+        <v>1766.027943538306</v>
       </c>
       <c r="G25">
         <v>751.9</v>
@@ -3337,28 +3337,28 @@
         <v>2022.56</v>
       </c>
       <c r="M25">
-        <v>117.0451376758822</v>
+        <v>122.1340567052684</v>
       </c>
       <c r="N25">
-        <v>1905.514862324118</v>
+        <v>1900.425943294731</v>
       </c>
       <c r="O25">
-        <v>171.4963376091706</v>
+        <v>171.0383348965258</v>
       </c>
       <c r="P25">
-        <v>1734.018524714947</v>
+        <v>1729.387608398206</v>
       </c>
       <c r="Q25">
-        <v>2984.918524714947</v>
+        <v>2980.287608398206</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1275148839267551</v>
+        <v>0.1285139937148066</v>
       </c>
       <c r="T25">
-        <v>1.189051127692131</v>
+        <v>1.20358939248653</v>
       </c>
       <c r="U25">
         <v>0.06915748822216712</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.28017105333167</v>
+        <v>16.56016392610951</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1127746306509743</v>
+        <v>0.1128881383934476</v>
       </c>
       <c r="C26">
-        <v>5782.216378082772</v>
+        <v>5704.533875537667</v>
       </c>
       <c r="D26">
-        <v>6796.344321621078</v>
+        <v>6792.246316723403</v>
       </c>
       <c r="E26">
-        <v>-1225.421821204636</v>
+        <v>-1151.837323557207</v>
       </c>
       <c r="F26">
-        <v>1766.027943538306</v>
+        <v>1839.612441185735</v>
       </c>
       <c r="G26">
         <v>751.9</v>
@@ -3419,28 +3419,28 @@
         <v>2022.56</v>
       </c>
       <c r="M26">
-        <v>122.1340567052684</v>
+        <v>127.2229757346546</v>
       </c>
       <c r="N26">
-        <v>1900.425943294731</v>
+        <v>1895.337024265345</v>
       </c>
       <c r="O26">
-        <v>171.0383348965258</v>
+        <v>170.5803321838811</v>
       </c>
       <c r="P26">
-        <v>1729.387608398206</v>
+        <v>1724.756692081464</v>
       </c>
       <c r="Q26">
-        <v>2980.287608398206</v>
+        <v>2975.656692081464</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1285139937148066</v>
+        <v>0.1295397464305394</v>
       </c>
       <c r="T26">
-        <v>1.20358939248653</v>
+        <v>1.218515344342114</v>
       </c>
       <c r="U26">
         <v>0.06915748822216712</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.56016392610952</v>
+        <v>15.89775736906514</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1128881383934476</v>
+        <v>0.1130016461359208</v>
       </c>
       <c r="C27">
-        <v>5704.533875537667</v>
+        <v>5626.856311978392</v>
       </c>
       <c r="D27">
-        <v>6792.246316723403</v>
+        <v>6788.153250811558</v>
       </c>
       <c r="E27">
-        <v>-1151.837323557207</v>
+        <v>-1078.252825909777</v>
       </c>
       <c r="F27">
-        <v>1839.612441185735</v>
+        <v>1913.196938833165</v>
       </c>
       <c r="G27">
         <v>751.9</v>
@@ -3501,28 +3501,28 @@
         <v>2022.56</v>
       </c>
       <c r="M27">
-        <v>127.2229757346546</v>
+        <v>132.3118947640408</v>
       </c>
       <c r="N27">
-        <v>1895.337024265345</v>
+        <v>1890.248105235959</v>
       </c>
       <c r="O27">
-        <v>170.5803321838811</v>
+        <v>170.1223294712363</v>
       </c>
       <c r="P27">
-        <v>1724.756692081464</v>
+        <v>1720.125775764723</v>
       </c>
       <c r="Q27">
-        <v>2975.656692081464</v>
+        <v>2971.025775764723</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1295397464305394</v>
+        <v>0.1305932221926434</v>
       </c>
       <c r="T27">
-        <v>1.218515344342114</v>
+        <v>1.233844700301903</v>
       </c>
       <c r="U27">
         <v>0.06915748822216712</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.89775736906514</v>
+        <v>15.28630516256263</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1130016461359208</v>
+        <v>0.1131151538783941</v>
       </c>
       <c r="C28">
-        <v>5626.856311978392</v>
+        <v>5549.183678481498</v>
       </c>
       <c r="D28">
-        <v>6788.153250811558</v>
+        <v>6784.065114962093</v>
       </c>
       <c r="E28">
-        <v>-1078.252825909777</v>
+        <v>-1004.668328262348</v>
       </c>
       <c r="F28">
-        <v>1913.196938833165</v>
+        <v>1986.781436480594</v>
       </c>
       <c r="G28">
         <v>751.9</v>
@@ -3583,28 +3583,28 @@
         <v>2022.56</v>
       </c>
       <c r="M28">
-        <v>132.3118947640408</v>
+        <v>137.400813793427</v>
       </c>
       <c r="N28">
-        <v>1890.248105235959</v>
+        <v>1885.159186206573</v>
       </c>
       <c r="O28">
-        <v>170.1223294712363</v>
+        <v>169.6643267585916</v>
       </c>
       <c r="P28">
-        <v>1720.125775764723</v>
+        <v>1715.494859447981</v>
       </c>
       <c r="Q28">
-        <v>2971.025775764723</v>
+        <v>2966.394859447982</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1305932221926434</v>
+        <v>0.131675560304394</v>
       </c>
       <c r="T28">
-        <v>1.233844700301903</v>
+        <v>1.249594038616755</v>
       </c>
       <c r="U28">
         <v>0.06915748822216712</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.28630516256263</v>
+        <v>14.72014571209735</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1131151538783941</v>
+        <v>0.1132286616208674</v>
       </c>
       <c r="C29">
-        <v>5549.183678481498</v>
+        <v>5471.515966145018</v>
       </c>
       <c r="D29">
-        <v>6784.065114962093</v>
+        <v>6779.981900273043</v>
       </c>
       <c r="E29">
-        <v>-1004.668328262348</v>
+        <v>-931.083830614918</v>
       </c>
       <c r="F29">
-        <v>1986.781436480594</v>
+        <v>2060.365934128024</v>
       </c>
       <c r="G29">
         <v>751.9</v>
@@ -3665,28 +3665,28 @@
         <v>2022.56</v>
       </c>
       <c r="M29">
-        <v>137.400813793427</v>
+        <v>142.4897328228132</v>
       </c>
       <c r="N29">
-        <v>1885.159186206573</v>
+        <v>1880.070267177187</v>
       </c>
       <c r="O29">
-        <v>169.6643267585916</v>
+        <v>169.2063240459468</v>
       </c>
       <c r="P29">
-        <v>1715.494859447981</v>
+        <v>1710.86394313124</v>
       </c>
       <c r="Q29">
-        <v>2966.394859447982</v>
+        <v>2961.76394313124</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.131675560304394</v>
+        <v>0.1327879633636933</v>
       </c>
       <c r="T29">
-        <v>1.249594038616755</v>
+        <v>1.265780858551463</v>
       </c>
       <c r="U29">
         <v>0.06915748822216712</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.72014571209735</v>
+        <v>14.19442622237958</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1132286616208674</v>
+        <v>0.1133421693633406</v>
       </c>
       <c r="C30">
-        <v>5471.515966145018</v>
+        <v>5393.853166088411</v>
       </c>
       <c r="D30">
-        <v>6779.981900273043</v>
+        <v>6775.903597863864</v>
       </c>
       <c r="E30">
-        <v>-931.083830614918</v>
+        <v>-857.499332967489</v>
       </c>
       <c r="F30">
-        <v>2060.365934128024</v>
+        <v>2133.950431775453</v>
       </c>
       <c r="G30">
         <v>751.9</v>
@@ -3747,28 +3747,28 @@
         <v>2022.56</v>
       </c>
       <c r="M30">
-        <v>142.4897328228132</v>
+        <v>147.5786518521993</v>
       </c>
       <c r="N30">
-        <v>1880.070267177187</v>
+        <v>1874.981348147801</v>
       </c>
       <c r="O30">
-        <v>169.2063240459468</v>
+        <v>168.748321333302</v>
       </c>
       <c r="P30">
-        <v>1710.86394313124</v>
+        <v>1706.233026814499</v>
       </c>
       <c r="Q30">
-        <v>2961.76394313124</v>
+        <v>2957.133026814498</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1327879633636933</v>
+        <v>0.1339317017204376</v>
       </c>
       <c r="T30">
-        <v>1.265780858551463</v>
+        <v>1.282423645244896</v>
       </c>
       <c r="U30">
         <v>0.06915748822216712</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.19442622237958</v>
+        <v>13.70496324919408</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1133421693633406</v>
+        <v>0.1134556771058139</v>
       </c>
       <c r="C31">
-        <v>5393.853166088411</v>
+        <v>5316.195269452481</v>
       </c>
       <c r="D31">
-        <v>6775.903597863864</v>
+        <v>6771.830198875364</v>
       </c>
       <c r="E31">
-        <v>-857.499332967489</v>
+        <v>-783.9148353200599</v>
       </c>
       <c r="F31">
-        <v>2133.950431775453</v>
+        <v>2207.534929422882</v>
       </c>
       <c r="G31">
         <v>751.9</v>
@@ -3829,28 +3829,28 @@
         <v>2022.56</v>
       </c>
       <c r="M31">
-        <v>147.5786518521993</v>
+        <v>152.6675708815855</v>
       </c>
       <c r="N31">
-        <v>1874.981348147801</v>
+        <v>1869.892429118414</v>
       </c>
       <c r="O31">
-        <v>168.748321333302</v>
+        <v>168.2903186206573</v>
       </c>
       <c r="P31">
-        <v>1706.233026814499</v>
+        <v>1701.602110497757</v>
       </c>
       <c r="Q31">
-        <v>2957.133026814498</v>
+        <v>2952.502110497757</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1339317017204376</v>
+        <v>0.1351081183159461</v>
       </c>
       <c r="T31">
-        <v>1.282423645244896</v>
+        <v>1.299541940129569</v>
       </c>
       <c r="U31">
         <v>0.06915748822216712</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.70496324919408</v>
+        <v>13.24813114088761</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1134556771058139</v>
+        <v>0.1135691848482872</v>
       </c>
       <c r="C32">
-        <v>5316.195269452481</v>
+        <v>5238.542267399328</v>
       </c>
       <c r="D32">
-        <v>6771.830198875364</v>
+        <v>6767.76169446964</v>
       </c>
       <c r="E32">
-        <v>-783.9148353200599</v>
+        <v>-710.3303376726303</v>
       </c>
       <c r="F32">
-        <v>2207.534929422882</v>
+        <v>2281.119427070312</v>
       </c>
       <c r="G32">
         <v>751.9</v>
@@ -3911,28 +3911,28 @@
         <v>2022.56</v>
       </c>
       <c r="M32">
-        <v>152.6675708815855</v>
+        <v>157.7564899109717</v>
       </c>
       <c r="N32">
-        <v>1869.892429118414</v>
+        <v>1864.803510089028</v>
       </c>
       <c r="O32">
-        <v>168.2903186206573</v>
+        <v>167.8323159080125</v>
       </c>
       <c r="P32">
-        <v>1701.602110497757</v>
+        <v>1696.971194181016</v>
       </c>
       <c r="Q32">
-        <v>2952.502110497757</v>
+        <v>2947.871194181016</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1351081183159461</v>
+        <v>0.1363186339432084</v>
       </c>
       <c r="T32">
-        <v>1.299541940129569</v>
+        <v>1.317156417474668</v>
       </c>
       <c r="U32">
         <v>0.06915748822216712</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.24813114088761</v>
+        <v>12.82077207182672</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1135691848482872</v>
+        <v>0.1141194925907604</v>
       </c>
       <c r="C33">
-        <v>5238.542267399328</v>
+        <v>5145.301968291707</v>
       </c>
       <c r="D33">
-        <v>6767.76169446964</v>
+        <v>6748.105893009449</v>
       </c>
       <c r="E33">
-        <v>-710.3303376726303</v>
+        <v>-636.7458400252008</v>
       </c>
       <c r="F33">
-        <v>2281.119427070312</v>
+        <v>2354.703924717741</v>
       </c>
       <c r="G33">
         <v>751.9</v>
@@ -3993,45 +3993,45 @@
         <v>2022.56</v>
       </c>
       <c r="M33">
-        <v>157.7564899109717</v>
+        <v>166.3774648274345</v>
       </c>
       <c r="N33">
-        <v>1864.803510089028</v>
+        <v>1856.182535172565</v>
       </c>
       <c r="O33">
-        <v>167.8323159080125</v>
+        <v>167.0564281655309</v>
       </c>
       <c r="P33">
-        <v>1696.971194181016</v>
+        <v>1689.126107007035</v>
       </c>
       <c r="Q33">
-        <v>2947.871194181016</v>
+        <v>2940.026107007035</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1363186339432084</v>
+        <v>0.1375647529712726</v>
       </c>
       <c r="T33">
-        <v>1.317156417474668</v>
+        <v>1.335288967682858</v>
       </c>
       <c r="U33">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V33">
         <v>0.09</v>
       </c>
       <c r="W33">
-        <v>0.06293331428217208</v>
+        <v>0.06429831428217207</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>12.82077207182672</v>
+        <v>12.15645401315488</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1141194925907604</v>
+        <v>0.1142466503332337</v>
       </c>
       <c r="C34">
-        <v>5145.301968291707</v>
+        <v>5067.1918992634</v>
       </c>
       <c r="D34">
-        <v>6748.105893009449</v>
+        <v>6743.580321628571</v>
       </c>
       <c r="E34">
-        <v>-636.7458400252008</v>
+        <v>-563.1613423777712</v>
       </c>
       <c r="F34">
-        <v>2354.703924717741</v>
+        <v>2428.288422365171</v>
       </c>
       <c r="G34">
         <v>751.9</v>
@@ -4075,28 +4075,28 @@
         <v>2022.56</v>
       </c>
       <c r="M34">
-        <v>166.3774648274345</v>
+        <v>171.5767606032918</v>
       </c>
       <c r="N34">
-        <v>1856.182535172565</v>
+        <v>1850.983239396708</v>
       </c>
       <c r="O34">
-        <v>167.0564281655309</v>
+        <v>166.5884915457037</v>
       </c>
       <c r="P34">
-        <v>1689.126107007035</v>
+        <v>1684.394747851004</v>
       </c>
       <c r="Q34">
-        <v>2940.026107007035</v>
+        <v>2935.294747851005</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1375647529712726</v>
+        <v>0.138848069582264</v>
       </c>
       <c r="T34">
-        <v>1.335288967682858</v>
+        <v>1.353962788046517</v>
       </c>
       <c r="U34">
         <v>0.07065748822216711</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.15645401315488</v>
+        <v>11.78807661881685</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1142466503332337</v>
+        <v>0.114373808075707</v>
       </c>
       <c r="C35">
-        <v>5067.1918992634</v>
+        <v>4989.087896254372</v>
       </c>
       <c r="D35">
-        <v>6743.580321628571</v>
+        <v>6739.060816266973</v>
       </c>
       <c r="E35">
-        <v>-563.1613423777712</v>
+        <v>-489.5768447303417</v>
       </c>
       <c r="F35">
-        <v>2428.288422365171</v>
+        <v>2501.8729200126</v>
       </c>
       <c r="G35">
         <v>751.9</v>
@@ -4157,28 +4157,28 @@
         <v>2022.56</v>
       </c>
       <c r="M35">
-        <v>171.5767606032918</v>
+        <v>176.7760563791491</v>
       </c>
       <c r="N35">
-        <v>1850.983239396708</v>
+        <v>1845.783943620851</v>
       </c>
       <c r="O35">
-        <v>166.5884915457037</v>
+        <v>166.1205549258766</v>
       </c>
       <c r="P35">
-        <v>1684.394747851004</v>
+        <v>1679.663388694974</v>
       </c>
       <c r="Q35">
-        <v>2935.294747851005</v>
+        <v>2930.563388694974</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.138848069582264</v>
+        <v>0.1401702745754068</v>
       </c>
       <c r="T35">
-        <v>1.353962788046517</v>
+        <v>1.373202481754529</v>
       </c>
       <c r="U35">
         <v>0.07065748822216711</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.78807661881685</v>
+        <v>11.44136848296929</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.114373808075707</v>
+        <v>0.1145009658181802</v>
       </c>
       <c r="C36">
-        <v>4989.087896254372</v>
+        <v>4910.989947076568</v>
       </c>
       <c r="D36">
-        <v>6739.060816266973</v>
+        <v>6734.547364736598</v>
       </c>
       <c r="E36">
-        <v>-489.5768447303417</v>
+        <v>-415.9923470829121</v>
       </c>
       <c r="F36">
-        <v>2501.8729200126</v>
+        <v>2575.45741766003</v>
       </c>
       <c r="G36">
         <v>751.9</v>
@@ -4239,28 +4239,28 @@
         <v>2022.56</v>
       </c>
       <c r="M36">
-        <v>176.7760563791491</v>
+        <v>181.9753521550065</v>
       </c>
       <c r="N36">
-        <v>1845.783943620851</v>
+        <v>1840.584647844993</v>
       </c>
       <c r="O36">
-        <v>166.1205549258766</v>
+        <v>165.6526183060494</v>
       </c>
       <c r="P36">
-        <v>1679.663388694974</v>
+        <v>1674.932029538944</v>
       </c>
       <c r="Q36">
-        <v>2930.563388694974</v>
+        <v>2925.832029538944</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1401702745754068</v>
+        <v>0.1415331627991077</v>
       </c>
       <c r="T36">
-        <v>1.373202481754529</v>
+        <v>1.393034166038172</v>
       </c>
       <c r="U36">
         <v>0.07065748822216711</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.44136848296929</v>
+        <v>11.11447224059874</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1145009658181802</v>
+        <v>0.1146281235606535</v>
       </c>
       <c r="C37">
-        <v>4910.989947076568</v>
+        <v>4832.89803957456</v>
       </c>
       <c r="D37">
-        <v>6734.547364736598</v>
+        <v>6730.039954882021</v>
       </c>
       <c r="E37">
-        <v>-415.9923470829121</v>
+        <v>-342.4078494354826</v>
       </c>
       <c r="F37">
-        <v>2575.45741766003</v>
+        <v>2649.041915307459</v>
       </c>
       <c r="G37">
         <v>751.9</v>
@@ -4321,28 +4321,28 @@
         <v>2022.56</v>
       </c>
       <c r="M37">
-        <v>181.9753521550065</v>
+        <v>187.1746479308638</v>
       </c>
       <c r="N37">
-        <v>1840.584647844993</v>
+        <v>1835.385352069136</v>
       </c>
       <c r="O37">
-        <v>165.6526183060494</v>
+        <v>165.1846816862223</v>
       </c>
       <c r="P37">
-        <v>1674.932029538944</v>
+        <v>1670.200670382914</v>
       </c>
       <c r="Q37">
-        <v>2925.832029538944</v>
+        <v>2921.100670382914</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1415331627991077</v>
+        <v>0.1429386412797993</v>
       </c>
       <c r="T37">
-        <v>1.393034166038172</v>
+        <v>1.413485590455678</v>
       </c>
       <c r="U37">
         <v>0.07065748822216711</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.11447224059874</v>
+        <v>10.80573690058211</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1146281235606535</v>
+        <v>0.1147552813031268</v>
       </c>
       <c r="C38">
-        <v>4832.898039574561</v>
+        <v>4754.812161625443</v>
       </c>
       <c r="D38">
-        <v>6730.039954882021</v>
+        <v>6725.538574580332</v>
       </c>
       <c r="E38">
-        <v>-342.4078494354831</v>
+        <v>-268.8233517880535</v>
       </c>
       <c r="F38">
-        <v>2649.041915307459</v>
+        <v>2722.626412954889</v>
       </c>
       <c r="G38">
         <v>751.9</v>
@@ -4403,28 +4403,28 @@
         <v>2022.56</v>
       </c>
       <c r="M38">
-        <v>187.1746479308638</v>
+        <v>192.3739437067211</v>
       </c>
       <c r="N38">
-        <v>1835.385352069136</v>
+        <v>1830.186056293279</v>
       </c>
       <c r="O38">
-        <v>165.1846816862223</v>
+        <v>164.7167450663951</v>
       </c>
       <c r="P38">
-        <v>1670.200670382914</v>
+        <v>1665.469311226884</v>
       </c>
       <c r="Q38">
-        <v>2921.100670382914</v>
+        <v>2916.369311226884</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1429386412797993</v>
+        <v>0.1443887381249573</v>
       </c>
       <c r="T38">
-        <v>1.413485590455678</v>
+        <v>1.434586266441995</v>
       </c>
       <c r="U38">
         <v>0.07065748822216711</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.80573690058211</v>
+        <v>10.51368995732314</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1147552813031268</v>
+        <v>0.1148824390456</v>
       </c>
       <c r="C39">
-        <v>4754.812161625443</v>
+        <v>4676.732301138722</v>
       </c>
       <c r="D39">
-        <v>6725.538574580332</v>
+        <v>6721.04321174104</v>
       </c>
       <c r="E39">
-        <v>-268.8233517880535</v>
+        <v>-195.2388541406244</v>
       </c>
       <c r="F39">
-        <v>2722.626412954889</v>
+        <v>2796.210910602318</v>
       </c>
       <c r="G39">
         <v>751.9</v>
@@ -4485,28 +4485,28 @@
         <v>2022.56</v>
       </c>
       <c r="M39">
-        <v>192.3739437067211</v>
+        <v>197.5732394825784</v>
       </c>
       <c r="N39">
-        <v>1830.186056293279</v>
+        <v>1824.986760517422</v>
       </c>
       <c r="O39">
-        <v>164.7167450663951</v>
+        <v>164.2488084465679</v>
       </c>
       <c r="P39">
-        <v>1665.469311226884</v>
+        <v>1660.737952070854</v>
       </c>
       <c r="Q39">
-        <v>2916.369311226884</v>
+        <v>2911.637952070854</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1443887381249573</v>
+        <v>0.145885612287701</v>
       </c>
       <c r="T39">
-        <v>1.434586266441995</v>
+        <v>1.456367609395611</v>
       </c>
       <c r="U39">
         <v>0.07065748822216711</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.51368995732314</v>
+        <v>10.23701390581463</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1148824390456</v>
+        <v>0.1150095967880733</v>
       </c>
       <c r="C40">
-        <v>4676.732301138722</v>
+        <v>4598.658446056207</v>
       </c>
       <c r="D40">
-        <v>6721.04321174104</v>
+        <v>6716.553854305955</v>
       </c>
       <c r="E40">
-        <v>-195.2388541406244</v>
+        <v>-121.6543564931949</v>
       </c>
       <c r="F40">
-        <v>2796.210910602318</v>
+        <v>2869.795408249747</v>
       </c>
       <c r="G40">
         <v>751.9</v>
@@ -4567,28 +4567,28 @@
         <v>2022.56</v>
       </c>
       <c r="M40">
-        <v>197.5732394825784</v>
+        <v>202.7725352584358</v>
       </c>
       <c r="N40">
-        <v>1824.986760517422</v>
+        <v>1819.787464741564</v>
       </c>
       <c r="O40">
-        <v>164.2488084465679</v>
+        <v>163.7808718267408</v>
       </c>
       <c r="P40">
-        <v>1660.737952070854</v>
+        <v>1656.006592914823</v>
       </c>
       <c r="Q40">
-        <v>2911.637952070854</v>
+        <v>2906.906592914824</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.145885612287701</v>
+        <v>0.1474315642918462</v>
       </c>
       <c r="T40">
-        <v>1.456367609395611</v>
+        <v>1.47886309474115</v>
       </c>
       <c r="U40">
         <v>0.07065748822216711</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.23701390581463</v>
+        <v>9.974526369768103</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1150095967880733</v>
+        <v>0.1157555545305466</v>
       </c>
       <c r="C41">
-        <v>4598.658446056207</v>
+        <v>4498.857916223962</v>
       </c>
       <c r="D41">
-        <v>6716.553854305955</v>
+        <v>6690.337822121139</v>
       </c>
       <c r="E41">
-        <v>-121.6543564931949</v>
+        <v>-48.06985884576534</v>
       </c>
       <c r="F41">
-        <v>2869.795408249747</v>
+        <v>2943.379905897177</v>
       </c>
       <c r="G41">
         <v>751.9</v>
@@ -4649,45 +4649,45 @@
         <v>2022.56</v>
       </c>
       <c r="M41">
-        <v>202.7725352584358</v>
+        <v>212.9755768743183</v>
       </c>
       <c r="N41">
-        <v>1819.787464741564</v>
+        <v>1809.584423125682</v>
       </c>
       <c r="O41">
-        <v>163.7808718267408</v>
+        <v>162.8625980813113</v>
       </c>
       <c r="P41">
-        <v>1656.006592914823</v>
+        <v>1646.72182504437</v>
       </c>
       <c r="Q41">
-        <v>2906.906592914824</v>
+        <v>2897.621825044371</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1474315642918462</v>
+        <v>0.1490290480294629</v>
       </c>
       <c r="T41">
-        <v>1.47886309474115</v>
+        <v>1.502108429598207</v>
       </c>
       <c r="U41">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V41">
         <v>0.09</v>
       </c>
       <c r="W41">
-        <v>0.06429831428217207</v>
+        <v>0.06584531428217208</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.974526369768103</v>
+        <v>9.496675767633011</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1157555545305466</v>
+        <v>0.1158981822730198</v>
       </c>
       <c r="C42">
-        <v>4498.857916223962</v>
+        <v>4420.284179681456</v>
       </c>
       <c r="D42">
-        <v>6690.337822121139</v>
+        <v>6685.348583226063</v>
       </c>
       <c r="E42">
-        <v>-48.06985884576534</v>
+        <v>25.5146388016642</v>
       </c>
       <c r="F42">
-        <v>2943.379905897177</v>
+        <v>3016.964403544606</v>
       </c>
       <c r="G42">
         <v>751.9</v>
@@ -4731,28 +4731,28 @@
         <v>2022.56</v>
       </c>
       <c r="M42">
-        <v>212.9755768743183</v>
+        <v>218.2999662961763</v>
       </c>
       <c r="N42">
-        <v>1809.584423125682</v>
+        <v>1804.260033703824</v>
       </c>
       <c r="O42">
-        <v>162.8625980813113</v>
+        <v>162.3834030333441</v>
       </c>
       <c r="P42">
-        <v>1646.72182504437</v>
+        <v>1641.876630670479</v>
       </c>
       <c r="Q42">
-        <v>2897.621825044371</v>
+        <v>2892.77663067048</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1490290480294629</v>
+        <v>0.1506806837581852</v>
       </c>
       <c r="T42">
-        <v>1.502108429598207</v>
+        <v>1.526141741908046</v>
       </c>
       <c r="U42">
         <v>0.07235748822216712</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.496675767633011</v>
+        <v>9.265049529398057</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1158981822730198</v>
+        <v>0.1160408100154931</v>
       </c>
       <c r="C43">
-        <v>4420.284179681456</v>
+        <v>4341.717878923499</v>
       </c>
       <c r="D43">
-        <v>6685.348583226063</v>
+        <v>6680.366780115535</v>
       </c>
       <c r="E43">
-        <v>25.5146388016642</v>
+        <v>99.09913644909375</v>
       </c>
       <c r="F43">
-        <v>3016.964403544606</v>
+        <v>3090.548901192036</v>
       </c>
       <c r="G43">
         <v>751.9</v>
@@ -4813,28 +4813,28 @@
         <v>2022.56</v>
       </c>
       <c r="M43">
-        <v>218.2999662961763</v>
+        <v>223.6243557180343</v>
       </c>
       <c r="N43">
-        <v>1804.260033703824</v>
+        <v>1798.935644281966</v>
       </c>
       <c r="O43">
-        <v>162.3834030333441</v>
+        <v>161.9042079853769</v>
       </c>
       <c r="P43">
-        <v>1641.876630670479</v>
+        <v>1637.031436296589</v>
       </c>
       <c r="Q43">
-        <v>2892.77663067048</v>
+        <v>2887.931436296589</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1506806837581852</v>
+        <v>0.1523892724430704</v>
       </c>
       <c r="T43">
-        <v>1.526141741908046</v>
+        <v>1.55100378912512</v>
       </c>
       <c r="U43">
         <v>0.07235748822216712</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.265049529398057</v>
+        <v>9.044453112031437</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1160408100154931</v>
+        <v>0.1161834377579664</v>
       </c>
       <c r="C44">
-        <v>4341.717878923499</v>
+        <v>4263.158997339426</v>
       </c>
       <c r="D44">
-        <v>6680.366780115535</v>
+        <v>6675.392396178891</v>
       </c>
       <c r="E44">
-        <v>99.09913644909329</v>
+        <v>172.6836340965228</v>
       </c>
       <c r="F44">
-        <v>3090.548901192035</v>
+        <v>3164.133398839465</v>
       </c>
       <c r="G44">
         <v>751.9</v>
@@ -4895,28 +4895,28 @@
         <v>2022.56</v>
       </c>
       <c r="M44">
-        <v>223.6243557180342</v>
+        <v>228.9487451398922</v>
       </c>
       <c r="N44">
-        <v>1798.935644281966</v>
+        <v>1793.611254860108</v>
       </c>
       <c r="O44">
-        <v>161.9042079853769</v>
+        <v>161.4250129374097</v>
       </c>
       <c r="P44">
-        <v>1637.031436296589</v>
+        <v>1632.186241922698</v>
       </c>
       <c r="Q44">
-        <v>2887.931436296589</v>
+        <v>2883.086241922698</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1523892724430704</v>
+        <v>0.1541578116081269</v>
       </c>
       <c r="T44">
-        <v>1.55100378912512</v>
+        <v>1.576738188876126</v>
       </c>
       <c r="U44">
         <v>0.07235748822216712</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.044453112031439</v>
+        <v>8.834116993146985</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1161834377579664</v>
+        <v>0.1163260655004396</v>
       </c>
       <c r="C45">
-        <v>4263.158997339426</v>
+        <v>4184.607518368005</v>
       </c>
       <c r="D45">
-        <v>6675.392396178891</v>
+        <v>6670.4254148549</v>
       </c>
       <c r="E45">
-        <v>172.6836340965228</v>
+        <v>246.2681317439524</v>
       </c>
       <c r="F45">
-        <v>3164.133398839465</v>
+        <v>3237.717896486894</v>
       </c>
       <c r="G45">
         <v>751.9</v>
@@ -4977,28 +4977,28 @@
         <v>2022.56</v>
       </c>
       <c r="M45">
-        <v>228.9487451398922</v>
+        <v>234.2731345617501</v>
       </c>
       <c r="N45">
-        <v>1793.611254860108</v>
+        <v>1788.28686543825</v>
       </c>
       <c r="O45">
-        <v>161.4250129374097</v>
+        <v>160.9458178894425</v>
       </c>
       <c r="P45">
-        <v>1632.186241922698</v>
+        <v>1627.341047548807</v>
       </c>
       <c r="Q45">
-        <v>2883.086241922698</v>
+        <v>2878.241047548808</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1541578116081269</v>
+        <v>0.1559895128862213</v>
       </c>
       <c r="T45">
-        <v>1.576738188876126</v>
+        <v>1.603391674332526</v>
       </c>
       <c r="U45">
         <v>0.07235748822216712</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.834116993146985</v>
+        <v>8.633341606939101</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1163260655004396</v>
+        <v>0.1164686932429129</v>
       </c>
       <c r="C46">
-        <v>4184.607518368005</v>
+        <v>4106.063425497265</v>
       </c>
       <c r="D46">
-        <v>6670.4254148549</v>
+        <v>6665.46581963159</v>
       </c>
       <c r="E46">
-        <v>246.2681317439524</v>
+        <v>319.8526293913819</v>
       </c>
       <c r="F46">
-        <v>3237.717896486894</v>
+        <v>3311.302394134324</v>
       </c>
       <c r="G46">
         <v>751.9</v>
@@ -5059,28 +5059,28 @@
         <v>2022.56</v>
       </c>
       <c r="M46">
-        <v>234.2731345617501</v>
+        <v>239.5975239836081</v>
       </c>
       <c r="N46">
-        <v>1788.28686543825</v>
+        <v>1782.962476016392</v>
       </c>
       <c r="O46">
-        <v>160.9458178894425</v>
+        <v>160.4666228414752</v>
       </c>
       <c r="P46">
-        <v>1627.341047548807</v>
+        <v>1622.495853174916</v>
       </c>
       <c r="Q46">
-        <v>2878.241047548808</v>
+        <v>2873.395853174917</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1559895128862213</v>
+        <v>0.157887821483519</v>
       </c>
       <c r="T46">
-        <v>1.603391674332526</v>
+        <v>1.631014377441886</v>
       </c>
       <c r="U46">
         <v>0.07235748822216712</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.633341606939101</v>
+        <v>8.44148957122934</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1164686932429129</v>
+        <v>0.1166113209853862</v>
       </c>
       <c r="C47">
-        <v>4106.063425497265</v>
+        <v>4027.526702264302</v>
       </c>
       <c r="D47">
-        <v>6665.46581963159</v>
+        <v>6660.513594046056</v>
       </c>
       <c r="E47">
-        <v>319.8526293913819</v>
+        <v>393.437127038811</v>
       </c>
       <c r="F47">
-        <v>3311.302394134324</v>
+        <v>3384.886891781753</v>
       </c>
       <c r="G47">
         <v>751.9</v>
@@ -5141,28 +5141,28 @@
         <v>2022.56</v>
       </c>
       <c r="M47">
-        <v>239.5975239836081</v>
+        <v>244.9219134054661</v>
       </c>
       <c r="N47">
-        <v>1782.962476016392</v>
+        <v>1777.638086594534</v>
       </c>
       <c r="O47">
-        <v>160.4666228414752</v>
+        <v>159.987427793508</v>
       </c>
       <c r="P47">
-        <v>1622.495853174916</v>
+        <v>1617.650658801026</v>
       </c>
       <c r="Q47">
-        <v>2873.395853174917</v>
+        <v>2868.550658801026</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.157887821483519</v>
+        <v>0.1598564378066426</v>
       </c>
       <c r="T47">
-        <v>1.631014377441886</v>
+        <v>1.65966014362937</v>
       </c>
       <c r="U47">
         <v>0.07235748822216712</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.44148957122934</v>
+        <v>8.257978928376531</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1166113209853862</v>
+        <v>0.1167539487278594</v>
       </c>
       <c r="C48">
-        <v>4027.526702264302</v>
+        <v>3948.997332255109</v>
       </c>
       <c r="D48">
-        <v>6660.513594046056</v>
+        <v>6655.568721684292</v>
       </c>
       <c r="E48">
-        <v>393.437127038811</v>
+        <v>467.0216246862406</v>
       </c>
       <c r="F48">
-        <v>3384.886891781753</v>
+        <v>3458.471389429183</v>
       </c>
       <c r="G48">
         <v>751.9</v>
@@ -5223,28 +5223,28 @@
         <v>2022.56</v>
       </c>
       <c r="M48">
-        <v>244.9219134054661</v>
+        <v>250.246302827324</v>
       </c>
       <c r="N48">
-        <v>1777.638086594534</v>
+        <v>1772.313697172676</v>
       </c>
       <c r="O48">
-        <v>159.987427793508</v>
+        <v>159.5082327455408</v>
       </c>
       <c r="P48">
-        <v>1617.650658801026</v>
+        <v>1612.805464427135</v>
       </c>
       <c r="Q48">
-        <v>2868.550658801026</v>
+        <v>2863.705464427135</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1598564378066426</v>
+        <v>0.1618993415381859</v>
       </c>
       <c r="T48">
-        <v>1.65966014362937</v>
+        <v>1.689386882125816</v>
       </c>
       <c r="U48">
         <v>0.07235748822216712</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.257978928376531</v>
+        <v>8.082277249049369</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1167539487278594</v>
+        <v>0.1168965764703327</v>
       </c>
       <c r="C49">
-        <v>3948.997332255109</v>
+        <v>3870.475299104376</v>
       </c>
       <c r="D49">
-        <v>6655.568721684292</v>
+        <v>6650.631186180988</v>
       </c>
       <c r="E49">
-        <v>467.0216246862406</v>
+        <v>540.6061223336701</v>
       </c>
       <c r="F49">
-        <v>3458.471389429183</v>
+        <v>3532.055887076612</v>
       </c>
       <c r="G49">
         <v>751.9</v>
@@ -5305,28 +5305,28 @@
         <v>2022.56</v>
       </c>
       <c r="M49">
-        <v>250.246302827324</v>
+        <v>255.570692249182</v>
       </c>
       <c r="N49">
-        <v>1772.313697172676</v>
+        <v>1766.989307750818</v>
       </c>
       <c r="O49">
-        <v>159.5082327455408</v>
+        <v>159.0290376975736</v>
       </c>
       <c r="P49">
-        <v>1612.805464427135</v>
+        <v>1607.960270053244</v>
       </c>
       <c r="Q49">
-        <v>2863.705464427135</v>
+        <v>2858.860270053245</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1618993415381859</v>
+        <v>0.1640208184901732</v>
       </c>
       <c r="T49">
-        <v>1.689386882125816</v>
+        <v>1.720256956718279</v>
       </c>
       <c r="U49">
         <v>0.07235748822216712</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.082277249049369</v>
+        <v>7.913896473027507</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1168965764703327</v>
+        <v>0.117039204212806</v>
       </c>
       <c r="C50">
-        <v>3870.475299104376</v>
+        <v>3791.960586495325</v>
       </c>
       <c r="D50">
-        <v>6650.631186180988</v>
+        <v>6645.700971219367</v>
       </c>
       <c r="E50">
-        <v>540.6061223336696</v>
+        <v>614.1906199810992</v>
       </c>
       <c r="F50">
-        <v>3532.055887076612</v>
+        <v>3605.640384724041</v>
       </c>
       <c r="G50">
         <v>751.9</v>
@@ -5387,28 +5387,28 @@
         <v>2022.56</v>
       </c>
       <c r="M50">
-        <v>255.5706922491819</v>
+        <v>260.8950816710399</v>
       </c>
       <c r="N50">
-        <v>1766.989307750818</v>
+        <v>1761.66491832896</v>
       </c>
       <c r="O50">
-        <v>159.0290376975736</v>
+        <v>158.5498426496064</v>
       </c>
       <c r="P50">
-        <v>1607.960270053244</v>
+        <v>1603.115075679354</v>
       </c>
       <c r="Q50">
-        <v>2858.860270053245</v>
+        <v>2854.015075679354</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1640208184901732</v>
+        <v>0.1662254906167483</v>
       </c>
       <c r="T50">
-        <v>1.720256956718279</v>
+        <v>1.752337622471231</v>
       </c>
       <c r="U50">
         <v>0.07235748822216712</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.913896473027509</v>
+        <v>7.752388381741233</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.117039204212806</v>
+        <v>0.1171818319552792</v>
       </c>
       <c r="C51">
-        <v>3791.960586495325</v>
+        <v>3713.453178159531</v>
       </c>
       <c r="D51">
-        <v>6645.700971219367</v>
+        <v>6640.778060531002</v>
       </c>
       <c r="E51">
-        <v>614.1906199810992</v>
+        <v>687.7751176285287</v>
       </c>
       <c r="F51">
-        <v>3605.640384724041</v>
+        <v>3679.224882371471</v>
       </c>
       <c r="G51">
         <v>751.9</v>
@@ -5469,28 +5469,28 @@
         <v>2022.56</v>
       </c>
       <c r="M51">
-        <v>260.8950816710399</v>
+        <v>266.2194710928979</v>
       </c>
       <c r="N51">
-        <v>1761.66491832896</v>
+        <v>1756.340528907102</v>
       </c>
       <c r="O51">
-        <v>158.5498426496064</v>
+        <v>158.0706476016392</v>
       </c>
       <c r="P51">
-        <v>1603.115075679354</v>
+        <v>1598.269881305463</v>
       </c>
       <c r="Q51">
-        <v>2854.015075679354</v>
+        <v>2849.169881305463</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1662254906167483</v>
+        <v>0.1685183496283864</v>
       </c>
       <c r="T51">
-        <v>1.752337622471231</v>
+        <v>1.785701514854301</v>
       </c>
       <c r="U51">
         <v>0.07235748822216712</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.752388381741233</v>
+        <v>7.597340614106407</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1171818319552792</v>
+        <v>0.1176957396977525</v>
       </c>
       <c r="C52">
-        <v>3713.453178159531</v>
+        <v>3622.191066167028</v>
       </c>
       <c r="D52">
-        <v>6640.778060531002</v>
+        <v>6623.100446185928</v>
       </c>
       <c r="E52">
-        <v>687.7751176285287</v>
+        <v>761.3596152759583</v>
       </c>
       <c r="F52">
-        <v>3679.224882371471</v>
+        <v>3752.8093800189</v>
       </c>
       <c r="G52">
         <v>751.9</v>
@@ -5551,45 +5551,45 @@
         <v>2022.56</v>
       </c>
       <c r="M52">
-        <v>266.2194710928979</v>
+        <v>274.546108018771</v>
       </c>
       <c r="N52">
-        <v>1756.340528907102</v>
+        <v>1748.013891981229</v>
       </c>
       <c r="O52">
-        <v>158.0706476016392</v>
+        <v>157.3212502783106</v>
       </c>
       <c r="P52">
-        <v>1598.269881305463</v>
+        <v>1590.692641702918</v>
       </c>
       <c r="Q52">
-        <v>2849.169881305463</v>
+        <v>2841.592641702919</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1685183496283864</v>
+        <v>0.1709047947221321</v>
       </c>
       <c r="T52">
-        <v>1.785701514854301</v>
+        <v>1.82042719876321</v>
       </c>
       <c r="U52">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V52">
         <v>0.09</v>
       </c>
       <c r="W52">
-        <v>0.06584531428217208</v>
+        <v>0.06657331428217207</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>7.597340614106407</v>
+        <v>7.366922862595144</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1176957396977525</v>
+        <v>0.1178456474402258</v>
       </c>
       <c r="C53">
-        <v>3622.191066167028</v>
+        <v>3543.467696128035</v>
       </c>
       <c r="D53">
-        <v>6623.100446185928</v>
+        <v>6617.961573794365</v>
       </c>
       <c r="E53">
-        <v>761.3596152759583</v>
+        <v>834.9441129233878</v>
       </c>
       <c r="F53">
-        <v>3752.8093800189</v>
+        <v>3826.39387766633</v>
       </c>
       <c r="G53">
         <v>751.9</v>
@@ -5633,28 +5633,28 @@
         <v>2022.56</v>
       </c>
       <c r="M53">
-        <v>274.546108018771</v>
+        <v>279.9293650387469</v>
       </c>
       <c r="N53">
-        <v>1748.013891981229</v>
+        <v>1742.630634961253</v>
       </c>
       <c r="O53">
-        <v>157.3212502783106</v>
+        <v>156.8367571465128</v>
       </c>
       <c r="P53">
-        <v>1590.692641702918</v>
+        <v>1585.79387781474</v>
       </c>
       <c r="Q53">
-        <v>2841.592641702919</v>
+        <v>2836.693877814741</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1709047947221321</v>
+        <v>0.1733906750281173</v>
       </c>
       <c r="T53">
-        <v>1.82042719876321</v>
+        <v>1.856599786168324</v>
       </c>
       <c r="U53">
         <v>0.07315748822216711</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.366922862595144</v>
+        <v>7.225251269083699</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1178456474402258</v>
+        <v>0.117995555182699</v>
       </c>
       <c r="C54">
-        <v>3543.467696128035</v>
+        <v>3464.752294422168</v>
       </c>
       <c r="D54">
-        <v>6617.961573794365</v>
+        <v>6612.830669735928</v>
       </c>
       <c r="E54">
-        <v>834.9441129233878</v>
+        <v>908.5286105708174</v>
       </c>
       <c r="F54">
-        <v>3826.39387766633</v>
+        <v>3899.978375313759</v>
       </c>
       <c r="G54">
         <v>751.9</v>
@@ -5715,28 +5715,28 @@
         <v>2022.56</v>
       </c>
       <c r="M54">
-        <v>279.9293650387469</v>
+        <v>285.3126220587228</v>
       </c>
       <c r="N54">
-        <v>1742.630634961253</v>
+        <v>1737.247377941277</v>
       </c>
       <c r="O54">
-        <v>156.8367571465128</v>
+        <v>156.3522640147149</v>
       </c>
       <c r="P54">
-        <v>1585.79387781474</v>
+        <v>1580.895113926562</v>
       </c>
       <c r="Q54">
-        <v>2836.693877814741</v>
+        <v>2831.795113926562</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1733906750281173</v>
+        <v>0.1759823374747826</v>
       </c>
       <c r="T54">
-        <v>1.856599786168324</v>
+        <v>1.894311632611953</v>
       </c>
       <c r="U54">
         <v>0.07315748822216711</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.225251269083699</v>
+        <v>7.088925773440611</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.117995555182699</v>
+        <v>0.1181454629251723</v>
       </c>
       <c r="C55">
-        <v>3464.752294422168</v>
+        <v>3386.044842530241</v>
       </c>
       <c r="D55">
-        <v>6612.830669735928</v>
+        <v>6607.70771549143</v>
       </c>
       <c r="E55">
-        <v>908.5286105708174</v>
+        <v>982.1131082182465</v>
       </c>
       <c r="F55">
-        <v>3899.978375313759</v>
+        <v>3973.562872961189</v>
       </c>
       <c r="G55">
         <v>751.9</v>
@@ -5797,28 +5797,28 @@
         <v>2022.56</v>
       </c>
       <c r="M55">
-        <v>285.3126220587228</v>
+        <v>290.6958790786987</v>
       </c>
       <c r="N55">
-        <v>1737.247377941277</v>
+        <v>1731.864120921301</v>
       </c>
       <c r="O55">
-        <v>156.3522640147149</v>
+        <v>155.8677708829171</v>
       </c>
       <c r="P55">
-        <v>1580.895113926562</v>
+        <v>1575.996350038384</v>
       </c>
       <c r="Q55">
-        <v>2831.795113926562</v>
+        <v>2826.896350038384</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1759823374747826</v>
+        <v>0.17868668089739</v>
       </c>
       <c r="T55">
-        <v>1.894311632611953</v>
+        <v>1.933663124553132</v>
       </c>
       <c r="U55">
         <v>0.07315748822216711</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.088925773440611</v>
+        <v>6.957649370228747</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1181454629251723</v>
+        <v>0.1182953706676455</v>
       </c>
       <c r="C56">
-        <v>3386.044842530241</v>
+        <v>3307.345321990416</v>
       </c>
       <c r="D56">
-        <v>6607.70771549143</v>
+        <v>6602.592692599034</v>
       </c>
       <c r="E56">
-        <v>982.1131082182465</v>
+        <v>1055.697605865676</v>
       </c>
       <c r="F56">
-        <v>3973.562872961189</v>
+        <v>4047.147370608618</v>
       </c>
       <c r="G56">
         <v>751.9</v>
@@ -5879,28 +5879,28 @@
         <v>2022.56</v>
       </c>
       <c r="M56">
-        <v>290.6958790786987</v>
+        <v>296.0791360986746</v>
       </c>
       <c r="N56">
-        <v>1731.864120921301</v>
+        <v>1726.480863901325</v>
       </c>
       <c r="O56">
-        <v>155.8677708829171</v>
+        <v>155.3832777511193</v>
       </c>
       <c r="P56">
-        <v>1575.996350038384</v>
+        <v>1571.097586150206</v>
       </c>
       <c r="Q56">
-        <v>2826.896350038384</v>
+        <v>2821.997586150206</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.17868668089739</v>
+        <v>0.181511217361002</v>
       </c>
       <c r="T56">
-        <v>1.933663124553132</v>
+        <v>1.974763571691696</v>
       </c>
       <c r="U56">
         <v>0.07315748822216711</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.957649370228747</v>
+        <v>6.831146654406407</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1182953706676455</v>
+        <v>0.1184452784101188</v>
       </c>
       <c r="C57">
-        <v>3307.345321990416</v>
+        <v>3228.653714397972</v>
       </c>
       <c r="D57">
-        <v>6602.592692599034</v>
+        <v>6597.485582654021</v>
       </c>
       <c r="E57">
-        <v>1055.697605865676</v>
+        <v>1129.282103513106</v>
       </c>
       <c r="F57">
-        <v>4047.147370608618</v>
+        <v>4120.731868256048</v>
       </c>
       <c r="G57">
         <v>751.9</v>
@@ -5961,28 +5961,28 @@
         <v>2022.56</v>
       </c>
       <c r="M57">
-        <v>296.0791360986746</v>
+        <v>301.4623931186505</v>
       </c>
       <c r="N57">
-        <v>1726.480863901325</v>
+        <v>1721.097606881349</v>
       </c>
       <c r="O57">
-        <v>155.3832777511193</v>
+        <v>154.8987846193214</v>
       </c>
       <c r="P57">
-        <v>1571.097586150206</v>
+        <v>1566.198822262028</v>
       </c>
       <c r="Q57">
-        <v>2821.997586150206</v>
+        <v>2817.098822262028</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.181511217361002</v>
+        <v>0.1844641418456874</v>
       </c>
       <c r="T57">
-        <v>1.974763571691696</v>
+        <v>2.017732220972922</v>
       </c>
       <c r="U57">
         <v>0.07315748822216711</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.831146654406407</v>
+        <v>6.709161892720577</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1184452784101188</v>
+        <v>0.1185951861525921</v>
       </c>
       <c r="C58">
-        <v>3228.653714397972</v>
+        <v>3149.970001405094</v>
       </c>
       <c r="D58">
-        <v>6597.485582654021</v>
+        <v>6592.386367308572</v>
       </c>
       <c r="E58">
-        <v>1129.282103513106</v>
+        <v>1202.866601160535</v>
       </c>
       <c r="F58">
-        <v>4120.731868256048</v>
+        <v>4194.316365903477</v>
       </c>
       <c r="G58">
         <v>751.9</v>
@@ -6043,28 +6043,28 @@
         <v>2022.56</v>
       </c>
       <c r="M58">
-        <v>301.4623931186505</v>
+        <v>306.8456501386264</v>
       </c>
       <c r="N58">
-        <v>1721.097606881349</v>
+        <v>1715.714349861374</v>
       </c>
       <c r="O58">
-        <v>154.8987846193214</v>
+        <v>154.4142914875236</v>
       </c>
       <c r="P58">
-        <v>1566.198822262028</v>
+        <v>1561.30005837385</v>
       </c>
       <c r="Q58">
-        <v>2817.098822262028</v>
+        <v>2812.20005837385</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1844641418456874</v>
+        <v>0.1875544116552419</v>
       </c>
       <c r="T58">
-        <v>2.017732220972922</v>
+        <v>2.062699412081182</v>
       </c>
       <c r="U58">
         <v>0.07315748822216711</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.709161892720577</v>
+        <v>6.591457298111445</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1185951861525921</v>
+        <v>0.1187450938950654</v>
       </c>
       <c r="C59">
-        <v>3149.970001405094</v>
+        <v>3071.294164720641</v>
       </c>
       <c r="D59">
-        <v>6592.386367308572</v>
+        <v>6587.295028271547</v>
       </c>
       <c r="E59">
-        <v>1202.866601160535</v>
+        <v>1276.451098807964</v>
       </c>
       <c r="F59">
-        <v>4194.316365903477</v>
+        <v>4267.900863550906</v>
       </c>
       <c r="G59">
         <v>751.9</v>
@@ -6125,28 +6125,28 @@
         <v>2022.56</v>
       </c>
       <c r="M59">
-        <v>306.8456501386264</v>
+        <v>312.2289071586023</v>
       </c>
       <c r="N59">
-        <v>1715.714349861374</v>
+        <v>1710.331092841398</v>
       </c>
       <c r="O59">
-        <v>154.4142914875236</v>
+        <v>153.9297983557258</v>
       </c>
       <c r="P59">
-        <v>1561.30005837385</v>
+        <v>1556.401294485672</v>
       </c>
       <c r="Q59">
-        <v>2812.20005837385</v>
+        <v>2807.301294485672</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1875544116552419</v>
+        <v>0.1907918371700132</v>
       </c>
       <c r="T59">
-        <v>2.062699412081182</v>
+        <v>2.109807898004121</v>
       </c>
       <c r="U59">
         <v>0.07315748822216711</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.591457298111445</v>
+        <v>6.477811482626764</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1187450938950654</v>
+        <v>0.1188950016375386</v>
       </c>
       <c r="C60">
-        <v>3071.294164720641</v>
+        <v>2992.626186109938</v>
       </c>
       <c r="D60">
-        <v>6587.295028271547</v>
+        <v>6582.211547308274</v>
       </c>
       <c r="E60">
-        <v>1276.451098807964</v>
+        <v>1350.035596455393</v>
       </c>
       <c r="F60">
-        <v>4267.900863550906</v>
+        <v>4341.485361198335</v>
       </c>
       <c r="G60">
         <v>751.9</v>
@@ -6207,28 +6207,28 @@
         <v>2022.56</v>
       </c>
       <c r="M60">
-        <v>312.2289071586023</v>
+        <v>317.6121641785782</v>
       </c>
       <c r="N60">
-        <v>1710.331092841398</v>
+        <v>1704.947835821422</v>
       </c>
       <c r="O60">
-        <v>153.9297983557258</v>
+        <v>153.445305223928</v>
       </c>
       <c r="P60">
-        <v>1556.401294485672</v>
+        <v>1551.502530597494</v>
       </c>
       <c r="Q60">
-        <v>2807.301294485672</v>
+        <v>2802.402530597494</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1907918371700132</v>
+        <v>0.1941871858806271</v>
       </c>
       <c r="T60">
-        <v>2.109807898004121</v>
+        <v>2.15921435885013</v>
       </c>
       <c r="U60">
         <v>0.07315748822216711</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.477811482626764</v>
+        <v>6.36801806766699</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1188950016375386</v>
+        <v>0.1190449093800119</v>
       </c>
       <c r="C61">
-        <v>2992.626186109938</v>
+        <v>2913.966047394554</v>
       </c>
       <c r="D61">
-        <v>6582.211547308274</v>
+        <v>6577.135906240319</v>
       </c>
       <c r="E61">
-        <v>1350.035596455393</v>
+        <v>1423.620094102822</v>
       </c>
       <c r="F61">
-        <v>4341.485361198335</v>
+        <v>4415.069858845764</v>
       </c>
       <c r="G61">
         <v>751.9</v>
@@ -6289,28 +6289,28 @@
         <v>2022.56</v>
       </c>
       <c r="M61">
-        <v>317.6121641785782</v>
+        <v>322.995421198554</v>
       </c>
       <c r="N61">
-        <v>1704.947835821422</v>
+        <v>1699.564578801446</v>
       </c>
       <c r="O61">
-        <v>153.445305223928</v>
+        <v>152.9608120921301</v>
       </c>
       <c r="P61">
-        <v>1551.502530597494</v>
+        <v>1546.603766709316</v>
       </c>
       <c r="Q61">
-        <v>2802.402530597494</v>
+        <v>2797.503766709316</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1941871858806271</v>
+        <v>0.1977523020267716</v>
       </c>
       <c r="T61">
-        <v>2.15921435885013</v>
+        <v>2.21109114273844</v>
       </c>
       <c r="U61">
         <v>0.07315748822216711</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.36801806766699</v>
+        <v>6.261884433205873</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1190449093800119</v>
+        <v>0.1191948171224851</v>
       </c>
       <c r="C62">
-        <v>2913.966047394554</v>
+        <v>2835.313730452081</v>
       </c>
       <c r="D62">
-        <v>6577.135906240319</v>
+        <v>6572.068086945276</v>
       </c>
       <c r="E62">
-        <v>1423.620094102822</v>
+        <v>1497.204591750252</v>
       </c>
       <c r="F62">
-        <v>4415.069858845764</v>
+        <v>4488.654356493194</v>
       </c>
       <c r="G62">
         <v>751.9</v>
@@ -6371,28 +6371,28 @@
         <v>2022.56</v>
       </c>
       <c r="M62">
-        <v>322.995421198554</v>
+        <v>328.37867821853</v>
       </c>
       <c r="N62">
-        <v>1699.564578801446</v>
+        <v>1694.18132178147</v>
       </c>
       <c r="O62">
-        <v>152.9608120921301</v>
+        <v>152.4763189603323</v>
       </c>
       <c r="P62">
-        <v>1546.603766709316</v>
+        <v>1541.705002821138</v>
       </c>
       <c r="Q62">
-        <v>2797.503766709316</v>
+        <v>2792.605002821138</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1977523020267716</v>
+        <v>0.2015002446419492</v>
       </c>
       <c r="T62">
-        <v>2.21109114273844</v>
+        <v>2.265628274518458</v>
       </c>
       <c r="U62">
         <v>0.07315748822216711</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.261884433205873</v>
+        <v>6.159230590038564</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1191948171224851</v>
+        <v>0.1199089248649584</v>
       </c>
       <c r="C63">
-        <v>2835.313730452081</v>
+        <v>2737.694744429046</v>
       </c>
       <c r="D63">
-        <v>6572.068086945276</v>
+        <v>6548.03359856967</v>
       </c>
       <c r="E63">
-        <v>1497.204591750252</v>
+        <v>1570.789089397681</v>
       </c>
       <c r="F63">
-        <v>4488.654356493194</v>
+        <v>4562.238854140624</v>
       </c>
       <c r="G63">
         <v>751.9</v>
@@ -6453,45 +6453,45 @@
         <v>2022.56</v>
       </c>
       <c r="M63">
-        <v>328.37867821853</v>
+        <v>338.3241740926464</v>
       </c>
       <c r="N63">
-        <v>1694.18132178147</v>
+        <v>1684.235825907354</v>
       </c>
       <c r="O63">
-        <v>152.4763189603323</v>
+        <v>151.5812243316618</v>
       </c>
       <c r="P63">
-        <v>1541.705002821138</v>
+        <v>1532.654601575692</v>
       </c>
       <c r="Q63">
-        <v>2792.605002821138</v>
+        <v>2783.554601575692</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2015002446419492</v>
+        <v>0.2054454473947677</v>
       </c>
       <c r="T63">
-        <v>2.265628274518458</v>
+        <v>2.323035781655319</v>
       </c>
       <c r="U63">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V63">
         <v>0.09</v>
       </c>
       <c r="W63">
-        <v>0.06657331428217207</v>
+        <v>0.06748331428217208</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>6.159230590038564</v>
+        <v>5.978171691172572</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1199089248649584</v>
+        <v>0.1200679326074317</v>
       </c>
       <c r="C64">
-        <v>2737.694744429046</v>
+        <v>2658.782485563783</v>
       </c>
       <c r="D64">
-        <v>6548.03359856967</v>
+        <v>6542.705837351837</v>
       </c>
       <c r="E64">
-        <v>1570.789089397681</v>
+        <v>1644.373587045111</v>
       </c>
       <c r="F64">
-        <v>4562.238854140624</v>
+        <v>4635.823351788054</v>
       </c>
       <c r="G64">
         <v>751.9</v>
@@ -6535,28 +6535,28 @@
         <v>2022.56</v>
       </c>
       <c r="M64">
-        <v>338.3241740926464</v>
+        <v>343.7810156102698</v>
       </c>
       <c r="N64">
-        <v>1684.235825907354</v>
+        <v>1678.77898438973</v>
       </c>
       <c r="O64">
-        <v>151.5812243316618</v>
+        <v>151.0901085950757</v>
       </c>
       <c r="P64">
-        <v>1532.654601575692</v>
+        <v>1527.688875794654</v>
       </c>
       <c r="Q64">
-        <v>2783.554601575692</v>
+        <v>2778.588875794655</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2054454473947677</v>
+        <v>0.2096039043504413</v>
       </c>
       <c r="T64">
-        <v>2.323035781655319</v>
+        <v>2.383546397286064</v>
       </c>
       <c r="U64">
         <v>0.07415748822216711</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.978171691172572</v>
+        <v>5.883280077026975</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1200679326074317</v>
+        <v>0.1202269403499049</v>
       </c>
       <c r="C65">
-        <v>2658.782485563783</v>
+        <v>2579.878889440596</v>
       </c>
       <c r="D65">
-        <v>6542.705837351837</v>
+        <v>6537.386738876079</v>
       </c>
       <c r="E65">
-        <v>1644.373587045111</v>
+        <v>1717.958084692541</v>
       </c>
       <c r="F65">
-        <v>4635.823351788054</v>
+        <v>4709.407849435483</v>
       </c>
       <c r="G65">
         <v>751.9</v>
@@ -6617,28 +6617,28 @@
         <v>2022.56</v>
       </c>
       <c r="M65">
-        <v>343.7810156102698</v>
+        <v>349.2378571278932</v>
       </c>
       <c r="N65">
-        <v>1678.77898438973</v>
+        <v>1673.322142872107</v>
       </c>
       <c r="O65">
-        <v>151.0901085950757</v>
+        <v>150.5989928584896</v>
       </c>
       <c r="P65">
-        <v>1527.688875794654</v>
+        <v>1522.723150013617</v>
       </c>
       <c r="Q65">
-        <v>2778.588875794655</v>
+        <v>2773.623150013617</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2096039043504413</v>
+        <v>0.2139933866925412</v>
       </c>
       <c r="T65">
-        <v>2.383546397286064</v>
+        <v>2.447418713785184</v>
       </c>
       <c r="U65">
         <v>0.07415748822216711</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.883280077026975</v>
+        <v>5.791353825823428</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1202269403499049</v>
+        <v>0.1203859480923782</v>
       </c>
       <c r="C66">
-        <v>2579.878889440596</v>
+        <v>2500.983934948701</v>
       </c>
       <c r="D66">
-        <v>6537.386738876079</v>
+        <v>6532.076282031614</v>
       </c>
       <c r="E66">
-        <v>1717.958084692541</v>
+        <v>1791.542582339971</v>
       </c>
       <c r="F66">
-        <v>4709.407849435483</v>
+        <v>4782.992347082913</v>
       </c>
       <c r="G66">
         <v>751.9</v>
@@ -6699,28 +6699,28 @@
         <v>2022.56</v>
       </c>
       <c r="M66">
-        <v>349.2378571278932</v>
+        <v>354.6946986455165</v>
       </c>
       <c r="N66">
-        <v>1673.322142872107</v>
+        <v>1667.865301354484</v>
       </c>
       <c r="O66">
-        <v>150.5989928584896</v>
+        <v>150.1078771219035</v>
       </c>
       <c r="P66">
-        <v>1522.723150013617</v>
+        <v>1517.75742423258</v>
       </c>
       <c r="Q66">
-        <v>2773.623150013617</v>
+        <v>2768.65742423258</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2139933866925412</v>
+        <v>0.2186336965970468</v>
       </c>
       <c r="T66">
-        <v>2.447418713785184</v>
+        <v>2.514940876941397</v>
       </c>
       <c r="U66">
         <v>0.07415748822216711</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.791353825823428</v>
+        <v>5.702256074656915</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1203859480923782</v>
+        <v>0.1205449558348515</v>
       </c>
       <c r="C67">
-        <v>2500.983934948701</v>
+        <v>2422.097601045855</v>
       </c>
       <c r="D67">
-        <v>6532.076282031614</v>
+        <v>6526.774445776197</v>
       </c>
       <c r="E67">
-        <v>1791.542582339971</v>
+        <v>1865.1270799874</v>
       </c>
       <c r="F67">
-        <v>4782.992347082913</v>
+        <v>4856.576844730342</v>
       </c>
       <c r="G67">
         <v>751.9</v>
@@ -6781,28 +6781,28 @@
         <v>2022.56</v>
       </c>
       <c r="M67">
-        <v>354.6946986455165</v>
+        <v>360.1515401631398</v>
       </c>
       <c r="N67">
-        <v>1667.865301354484</v>
+        <v>1662.40845983686</v>
       </c>
       <c r="O67">
-        <v>150.1078771219035</v>
+        <v>149.6167613853174</v>
       </c>
       <c r="P67">
-        <v>1517.75742423258</v>
+        <v>1512.791698451543</v>
       </c>
       <c r="Q67">
-        <v>2768.65742423258</v>
+        <v>2763.691698451543</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2186336965970468</v>
+        <v>0.2235469659076998</v>
       </c>
       <c r="T67">
-        <v>2.514940876941397</v>
+        <v>2.586434932047975</v>
       </c>
       <c r="U67">
         <v>0.07415748822216711</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.702256074656915</v>
+        <v>5.61585825534393</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1205449558348515</v>
+        <v>0.1207039635773248</v>
       </c>
       <c r="C68">
-        <v>2422.097601045855</v>
+        <v>2343.219866758075</v>
       </c>
       <c r="D68">
-        <v>6526.774445776197</v>
+        <v>6521.481209135846</v>
       </c>
       <c r="E68">
-        <v>1865.1270799874</v>
+        <v>1938.711577634829</v>
       </c>
       <c r="F68">
-        <v>4856.576844730342</v>
+        <v>4930.161342377771</v>
       </c>
       <c r="G68">
         <v>751.9</v>
@@ -6863,28 +6863,28 @@
         <v>2022.56</v>
       </c>
       <c r="M68">
-        <v>360.1515401631398</v>
+        <v>365.6083816807632</v>
       </c>
       <c r="N68">
-        <v>1662.40845983686</v>
+        <v>1656.951618319237</v>
       </c>
       <c r="O68">
-        <v>149.6167613853174</v>
+        <v>149.1256456487313</v>
       </c>
       <c r="P68">
-        <v>1512.791698451543</v>
+        <v>1507.825972670506</v>
       </c>
       <c r="Q68">
-        <v>2763.691698451543</v>
+        <v>2758.725972670506</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2235469659076998</v>
+        <v>0.2287580091159681</v>
       </c>
       <c r="T68">
-        <v>2.586434932047975</v>
+        <v>2.662261960191316</v>
       </c>
       <c r="U68">
         <v>0.07415748822216711</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.61585825534393</v>
+        <v>5.532039475413424</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1207039635773248</v>
+        <v>0.120862971319798</v>
       </c>
       <c r="C69">
-        <v>2343.219866758075</v>
+        <v>2264.350711179364</v>
       </c>
       <c r="D69">
-        <v>6521.481209135846</v>
+        <v>6516.196551204565</v>
       </c>
       <c r="E69">
-        <v>1938.711577634829</v>
+        <v>2012.296075282259</v>
       </c>
       <c r="F69">
-        <v>4930.161342377771</v>
+        <v>5003.745840025201</v>
       </c>
       <c r="G69">
         <v>751.9</v>
@@ -6945,28 +6945,28 @@
         <v>2022.56</v>
       </c>
       <c r="M69">
-        <v>365.6083816807632</v>
+        <v>371.0652231983865</v>
       </c>
       <c r="N69">
-        <v>1656.951618319237</v>
+        <v>1651.494776801613</v>
       </c>
       <c r="O69">
-        <v>149.1256456487313</v>
+        <v>148.6345299121452</v>
       </c>
       <c r="P69">
-        <v>1507.825972670506</v>
+        <v>1502.860246889468</v>
       </c>
       <c r="Q69">
-        <v>2758.725972670506</v>
+        <v>2753.760246889468</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2287580091159681</v>
+        <v>0.2342947425247532</v>
       </c>
       <c r="T69">
-        <v>2.662261960191316</v>
+        <v>2.742828177593615</v>
       </c>
       <c r="U69">
         <v>0.07415748822216711</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.532039475413424</v>
+        <v>5.450685953716167</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.120862971319798</v>
+        <v>0.1210219790622713</v>
       </c>
       <c r="C70">
-        <v>2264.350711179364</v>
+        <v>2185.490113471432</v>
       </c>
       <c r="D70">
-        <v>6516.196551204565</v>
+        <v>6510.920451144062</v>
       </c>
       <c r="E70">
-        <v>2012.296075282259</v>
+        <v>2085.880572929688</v>
       </c>
       <c r="F70">
-        <v>5003.745840025201</v>
+        <v>5077.33033767263</v>
       </c>
       <c r="G70">
         <v>751.9</v>
@@ -7027,28 +7027,28 @@
         <v>2022.56</v>
       </c>
       <c r="M70">
-        <v>371.0652231983865</v>
+        <v>376.5220647160098</v>
       </c>
       <c r="N70">
-        <v>1651.494776801613</v>
+        <v>1646.03793528399</v>
       </c>
       <c r="O70">
-        <v>148.6345299121452</v>
+        <v>148.1434141755591</v>
       </c>
       <c r="P70">
-        <v>1502.860246889468</v>
+        <v>1497.894521108431</v>
       </c>
       <c r="Q70">
-        <v>2753.760246889468</v>
+        <v>2748.794521108431</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2342947425247532</v>
+        <v>0.2401886845405567</v>
       </c>
       <c r="T70">
-        <v>2.742828177593615</v>
+        <v>2.828592215473482</v>
       </c>
       <c r="U70">
         <v>0.07415748822216711</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.450685953716167</v>
+        <v>5.371690505111586</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1210219790622713</v>
+        <v>0.1211809868047446</v>
       </c>
       <c r="C71">
-        <v>2185.490113471432</v>
+        <v>2106.638052863427</v>
       </c>
       <c r="D71">
-        <v>6510.920451144062</v>
+        <v>6505.652888183487</v>
       </c>
       <c r="E71">
-        <v>2085.880572929688</v>
+        <v>2159.465070577118</v>
       </c>
       <c r="F71">
-        <v>5077.33033767263</v>
+        <v>5150.91483532006</v>
       </c>
       <c r="G71">
         <v>751.9</v>
@@ -7109,28 +7109,28 @@
         <v>2022.56</v>
       </c>
       <c r="M71">
-        <v>376.5220647160098</v>
+        <v>381.9789062336332</v>
       </c>
       <c r="N71">
-        <v>1646.03793528399</v>
+        <v>1640.581093766367</v>
       </c>
       <c r="O71">
-        <v>148.1434141755591</v>
+        <v>147.652298438973</v>
       </c>
       <c r="P71">
-        <v>1497.894521108431</v>
+        <v>1492.928795327394</v>
       </c>
       <c r="Q71">
-        <v>2748.794521108431</v>
+        <v>2743.828795327394</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2401886845405567</v>
+        <v>0.2464755560240804</v>
       </c>
       <c r="T71">
-        <v>2.828592215473482</v>
+        <v>2.920073855878673</v>
       </c>
       <c r="U71">
         <v>0.07415748822216711</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.371690505111586</v>
+        <v>5.294952069324276</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1211809868047446</v>
+        <v>0.1213399945472178</v>
       </c>
       <c r="C72">
-        <v>2106.638052863427</v>
+        <v>2027.794508651661</v>
       </c>
       <c r="D72">
-        <v>6505.652888183487</v>
+        <v>6500.39384161915</v>
       </c>
       <c r="E72">
-        <v>2159.465070577118</v>
+        <v>2233.049568224547</v>
       </c>
       <c r="F72">
-        <v>5150.91483532006</v>
+        <v>5224.499332967489</v>
       </c>
       <c r="G72">
         <v>751.9</v>
@@ -7191,28 +7191,28 @@
         <v>2022.56</v>
       </c>
       <c r="M72">
-        <v>381.9789062336332</v>
+        <v>387.4357477512565</v>
       </c>
       <c r="N72">
-        <v>1640.581093766367</v>
+        <v>1635.124252248743</v>
       </c>
       <c r="O72">
-        <v>147.652298438973</v>
+        <v>147.1611827023869</v>
       </c>
       <c r="P72">
-        <v>1492.928795327394</v>
+        <v>1487.963069546357</v>
       </c>
       <c r="Q72">
-        <v>2743.828795327394</v>
+        <v>2738.863069546357</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2464755560240804</v>
+        <v>0.2531960048512954</v>
       </c>
       <c r="T72">
-        <v>2.920073855878673</v>
+        <v>3.017864574932499</v>
       </c>
       <c r="U72">
         <v>0.07415748822216711</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.294952069324276</v>
+        <v>5.220375279615484</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1213399945472178</v>
+        <v>0.1214990022896911</v>
       </c>
       <c r="C73">
-        <v>2027.794508651662</v>
+        <v>1948.959460199334</v>
       </c>
       <c r="D73">
-        <v>6500.39384161915</v>
+        <v>6495.143290814252</v>
       </c>
       <c r="E73">
-        <v>2233.049568224546</v>
+        <v>2306.634065871976</v>
       </c>
       <c r="F73">
-        <v>5224.499332967488</v>
+        <v>5298.083830614918</v>
       </c>
       <c r="G73">
         <v>751.9</v>
@@ -7273,28 +7273,28 @@
         <v>2022.56</v>
       </c>
       <c r="M73">
-        <v>387.4357477512564</v>
+        <v>392.8925892688798</v>
       </c>
       <c r="N73">
-        <v>1635.124252248743</v>
+        <v>1629.66741073112</v>
       </c>
       <c r="O73">
-        <v>147.1611827023869</v>
+        <v>146.6700669658008</v>
       </c>
       <c r="P73">
-        <v>1487.963069546357</v>
+        <v>1482.997343765319</v>
       </c>
       <c r="Q73">
-        <v>2738.863069546357</v>
+        <v>2733.897343765319</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2531960048512953</v>
+        <v>0.2603964857375971</v>
       </c>
       <c r="T73">
-        <v>3.017864574932497</v>
+        <v>3.12264034534731</v>
       </c>
       <c r="U73">
         <v>0.07415748822216711</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.220375279615485</v>
+        <v>5.147870067398602</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1214990022896911</v>
+        <v>0.1216580100321643</v>
       </c>
       <c r="C74">
-        <v>1948.959460199334</v>
+        <v>1870.132886936272</v>
       </c>
       <c r="D74">
-        <v>6495.143290814252</v>
+        <v>6489.90121519862</v>
       </c>
       <c r="E74">
-        <v>2306.634065871976</v>
+        <v>2380.218563519405</v>
       </c>
       <c r="F74">
-        <v>5298.083830614918</v>
+        <v>5371.668328262347</v>
       </c>
       <c r="G74">
         <v>751.9</v>
@@ -7355,28 +7355,28 @@
         <v>2022.56</v>
       </c>
       <c r="M74">
-        <v>392.8925892688798</v>
+        <v>398.3494307865031</v>
       </c>
       <c r="N74">
-        <v>1629.66741073112</v>
+        <v>1624.210569213497</v>
       </c>
       <c r="O74">
-        <v>146.6700669658008</v>
+        <v>146.1789512292147</v>
       </c>
       <c r="P74">
-        <v>1482.997343765319</v>
+        <v>1478.031617984282</v>
       </c>
       <c r="Q74">
-        <v>2733.897343765319</v>
+        <v>2728.931617984282</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2603964857375971</v>
+        <v>0.2681303355784397</v>
       </c>
       <c r="T74">
-        <v>3.12264034534731</v>
+        <v>3.235177283940998</v>
       </c>
       <c r="U74">
         <v>0.07415748822216711</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.147870067398602</v>
+        <v>5.077351299352047</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1216580100321643</v>
+        <v>0.1218170177746376</v>
       </c>
       <c r="C75">
-        <v>1870.132886936272</v>
+        <v>1791.314768358649</v>
       </c>
       <c r="D75">
-        <v>6489.90121519862</v>
+        <v>6484.667594268427</v>
       </c>
       <c r="E75">
-        <v>2380.218563519405</v>
+        <v>2453.803061166835</v>
       </c>
       <c r="F75">
-        <v>5371.668328262347</v>
+        <v>5445.252825909777</v>
       </c>
       <c r="G75">
         <v>751.9</v>
@@ -7437,28 +7437,28 @@
         <v>2022.56</v>
       </c>
       <c r="M75">
-        <v>398.3494307865031</v>
+        <v>403.8062723041265</v>
       </c>
       <c r="N75">
-        <v>1624.210569213497</v>
+        <v>1618.753727695874</v>
       </c>
       <c r="O75">
-        <v>146.1789512292147</v>
+        <v>145.6878354926286</v>
       </c>
       <c r="P75">
-        <v>1478.031617984282</v>
+        <v>1473.065892203245</v>
       </c>
       <c r="Q75">
-        <v>2728.931617984282</v>
+        <v>2723.965892203245</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2681303355784397</v>
+        <v>0.276459096945501</v>
       </c>
       <c r="T75">
-        <v>3.235177283940998</v>
+        <v>3.356370910118815</v>
       </c>
       <c r="U75">
         <v>0.07415748822216711</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.077351299352047</v>
+        <v>5.008738443955398</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1218170177746376</v>
+        <v>0.1219760255171109</v>
       </c>
       <c r="C76">
-        <v>1791.314768358649</v>
+        <v>1712.505084028733</v>
       </c>
       <c r="D76">
-        <v>6484.667594268427</v>
+        <v>6479.44240758594</v>
       </c>
       <c r="E76">
-        <v>2453.803061166835</v>
+        <v>2527.387558814264</v>
       </c>
       <c r="F76">
-        <v>5445.252825909777</v>
+        <v>5518.837323557206</v>
       </c>
       <c r="G76">
         <v>751.9</v>
@@ -7519,28 +7519,28 @@
         <v>2022.56</v>
       </c>
       <c r="M76">
-        <v>403.8062723041265</v>
+        <v>409.2631138217498</v>
       </c>
       <c r="N76">
-        <v>1618.753727695874</v>
+        <v>1613.29688617825</v>
       </c>
       <c r="O76">
-        <v>145.6878354926286</v>
+        <v>145.1967197560425</v>
       </c>
       <c r="P76">
-        <v>1473.065892203245</v>
+        <v>1468.100166422208</v>
       </c>
       <c r="Q76">
-        <v>2723.965892203245</v>
+        <v>2719.000166422208</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.276459096945501</v>
+        <v>0.2854541592219273</v>
       </c>
       <c r="T76">
-        <v>3.356370910118815</v>
+        <v>3.487260026390859</v>
       </c>
       <c r="U76">
         <v>0.07415748822216711</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.008738443955398</v>
+        <v>4.941955264702658</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1219760255171109</v>
+        <v>0.1221350332595841</v>
       </c>
       <c r="C77">
-        <v>1712.505084028733</v>
+        <v>1633.703813574604</v>
       </c>
       <c r="D77">
-        <v>6479.44240758594</v>
+        <v>6474.22563477924</v>
       </c>
       <c r="E77">
-        <v>2527.387558814264</v>
+        <v>2600.972056461693</v>
       </c>
       <c r="F77">
-        <v>5518.837323557206</v>
+        <v>5592.421821204635</v>
       </c>
       <c r="G77">
         <v>751.9</v>
@@ -7601,28 +7601,28 @@
         <v>2022.56</v>
       </c>
       <c r="M77">
-        <v>409.2631138217498</v>
+        <v>414.7199553393731</v>
       </c>
       <c r="N77">
-        <v>1613.29688617825</v>
+        <v>1607.840044660627</v>
       </c>
       <c r="O77">
-        <v>145.1967197560425</v>
+        <v>144.7056040194564</v>
       </c>
       <c r="P77">
-        <v>1468.100166422208</v>
+        <v>1463.134440641171</v>
       </c>
       <c r="Q77">
-        <v>2719.000166422208</v>
+        <v>2714.03444064117</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2854541592219273</v>
+        <v>0.295198810021389</v>
       </c>
       <c r="T77">
-        <v>3.487260026390859</v>
+        <v>3.629056569018906</v>
       </c>
       <c r="U77">
         <v>0.07415748822216711</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.941955264702658</v>
+        <v>4.876929537535519</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1221350332595841</v>
+        <v>0.1222940410020574</v>
       </c>
       <c r="C78">
-        <v>1633.703813574604</v>
+        <v>1554.910936689898</v>
       </c>
       <c r="D78">
-        <v>6474.22563477924</v>
+        <v>6469.017255541964</v>
       </c>
       <c r="E78">
-        <v>2600.972056461693</v>
+        <v>2674.556554109123</v>
       </c>
       <c r="F78">
-        <v>5592.421821204635</v>
+        <v>5666.006318852065</v>
       </c>
       <c r="G78">
         <v>751.9</v>
@@ -7683,28 +7683,28 @@
         <v>2022.56</v>
       </c>
       <c r="M78">
-        <v>414.7199553393731</v>
+        <v>420.1767968569965</v>
       </c>
       <c r="N78">
-        <v>1607.840044660627</v>
+        <v>1602.383203143003</v>
       </c>
       <c r="O78">
-        <v>144.7056040194564</v>
+        <v>144.2144882828703</v>
       </c>
       <c r="P78">
-        <v>1463.134440641171</v>
+        <v>1458.168714860133</v>
       </c>
       <c r="Q78">
-        <v>2714.03444064117</v>
+        <v>2709.068714860133</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.295198810021389</v>
+        <v>0.3057908217599344</v>
       </c>
       <c r="T78">
-        <v>3.629056569018906</v>
+        <v>3.783183245788522</v>
       </c>
       <c r="U78">
         <v>0.07415748822216711</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.876929537535519</v>
+        <v>4.813592790294797</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1222940410020574</v>
+        <v>0.1224530487445307</v>
       </c>
       <c r="C79">
-        <v>1554.910936689898</v>
+        <v>1476.126433133551</v>
       </c>
       <c r="D79">
-        <v>6469.017255541964</v>
+        <v>6463.817249633046</v>
       </c>
       <c r="E79">
-        <v>2674.556554109123</v>
+        <v>2748.141051756552</v>
       </c>
       <c r="F79">
-        <v>5666.006318852065</v>
+        <v>5739.590816499494</v>
       </c>
       <c r="G79">
         <v>751.9</v>
@@ -7765,28 +7765,28 @@
         <v>2022.56</v>
       </c>
       <c r="M79">
-        <v>420.1767968569965</v>
+        <v>425.6336383746197</v>
       </c>
       <c r="N79">
-        <v>1602.383203143003</v>
+        <v>1596.92636162538</v>
       </c>
       <c r="O79">
-        <v>144.2144882828703</v>
+        <v>143.7233725462842</v>
       </c>
       <c r="P79">
-        <v>1458.168714860133</v>
+        <v>1453.202989079096</v>
       </c>
       <c r="Q79">
-        <v>2709.068714860133</v>
+        <v>2704.102989079096</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3057908217599344</v>
+        <v>0.3173457436565294</v>
       </c>
       <c r="T79">
-        <v>3.783183245788522</v>
+        <v>3.951321438628102</v>
       </c>
       <c r="U79">
         <v>0.07415748822216711</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.813592790294797</v>
+        <v>4.751880062214095</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1224530487445307</v>
+        <v>0.1226120564870039</v>
       </c>
       <c r="C80">
-        <v>1476.126433133551</v>
+        <v>1397.350282729518</v>
       </c>
       <c r="D80">
-        <v>6463.817249633046</v>
+        <v>6458.625596876443</v>
       </c>
       <c r="E80">
-        <v>2748.141051756552</v>
+        <v>2821.725549403982</v>
       </c>
       <c r="F80">
-        <v>5739.590816499494</v>
+        <v>5813.175314146924</v>
       </c>
       <c r="G80">
         <v>751.9</v>
@@ -7847,28 +7847,28 @@
         <v>2022.56</v>
       </c>
       <c r="M80">
-        <v>425.6336383746197</v>
+        <v>431.0904798922431</v>
       </c>
       <c r="N80">
-        <v>1596.92636162538</v>
+        <v>1591.469520107757</v>
       </c>
       <c r="O80">
-        <v>143.7233725462842</v>
+        <v>143.2322568096981</v>
       </c>
       <c r="P80">
-        <v>1453.202989079096</v>
+        <v>1448.237263298059</v>
       </c>
       <c r="Q80">
-        <v>2704.102989079096</v>
+        <v>2699.137263298059</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3173457436565294</v>
+        <v>0.330001134305181</v>
       </c>
       <c r="T80">
-        <v>3.951321438628102</v>
+        <v>4.135472792690501</v>
       </c>
       <c r="U80">
         <v>0.07415748822216711</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.751880062214095</v>
+        <v>4.691729681679739</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1226120564870039</v>
+        <v>0.1227710642294772</v>
       </c>
       <c r="C81">
-        <v>1397.350282729518</v>
+        <v>1318.582465366528</v>
       </c>
       <c r="D81">
-        <v>6458.625596876443</v>
+        <v>6453.442277160882</v>
       </c>
       <c r="E81">
-        <v>2821.725549403982</v>
+        <v>2895.310047051411</v>
       </c>
       <c r="F81">
-        <v>5813.175314146924</v>
+        <v>5886.759811794353</v>
       </c>
       <c r="G81">
         <v>751.9</v>
@@ -7929,28 +7929,28 @@
         <v>2022.56</v>
       </c>
       <c r="M81">
-        <v>431.0904798922431</v>
+        <v>436.5473214098665</v>
       </c>
       <c r="N81">
-        <v>1591.469520107757</v>
+        <v>1586.012678590133</v>
       </c>
       <c r="O81">
-        <v>143.2322568096981</v>
+        <v>142.741141073112</v>
       </c>
       <c r="P81">
-        <v>1448.237263298059</v>
+        <v>1443.271537517021</v>
       </c>
       <c r="Q81">
-        <v>2699.137263298059</v>
+        <v>2694.171537517022</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.330001134305181</v>
+        <v>0.3439220640186978</v>
       </c>
       <c r="T81">
-        <v>4.135472792690501</v>
+        <v>4.338039282159139</v>
       </c>
       <c r="U81">
         <v>0.07415748822216711</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.691729681679739</v>
+        <v>4.633083060658743</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1227710642294772</v>
+        <v>0.1229300719719505</v>
       </c>
       <c r="C82">
-        <v>1318.582465366528</v>
+        <v>1239.822960997817</v>
       </c>
       <c r="D82">
-        <v>6453.442277160882</v>
+        <v>6448.267270439601</v>
       </c>
       <c r="E82">
-        <v>2895.310047051411</v>
+        <v>2968.894544698841</v>
       </c>
       <c r="F82">
-        <v>5886.759811794353</v>
+        <v>5960.344309441783</v>
       </c>
       <c r="G82">
         <v>751.9</v>
@@ -8011,28 +8011,28 @@
         <v>2022.56</v>
       </c>
       <c r="M82">
-        <v>436.5473214098665</v>
+        <v>442.0041629274898</v>
       </c>
       <c r="N82">
-        <v>1586.012678590133</v>
+        <v>1580.55583707251</v>
       </c>
       <c r="O82">
-        <v>142.741141073112</v>
+        <v>142.2500253365259</v>
       </c>
       <c r="P82">
-        <v>1443.271537517021</v>
+        <v>1438.305811735984</v>
       </c>
       <c r="Q82">
-        <v>2694.171537517022</v>
+        <v>2689.205811735985</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3439220640186978</v>
+        <v>0.35930835475469</v>
       </c>
       <c r="T82">
-        <v>4.338039282159139</v>
+        <v>4.561928559992896</v>
       </c>
       <c r="U82">
         <v>0.07415748822216711</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.633083060658743</v>
+        <v>4.575884504354313</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1229300719719505</v>
+        <v>0.1230890797144237</v>
       </c>
       <c r="C83">
-        <v>1239.822960997817</v>
+        <v>1161.071749640873</v>
       </c>
       <c r="D83">
-        <v>6448.267270439601</v>
+        <v>6443.100556730086</v>
       </c>
       <c r="E83">
-        <v>2968.894544698841</v>
+        <v>3042.47904234627</v>
       </c>
       <c r="F83">
-        <v>5960.344309441783</v>
+        <v>6033.928807089213</v>
       </c>
       <c r="G83">
         <v>751.9</v>
@@ -8093,28 +8093,28 @@
         <v>2022.56</v>
       </c>
       <c r="M83">
-        <v>442.0041629274898</v>
+        <v>447.4610044451131</v>
       </c>
       <c r="N83">
-        <v>1580.55583707251</v>
+        <v>1575.098995554887</v>
       </c>
       <c r="O83">
-        <v>142.2500253365259</v>
+        <v>141.7589095999398</v>
       </c>
       <c r="P83">
-        <v>1438.305811735984</v>
+        <v>1433.340085954947</v>
       </c>
       <c r="Q83">
-        <v>2689.205811735985</v>
+        <v>2684.240085954947</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.35930835475469</v>
+        <v>0.376404233350237</v>
       </c>
       <c r="T83">
-        <v>4.561928559992896</v>
+        <v>4.810694424252627</v>
       </c>
       <c r="U83">
         <v>0.07415748822216711</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.575884504354313</v>
+        <v>4.520081034789017</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1230890797144237</v>
+        <v>0.125136337456897</v>
       </c>
       <c r="C84">
-        <v>1161.071749640873</v>
+        <v>1021.696757447519</v>
       </c>
       <c r="D84">
-        <v>6443.100556730086</v>
+        <v>6377.310062184161</v>
       </c>
       <c r="E84">
-        <v>3042.47904234627</v>
+        <v>3116.0635399937</v>
       </c>
       <c r="F84">
-        <v>6033.928807089213</v>
+        <v>6107.513304736642</v>
       </c>
       <c r="G84">
         <v>751.9</v>
@@ -8175,45 +8175,45 @@
         <v>2022.56</v>
       </c>
       <c r="M84">
-        <v>447.4610044451131</v>
+        <v>468.186629224578</v>
       </c>
       <c r="N84">
-        <v>1575.098995554887</v>
+        <v>1554.373370775422</v>
       </c>
       <c r="O84">
-        <v>141.7589095999398</v>
+        <v>139.893603369788</v>
       </c>
       <c r="P84">
-        <v>1433.340085954947</v>
+        <v>1414.479767405634</v>
       </c>
       <c r="Q84">
-        <v>2684.240085954947</v>
+        <v>2665.379767405634</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.376404233350237</v>
+        <v>0.3955113917805542</v>
       </c>
       <c r="T84">
-        <v>4.810694424252627</v>
+        <v>5.08872686077821</v>
       </c>
       <c r="U84">
-        <v>0.07415748822216711</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V84">
         <v>0.09</v>
       </c>
       <c r="W84">
-        <v>0.06748331428217208</v>
+        <v>0.06975831428217208</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.520081034789017</v>
+        <v>4.319986675719067</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.125136337456897</v>
+        <v>0.1253180951993703</v>
       </c>
       <c r="C85">
-        <v>1021.696757447519</v>
+        <v>942.3361871971092</v>
       </c>
       <c r="D85">
-        <v>6377.310062184161</v>
+        <v>6371.533989581181</v>
       </c>
       <c r="E85">
-        <v>3116.0635399937</v>
+        <v>3189.64803764113</v>
       </c>
       <c r="F85">
-        <v>6107.513304736642</v>
+        <v>6181.097802384072</v>
       </c>
       <c r="G85">
         <v>751.9</v>
@@ -8257,28 +8257,28 @@
         <v>2022.56</v>
       </c>
       <c r="M85">
-        <v>468.186629224578</v>
+        <v>473.82743198632</v>
       </c>
       <c r="N85">
-        <v>1554.373370775422</v>
+        <v>1548.73256801368</v>
       </c>
       <c r="O85">
-        <v>139.893603369788</v>
+        <v>139.3859311212312</v>
       </c>
       <c r="P85">
-        <v>1414.479767405634</v>
+        <v>1409.346636892449</v>
       </c>
       <c r="Q85">
-        <v>2665.379767405634</v>
+        <v>2660.246636892449</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3955113917805542</v>
+        <v>0.4170069450146611</v>
       </c>
       <c r="T85">
-        <v>5.08872686077821</v>
+        <v>5.40151335186949</v>
       </c>
       <c r="U85">
         <v>0.07665748822216711</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.319986675719067</v>
+        <v>4.268558262912887</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1253180951993703</v>
+        <v>0.1254998529418436</v>
       </c>
       <c r="C86">
-        <v>942.3361871971101</v>
+        <v>862.9860705154006</v>
       </c>
       <c r="D86">
-        <v>6371.533989581181</v>
+        <v>6365.768370546901</v>
       </c>
       <c r="E86">
-        <v>3189.648037641129</v>
+        <v>3263.232535288558</v>
       </c>
       <c r="F86">
-        <v>6181.097802384071</v>
+        <v>6254.6823000315</v>
       </c>
       <c r="G86">
         <v>751.9</v>
@@ -8339,28 +8339,28 @@
         <v>2022.56</v>
       </c>
       <c r="M86">
-        <v>473.8274319863199</v>
+        <v>479.4682347480618</v>
       </c>
       <c r="N86">
-        <v>1548.73256801368</v>
+        <v>1543.091765251938</v>
       </c>
       <c r="O86">
-        <v>139.3859311212312</v>
+        <v>138.8782588726744</v>
       </c>
       <c r="P86">
-        <v>1409.346636892449</v>
+        <v>1404.213506379264</v>
       </c>
       <c r="Q86">
-        <v>2660.246636892449</v>
+        <v>2655.113506379264</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4170069450146608</v>
+        <v>0.4413685720133152</v>
       </c>
       <c r="T86">
-        <v>5.401513351869486</v>
+        <v>5.756004708439603</v>
       </c>
       <c r="U86">
         <v>0.07665748822216711</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.268558262912887</v>
+        <v>4.21833993040803</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1254998529418436</v>
+        <v>0.1256816106843168</v>
       </c>
       <c r="C87">
-        <v>862.9860705154006</v>
+        <v>783.6463790496573</v>
       </c>
       <c r="D87">
-        <v>6365.768370546901</v>
+        <v>6360.013176728587</v>
       </c>
       <c r="E87">
-        <v>3263.232535288558</v>
+        <v>3336.817032935988</v>
       </c>
       <c r="F87">
-        <v>6254.6823000315</v>
+        <v>6328.26679767893</v>
       </c>
       <c r="G87">
         <v>751.9</v>
@@ -8421,28 +8421,28 @@
         <v>2022.56</v>
       </c>
       <c r="M87">
-        <v>479.4682347480618</v>
+        <v>485.1090375098038</v>
       </c>
       <c r="N87">
-        <v>1543.091765251938</v>
+        <v>1537.450962490196</v>
       </c>
       <c r="O87">
-        <v>138.8782588726744</v>
+        <v>138.3705866241176</v>
       </c>
       <c r="P87">
-        <v>1404.213506379264</v>
+        <v>1399.080375866079</v>
       </c>
       <c r="Q87">
-        <v>2655.113506379264</v>
+        <v>2649.980375866079</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4413685720133152</v>
+        <v>0.4692104314403487</v>
       </c>
       <c r="T87">
-        <v>5.756004708439603</v>
+        <v>6.161137687376879</v>
       </c>
       <c r="U87">
         <v>0.07665748822216711</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.21833993040803</v>
+        <v>4.16928946610096</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1256816106843168</v>
+        <v>0.1258633684267901</v>
       </c>
       <c r="C88">
-        <v>783.6463790496573</v>
+        <v>704.3170845495861</v>
       </c>
       <c r="D88">
-        <v>6360.013176728587</v>
+        <v>6354.268379875945</v>
       </c>
       <c r="E88">
-        <v>3336.817032935988</v>
+        <v>3410.401530583417</v>
       </c>
       <c r="F88">
-        <v>6328.26679767893</v>
+        <v>6401.851295326359</v>
       </c>
       <c r="G88">
         <v>751.9</v>
@@ -8503,28 +8503,28 @@
         <v>2022.56</v>
       </c>
       <c r="M88">
-        <v>485.1090375098038</v>
+        <v>490.7498402715456</v>
       </c>
       <c r="N88">
-        <v>1537.450962490196</v>
+        <v>1531.810159728454</v>
       </c>
       <c r="O88">
-        <v>138.3705866241176</v>
+        <v>137.8629143755609</v>
       </c>
       <c r="P88">
-        <v>1399.080375866079</v>
+        <v>1393.947245352894</v>
       </c>
       <c r="Q88">
-        <v>2649.980375866079</v>
+        <v>2644.847245352894</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4692104314403487</v>
+        <v>0.5013356538561566</v>
       </c>
       <c r="T88">
-        <v>6.161137687376879</v>
+        <v>6.628598816919889</v>
       </c>
       <c r="U88">
         <v>0.07665748822216711</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.16928946610096</v>
+        <v>4.121366598674513</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1258633684267901</v>
+        <v>0.1260451261692633</v>
       </c>
       <c r="C89">
-        <v>704.3170845495861</v>
+        <v>624.9981588668697</v>
       </c>
       <c r="D89">
-        <v>6354.268379875945</v>
+        <v>6348.533951840659</v>
       </c>
       <c r="E89">
-        <v>3410.401530583417</v>
+        <v>3483.986028230847</v>
       </c>
       <c r="F89">
-        <v>6401.851295326359</v>
+        <v>6475.435792973789</v>
       </c>
       <c r="G89">
         <v>751.9</v>
@@ -8585,28 +8585,28 @@
         <v>2022.56</v>
       </c>
       <c r="M89">
-        <v>490.7498402715456</v>
+        <v>496.3906430332876</v>
       </c>
       <c r="N89">
-        <v>1531.810159728454</v>
+        <v>1526.169356966712</v>
       </c>
       <c r="O89">
-        <v>137.8629143755609</v>
+        <v>137.3552421270041</v>
       </c>
       <c r="P89">
-        <v>1393.947245352894</v>
+        <v>1388.814114839708</v>
       </c>
       <c r="Q89">
-        <v>2644.847245352894</v>
+        <v>2639.714114839708</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5013356538561566</v>
+        <v>0.5388150800079327</v>
       </c>
       <c r="T89">
-        <v>6.628598816919889</v>
+        <v>7.17397013472007</v>
       </c>
       <c r="U89">
         <v>0.07665748822216711</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.121366598674513</v>
+        <v>4.074532887325937</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1260451261692633</v>
+        <v>0.1262268839117366</v>
       </c>
       <c r="C90">
-        <v>624.9981588668697</v>
+        <v>545.6895739547117</v>
       </c>
       <c r="D90">
-        <v>6348.533951840659</v>
+        <v>6342.80986457593</v>
       </c>
       <c r="E90">
-        <v>3483.986028230847</v>
+        <v>3557.570525878276</v>
       </c>
       <c r="F90">
-        <v>6475.435792973789</v>
+        <v>6549.020290621218</v>
       </c>
       <c r="G90">
         <v>751.9</v>
@@ -8667,28 +8667,28 @@
         <v>2022.56</v>
       </c>
       <c r="M90">
-        <v>496.3906430332876</v>
+        <v>502.0314457950295</v>
       </c>
       <c r="N90">
-        <v>1526.169356966712</v>
+        <v>1520.528554204971</v>
       </c>
       <c r="O90">
-        <v>137.3552421270041</v>
+        <v>136.8475698784473</v>
       </c>
       <c r="P90">
-        <v>1388.814114839708</v>
+        <v>1383.680984326523</v>
       </c>
       <c r="Q90">
-        <v>2639.714114839708</v>
+        <v>2634.580984326523</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5388150800079327</v>
+        <v>0.5831089472782133</v>
       </c>
       <c r="T90">
-        <v>7.17397013472007</v>
+        <v>7.818499873938462</v>
       </c>
       <c r="U90">
         <v>0.07665748822216711</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.074532887325937</v>
+        <v>4.028751618929017</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1262268839117366</v>
+        <v>0.1292751416542099</v>
       </c>
       <c r="C91">
-        <v>545.6895739547117</v>
+        <v>377.621726724431</v>
       </c>
       <c r="D91">
-        <v>6342.80986457593</v>
+        <v>6248.326514993079</v>
       </c>
       <c r="E91">
-        <v>3557.570525878276</v>
+        <v>3631.155023525706</v>
       </c>
       <c r="F91">
-        <v>6549.020290621218</v>
+        <v>6622.604788268648</v>
       </c>
       <c r="G91">
         <v>751.9</v>
@@ -8749,45 +8749,45 @@
         <v>2022.56</v>
       </c>
       <c r="M91">
-        <v>502.0314457950295</v>
+        <v>530.8513653157117</v>
       </c>
       <c r="N91">
-        <v>1520.528554204971</v>
+        <v>1491.708634684288</v>
       </c>
       <c r="O91">
-        <v>136.8475698784473</v>
+        <v>134.2537771215859</v>
       </c>
       <c r="P91">
-        <v>1383.680984326523</v>
+        <v>1357.454857562702</v>
       </c>
       <c r="Q91">
-        <v>2634.580984326523</v>
+        <v>2608.354857562702</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5831089472782133</v>
+        <v>0.6362615880025501</v>
       </c>
       <c r="T91">
-        <v>7.818499873938462</v>
+        <v>8.591935561000534</v>
       </c>
       <c r="U91">
-        <v>0.07665748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V91">
         <v>0.09</v>
       </c>
       <c r="W91">
-        <v>0.06975831428217208</v>
+        <v>0.07294331428217207</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.028751618929017</v>
+        <v>3.810030701903024</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1292751416542099</v>
+        <v>0.1294887493966831</v>
       </c>
       <c r="C92">
-        <v>377.621726724431</v>
+        <v>297.521702713444</v>
       </c>
       <c r="D92">
-        <v>6248.326514993079</v>
+        <v>6241.810988629521</v>
       </c>
       <c r="E92">
-        <v>3631.155023525706</v>
+        <v>3704.739521173135</v>
       </c>
       <c r="F92">
-        <v>6622.604788268648</v>
+        <v>6696.189285916077</v>
       </c>
       <c r="G92">
         <v>751.9</v>
@@ -8831,28 +8831,28 @@
         <v>2022.56</v>
       </c>
       <c r="M92">
-        <v>530.8513653157117</v>
+        <v>536.7497138192196</v>
       </c>
       <c r="N92">
-        <v>1491.708634684288</v>
+        <v>1485.81028618078</v>
       </c>
       <c r="O92">
-        <v>134.2537771215859</v>
+        <v>133.7229257562702</v>
       </c>
       <c r="P92">
-        <v>1357.454857562702</v>
+        <v>1352.08736042451</v>
       </c>
       <c r="Q92">
-        <v>2608.354857562702</v>
+        <v>2602.98736042451</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6362615880025501</v>
+        <v>0.7012259266656286</v>
       </c>
       <c r="T92">
-        <v>8.591935561000534</v>
+        <v>9.537245845187513</v>
       </c>
       <c r="U92">
         <v>0.08015748822216712</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.810030701903024</v>
+        <v>3.768162232651343</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1294887493966831</v>
+        <v>0.1297023571391564</v>
       </c>
       <c r="C93">
-        <v>297.521702713444</v>
+        <v>217.4352528530162</v>
       </c>
       <c r="D93">
-        <v>6241.810988629521</v>
+        <v>6235.309036416523</v>
       </c>
       <c r="E93">
-        <v>3704.739521173135</v>
+        <v>3778.324018820564</v>
       </c>
       <c r="F93">
-        <v>6696.189285916077</v>
+        <v>6769.773783563506</v>
       </c>
       <c r="G93">
         <v>751.9</v>
@@ -8913,28 +8913,28 @@
         <v>2022.56</v>
       </c>
       <c r="M93">
-        <v>536.7497138192196</v>
+        <v>542.6480623227275</v>
       </c>
       <c r="N93">
-        <v>1485.81028618078</v>
+        <v>1479.911937677272</v>
       </c>
       <c r="O93">
-        <v>133.7229257562702</v>
+        <v>133.1920743909545</v>
       </c>
       <c r="P93">
-        <v>1352.08736042451</v>
+        <v>1346.719863286318</v>
       </c>
       <c r="Q93">
-        <v>2602.98736042451</v>
+        <v>2597.619863286318</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7012259266656286</v>
+        <v>0.7824313499944767</v>
       </c>
       <c r="T93">
-        <v>9.537245845187513</v>
+        <v>10.71888370042124</v>
       </c>
       <c r="U93">
         <v>0.08015748822216712</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.768162232651343</v>
+        <v>3.727203947513829</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1297023571391564</v>
+        <v>0.1299159648816297</v>
       </c>
       <c r="C94">
-        <v>217.4352528530162</v>
+        <v>137.3623347676394</v>
       </c>
       <c r="D94">
-        <v>6235.309036416523</v>
+        <v>6228.820615978576</v>
       </c>
       <c r="E94">
-        <v>3778.324018820564</v>
+        <v>3851.908516467994</v>
       </c>
       <c r="F94">
-        <v>6769.773783563506</v>
+        <v>6843.358281210936</v>
       </c>
       <c r="G94">
         <v>751.9</v>
@@ -8995,28 +8995,28 @@
         <v>2022.56</v>
       </c>
       <c r="M94">
-        <v>542.6480623227275</v>
+        <v>548.5464108262354</v>
       </c>
       <c r="N94">
-        <v>1479.911937677272</v>
+        <v>1474.013589173765</v>
       </c>
       <c r="O94">
-        <v>133.1920743909545</v>
+        <v>132.6612230256388</v>
       </c>
       <c r="P94">
-        <v>1346.719863286318</v>
+        <v>1341.352366148126</v>
       </c>
       <c r="Q94">
-        <v>2597.619863286318</v>
+        <v>2592.252366148126</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7824313499944767</v>
+        <v>0.8868383228458526</v>
       </c>
       <c r="T94">
-        <v>10.71888370042124</v>
+        <v>12.23813237143603</v>
       </c>
       <c r="U94">
         <v>0.08015748822216712</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.727203947513829</v>
+        <v>3.687126485712604</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1299159648816297</v>
+        <v>0.130129572624103</v>
       </c>
       <c r="C95">
-        <v>137.3623347676394</v>
+        <v>57.30290625800444</v>
       </c>
       <c r="D95">
-        <v>6228.820615978576</v>
+        <v>6222.34568511637</v>
       </c>
       <c r="E95">
-        <v>3851.908516467994</v>
+        <v>3925.493014115423</v>
       </c>
       <c r="F95">
-        <v>6843.358281210936</v>
+        <v>6916.942778858365</v>
       </c>
       <c r="G95">
         <v>751.9</v>
@@ -9077,28 +9077,28 @@
         <v>2022.56</v>
       </c>
       <c r="M95">
-        <v>548.5464108262354</v>
+        <v>554.4447593297433</v>
       </c>
       <c r="N95">
-        <v>1474.013589173765</v>
+        <v>1468.115240670257</v>
       </c>
       <c r="O95">
-        <v>132.6612230256388</v>
+        <v>132.1303716603231</v>
       </c>
       <c r="P95">
-        <v>1341.352366148126</v>
+        <v>1335.984869009934</v>
       </c>
       <c r="Q95">
-        <v>2592.252366148126</v>
+        <v>2586.884869009934</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8868383228458526</v>
+        <v>1.026047619981021</v>
       </c>
       <c r="T95">
-        <v>12.23813237143603</v>
+        <v>14.26379726612241</v>
       </c>
       <c r="U95">
         <v>0.08015748822216712</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.687126485712604</v>
+        <v>3.647901735864598</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.130129572624103</v>
+        <v>0.1303431803665762</v>
       </c>
       <c r="C96">
-        <v>57.30290625800444</v>
+        <v>-22.74307469991436</v>
       </c>
       <c r="D96">
-        <v>6222.34568511637</v>
+        <v>6215.884201805881</v>
       </c>
       <c r="E96">
-        <v>3925.493014115423</v>
+        <v>3999.077511762853</v>
       </c>
       <c r="F96">
-        <v>6916.942778858365</v>
+        <v>6990.527276505795</v>
       </c>
       <c r="G96">
         <v>751.9</v>
@@ -9159,28 +9159,28 @@
         <v>2022.56</v>
       </c>
       <c r="M96">
-        <v>554.4447593297433</v>
+        <v>560.3431078332512</v>
       </c>
       <c r="N96">
-        <v>1468.115240670257</v>
+        <v>1462.216892166749</v>
       </c>
       <c r="O96">
-        <v>132.1303716603231</v>
+        <v>131.5995202950074</v>
       </c>
       <c r="P96">
-        <v>1335.984869009934</v>
+        <v>1330.617371871741</v>
       </c>
       <c r="Q96">
-        <v>2586.884869009934</v>
+        <v>2581.517371871741</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.026047619981021</v>
+        <v>1.220940635970257</v>
       </c>
       <c r="T96">
-        <v>14.26379726612241</v>
+        <v>17.09972811868335</v>
       </c>
       <c r="U96">
         <v>0.08015748822216712</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.647901735864598</v>
+        <v>3.609502770223918</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1303431803665762</v>
+        <v>0.1305567881090495</v>
       </c>
       <c r="C97">
-        <v>-22.74307469991436</v>
+        <v>-102.7756499557627</v>
       </c>
       <c r="D97">
-        <v>6215.884201805881</v>
+        <v>6209.436124197462</v>
       </c>
       <c r="E97">
-        <v>3999.077511762853</v>
+        <v>4072.662009410282</v>
       </c>
       <c r="F97">
-        <v>6990.527276505795</v>
+        <v>7064.111774153224</v>
       </c>
       <c r="G97">
         <v>751.9</v>
@@ -9241,28 +9241,28 @@
         <v>2022.56</v>
       </c>
       <c r="M97">
-        <v>560.3431078332512</v>
+        <v>566.2414563367591</v>
       </c>
       <c r="N97">
-        <v>1462.216892166749</v>
+        <v>1456.318543663241</v>
       </c>
       <c r="O97">
-        <v>131.5995202950074</v>
+        <v>131.0686689296917</v>
       </c>
       <c r="P97">
-        <v>1330.617371871741</v>
+        <v>1325.249874733549</v>
       </c>
       <c r="Q97">
-        <v>2581.517371871741</v>
+        <v>2576.149874733549</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.220940635970257</v>
+        <v>1.51328015995411</v>
       </c>
       <c r="T97">
-        <v>17.09972811868335</v>
+        <v>21.35362439752476</v>
       </c>
       <c r="U97">
         <v>0.08015748822216712</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.609502770223918</v>
+        <v>3.571903783034085</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1305567881090495</v>
+        <v>0.1307703958515227</v>
       </c>
       <c r="C98">
-        <v>-102.7756499557618</v>
+        <v>-182.7948611857191</v>
       </c>
       <c r="D98">
-        <v>6209.436124197462</v>
+        <v>6203.001410614935</v>
       </c>
       <c r="E98">
-        <v>4072.662009410281</v>
+        <v>4146.246507057711</v>
       </c>
       <c r="F98">
-        <v>7064.111774153223</v>
+        <v>7137.696271800653</v>
       </c>
       <c r="G98">
         <v>751.9</v>
@@ -9323,28 +9323,28 @@
         <v>2022.56</v>
       </c>
       <c r="M98">
-        <v>566.241456336759</v>
+        <v>572.1398048402671</v>
       </c>
       <c r="N98">
-        <v>1456.318543663241</v>
+        <v>1450.420195159733</v>
       </c>
       <c r="O98">
-        <v>131.0686689296917</v>
+        <v>130.537817564376</v>
       </c>
       <c r="P98">
-        <v>1325.249874733549</v>
+        <v>1319.882377595357</v>
       </c>
       <c r="Q98">
-        <v>2576.149874733549</v>
+        <v>2570.782377595357</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.513280159954106</v>
+        <v>2.000512699927193</v>
       </c>
       <c r="T98">
-        <v>21.3536243975247</v>
+        <v>28.44345152892703</v>
       </c>
       <c r="U98">
         <v>0.08015748822216712</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.571903783034086</v>
+        <v>3.535080032693528</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1307703958515227</v>
+        <v>0.133481043593996</v>
       </c>
       <c r="C99">
-        <v>-182.7948611857191</v>
+        <v>-336.8914644849083</v>
       </c>
       <c r="D99">
-        <v>6203.001410614935</v>
+        <v>6122.489304963175</v>
       </c>
       <c r="E99">
-        <v>4146.246507057711</v>
+        <v>4219.83100470514</v>
       </c>
       <c r="F99">
-        <v>7137.696271800653</v>
+        <v>7211.280769448083</v>
       </c>
       <c r="G99">
         <v>751.9</v>
@@ -9405,45 +9405,45 @@
         <v>2022.56</v>
       </c>
       <c r="M99">
-        <v>572.1398048402671</v>
+        <v>598.2297394982295</v>
       </c>
       <c r="N99">
-        <v>1450.420195159733</v>
+        <v>1424.33026050177</v>
       </c>
       <c r="O99">
-        <v>130.537817564376</v>
+        <v>128.1897234451593</v>
       </c>
       <c r="P99">
-        <v>1319.882377595357</v>
+        <v>1296.140537056611</v>
       </c>
       <c r="Q99">
-        <v>2570.782377595357</v>
+        <v>2547.040537056611</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.000512699927193</v>
+        <v>2.974977779873366</v>
       </c>
       <c r="T99">
-        <v>28.44345152892703</v>
+        <v>42.62310579173167</v>
       </c>
       <c r="U99">
-        <v>0.08015748822216712</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V99">
         <v>0.09</v>
       </c>
       <c r="W99">
-        <v>0.07294331428217207</v>
+        <v>0.07549131428217208</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y99">
-        <v>3.535080032693528</v>
+        <v>3.380908481240736</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.133481043593996</v>
+        <v>0.1337201313364693</v>
       </c>
       <c r="C100">
-        <v>-336.8914644849083</v>
+        <v>-417.4771971517739</v>
       </c>
       <c r="D100">
-        <v>6122.489304963175</v>
+        <v>6115.488069943739</v>
       </c>
       <c r="E100">
-        <v>4219.83100470514</v>
+        <v>4293.415502352571</v>
       </c>
       <c r="F100">
-        <v>7211.280769448083</v>
+        <v>7284.865267095513</v>
       </c>
       <c r="G100">
         <v>751.9</v>
@@ -9487,28 +9487,28 @@
         <v>2022.56</v>
       </c>
       <c r="M100">
-        <v>598.2297394982295</v>
+        <v>604.3341245951502</v>
       </c>
       <c r="N100">
-        <v>1424.33026050177</v>
+        <v>1418.22587540485</v>
       </c>
       <c r="O100">
-        <v>128.1897234451593</v>
+        <v>127.6403287864365</v>
       </c>
       <c r="P100">
-        <v>1296.140537056611</v>
+        <v>1290.585546618413</v>
       </c>
       <c r="Q100">
-        <v>2547.040537056611</v>
+        <v>2541.485546618414</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.974977779873366</v>
+        <v>5.898373019711888</v>
       </c>
       <c r="T100">
-        <v>42.62310579173167</v>
+        <v>85.1620685801456</v>
       </c>
       <c r="U100">
         <v>0.08295748822216711</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.380908481240736</v>
+        <v>3.346757890521132</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1337201313364693</v>
-      </c>
-      <c r="C101">
-        <v>-417.4771971517739</v>
-      </c>
-      <c r="D101">
-        <v>6115.488069943739</v>
-      </c>
-      <c r="E101">
-        <v>4293.415502352571</v>
-      </c>
-      <c r="F101">
-        <v>7284.865267095513</v>
-      </c>
-      <c r="G101">
-        <v>751.9</v>
-      </c>
-      <c r="H101">
-        <v>4367</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3273.46</v>
-      </c>
-      <c r="K101">
-        <v>1250.9</v>
-      </c>
-      <c r="L101">
-        <v>2022.56</v>
-      </c>
-      <c r="M101">
-        <v>604.3341245951502</v>
-      </c>
-      <c r="N101">
-        <v>1418.22587540485</v>
-      </c>
-      <c r="O101">
-        <v>127.6403287864365</v>
-      </c>
-      <c r="P101">
-        <v>1290.585546618413</v>
-      </c>
-      <c r="Q101">
-        <v>2541.485546618414</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.898373019711888</v>
-      </c>
-      <c r="T101">
-        <v>85.1620685801456</v>
-      </c>
-      <c r="U101">
-        <v>0.08295748822216711</v>
-      </c>
-      <c r="V101">
-        <v>0.09</v>
-      </c>
-      <c r="W101">
-        <v>0.07549131428217208</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.346757890521132</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
